--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -9936,7 +9936,7 @@
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de créer les bases légales nécessaires pour que l’administration fédérale puisse fournir aussi rapidement que possible des données structurées de qualité, à jour et surtout interopérables et comparables à l’échelle internationale qui puissent être réutilisées (notamment par l’intelligence artificielle [IA]) à des fins de recherche, de planification et de pilotage. Les normes contraignantes en la matière pour l’administration fédérale devront être édictées. Le Conseil fédéral est en outre chargé de désigner les données administratives qui devront être ainsi harmonisées, normalisées et rendues techniquement accessibles en priorité. Il faudra notamment examiner l’opportunité de fournir au public des données de registre supplémentaires. Les projets pilotes visés à l’art.&amp;nbsp;15 de la loi fédérale du 17&amp;nbsp;mars 2023 sur l’utilisation des moyens électroniques pour l’exécution des tâches des autorités (RS&amp;nbsp;172.019) sont susceptibles d’accélérer ce processus et devront être proposés par le Conseil fédéral avec les ressources nécessaires.&lt;/p&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die rechtlichen Grundlagen zu erlassen, damit baldmöglichst&amp;nbsp; qualitätsgesicherte, aktuelle und insbesondere international anschlussfähige und vergleichbare strukturierte Daten der Bundesverwaltung zur Mehrfachnutzung (unter anderem durch KI) für Forschung, Planung und Steuerung zur Verfügung gestellt werden.&amp;nbsp;Diesbezügliche verbindliche Standards für die Bundesverwaltung sind zu erlassen.&amp;nbsp;Der Bundesrat wird zudem beauftragt, eine prioritäre Auswahl jener Verwaltungsdaten zu definieren, die für eine zügige und KI-taugliche Mehrfachnutzung zuerst harmonisiert, standardisiert und technisch zugänglich gemacht werden sollen.&amp;nbsp;Insbesondere die öffentliche Bereitstellung weiterer Registerdaten ist zu prüfen. Gezielte Pilotversuche nach Art. 15 EMBAG können dies beschleunigen und sind vom Bundesrat mit den benötigten Mitteln zu beantragen.&lt;/p&gt;</t>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die rechtlichen Grundlagen zu erlassen, damit baldmöglichst qualitätsgesicherte, aktuelle und insbesondere international anschlussfähige und vergleichbare strukturierte Daten der Bundesverwaltung zur Mehrfachnutzung (unter anderem durch KI) für Forschung, Planung und Steuerung zur Verfügung gestellt werden.&amp;nbsp;Diesbezügliche verbindliche Standards für die Bundesverwaltung sind zu erlassen.&amp;nbsp;Der Bundesrat wird zudem beauftragt, eine prioritäre Auswahl jener Verwaltungsdaten zu definieren, die für eine zügige und KI-taugliche Mehrfachnutzung zuerst harmonisiert, standardisiert und technisch zugänglich gemacht werden sollen.&amp;nbsp;Insbesondere die öffentliche Bereitstellung weiterer Registerdaten ist zu prüfen. Gezielte Pilotversuche nach Art. 15 EMBAG können dies beschleunigen und sind vom Bundesrat mit den benötigten Mitteln zu beantragen.&lt;/p&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Zugewiesen an die behandelnde Kommission / Attribué à la commission compétente</t>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -113,7 +113,7 @@
     <t xml:space="preserve">&lt;p&gt;Bei der Volksabstimmung vom 8.3.2025 SRG-Initiative hat die SP Schweiz Einnahmen mit angeblichen Rekordkleinstspenden von 1.6 Millionen deklariert. Spenden über 15'000 wurden keine offen gelegt.&amp;nbsp;&lt;br&gt;Kann der Bundesrat bestätigen, dass solche ausserordentlichen Rekordeinnahmen nicht automatisch zu einer Revision führen und dieser Entscheid für eine Revision im Ermessen der EFK liegt?&lt;/p&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Eingereicht / Déposé</t>
+    <t xml:space="preserve">Erledigt / Liquidé</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267185</t>
@@ -125,6 +125,9 @@
     <t xml:space="preserve">Élu</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-03-16</t>
+  </si>
+  <si>
     <t xml:space="preserve">Staatspolitik</t>
   </si>
   <si>
@@ -201,9 +204,6 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Seit Beginn des Projekts im Jahr 2017 hat die Eidgenössische Finanzkontrolle sechs sehr kritische Prüfberichte zur Steuerung des neuen Auszahlungssystems der Arbeitslosenkassen veröffentlicht.&lt;br&gt;Kann uns der Bundesrat mitteilen, ob das SECO die Bemerkungen der Eidgenössischen Finanzkontrolle ausreichend berücksichtigt hat?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erledigt / Liquidé</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267129</t>
@@ -11231,17 +11231,19 @@
         <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2"/>
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
+        <v>37</v>
+      </c>
       <c r="T2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -11249,63 +11251,65 @@
         <v>20267161</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
         <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K3"/>
       <c r="L3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N3" t="s">
         <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q3" t="s">
         <v>36</v>
       </c>
       <c r="R3" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3"/>
+        <v>37</v>
+      </c>
+      <c r="S3" t="s">
+        <v>37</v>
+      </c>
       <c r="T3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -11313,41 +11317,41 @@
         <v>20267129</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K4"/>
       <c r="L4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N4" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O4" t="s">
         <v>64</v>
@@ -11359,7 +11363,7 @@
         <v>36</v>
       </c>
       <c r="R4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S4"/>
       <c r="T4" t="s">
@@ -11395,7 +11399,7 @@
         <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I5" t="s">
         <v>74</v>
@@ -11545,7 +11549,7 @@
         <v>111</v>
       </c>
       <c r="N7" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O7" t="s">
         <v>112</v>
@@ -11659,7 +11663,7 @@
         <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I9" t="s">
         <v>137</v>
@@ -11791,7 +11795,7 @@
         <v>164</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s">
         <v>137</v>
@@ -12055,7 +12059,7 @@
         <v>27</v>
       </c>
       <c r="H15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I15" t="s">
         <v>209</v>
@@ -12121,7 +12125,7 @@
         <v>164</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s">
         <v>222</v>
@@ -12139,7 +12143,7 @@
         <v>226</v>
       </c>
       <c r="N16" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O16" t="s">
         <v>227</v>
@@ -12269,7 +12273,7 @@
         <v>250</v>
       </c>
       <c r="N18" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O18" t="s">
         <v>251</v>
@@ -12335,7 +12339,7 @@
         <v>262</v>
       </c>
       <c r="N19" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O19" t="s">
         <v>263</v>
@@ -12383,7 +12387,7 @@
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I20" t="s">
         <v>272</v>
@@ -12449,7 +12453,7 @@
         <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I21" t="s">
         <v>285</v>
@@ -12581,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I23" t="s">
         <v>311</v>
@@ -12797,7 +12801,7 @@
         <v>353</v>
       </c>
       <c r="N26" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O26" t="s">
         <v>354</v>
@@ -12863,7 +12867,7 @@
         <v>366</v>
       </c>
       <c r="N27" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O27" t="s">
         <v>367</v>
@@ -12929,7 +12933,7 @@
         <v>378</v>
       </c>
       <c r="N28" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O28" t="s">
         <v>379</v>
@@ -12995,7 +12999,7 @@
         <v>390</v>
       </c>
       <c r="N29" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O29" t="s">
         <v>391</v>
@@ -13061,7 +13065,7 @@
         <v>401</v>
       </c>
       <c r="N30" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O30" t="s">
         <v>402</v>
@@ -13109,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I31" t="s">
         <v>407</v>
@@ -13175,7 +13179,7 @@
         <v>27</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I32" t="s">
         <v>419</v>
@@ -13191,7 +13195,7 @@
         <v>422</v>
       </c>
       <c r="N32" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O32" t="s">
         <v>423</v>
@@ -13321,7 +13325,7 @@
         <v>446</v>
       </c>
       <c r="N34" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O34" t="s">
         <v>447</v>
@@ -13385,7 +13389,7 @@
         <v>456</v>
       </c>
       <c r="N35" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O35" t="s">
         <v>457</v>
@@ -13449,7 +13453,7 @@
         <v>467</v>
       </c>
       <c r="N36" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O36" t="s">
         <v>468</v>
@@ -13579,7 +13583,7 @@
         <v>490</v>
       </c>
       <c r="N38" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O38" t="s">
         <v>491</v>
@@ -13643,7 +13647,7 @@
         <v>503</v>
       </c>
       <c r="N39" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O39" t="s">
         <v>504</v>
@@ -13709,7 +13713,7 @@
         <v>513</v>
       </c>
       <c r="N40" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O40" t="s">
         <v>514</v>
@@ -13775,7 +13779,7 @@
         <v>524</v>
       </c>
       <c r="N41" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O41" t="s">
         <v>525</v>
@@ -13823,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I42" t="s">
         <v>533</v>
@@ -13839,7 +13843,7 @@
         <v>536</v>
       </c>
       <c r="N42" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O42" t="s">
         <v>537</v>
@@ -14151,7 +14155,7 @@
         <v>27</v>
       </c>
       <c r="H47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I47" t="s">
         <v>591</v>
@@ -14217,7 +14221,7 @@
         <v>27</v>
       </c>
       <c r="H48" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I48" t="s">
         <v>599</v>
@@ -14283,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I49" t="s">
         <v>610</v>
@@ -14349,7 +14353,7 @@
         <v>27</v>
       </c>
       <c r="H50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I50" t="s">
         <v>619</v>
@@ -14433,7 +14437,7 @@
         <v>636</v>
       </c>
       <c r="N51" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O51" t="s">
         <v>637</v>
@@ -14497,7 +14501,7 @@
         <v>644</v>
       </c>
       <c r="N52" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O52" t="s">
         <v>645</v>
@@ -14545,7 +14549,7 @@
         <v>27</v>
       </c>
       <c r="H53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I53" t="s">
         <v>651</v>
@@ -14561,7 +14565,7 @@
         <v>654</v>
       </c>
       <c r="N53" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O53" t="s">
         <v>655</v>
@@ -14609,7 +14613,7 @@
         <v>27</v>
       </c>
       <c r="H54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I54" t="s">
         <v>663</v>
@@ -14625,7 +14629,7 @@
         <v>666</v>
       </c>
       <c r="N54" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O54" t="s">
         <v>667</v>
@@ -14673,7 +14677,7 @@
         <v>27</v>
       </c>
       <c r="H55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I55" t="s">
         <v>673</v>
@@ -14689,7 +14693,7 @@
         <v>676</v>
       </c>
       <c r="N55" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O55" t="s">
         <v>677</v>
@@ -14819,7 +14823,7 @@
         <v>697</v>
       </c>
       <c r="N57" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O57" t="s">
         <v>698</v>
@@ -14867,7 +14871,7 @@
         <v>27</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I58" t="s">
         <v>702</v>
@@ -14883,7 +14887,7 @@
         <v>705</v>
       </c>
       <c r="N58" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O58" t="s">
         <v>706</v>
@@ -14997,7 +15001,7 @@
         <v>27</v>
       </c>
       <c r="H60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I60" t="s">
         <v>724</v>
@@ -15081,7 +15085,7 @@
         <v>739</v>
       </c>
       <c r="N61" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O61" t="s">
         <v>740</v>
@@ -15147,7 +15151,7 @@
         <v>751</v>
       </c>
       <c r="N62" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O62" t="s">
         <v>752</v>
@@ -15213,7 +15217,7 @@
         <v>761</v>
       </c>
       <c r="N63" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O63" t="s">
         <v>762</v>
@@ -15277,7 +15281,7 @@
         <v>771</v>
       </c>
       <c r="N64" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O64" t="s">
         <v>772</v>
@@ -15323,7 +15327,7 @@
         <v>27</v>
       </c>
       <c r="H65" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I65" t="s">
         <v>777</v>
@@ -15473,7 +15477,7 @@
         <v>804</v>
       </c>
       <c r="N67" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O67" t="s">
         <v>805</v>
@@ -15539,7 +15543,7 @@
         <v>813</v>
       </c>
       <c r="N68" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O68" t="s">
         <v>814</v>
@@ -15605,7 +15609,7 @@
         <v>826</v>
       </c>
       <c r="N69" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O69" t="s">
         <v>827</v>
@@ -15653,7 +15657,7 @@
         <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I70" t="s">
         <v>832</v>
@@ -15669,7 +15673,7 @@
         <v>835</v>
       </c>
       <c r="N70" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O70" t="s">
         <v>836</v>
@@ -15733,7 +15737,7 @@
         <v>846</v>
       </c>
       <c r="N71" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O71" t="s">
         <v>847</v>
@@ -15781,7 +15785,7 @@
         <v>27</v>
       </c>
       <c r="H72" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I72" t="s">
         <v>851</v>
@@ -15799,7 +15803,7 @@
         <v>855</v>
       </c>
       <c r="N72" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O72" t="s">
         <v>856</v>
@@ -15865,7 +15869,7 @@
         <v>868</v>
       </c>
       <c r="N73" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O73" t="s">
         <v>869</v>
@@ -15913,7 +15917,7 @@
         <v>27</v>
       </c>
       <c r="H74" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I74" t="s">
         <v>877</v>
@@ -15931,7 +15935,7 @@
         <v>881</v>
       </c>
       <c r="N74" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O74" t="s">
         <v>882</v>
@@ -15997,7 +16001,7 @@
         <v>894</v>
       </c>
       <c r="N75" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O75" t="s">
         <v>895</v>
@@ -16061,7 +16065,7 @@
         <v>907</v>
       </c>
       <c r="N76" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O76" t="s">
         <v>908</v>
@@ -16127,7 +16131,7 @@
         <v>920</v>
       </c>
       <c r="N77" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O77" t="s">
         <v>921</v>
@@ -16169,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="H78" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I78" t="s">
         <v>925</v>
@@ -16185,7 +16189,7 @@
         <v>928</v>
       </c>
       <c r="N78" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O78" t="s">
         <v>929</v>
@@ -16251,7 +16255,7 @@
         <v>940</v>
       </c>
       <c r="N79" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O79" t="s">
         <v>941</v>
@@ -16299,7 +16303,7 @@
         <v>27</v>
       </c>
       <c r="H80" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I80" t="s">
         <v>944</v>
@@ -16317,7 +16321,7 @@
         <v>948</v>
       </c>
       <c r="N80" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O80" t="s">
         <v>949</v>
@@ -16383,7 +16387,7 @@
         <v>958</v>
       </c>
       <c r="N81" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O81" t="s">
         <v>959</v>
@@ -16515,7 +16519,7 @@
         <v>983</v>
       </c>
       <c r="N83" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O83" t="s">
         <v>984</v>
@@ -16581,7 +16585,7 @@
         <v>995</v>
       </c>
       <c r="N84" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O84" t="s">
         <v>996</v>
@@ -16647,7 +16651,7 @@
         <v>1004</v>
       </c>
       <c r="N85" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O85" t="s">
         <v>1005</v>
@@ -16695,7 +16699,7 @@
         <v>27</v>
       </c>
       <c r="H86" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I86" t="s">
         <v>1011</v>
@@ -16713,7 +16717,7 @@
         <v>1015</v>
       </c>
       <c r="N86" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O86" t="s">
         <v>1016</v>
@@ -16779,7 +16783,7 @@
         <v>1027</v>
       </c>
       <c r="N87" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O87" t="s">
         <v>1028</v>
@@ -16827,7 +16831,7 @@
         <v>27</v>
       </c>
       <c r="H88" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I88" t="s">
         <v>1036</v>
@@ -16845,7 +16849,7 @@
         <v>1040</v>
       </c>
       <c r="N88" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O88" t="s">
         <v>1041</v>
@@ -16893,7 +16897,7 @@
         <v>27</v>
       </c>
       <c r="H89" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I89" t="s">
         <v>1049</v>
@@ -16911,7 +16915,7 @@
         <v>1053</v>
       </c>
       <c r="N89" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O89" t="s">
         <v>1054</v>
@@ -16977,7 +16981,7 @@
         <v>1065</v>
       </c>
       <c r="N90" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O90" t="s">
         <v>1066</v>
@@ -17025,7 +17029,7 @@
         <v>27</v>
       </c>
       <c r="H91" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I91" t="s">
         <v>1072</v>
@@ -17043,7 +17047,7 @@
         <v>1076</v>
       </c>
       <c r="N91" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O91" t="s">
         <v>1077</v>
@@ -17091,7 +17095,7 @@
         <v>27</v>
       </c>
       <c r="H92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I92" t="s">
         <v>1081</v>
@@ -17109,7 +17113,7 @@
         <v>1085</v>
       </c>
       <c r="N92" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O92" t="s">
         <v>1086</v>
@@ -17175,7 +17179,7 @@
         <v>1095</v>
       </c>
       <c r="N93" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O93" t="s">
         <v>1096</v>
@@ -17211,7 +17215,7 @@
         <v>135</v>
       </c>
       <c r="D94" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E94" t="s">
         <v>270</v>
@@ -17241,7 +17245,7 @@
         <v>1107</v>
       </c>
       <c r="N94" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O94" t="s">
         <v>1108</v>
@@ -17277,7 +17281,7 @@
         <v>135</v>
       </c>
       <c r="D95" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E95" t="s">
         <v>270</v>
@@ -17307,7 +17311,7 @@
         <v>1118</v>
       </c>
       <c r="N95" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O95" t="s">
         <v>1119</v>
@@ -17355,7 +17359,7 @@
         <v>27</v>
       </c>
       <c r="H96" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I96" t="s">
         <v>1127</v>
@@ -17373,7 +17377,7 @@
         <v>1131</v>
       </c>
       <c r="N96" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O96" t="s">
         <v>1132</v>
@@ -17421,7 +17425,7 @@
         <v>27</v>
       </c>
       <c r="H97" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I97" t="s">
         <v>1138</v>
@@ -17439,7 +17443,7 @@
         <v>1142</v>
       </c>
       <c r="N97" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O97" t="s">
         <v>1143</v>
@@ -17505,7 +17509,7 @@
         <v>1153</v>
       </c>
       <c r="N98" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O98" t="s">
         <v>1154</v>
@@ -17553,7 +17557,7 @@
         <v>27</v>
       </c>
       <c r="H99" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I99" t="s">
         <v>1159</v>
@@ -17571,7 +17575,7 @@
         <v>1163</v>
       </c>
       <c r="N99" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O99" t="s">
         <v>1164</v>
@@ -17637,7 +17641,7 @@
         <v>1174</v>
       </c>
       <c r="N100" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O100" t="s">
         <v>1175</v>
@@ -17703,7 +17707,7 @@
         <v>1185</v>
       </c>
       <c r="N101" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O101" t="s">
         <v>1186</v>
@@ -17769,7 +17773,7 @@
         <v>1194</v>
       </c>
       <c r="N102" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O102" t="s">
         <v>1195</v>
@@ -17899,7 +17903,7 @@
         <v>1211</v>
       </c>
       <c r="N104" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O104" t="s">
         <v>1212</v>
@@ -17963,7 +17967,7 @@
         <v>1221</v>
       </c>
       <c r="N105" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O105" t="s">
         <v>1222</v>
@@ -18029,7 +18033,7 @@
         <v>1234</v>
       </c>
       <c r="N106" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O106" t="s">
         <v>1235</v>
@@ -18077,7 +18081,7 @@
         <v>27</v>
       </c>
       <c r="H107" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I107" t="s">
         <v>1241</v>
@@ -18095,7 +18099,7 @@
         <v>1245</v>
       </c>
       <c r="N107" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O107" t="s">
         <v>1246</v>
@@ -18161,7 +18165,7 @@
         <v>1255</v>
       </c>
       <c r="N108" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O108" t="s">
         <v>1256</v>
@@ -18209,7 +18213,7 @@
         <v>27</v>
       </c>
       <c r="H109" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I109" t="s">
         <v>1260</v>
@@ -18227,7 +18231,7 @@
         <v>1264</v>
       </c>
       <c r="N109" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O109" t="s">
         <v>1265</v>
@@ -18275,7 +18279,7 @@
         <v>27</v>
       </c>
       <c r="H110" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I110" t="s">
         <v>1273</v>
@@ -18357,7 +18361,7 @@
         <v>1289</v>
       </c>
       <c r="N111" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O111" t="s">
         <v>1290</v>
@@ -18421,7 +18425,7 @@
         <v>1298</v>
       </c>
       <c r="N112" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O112" t="s">
         <v>1299</v>
@@ -18485,7 +18489,7 @@
         <v>1310</v>
       </c>
       <c r="N113" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O113" t="s">
         <v>1311</v>
@@ -18533,7 +18537,7 @@
         <v>27</v>
       </c>
       <c r="H114" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I114" t="s">
         <v>1316</v>
@@ -18551,7 +18555,7 @@
         <v>1320</v>
       </c>
       <c r="N114" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O114" t="s">
         <v>1321</v>
@@ -18617,7 +18621,7 @@
         <v>1332</v>
       </c>
       <c r="N115" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O115" t="s">
         <v>1333</v>
@@ -18681,7 +18685,7 @@
         <v>1345</v>
       </c>
       <c r="N116" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O116" t="s">
         <v>1346</v>
@@ -18729,7 +18733,7 @@
         <v>27</v>
       </c>
       <c r="H117" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I117" t="s">
         <v>1353</v>
@@ -18745,7 +18749,7 @@
         <v>1356</v>
       </c>
       <c r="N117" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O117" t="s">
         <v>1357</v>
@@ -18811,7 +18815,7 @@
         <v>1369</v>
       </c>
       <c r="N118" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O118" t="s">
         <v>1370</v>
@@ -18877,7 +18881,7 @@
         <v>1382</v>
       </c>
       <c r="N119" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O119" t="s">
         <v>1383</v>
@@ -18925,7 +18929,7 @@
         <v>27</v>
       </c>
       <c r="H120" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I120" t="s">
         <v>1391</v>
@@ -18941,7 +18945,7 @@
         <v>1394</v>
       </c>
       <c r="N120" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O120" t="s">
         <v>1395</v>
@@ -19007,7 +19011,7 @@
         <v>1407</v>
       </c>
       <c r="N121" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O121" t="s">
         <v>1408</v>
@@ -19073,7 +19077,7 @@
         <v>1420</v>
       </c>
       <c r="N122" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O122" t="s">
         <v>1421</v>
@@ -19139,7 +19143,7 @@
         <v>1431</v>
       </c>
       <c r="N123" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O123" t="s">
         <v>1432</v>
@@ -19205,7 +19209,7 @@
         <v>1440</v>
       </c>
       <c r="N124" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O124" t="s">
         <v>1441</v>
@@ -19271,7 +19275,7 @@
         <v>1453</v>
       </c>
       <c r="N125" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O125" t="s">
         <v>1454</v>
@@ -19319,7 +19323,7 @@
         <v>27</v>
       </c>
       <c r="H126" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I126" t="s">
         <v>1461</v>
@@ -19335,7 +19339,7 @@
         <v>1464</v>
       </c>
       <c r="N126" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O126" t="s">
         <v>1465</v>
@@ -19383,7 +19387,7 @@
         <v>27</v>
       </c>
       <c r="H127" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I127" t="s">
         <v>1473</v>
@@ -19399,7 +19403,7 @@
         <v>1476</v>
       </c>
       <c r="N127" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O127" t="s">
         <v>1477</v>
@@ -19529,7 +19533,7 @@
         <v>1495</v>
       </c>
       <c r="N129" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O129" t="s">
         <v>1496</v>
@@ -19577,7 +19581,7 @@
         <v>27</v>
       </c>
       <c r="H130" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I130" t="s">
         <v>1503</v>
@@ -19595,7 +19599,7 @@
         <v>1507</v>
       </c>
       <c r="N130" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O130" t="s">
         <v>1508</v>
@@ -19643,7 +19647,7 @@
         <v>27</v>
       </c>
       <c r="H131" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I131" t="s">
         <v>1514</v>
@@ -19661,7 +19665,7 @@
         <v>1518</v>
       </c>
       <c r="N131" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O131" t="s">
         <v>1519</v>
@@ -19727,7 +19731,7 @@
         <v>1530</v>
       </c>
       <c r="N132" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O132" t="s">
         <v>1531</v>
@@ -19775,7 +19779,7 @@
         <v>164</v>
       </c>
       <c r="H133" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I133" t="s">
         <v>1539</v>
@@ -19841,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="H134" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I134" t="s">
         <v>1551</v>
@@ -19859,7 +19863,7 @@
         <v>1555</v>
       </c>
       <c r="N134" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O134" t="s">
         <v>1556</v>
@@ -19925,7 +19929,7 @@
         <v>1567</v>
       </c>
       <c r="N135" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O135" t="s">
         <v>1568</v>
@@ -19991,7 +19995,7 @@
         <v>1576</v>
       </c>
       <c r="N136" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O136" t="s">
         <v>1577</v>
@@ -20055,7 +20059,7 @@
         <v>1585</v>
       </c>
       <c r="N137" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O137" t="s">
         <v>1586</v>
@@ -20119,7 +20123,7 @@
         <v>1592</v>
       </c>
       <c r="N138" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O138" t="s">
         <v>1593</v>
@@ -20185,7 +20189,7 @@
         <v>1601</v>
       </c>
       <c r="N139" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O139" t="s">
         <v>1602</v>
@@ -20251,7 +20255,7 @@
         <v>1613</v>
       </c>
       <c r="N140" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O140" t="s">
         <v>1614</v>
@@ -20317,7 +20321,7 @@
         <v>1624</v>
       </c>
       <c r="N141" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O141" t="s">
         <v>1625</v>
@@ -20383,7 +20387,7 @@
         <v>1636</v>
       </c>
       <c r="N142" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O142" t="s">
         <v>1637</v>
@@ -20449,7 +20453,7 @@
         <v>1645</v>
       </c>
       <c r="N143" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O143" t="s">
         <v>1646</v>
@@ -20515,7 +20519,7 @@
         <v>1657</v>
       </c>
       <c r="N144" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O144" t="s">
         <v>1658</v>
@@ -20581,7 +20585,7 @@
         <v>1669</v>
       </c>
       <c r="N145" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O145" t="s">
         <v>1670</v>
@@ -20647,7 +20651,7 @@
         <v>1678</v>
       </c>
       <c r="N146" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O146" t="s">
         <v>1679</v>
@@ -20711,7 +20715,7 @@
         <v>1690</v>
       </c>
       <c r="N147" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O147" t="s">
         <v>1691</v>
@@ -20775,7 +20779,7 @@
         <v>1701</v>
       </c>
       <c r="N148" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O148" t="s">
         <v>1702</v>
@@ -20839,7 +20843,7 @@
         <v>1708</v>
       </c>
       <c r="N149" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O149" t="s">
         <v>1709</v>
@@ -20949,7 +20953,7 @@
         <v>27</v>
       </c>
       <c r="H151" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I151" t="s">
         <v>1724</v>
@@ -20967,7 +20971,7 @@
         <v>1728</v>
       </c>
       <c r="N151" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O151" t="s">
         <v>1729</v>
@@ -21033,7 +21037,7 @@
         <v>1740</v>
       </c>
       <c r="N152" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O152" t="s">
         <v>1741</v>
@@ -21099,7 +21103,7 @@
         <v>1752</v>
       </c>
       <c r="N153" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O153" t="s">
         <v>1753</v>
@@ -21165,7 +21169,7 @@
         <v>1765</v>
       </c>
       <c r="N154" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O154" t="s">
         <v>1766</v>
@@ -21229,7 +21233,7 @@
         <v>1774</v>
       </c>
       <c r="N155" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O155" t="s">
         <v>1775</v>
@@ -21295,7 +21299,7 @@
         <v>1787</v>
       </c>
       <c r="N156" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O156" t="s">
         <v>1788</v>
@@ -21361,7 +21365,7 @@
         <v>1799</v>
       </c>
       <c r="N157" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O157" t="s">
         <v>1800</v>
@@ -21427,7 +21431,7 @@
         <v>1811</v>
       </c>
       <c r="N158" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O158" t="s">
         <v>1812</v>
@@ -21493,7 +21497,7 @@
         <v>1823</v>
       </c>
       <c r="N159" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O159" t="s">
         <v>1824</v>
@@ -21541,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="H160" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I160" t="s">
         <v>1830</v>
@@ -21559,7 +21563,7 @@
         <v>1834</v>
       </c>
       <c r="N160" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O160" t="s">
         <v>1835</v>
@@ -21607,7 +21611,7 @@
         <v>27</v>
       </c>
       <c r="H161" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I161" t="s">
         <v>1841</v>
@@ -21625,7 +21629,7 @@
         <v>1845</v>
       </c>
       <c r="N161" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O161" t="s">
         <v>1846</v>
@@ -21691,7 +21695,7 @@
         <v>1854</v>
       </c>
       <c r="N162" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O162" t="s">
         <v>1855</v>
@@ -21757,7 +21761,7 @@
         <v>1864</v>
       </c>
       <c r="N163" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O163" t="s">
         <v>1865</v>
@@ -21805,7 +21809,7 @@
         <v>27</v>
       </c>
       <c r="H164" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I164" t="s">
         <v>1872</v>
@@ -21823,7 +21827,7 @@
         <v>1876</v>
       </c>
       <c r="N164" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O164" t="s">
         <v>1877</v>
@@ -21889,7 +21893,7 @@
         <v>1888</v>
       </c>
       <c r="N165" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O165" t="s">
         <v>1889</v>
@@ -21955,7 +21959,7 @@
         <v>1897</v>
       </c>
       <c r="N166" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O166" t="s">
         <v>1898</v>
@@ -22021,7 +22025,7 @@
         <v>1906</v>
       </c>
       <c r="N167" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O167" t="s">
         <v>1907</v>
@@ -22087,7 +22091,7 @@
         <v>1919</v>
       </c>
       <c r="N168" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O168" t="s">
         <v>1920</v>
@@ -22153,7 +22157,7 @@
         <v>1931</v>
       </c>
       <c r="N169" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O169" t="s">
         <v>1932</v>
@@ -22201,7 +22205,7 @@
         <v>27</v>
       </c>
       <c r="H170" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I170" t="s">
         <v>1939</v>
@@ -22219,7 +22223,7 @@
         <v>1943</v>
       </c>
       <c r="N170" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O170" t="s">
         <v>1944</v>
@@ -22267,7 +22271,7 @@
         <v>27</v>
       </c>
       <c r="H171" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I171" t="s">
         <v>1951</v>
@@ -22285,7 +22289,7 @@
         <v>1955</v>
       </c>
       <c r="N171" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O171" t="s">
         <v>1956</v>
@@ -22351,7 +22355,7 @@
         <v>1967</v>
       </c>
       <c r="N172" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O172" t="s">
         <v>1968</v>
@@ -22399,7 +22403,7 @@
         <v>27</v>
       </c>
       <c r="H173" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I173" t="s">
         <v>1973</v>
@@ -22417,7 +22421,7 @@
         <v>1977</v>
       </c>
       <c r="N173" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O173" t="s">
         <v>1978</v>
@@ -22481,7 +22485,7 @@
         <v>1985</v>
       </c>
       <c r="N174" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O174" t="s">
         <v>1986</v>
@@ -22545,7 +22549,7 @@
         <v>1996</v>
       </c>
       <c r="N175" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O175" t="s">
         <v>1997</v>
@@ -22611,7 +22615,7 @@
         <v>2008</v>
       </c>
       <c r="N176" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O176" t="s">
         <v>2009</v>
@@ -22659,7 +22663,7 @@
         <v>27</v>
       </c>
       <c r="H177" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I177" t="s">
         <v>2016</v>
@@ -22677,7 +22681,7 @@
         <v>2020</v>
       </c>
       <c r="N177" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O177" t="s">
         <v>2021</v>
@@ -22725,7 +22729,7 @@
         <v>27</v>
       </c>
       <c r="H178" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I178" t="s">
         <v>2030</v>
@@ -22743,7 +22747,7 @@
         <v>2034</v>
       </c>
       <c r="N178" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O178" t="s">
         <v>2035</v>
@@ -22809,7 +22813,7 @@
         <v>2045</v>
       </c>
       <c r="N179" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O179" t="s">
         <v>2046</v>
@@ -22875,7 +22879,7 @@
         <v>2058</v>
       </c>
       <c r="N180" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O180" t="s">
         <v>2059</v>
@@ -22923,7 +22927,7 @@
         <v>27</v>
       </c>
       <c r="H181" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I181" t="s">
         <v>2067</v>
@@ -22939,7 +22943,7 @@
         <v>2070</v>
       </c>
       <c r="N181" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O181" t="s">
         <v>2071</v>
@@ -22987,7 +22991,7 @@
         <v>27</v>
       </c>
       <c r="H182" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I182" t="s">
         <v>2078</v>
@@ -23005,7 +23009,7 @@
         <v>2082</v>
       </c>
       <c r="N182" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O182" t="s">
         <v>2083</v>
@@ -23071,7 +23075,7 @@
         <v>2094</v>
       </c>
       <c r="N183" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O183" t="s">
         <v>2095</v>
@@ -23135,7 +23139,7 @@
         <v>2103</v>
       </c>
       <c r="N184" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O184" t="s">
         <v>2104</v>
@@ -23183,7 +23187,7 @@
         <v>27</v>
       </c>
       <c r="H185" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I185" t="s">
         <v>2112</v>
@@ -23201,7 +23205,7 @@
         <v>2116</v>
       </c>
       <c r="N185" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O185" t="s">
         <v>2117</v>
@@ -23249,7 +23253,7 @@
         <v>27</v>
       </c>
       <c r="H186" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I186" t="s">
         <v>2125</v>
@@ -23267,7 +23271,7 @@
         <v>2129</v>
       </c>
       <c r="N186" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O186" t="s">
         <v>2130</v>
@@ -23315,7 +23319,7 @@
         <v>27</v>
       </c>
       <c r="H187" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I187" t="s">
         <v>2137</v>
@@ -23331,7 +23335,7 @@
         <v>2140</v>
       </c>
       <c r="N187" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O187" t="s">
         <v>2141</v>
@@ -23379,7 +23383,7 @@
         <v>27</v>
       </c>
       <c r="H188" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I188" t="s">
         <v>2148</v>
@@ -23397,7 +23401,7 @@
         <v>2152</v>
       </c>
       <c r="N188" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O188" t="s">
         <v>2153</v>
@@ -23461,7 +23465,7 @@
         <v>2165</v>
       </c>
       <c r="N189" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O189" t="s">
         <v>2166</v>
@@ -23525,7 +23529,7 @@
         <v>2178</v>
       </c>
       <c r="N190" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O190" t="s">
         <v>2179</v>
@@ -23571,7 +23575,7 @@
         <v>164</v>
       </c>
       <c r="H191" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I191" t="s">
         <v>2185</v>
@@ -23589,7 +23593,7 @@
         <v>2189</v>
       </c>
       <c r="N191" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O191" t="s">
         <v>2190</v>
@@ -23829,7 +23833,7 @@
         <v>27</v>
       </c>
       <c r="H195" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I195" t="s">
         <v>2230</v>
@@ -23884,7 +23888,7 @@
         <v>373</v>
       </c>
       <c r="E196" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F196" t="s">
         <v>89</v>
@@ -23893,7 +23897,7 @@
         <v>27</v>
       </c>
       <c r="H196" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I196" t="s">
         <v>2241</v>
@@ -23948,7 +23952,7 @@
         <v>2252</v>
       </c>
       <c r="E197" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F197" t="s">
         <v>89</v>
@@ -24012,7 +24016,7 @@
         <v>808</v>
       </c>
       <c r="E198" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F198" t="s">
         <v>89</v>
@@ -24101,7 +24105,7 @@
         <v>2278</v>
       </c>
       <c r="N199" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O199" t="s">
         <v>2279</v>
@@ -24163,7 +24167,7 @@
         <v>2285</v>
       </c>
       <c r="N200" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O200" t="s">
         <v>2286</v>
@@ -24227,7 +24231,7 @@
         <v>2297</v>
       </c>
       <c r="N201" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O201" t="s">
         <v>2298</v>
@@ -24264,7 +24268,7 @@
         <v>2301</v>
       </c>
       <c r="E202" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F202" t="s">
         <v>2302</v>
@@ -24273,7 +24277,7 @@
         <v>27</v>
       </c>
       <c r="H202" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I202" t="s">
         <v>2303</v>
@@ -24337,7 +24341,7 @@
         <v>27</v>
       </c>
       <c r="H203" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I203" t="s">
         <v>2311</v>
@@ -24419,7 +24423,7 @@
         <v>2328</v>
       </c>
       <c r="N204" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O204" t="s">
         <v>2329</v>
@@ -24584,7 +24588,7 @@
         <v>2352</v>
       </c>
       <c r="E207" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F207" t="s">
         <v>2323</v>
@@ -24611,7 +24615,7 @@
         <v>2357</v>
       </c>
       <c r="N207" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O207" t="s">
         <v>2358</v>
@@ -24675,7 +24679,7 @@
         <v>2370</v>
       </c>
       <c r="N208" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O208" t="s">
         <v>2371</v>
@@ -24712,7 +24716,7 @@
         <v>442</v>
       </c>
       <c r="E209" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F209" t="s">
         <v>2377</v>
@@ -24801,7 +24805,7 @@
         <v>2389</v>
       </c>
       <c r="N210" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O210" t="s">
         <v>2390</v>
@@ -24863,7 +24867,7 @@
         <v>2396</v>
       </c>
       <c r="N211" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O211" t="s">
         <v>2397</v>
@@ -24909,7 +24913,7 @@
         <v>27</v>
       </c>
       <c r="H212" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I212" t="s">
         <v>2403</v>
@@ -24925,7 +24929,7 @@
         <v>2406</v>
       </c>
       <c r="N212" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O212" t="s">
         <v>2407</v>
@@ -25111,7 +25115,7 @@
         <v>2433</v>
       </c>
       <c r="N215" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O215" t="s">
         <v>2434</v>
@@ -25148,7 +25152,7 @@
         <v>2440</v>
       </c>
       <c r="E216" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F216" t="s">
         <v>2424</v>
@@ -25173,7 +25177,7 @@
         <v>2444</v>
       </c>
       <c r="N216" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O216" t="s">
         <v>2445</v>
@@ -25219,7 +25223,7 @@
         <v>164</v>
       </c>
       <c r="H217" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I217" t="s">
         <v>2450</v>
@@ -25237,7 +25241,7 @@
         <v>2454</v>
       </c>
       <c r="N217" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O217" t="s">
         <v>2455</v>
@@ -25299,7 +25303,7 @@
         <v>2462</v>
       </c>
       <c r="N218" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O218" t="s">
         <v>2463</v>
@@ -25419,7 +25423,7 @@
         <v>2482</v>
       </c>
       <c r="N220" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O220" t="s">
         <v>2483</v>
@@ -25483,7 +25487,7 @@
         <v>2494</v>
       </c>
       <c r="N221" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O221" t="s">
         <v>2495</v>
@@ -25529,7 +25533,7 @@
         <v>27</v>
       </c>
       <c r="H222" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I222" t="s">
         <v>2503</v>
@@ -25547,7 +25551,7 @@
         <v>2507</v>
       </c>
       <c r="N222" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O222" t="s">
         <v>2508</v>
@@ -25609,7 +25613,7 @@
         <v>2518</v>
       </c>
       <c r="N223" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O223" t="s">
         <v>2519</v>
@@ -25655,7 +25659,7 @@
         <v>27</v>
       </c>
       <c r="H224" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I224" t="s">
         <v>2524</v>
@@ -25673,7 +25677,7 @@
         <v>2528</v>
       </c>
       <c r="N224" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O224" t="s">
         <v>2529</v>
@@ -25737,7 +25741,7 @@
         <v>2539</v>
       </c>
       <c r="N225" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O225" t="s">
         <v>2540</v>
@@ -25801,7 +25805,7 @@
         <v>2548</v>
       </c>
       <c r="N226" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O226" t="s">
         <v>2549</v>
@@ -25865,7 +25869,7 @@
         <v>2560</v>
       </c>
       <c r="N227" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O227" t="s">
         <v>2561</v>
@@ -25929,7 +25933,7 @@
         <v>2569</v>
       </c>
       <c r="N228" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O228" t="s">
         <v>2570</v>
@@ -25975,7 +25979,7 @@
         <v>27</v>
       </c>
       <c r="H229" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I229" t="s">
         <v>2574</v>
@@ -25993,7 +25997,7 @@
         <v>2578</v>
       </c>
       <c r="N229" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O229" t="s">
         <v>2579</v>
@@ -26057,7 +26061,7 @@
         <v>2590</v>
       </c>
       <c r="N230" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O230" t="s">
         <v>2591</v>
@@ -26103,7 +26107,7 @@
         <v>27</v>
       </c>
       <c r="H231" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I231" t="s">
         <v>2595</v>
@@ -26121,7 +26125,7 @@
         <v>2599</v>
       </c>
       <c r="N231" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O231" t="s">
         <v>2600</v>
@@ -26185,7 +26189,7 @@
         <v>2612</v>
       </c>
       <c r="N232" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O232" t="s">
         <v>2613</v>
@@ -26247,7 +26251,7 @@
         <v>2623</v>
       </c>
       <c r="N233" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O233" t="s">
         <v>2624</v>
@@ -26311,7 +26315,7 @@
         <v>2635</v>
       </c>
       <c r="N234" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O234" t="s">
         <v>2636</v>
@@ -26375,7 +26379,7 @@
         <v>2648</v>
       </c>
       <c r="N235" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O235" t="s">
         <v>2649</v>
@@ -26439,7 +26443,7 @@
         <v>2659</v>
       </c>
       <c r="N236" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O236" t="s">
         <v>2660</v>
@@ -26485,7 +26489,7 @@
         <v>27</v>
       </c>
       <c r="H237" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I237" t="s">
         <v>2666</v>
@@ -26503,7 +26507,7 @@
         <v>2670</v>
       </c>
       <c r="N237" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O237" t="s">
         <v>2671</v>
@@ -26567,7 +26571,7 @@
         <v>2682</v>
       </c>
       <c r="N238" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O238" t="s">
         <v>2683</v>
@@ -26631,7 +26635,7 @@
         <v>2694</v>
       </c>
       <c r="N239" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O239" t="s">
         <v>2695</v>
@@ -26695,7 +26699,7 @@
         <v>2707</v>
       </c>
       <c r="N240" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O240" t="s">
         <v>2708</v>
@@ -26759,7 +26763,7 @@
         <v>2721</v>
       </c>
       <c r="N241" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O241" t="s">
         <v>2722</v>
@@ -26805,7 +26809,7 @@
         <v>27</v>
       </c>
       <c r="H242" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I242" t="s">
         <v>2727</v>
@@ -26821,7 +26825,7 @@
         <v>2730</v>
       </c>
       <c r="N242" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O242" t="s">
         <v>2731</v>
@@ -26867,7 +26871,7 @@
         <v>27</v>
       </c>
       <c r="H243" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I243" t="s">
         <v>2734</v>
@@ -26883,7 +26887,7 @@
         <v>2737</v>
       </c>
       <c r="N243" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O243" t="s">
         <v>2738</v>
@@ -26929,7 +26933,7 @@
         <v>27</v>
       </c>
       <c r="H244" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I244" t="s">
         <v>2743</v>
@@ -26947,7 +26951,7 @@
         <v>2747</v>
       </c>
       <c r="N244" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O244" t="s">
         <v>2748</v>
@@ -26993,7 +26997,7 @@
         <v>27</v>
       </c>
       <c r="H245" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I245" t="s">
         <v>2753</v>
@@ -27011,7 +27015,7 @@
         <v>2757</v>
       </c>
       <c r="N245" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O245" t="s">
         <v>2758</v>
@@ -27075,7 +27079,7 @@
         <v>2765</v>
       </c>
       <c r="N246" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O246" t="s">
         <v>2766</v>
@@ -27121,7 +27125,7 @@
         <v>27</v>
       </c>
       <c r="H247" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I247" t="s">
         <v>2773</v>
@@ -27137,7 +27141,7 @@
         <v>2776</v>
       </c>
       <c r="N247" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O247" t="s">
         <v>2777</v>
@@ -27199,7 +27203,7 @@
         <v>2784</v>
       </c>
       <c r="N248" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O248" t="s">
         <v>2785</v>
@@ -27261,7 +27265,7 @@
         <v>2794</v>
       </c>
       <c r="N249" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O249" t="s">
         <v>2795</v>
@@ -27305,7 +27309,7 @@
         <v>27</v>
       </c>
       <c r="H250" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I250" t="s">
         <v>2799</v>
@@ -27323,7 +27327,7 @@
         <v>2803</v>
       </c>
       <c r="N250" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O250" t="s">
         <v>2804</v>
@@ -27385,7 +27389,7 @@
         <v>2816</v>
       </c>
       <c r="N251" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O251" t="s">
         <v>2817</v>
@@ -27431,7 +27435,7 @@
         <v>164</v>
       </c>
       <c r="H252" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I252" t="s">
         <v>2825</v>
@@ -27449,7 +27453,7 @@
         <v>2829</v>
       </c>
       <c r="N252" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O252" t="s">
         <v>2830</v>
@@ -27513,7 +27517,7 @@
         <v>2838</v>
       </c>
       <c r="N253" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O253" t="s">
         <v>2839</v>
@@ -27577,7 +27581,7 @@
         <v>2847</v>
       </c>
       <c r="N254" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O254" t="s">
         <v>2848</v>
@@ -27623,7 +27627,7 @@
         <v>27</v>
       </c>
       <c r="H255" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I255" t="s">
         <v>2854</v>
@@ -27641,7 +27645,7 @@
         <v>2858</v>
       </c>
       <c r="N255" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O255" t="s">
         <v>2859</v>
@@ -27687,7 +27691,7 @@
         <v>27</v>
       </c>
       <c r="H256" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I256" t="s">
         <v>2862</v>
@@ -27705,7 +27709,7 @@
         <v>2866</v>
       </c>
       <c r="N256" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O256" t="s">
         <v>2867</v>
@@ -27751,7 +27755,7 @@
         <v>27</v>
       </c>
       <c r="H257" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I257" t="s">
         <v>2871</v>
@@ -27769,7 +27773,7 @@
         <v>2875</v>
       </c>
       <c r="N257" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O257" t="s">
         <v>2876</v>
@@ -27833,7 +27837,7 @@
         <v>2888</v>
       </c>
       <c r="N258" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O258" t="s">
         <v>2889</v>
@@ -27897,7 +27901,7 @@
         <v>2899</v>
       </c>
       <c r="N259" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O259" t="s">
         <v>2900</v>
@@ -27943,7 +27947,7 @@
         <v>27</v>
       </c>
       <c r="H260" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I260" t="s">
         <v>2908</v>
@@ -27961,7 +27965,7 @@
         <v>2912</v>
       </c>
       <c r="N260" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O260" t="s">
         <v>2913</v>
@@ -28007,7 +28011,7 @@
         <v>27</v>
       </c>
       <c r="H261" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I261" t="s">
         <v>2920</v>
@@ -28025,7 +28029,7 @@
         <v>2924</v>
       </c>
       <c r="N261" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O261" t="s">
         <v>2925</v>
@@ -28071,7 +28075,7 @@
         <v>27</v>
       </c>
       <c r="H262" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I262" t="s">
         <v>2928</v>
@@ -28087,7 +28091,7 @@
         <v>2931</v>
       </c>
       <c r="N262" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O262" t="s">
         <v>2932</v>
@@ -28133,7 +28137,7 @@
         <v>27</v>
       </c>
       <c r="H263" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I263" t="s">
         <v>2939</v>
@@ -28151,7 +28155,7 @@
         <v>2943</v>
       </c>
       <c r="N263" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O263" t="s">
         <v>2944</v>
@@ -28195,7 +28199,7 @@
         <v>27</v>
       </c>
       <c r="H264" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I264" t="s">
         <v>2951</v>
@@ -28213,7 +28217,7 @@
         <v>2955</v>
       </c>
       <c r="N264" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O264" t="s">
         <v>2956</v>
@@ -28257,7 +28261,7 @@
         <v>27</v>
       </c>
       <c r="H265" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I265" t="s">
         <v>2960</v>
@@ -28275,7 +28279,7 @@
         <v>2964</v>
       </c>
       <c r="N265" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O265" t="s">
         <v>2965</v>
@@ -28319,7 +28323,7 @@
         <v>27</v>
       </c>
       <c r="H266" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I266" t="s">
         <v>2968</v>
@@ -28337,7 +28341,7 @@
         <v>2972</v>
       </c>
       <c r="N266" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O266" t="s">
         <v>2973</v>
@@ -28381,7 +28385,7 @@
         <v>27</v>
       </c>
       <c r="H267" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I267" t="s">
         <v>2976</v>
@@ -28399,7 +28403,7 @@
         <v>2980</v>
       </c>
       <c r="N267" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O267" t="s">
         <v>2981</v>
@@ -28443,7 +28447,7 @@
         <v>27</v>
       </c>
       <c r="H268" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I268" t="s">
         <v>2986</v>
@@ -28461,7 +28465,7 @@
         <v>2990</v>
       </c>
       <c r="N268" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O268" t="s">
         <v>2991</v>
@@ -28507,7 +28511,7 @@
         <v>27</v>
       </c>
       <c r="H269" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I269" t="s">
         <v>2999</v>
@@ -28525,7 +28529,7 @@
         <v>3003</v>
       </c>
       <c r="N269" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O269" t="s">
         <v>3004</v>
@@ -28589,7 +28593,7 @@
         <v>3013</v>
       </c>
       <c r="N270" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O270" t="s">
         <v>3014</v>
@@ -28651,7 +28655,7 @@
         <v>3024</v>
       </c>
       <c r="N271" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O271" t="s">
         <v>3025</v>
@@ -28697,7 +28701,7 @@
         <v>27</v>
       </c>
       <c r="H272" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I272" t="s">
         <v>3034</v>
@@ -28715,7 +28719,7 @@
         <v>3038</v>
       </c>
       <c r="N272" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O272" t="s">
         <v>3039</v>
@@ -28779,7 +28783,7 @@
         <v>3051</v>
       </c>
       <c r="N273" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O273" t="s">
         <v>3052</v>
@@ -28843,7 +28847,7 @@
         <v>3062</v>
       </c>
       <c r="N274" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O274" t="s">
         <v>3063</v>
@@ -28889,7 +28893,7 @@
         <v>27</v>
       </c>
       <c r="H275" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I275" t="s">
         <v>3066</v>
@@ -28907,7 +28911,7 @@
         <v>3070</v>
       </c>
       <c r="N275" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O275" t="s">
         <v>3071</v>
@@ -28971,7 +28975,7 @@
         <v>3081</v>
       </c>
       <c r="N276" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O276" t="s">
         <v>3082</v>
@@ -29017,7 +29021,7 @@
         <v>27</v>
       </c>
       <c r="H277" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I277" t="s">
         <v>3088</v>
@@ -29035,7 +29039,7 @@
         <v>3092</v>
       </c>
       <c r="N277" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O277" t="s">
         <v>3093</v>
@@ -29099,7 +29103,7 @@
         <v>3103</v>
       </c>
       <c r="N278" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O278" t="s">
         <v>3104</v>
@@ -29163,7 +29167,7 @@
         <v>3111</v>
       </c>
       <c r="N279" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O279" t="s">
         <v>3112</v>
@@ -29227,7 +29231,7 @@
         <v>3120</v>
       </c>
       <c r="N280" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O280" t="s">
         <v>3121</v>
@@ -29291,7 +29295,7 @@
         <v>3129</v>
       </c>
       <c r="N281" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O281" t="s">
         <v>3130</v>
@@ -29353,7 +29357,7 @@
         <v>3137</v>
       </c>
       <c r="N282" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O282" t="s">
         <v>3138</v>
@@ -29399,7 +29403,7 @@
         <v>27</v>
       </c>
       <c r="H283" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I283" t="s">
         <v>3145</v>
@@ -29415,7 +29419,7 @@
         <v>3148</v>
       </c>
       <c r="N283" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O283" t="s">
         <v>3149</v>
@@ -29479,7 +29483,7 @@
         <v>3157</v>
       </c>
       <c r="N284" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O284" t="s">
         <v>3158</v>
@@ -29523,7 +29527,7 @@
         <v>27</v>
       </c>
       <c r="H285" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I285" t="s">
         <v>3165</v>
@@ -29541,7 +29545,7 @@
         <v>3169</v>
       </c>
       <c r="N285" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O285" t="s">
         <v>3170</v>
@@ -29585,7 +29589,7 @@
         <v>27</v>
       </c>
       <c r="H286" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I286" t="s">
         <v>3173</v>
@@ -29603,7 +29607,7 @@
         <v>3177</v>
       </c>
       <c r="N286" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O286" t="s">
         <v>3178</v>
@@ -29647,7 +29651,7 @@
         <v>27</v>
       </c>
       <c r="H287" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I287" t="s">
         <v>3181</v>
@@ -29665,7 +29669,7 @@
         <v>3185</v>
       </c>
       <c r="N287" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O287" t="s">
         <v>3186</v>
@@ -29711,7 +29715,7 @@
         <v>27</v>
       </c>
       <c r="H288" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I288" t="s">
         <v>3189</v>
@@ -29729,7 +29733,7 @@
         <v>3193</v>
       </c>
       <c r="N288" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O288" t="s">
         <v>3194</v>
@@ -29773,7 +29777,7 @@
         <v>27</v>
       </c>
       <c r="H289" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I289" t="s">
         <v>3201</v>
@@ -29791,7 +29795,7 @@
         <v>3205</v>
       </c>
       <c r="N289" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O289" t="s">
         <v>3206</v>
@@ -29855,7 +29859,7 @@
         <v>3215</v>
       </c>
       <c r="N290" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O290" t="s">
         <v>3216</v>
@@ -29901,7 +29905,7 @@
         <v>27</v>
       </c>
       <c r="H291" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I291" t="s">
         <v>3222</v>
@@ -29917,7 +29921,7 @@
         <v>3225</v>
       </c>
       <c r="N291" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O291" t="s">
         <v>3226</v>
@@ -29963,7 +29967,7 @@
         <v>27</v>
       </c>
       <c r="H292" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I292" t="s">
         <v>3231</v>
@@ -29981,7 +29985,7 @@
         <v>3235</v>
       </c>
       <c r="N292" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O292" t="s">
         <v>3236</v>
@@ -30045,7 +30049,7 @@
         <v>3244</v>
       </c>
       <c r="N293" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O293" t="s">
         <v>3245</v>
@@ -30091,7 +30095,7 @@
         <v>27</v>
       </c>
       <c r="H294" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I294" t="s">
         <v>3250</v>
@@ -30109,7 +30113,7 @@
         <v>3254</v>
       </c>
       <c r="N294" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O294" t="s">
         <v>3255</v>
@@ -30173,7 +30177,7 @@
         <v>3265</v>
       </c>
       <c r="N295" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O295" t="s">
         <v>3266</v>
@@ -30237,7 +30241,7 @@
         <v>3277</v>
       </c>
       <c r="N296" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O296" t="s">
         <v>3278</v>
@@ -30299,7 +30303,7 @@
         <v>3286</v>
       </c>
       <c r="N297" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O297" t="s">
         <v>3287</v>
@@ -30361,7 +30365,7 @@
         <v>3298</v>
       </c>
       <c r="N298" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O298" t="s">
         <v>3299</v>
@@ -30425,7 +30429,7 @@
         <v>3310</v>
       </c>
       <c r="N299" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O299" t="s">
         <v>3311</v>
@@ -30489,7 +30493,7 @@
         <v>3319</v>
       </c>
       <c r="N300" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O300" t="s">
         <v>3320</v>
@@ -30553,7 +30557,7 @@
         <v>3329</v>
       </c>
       <c r="N301" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O301" t="s">
         <v>3330</v>
@@ -30599,7 +30603,7 @@
         <v>27</v>
       </c>
       <c r="H302" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I302" t="s">
         <v>3338</v>
@@ -30617,7 +30621,7 @@
         <v>3342</v>
       </c>
       <c r="N302" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O302" t="s">
         <v>3343</v>
@@ -30663,7 +30667,7 @@
         <v>27</v>
       </c>
       <c r="H303" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I303" t="s">
         <v>3350</v>
@@ -30681,7 +30685,7 @@
         <v>3354</v>
       </c>
       <c r="N303" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O303" t="s">
         <v>3355</v>
@@ -30745,7 +30749,7 @@
         <v>3366</v>
       </c>
       <c r="N304" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O304" t="s">
         <v>3367</v>
@@ -30809,7 +30813,7 @@
         <v>3375</v>
       </c>
       <c r="N305" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O305" t="s">
         <v>3376</v>
@@ -30873,7 +30877,7 @@
         <v>3384</v>
       </c>
       <c r="N306" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O306" t="s">
         <v>3385</v>
@@ -30937,7 +30941,7 @@
         <v>3396</v>
       </c>
       <c r="N307" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O307" t="s">
         <v>3397</v>
@@ -30999,7 +31003,7 @@
         <v>3404</v>
       </c>
       <c r="N308" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O308" t="s">
         <v>3405</v>
@@ -31061,7 +31065,7 @@
         <v>3412</v>
       </c>
       <c r="N309" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O309" t="s">
         <v>3413</v>
@@ -31125,7 +31129,7 @@
         <v>3421</v>
       </c>
       <c r="N310" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O310" t="s">
         <v>3422</v>
@@ -31189,7 +31193,7 @@
         <v>3434</v>
       </c>
       <c r="N311" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O311" t="s">
         <v>3435</v>
@@ -31235,7 +31239,7 @@
         <v>27</v>
       </c>
       <c r="H312" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I312" t="s">
         <v>3443</v>
@@ -31253,7 +31257,7 @@
         <v>3447</v>
       </c>
       <c r="N312" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O312" t="s">
         <v>3448</v>
@@ -31317,7 +31321,7 @@
         <v>3457</v>
       </c>
       <c r="N313" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O313" t="s">
         <v>3458</v>
@@ -31381,7 +31385,7 @@
         <v>3466</v>
       </c>
       <c r="N314" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O314" t="s">
         <v>3467</v>
@@ -31445,7 +31449,7 @@
         <v>3475</v>
       </c>
       <c r="N315" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O315" t="s">
         <v>3476</v>
@@ -31491,7 +31495,7 @@
         <v>164</v>
       </c>
       <c r="H316" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I316" t="s">
         <v>3482</v>
@@ -31509,7 +31513,7 @@
         <v>3486</v>
       </c>
       <c r="N316" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O316" t="s">
         <v>3487</v>
@@ -31573,7 +31577,7 @@
         <v>3497</v>
       </c>
       <c r="N317" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O317" t="s">
         <v>3498</v>
@@ -31637,7 +31641,7 @@
         <v>3509</v>
       </c>
       <c r="N318" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O318" t="s">
         <v>3510</v>
@@ -31701,7 +31705,7 @@
         <v>3519</v>
       </c>
       <c r="N319" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O319" t="s">
         <v>3520</v>
@@ -31765,7 +31769,7 @@
         <v>3528</v>
       </c>
       <c r="N320" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O320" t="s">
         <v>3529</v>
@@ -31829,7 +31833,7 @@
         <v>3537</v>
       </c>
       <c r="N321" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O321" t="s">
         <v>3538</v>
@@ -31875,7 +31879,7 @@
         <v>27</v>
       </c>
       <c r="H322" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I322" t="s">
         <v>3542</v>
@@ -31893,7 +31897,7 @@
         <v>3546</v>
       </c>
       <c r="N322" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O322" t="s">
         <v>3547</v>
@@ -31957,7 +31961,7 @@
         <v>3557</v>
       </c>
       <c r="N323" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O323" t="s">
         <v>3558</v>
@@ -32021,7 +32025,7 @@
         <v>3565</v>
       </c>
       <c r="N324" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O324" t="s">
         <v>3566</v>
@@ -32085,7 +32089,7 @@
         <v>3574</v>
       </c>
       <c r="N325" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="O325" t="s">
         <v>3575</v>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -11233,9 +11233,7 @@
       <c r="R2" t="s">
         <v>37</v>
       </c>
-      <c r="S2" t="s">
-        <v>37</v>
-      </c>
+      <c r="S2"/>
       <c r="T2" t="s">
         <v>38</v>
       </c>
@@ -11299,9 +11297,7 @@
       <c r="R3" t="s">
         <v>37</v>
       </c>
-      <c r="S3" t="s">
-        <v>37</v>
-      </c>
+      <c r="S3"/>
       <c r="T3" t="s">
         <v>52</v>
       </c>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3580" uniqueCount="3580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3581" uniqueCount="3581">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -7300,6 +7300,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20253984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-18</t>
   </si>
   <si>
     <t xml:space="preserve">25.7663</t>
@@ -25049,7 +25052,7 @@
         <v>2426</v>
       </c>
       <c r="N214" t="s">
-        <v>2258</v>
+        <v>33</v>
       </c>
       <c r="O214" t="s">
         <v>2427</v>
@@ -25060,8 +25063,12 @@
       <c r="Q214" t="s">
         <v>98</v>
       </c>
-      <c r="R214"/>
-      <c r="S214"/>
+      <c r="R214" t="s">
+        <v>2429</v>
+      </c>
+      <c r="S214" t="s">
+        <v>2429</v>
+      </c>
       <c r="T214" t="s">
         <v>718</v>
       </c>
@@ -25077,7 +25084,7 @@
         <v>20257663</v>
       </c>
       <c r="B215" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="C215" t="s">
         <v>23</v>
@@ -25098,26 +25105,26 @@
         <v>90</v>
       </c>
       <c r="I215" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="J215" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="K215"/>
       <c r="L215" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="M215" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="N215" t="s">
         <v>33</v>
       </c>
       <c r="O215" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="P215" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="Q215" t="s">
         <v>98</v>
@@ -25125,13 +25132,13 @@
       <c r="R215"/>
       <c r="S215"/>
       <c r="T215" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="U215" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="V215" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="216">
@@ -25139,13 +25146,13 @@
         <v>20257698</v>
       </c>
       <c r="B216" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="C216" t="s">
         <v>23</v>
       </c>
       <c r="D216" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="E216" t="s">
         <v>57</v>
@@ -25160,26 +25167,26 @@
         <v>90</v>
       </c>
       <c r="I216" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="J216" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="K216"/>
       <c r="L216" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="M216" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="N216" t="s">
         <v>33</v>
       </c>
       <c r="O216" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="P216" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="Q216" t="s">
         <v>98</v>
@@ -25201,19 +25208,19 @@
         <v>20253971</v>
       </c>
       <c r="B217" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="C217" t="s">
         <v>87</v>
       </c>
       <c r="D217" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="E217" t="s">
         <v>25</v>
       </c>
       <c r="F217" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="G217" t="s">
         <v>164</v>
@@ -25222,28 +25229,28 @@
         <v>45</v>
       </c>
       <c r="I217" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="J217" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="K217" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="L217" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="M217" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="N217" t="s">
         <v>33</v>
       </c>
       <c r="O217" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="P217" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="Q217" t="s">
         <v>82</v>
@@ -25265,7 +25272,7 @@
         <v>20257601</v>
       </c>
       <c r="B218" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="C218" t="s">
         <v>23</v>
@@ -25277,7 +25284,7 @@
         <v>150</v>
       </c>
       <c r="F218" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="G218" t="s">
         <v>27</v>
@@ -25286,26 +25293,26 @@
         <v>151</v>
       </c>
       <c r="I218" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="J218" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="K218"/>
       <c r="L218" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="M218" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="N218" t="s">
         <v>33</v>
       </c>
       <c r="O218" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="P218" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="Q218" t="s">
         <v>82</v>
@@ -25327,17 +25334,17 @@
         <v>20253941</v>
       </c>
       <c r="B219" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="C219" t="s">
         <v>135</v>
       </c>
       <c r="D219" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="E219"/>
       <c r="F219" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="G219" t="s">
         <v>27</v>
@@ -25346,28 +25353,28 @@
         <v>361</v>
       </c>
       <c r="I219" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="J219" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="K219" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="L219" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="M219" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="N219" t="s">
         <v>782</v>
       </c>
       <c r="O219" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="P219" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="Q219" t="s">
         <v>98</v>
@@ -25383,19 +25390,19 @@
         <v>20194371</v>
       </c>
       <c r="B220" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="C220" t="s">
         <v>135</v>
       </c>
       <c r="D220" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="E220" t="s">
         <v>183</v>
       </c>
       <c r="F220" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="G220" t="s">
         <v>164</v>
@@ -25404,28 +25411,28 @@
         <v>28</v>
       </c>
       <c r="I220" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="J220" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="K220" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="L220" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="M220" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="N220" t="s">
         <v>33</v>
       </c>
       <c r="O220" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="P220" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="Q220" t="s">
         <v>82</v>
@@ -25433,13 +25440,13 @@
       <c r="R220"/>
       <c r="S220"/>
       <c r="T220" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="U220" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="V220" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="221">
@@ -25447,7 +25454,7 @@
         <v>20194061</v>
       </c>
       <c r="B221" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="C221" t="s">
         <v>87</v>
@@ -25459,7 +25466,7 @@
         <v>105</v>
       </c>
       <c r="F221" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="G221" t="s">
         <v>27</v>
@@ -25468,28 +25475,28 @@
         <v>151</v>
       </c>
       <c r="I221" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="J221" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="K221" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="L221" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="M221" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="N221" t="s">
         <v>33</v>
       </c>
       <c r="O221" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="P221" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="Q221" t="s">
         <v>36</v>
@@ -25497,13 +25504,13 @@
       <c r="R221"/>
       <c r="S221"/>
       <c r="T221" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="U221" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="V221" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="222">
@@ -25511,19 +25518,19 @@
         <v>20194017</v>
       </c>
       <c r="B222" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="C222" t="s">
         <v>87</v>
       </c>
       <c r="D222" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="E222" t="s">
         <v>723</v>
       </c>
       <c r="F222" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="G222" t="s">
         <v>27</v>
@@ -25532,28 +25539,28 @@
         <v>59</v>
       </c>
       <c r="I222" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="J222" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="K222" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="L222" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="M222" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="N222" t="s">
         <v>33</v>
       </c>
       <c r="O222" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="P222" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="Q222" t="s">
         <v>82</v>
@@ -25561,13 +25568,13 @@
       <c r="R222"/>
       <c r="S222"/>
       <c r="T222" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="U222" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="V222" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="223">
@@ -25575,7 +25582,7 @@
         <v>20195385</v>
       </c>
       <c r="B223" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="C223" t="s">
         <v>23</v>
@@ -25587,7 +25594,7 @@
         <v>25</v>
       </c>
       <c r="F223" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="G223" t="s">
         <v>27</v>
@@ -25596,26 +25603,26 @@
         <v>28</v>
       </c>
       <c r="I223" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="J223" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="K223"/>
       <c r="L223" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="M223" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="N223" t="s">
         <v>33</v>
       </c>
       <c r="O223" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="P223" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="Q223" t="s">
         <v>36</v>
@@ -25637,19 +25644,19 @@
         <v>20193845</v>
       </c>
       <c r="B224" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="C224" t="s">
         <v>87</v>
       </c>
       <c r="D224" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="E224" t="s">
         <v>105</v>
       </c>
       <c r="F224" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="G224" t="s">
         <v>27</v>
@@ -25658,28 +25665,28 @@
         <v>59</v>
       </c>
       <c r="I224" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="J224" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="K224" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="L224" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="M224" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="N224" t="s">
         <v>33</v>
       </c>
       <c r="O224" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="P224" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="Q224" t="s">
         <v>98</v>
@@ -25687,13 +25694,13 @@
       <c r="R224"/>
       <c r="S224"/>
       <c r="T224" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="U224" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="V224" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="225">
@@ -25701,7 +25708,7 @@
         <v>20193881</v>
       </c>
       <c r="B225" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="C225" t="s">
         <v>87</v>
@@ -25713,7 +25720,7 @@
         <v>105</v>
       </c>
       <c r="F225" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="G225" t="s">
         <v>27</v>
@@ -25722,28 +25729,28 @@
         <v>90</v>
       </c>
       <c r="I225" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="J225" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="K225" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="L225" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="M225" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="N225" t="s">
         <v>33</v>
       </c>
       <c r="O225" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="P225" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="Q225" t="s">
         <v>82</v>
@@ -25765,19 +25772,19 @@
         <v>20193905</v>
       </c>
       <c r="B226" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="C226" t="s">
         <v>87</v>
       </c>
       <c r="D226" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="E226" t="s">
         <v>270</v>
       </c>
       <c r="F226" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="G226" t="s">
         <v>27</v>
@@ -25786,28 +25793,28 @@
         <v>474</v>
       </c>
       <c r="I226" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="J226" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="K226" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="L226" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="M226" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="N226" t="s">
         <v>33</v>
       </c>
       <c r="O226" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="P226" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="Q226" t="s">
         <v>98</v>
@@ -25815,13 +25822,13 @@
       <c r="R226"/>
       <c r="S226"/>
       <c r="T226" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="U226" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="V226" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="227">
@@ -25829,7 +25836,7 @@
         <v>20191042</v>
       </c>
       <c r="B227" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="C227" t="s">
         <v>23</v>
@@ -25841,7 +25848,7 @@
         <v>105</v>
       </c>
       <c r="F227" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="G227" t="s">
         <v>27</v>
@@ -25850,28 +25857,28 @@
         <v>28</v>
       </c>
       <c r="I227" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="J227" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="K227" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="L227" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="M227" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="N227" t="s">
         <v>33</v>
       </c>
       <c r="O227" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="P227" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="Q227" t="s">
         <v>98</v>
@@ -25893,19 +25900,19 @@
         <v>20193786</v>
       </c>
       <c r="B228" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="C228" t="s">
         <v>87</v>
       </c>
       <c r="D228" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="E228" t="s">
         <v>270</v>
       </c>
       <c r="F228" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="G228" t="s">
         <v>27</v>
@@ -25914,28 +25921,28 @@
         <v>90</v>
       </c>
       <c r="I228" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="J228" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="K228" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="L228" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="M228" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="N228" t="s">
         <v>33</v>
       </c>
       <c r="O228" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="P228" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="Q228" t="s">
         <v>36</v>
@@ -25957,7 +25964,7 @@
         <v>20193700</v>
       </c>
       <c r="B229" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="C229" t="s">
         <v>87</v>
@@ -25969,7 +25976,7 @@
         <v>270</v>
       </c>
       <c r="F229" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="G229" t="s">
         <v>27</v>
@@ -25978,28 +25985,28 @@
         <v>59</v>
       </c>
       <c r="I229" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="J229" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="K229" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="L229" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="M229" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="N229" t="s">
         <v>33</v>
       </c>
       <c r="O229" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="P229" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="Q229" t="s">
         <v>98</v>
@@ -26007,13 +26014,13 @@
       <c r="R229"/>
       <c r="S229"/>
       <c r="T229" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="U229" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="V229" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="230">
@@ -26021,19 +26028,19 @@
         <v>20193704</v>
       </c>
       <c r="B230" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="C230" t="s">
         <v>87</v>
       </c>
       <c r="D230" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="E230" t="s">
         <v>183</v>
       </c>
       <c r="F230" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="G230" t="s">
         <v>164</v>
@@ -26042,28 +26049,28 @@
         <v>90</v>
       </c>
       <c r="I230" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="J230" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="K230" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="L230" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="M230" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="N230" t="s">
         <v>33</v>
       </c>
       <c r="O230" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="P230" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="Q230" t="s">
         <v>98</v>
@@ -26085,7 +26092,7 @@
         <v>20193636</v>
       </c>
       <c r="B231" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="C231" t="s">
         <v>87</v>
@@ -26097,7 +26104,7 @@
         <v>25</v>
       </c>
       <c r="F231" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="G231" t="s">
         <v>27</v>
@@ -26106,28 +26113,28 @@
         <v>59</v>
       </c>
       <c r="I231" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="J231" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="K231" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="L231" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="M231" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="N231" t="s">
         <v>33</v>
       </c>
       <c r="O231" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="P231" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="Q231" t="s">
         <v>82</v>
@@ -26135,13 +26142,13 @@
       <c r="R231"/>
       <c r="S231"/>
       <c r="T231" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="U231" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="V231" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="232">
@@ -26149,19 +26156,19 @@
         <v>20193621</v>
       </c>
       <c r="B232" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
       <c r="C232" t="s">
         <v>195</v>
       </c>
       <c r="D232" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="E232" t="s">
         <v>25</v>
       </c>
       <c r="F232" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="G232" t="s">
         <v>27</v>
@@ -26170,28 +26177,28 @@
         <v>151</v>
       </c>
       <c r="I232" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="J232" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="K232" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="L232" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="M232" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="N232" t="s">
         <v>33</v>
       </c>
       <c r="O232" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="P232" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="Q232" t="s">
         <v>98</v>
@@ -26199,13 +26206,13 @@
       <c r="R232"/>
       <c r="S232"/>
       <c r="T232" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="U232" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="V232" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="233">
@@ -26213,7 +26220,7 @@
         <v>20195311</v>
       </c>
       <c r="B233" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="C233" t="s">
         <v>23</v>
@@ -26225,7 +26232,7 @@
         <v>270</v>
       </c>
       <c r="F233" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="G233" t="s">
         <v>27</v>
@@ -26234,26 +26241,26 @@
         <v>90</v>
       </c>
       <c r="I233" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="J233" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="K233"/>
       <c r="L233" t="s">
-        <v>2622</v>
+        <v>2623</v>
       </c>
       <c r="M233" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="N233" t="s">
         <v>33</v>
       </c>
       <c r="O233" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="P233" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="Q233" t="s">
         <v>36</v>
@@ -26261,13 +26268,13 @@
       <c r="R233"/>
       <c r="S233"/>
       <c r="T233" t="s">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="U233" t="s">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="V233" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="234">
@@ -26275,19 +26282,19 @@
         <v>20193424</v>
       </c>
       <c r="B234" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="C234" t="s">
         <v>87</v>
       </c>
       <c r="D234" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="E234" t="s">
         <v>25</v>
       </c>
       <c r="F234" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="G234" t="s">
         <v>27</v>
@@ -26296,28 +26303,28 @@
         <v>151</v>
       </c>
       <c r="I234" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="J234" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="K234" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="L234" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="M234" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="N234" t="s">
         <v>33</v>
       </c>
       <c r="O234" t="s">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="P234" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="Q234" t="s">
         <v>98</v>
@@ -26325,13 +26332,13 @@
       <c r="R234"/>
       <c r="S234"/>
       <c r="T234" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="U234" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="V234" t="s">
-        <v>2640</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="235">
@@ -26339,19 +26346,19 @@
         <v>20193210</v>
       </c>
       <c r="B235" t="s">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="C235" t="s">
         <v>87</v>
       </c>
       <c r="D235" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="E235" t="s">
         <v>105</v>
       </c>
       <c r="F235" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="G235" t="s">
         <v>27</v>
@@ -26360,28 +26367,28 @@
         <v>28</v>
       </c>
       <c r="I235" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="J235" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="K235" t="s">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="L235" t="s">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="M235" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="N235" t="s">
         <v>33</v>
       </c>
       <c r="O235" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="P235" t="s">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="Q235" t="s">
         <v>82</v>
@@ -26389,13 +26396,13 @@
       <c r="R235"/>
       <c r="S235"/>
       <c r="T235" t="s">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="U235" t="s">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="V235" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="236">
@@ -26403,7 +26410,7 @@
         <v>20193249</v>
       </c>
       <c r="B236" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="C236" t="s">
         <v>135</v>
@@ -26415,7 +26422,7 @@
         <v>105</v>
       </c>
       <c r="F236" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="G236" t="s">
         <v>27</v>
@@ -26424,28 +26431,28 @@
         <v>28</v>
       </c>
       <c r="I236" t="s">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="J236" t="s">
-        <v>2656</v>
+        <v>2657</v>
       </c>
       <c r="K236" t="s">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="L236" t="s">
-        <v>2658</v>
+        <v>2659</v>
       </c>
       <c r="M236" t="s">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="N236" t="s">
         <v>33</v>
       </c>
       <c r="O236" t="s">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="P236" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="Q236" t="s">
         <v>36</v>
@@ -26453,13 +26460,13 @@
       <c r="R236"/>
       <c r="S236"/>
       <c r="T236" t="s">
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="U236" t="s">
-        <v>2663</v>
+        <v>2664</v>
       </c>
       <c r="V236" t="s">
-        <v>2664</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="237">
@@ -26467,7 +26474,7 @@
         <v>20193253</v>
       </c>
       <c r="B237" t="s">
-        <v>2665</v>
+        <v>2666</v>
       </c>
       <c r="C237" t="s">
         <v>87</v>
@@ -26479,7 +26486,7 @@
         <v>723</v>
       </c>
       <c r="F237" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="G237" t="s">
         <v>27</v>
@@ -26488,28 +26495,28 @@
         <v>59</v>
       </c>
       <c r="I237" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="J237" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="K237" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="L237" t="s">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="M237" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="N237" t="s">
         <v>33</v>
       </c>
       <c r="O237" t="s">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="P237" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="Q237" t="s">
         <v>36</v>
@@ -26517,13 +26524,13 @@
       <c r="R237"/>
       <c r="S237"/>
       <c r="T237" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="U237" t="s">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="V237" t="s">
-        <v>2675</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="238">
@@ -26531,19 +26538,19 @@
         <v>20193160</v>
       </c>
       <c r="B238" t="s">
-        <v>2676</v>
+        <v>2677</v>
       </c>
       <c r="C238" t="s">
         <v>135</v>
       </c>
       <c r="D238" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="E238" t="s">
         <v>270</v>
       </c>
       <c r="F238" t="s">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="G238" t="s">
         <v>27</v>
@@ -26552,28 +26559,28 @@
         <v>151</v>
       </c>
       <c r="I238" t="s">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="J238" t="s">
-        <v>2679</v>
+        <v>2680</v>
       </c>
       <c r="K238" t="s">
-        <v>2680</v>
+        <v>2681</v>
       </c>
       <c r="L238" t="s">
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="M238" t="s">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="N238" t="s">
         <v>33</v>
       </c>
       <c r="O238" t="s">
-        <v>2683</v>
+        <v>2684</v>
       </c>
       <c r="P238" t="s">
-        <v>2684</v>
+        <v>2685</v>
       </c>
       <c r="Q238" t="s">
         <v>82</v>
@@ -26581,13 +26588,13 @@
       <c r="R238"/>
       <c r="S238"/>
       <c r="T238" t="s">
-        <v>2685</v>
+        <v>2686</v>
       </c>
       <c r="U238" t="s">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="V238" t="s">
-        <v>2687</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="239">
@@ -26595,19 +26602,19 @@
         <v>20193171</v>
       </c>
       <c r="B239" t="s">
-        <v>2688</v>
+        <v>2689</v>
       </c>
       <c r="C239" t="s">
         <v>87</v>
       </c>
       <c r="D239" t="s">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="E239" t="s">
         <v>105</v>
       </c>
       <c r="F239" t="s">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="G239" t="s">
         <v>164</v>
@@ -26616,28 +26623,28 @@
         <v>28</v>
       </c>
       <c r="I239" t="s">
-        <v>2690</v>
+        <v>2691</v>
       </c>
       <c r="J239" t="s">
-        <v>2691</v>
+        <v>2692</v>
       </c>
       <c r="K239" t="s">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="L239" t="s">
-        <v>2693</v>
+        <v>2694</v>
       </c>
       <c r="M239" t="s">
-        <v>2694</v>
+        <v>2695</v>
       </c>
       <c r="N239" t="s">
         <v>33</v>
       </c>
       <c r="O239" t="s">
-        <v>2695</v>
+        <v>2696</v>
       </c>
       <c r="P239" t="s">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="Q239" t="s">
         <v>82</v>
@@ -26645,13 +26652,13 @@
       <c r="R239"/>
       <c r="S239"/>
       <c r="T239" t="s">
-        <v>2697</v>
+        <v>2698</v>
       </c>
       <c r="U239" t="s">
-        <v>2698</v>
+        <v>2699</v>
       </c>
       <c r="V239" t="s">
-        <v>2699</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="240">
@@ -26659,19 +26666,19 @@
         <v>20193123</v>
       </c>
       <c r="B240" t="s">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="C240" t="s">
         <v>87</v>
       </c>
       <c r="D240" t="s">
-        <v>2701</v>
+        <v>2702</v>
       </c>
       <c r="E240" t="s">
         <v>270</v>
       </c>
       <c r="F240" t="s">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="G240" t="s">
         <v>27</v>
@@ -26680,28 +26687,28 @@
         <v>151</v>
       </c>
       <c r="I240" t="s">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="J240" t="s">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="K240" t="s">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="L240" t="s">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="M240" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="N240" t="s">
         <v>33</v>
       </c>
       <c r="O240" t="s">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="P240" t="s">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="Q240" t="s">
         <v>36</v>
@@ -26709,13 +26716,13 @@
       <c r="R240"/>
       <c r="S240"/>
       <c r="T240" t="s">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="U240" t="s">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="V240" t="s">
-        <v>2712</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="241">
@@ -26723,19 +26730,19 @@
         <v>20193085</v>
       </c>
       <c r="B241" t="s">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="C241" t="s">
         <v>135</v>
       </c>
       <c r="D241" t="s">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="E241" t="s">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="F241" t="s">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="G241" t="s">
         <v>27</v>
@@ -26744,28 +26751,28 @@
         <v>28</v>
       </c>
       <c r="I241" t="s">
-        <v>2717</v>
+        <v>2718</v>
       </c>
       <c r="J241" t="s">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="K241" t="s">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="L241" t="s">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="M241" t="s">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="N241" t="s">
         <v>33</v>
       </c>
       <c r="O241" t="s">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="P241" t="s">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="Q241" t="s">
         <v>36</v>
@@ -26787,19 +26794,19 @@
         <v>20195083</v>
       </c>
       <c r="B242" t="s">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="C242" t="s">
         <v>23</v>
       </c>
       <c r="D242" t="s">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="E242" t="s">
         <v>25</v>
       </c>
       <c r="F242" t="s">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="G242" t="s">
         <v>27</v>
@@ -26808,26 +26815,26 @@
         <v>59</v>
       </c>
       <c r="I242" t="s">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="J242" t="s">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="K242"/>
       <c r="L242" t="s">
-        <v>2729</v>
+        <v>2730</v>
       </c>
       <c r="M242" t="s">
-        <v>2730</v>
+        <v>2731</v>
       </c>
       <c r="N242" t="s">
         <v>33</v>
       </c>
       <c r="O242" t="s">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="P242" t="s">
-        <v>2732</v>
+        <v>2733</v>
       </c>
       <c r="Q242" t="s">
         <v>98</v>
@@ -26849,19 +26856,19 @@
         <v>20195086</v>
       </c>
       <c r="B243" t="s">
-        <v>2733</v>
+        <v>2734</v>
       </c>
       <c r="C243" t="s">
         <v>23</v>
       </c>
       <c r="D243" t="s">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="E243" t="s">
         <v>25</v>
       </c>
       <c r="F243" t="s">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="G243" t="s">
         <v>27</v>
@@ -26870,26 +26877,26 @@
         <v>59</v>
       </c>
       <c r="I243" t="s">
-        <v>2734</v>
+        <v>2735</v>
       </c>
       <c r="J243" t="s">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="K243"/>
       <c r="L243" t="s">
-        <v>2736</v>
+        <v>2737</v>
       </c>
       <c r="M243" t="s">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="N243" t="s">
         <v>33</v>
       </c>
       <c r="O243" t="s">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="P243" t="s">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="Q243" t="s">
         <v>98</v>
@@ -26911,19 +26918,19 @@
         <v>20184408</v>
       </c>
       <c r="B244" t="s">
-        <v>2740</v>
+        <v>2741</v>
       </c>
       <c r="C244" t="s">
         <v>135</v>
       </c>
       <c r="D244" t="s">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="E244" t="s">
         <v>723</v>
       </c>
       <c r="F244" t="s">
-        <v>2742</v>
+        <v>2743</v>
       </c>
       <c r="G244" t="s">
         <v>27</v>
@@ -26932,28 +26939,28 @@
         <v>59</v>
       </c>
       <c r="I244" t="s">
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="J244" t="s">
-        <v>2744</v>
+        <v>2745</v>
       </c>
       <c r="K244" t="s">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="L244" t="s">
-        <v>2746</v>
+        <v>2747</v>
       </c>
       <c r="M244" t="s">
-        <v>2747</v>
+        <v>2748</v>
       </c>
       <c r="N244" t="s">
         <v>33</v>
       </c>
       <c r="O244" t="s">
-        <v>2748</v>
+        <v>2749</v>
       </c>
       <c r="P244" t="s">
-        <v>2749</v>
+        <v>2750</v>
       </c>
       <c r="Q244" t="s">
         <v>82</v>
@@ -26975,19 +26982,19 @@
         <v>20184243</v>
       </c>
       <c r="B245" t="s">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="C245" t="s">
         <v>87</v>
       </c>
       <c r="D245" t="s">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="E245" t="s">
         <v>270</v>
       </c>
       <c r="F245" t="s">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="G245" t="s">
         <v>27</v>
@@ -26996,28 +27003,28 @@
         <v>59</v>
       </c>
       <c r="I245" t="s">
-        <v>2753</v>
+        <v>2754</v>
       </c>
       <c r="J245" t="s">
-        <v>2754</v>
+        <v>2755</v>
       </c>
       <c r="K245" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="L245" t="s">
-        <v>2756</v>
+        <v>2757</v>
       </c>
       <c r="M245" t="s">
-        <v>2757</v>
+        <v>2758</v>
       </c>
       <c r="N245" t="s">
         <v>33</v>
       </c>
       <c r="O245" t="s">
-        <v>2758</v>
+        <v>2759</v>
       </c>
       <c r="P245" t="s">
-        <v>2759</v>
+        <v>2760</v>
       </c>
       <c r="Q245" t="s">
         <v>82</v>
@@ -27039,7 +27046,7 @@
         <v>20184261</v>
       </c>
       <c r="B246" t="s">
-        <v>2760</v>
+        <v>2761</v>
       </c>
       <c r="C246" t="s">
         <v>135</v>
@@ -27051,7 +27058,7 @@
         <v>723</v>
       </c>
       <c r="F246" t="s">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="G246" t="s">
         <v>27</v>
@@ -27060,28 +27067,28 @@
         <v>28</v>
       </c>
       <c r="I246" t="s">
-        <v>2761</v>
+        <v>2762</v>
       </c>
       <c r="J246" t="s">
-        <v>2762</v>
+        <v>2763</v>
       </c>
       <c r="K246" t="s">
-        <v>2763</v>
+        <v>2764</v>
       </c>
       <c r="L246" t="s">
-        <v>2764</v>
+        <v>2765</v>
       </c>
       <c r="M246" t="s">
-        <v>2765</v>
+        <v>2766</v>
       </c>
       <c r="N246" t="s">
         <v>33</v>
       </c>
       <c r="O246" t="s">
-        <v>2766</v>
+        <v>2767</v>
       </c>
       <c r="P246" t="s">
-        <v>2767</v>
+        <v>2768</v>
       </c>
       <c r="Q246" t="s">
         <v>82</v>
@@ -27089,13 +27096,13 @@
       <c r="R246"/>
       <c r="S246"/>
       <c r="T246" t="s">
-        <v>2768</v>
+        <v>2769</v>
       </c>
       <c r="U246" t="s">
-        <v>2769</v>
+        <v>2770</v>
       </c>
       <c r="V246" t="s">
-        <v>2770</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="247">
@@ -27103,19 +27110,19 @@
         <v>20185747</v>
       </c>
       <c r="B247" t="s">
-        <v>2771</v>
+        <v>2772</v>
       </c>
       <c r="C247" t="s">
         <v>23</v>
       </c>
       <c r="D247" t="s">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="E247" t="s">
         <v>723</v>
       </c>
       <c r="F247" t="s">
-        <v>2772</v>
+        <v>2773</v>
       </c>
       <c r="G247" t="s">
         <v>27</v>
@@ -27124,26 +27131,26 @@
         <v>59</v>
       </c>
       <c r="I247" t="s">
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="J247" t="s">
-        <v>2774</v>
+        <v>2775</v>
       </c>
       <c r="K247"/>
       <c r="L247" t="s">
-        <v>2775</v>
+        <v>2776</v>
       </c>
       <c r="M247" t="s">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="N247" t="s">
         <v>33</v>
       </c>
       <c r="O247" t="s">
-        <v>2777</v>
+        <v>2778</v>
       </c>
       <c r="P247" t="s">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="Q247" t="s">
         <v>82</v>
@@ -27165,7 +27172,7 @@
         <v>20185704</v>
       </c>
       <c r="B248" t="s">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="C248" t="s">
         <v>23</v>
@@ -27177,7 +27184,7 @@
         <v>25</v>
       </c>
       <c r="F248" t="s">
-        <v>2780</v>
+        <v>2781</v>
       </c>
       <c r="G248" t="s">
         <v>27</v>
@@ -27186,26 +27193,26 @@
         <v>28</v>
       </c>
       <c r="I248" t="s">
-        <v>2781</v>
+        <v>2782</v>
       </c>
       <c r="J248" t="s">
-        <v>2782</v>
+        <v>2783</v>
       </c>
       <c r="K248"/>
       <c r="L248" t="s">
-        <v>2783</v>
+        <v>2784</v>
       </c>
       <c r="M248" t="s">
-        <v>2784</v>
+        <v>2785</v>
       </c>
       <c r="N248" t="s">
         <v>33</v>
       </c>
       <c r="O248" t="s">
-        <v>2785</v>
+        <v>2786</v>
       </c>
       <c r="P248" t="s">
-        <v>2786</v>
+        <v>2787</v>
       </c>
       <c r="Q248" t="s">
         <v>36</v>
@@ -27213,13 +27220,13 @@
       <c r="R248"/>
       <c r="S248"/>
       <c r="T248" t="s">
-        <v>2787</v>
+        <v>2788</v>
       </c>
       <c r="U248" t="s">
-        <v>2788</v>
+        <v>2789</v>
       </c>
       <c r="V248" t="s">
-        <v>2789</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="249">
@@ -27227,19 +27234,19 @@
         <v>20185710</v>
       </c>
       <c r="B249" t="s">
-        <v>2790</v>
+        <v>2791</v>
       </c>
       <c r="C249" t="s">
         <v>23</v>
       </c>
       <c r="D249" t="s">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="E249" t="s">
         <v>270</v>
       </c>
       <c r="F249" t="s">
-        <v>2780</v>
+        <v>2781</v>
       </c>
       <c r="G249" t="s">
         <v>27</v>
@@ -27248,26 +27255,26 @@
         <v>28</v>
       </c>
       <c r="I249" t="s">
-        <v>2791</v>
+        <v>2792</v>
       </c>
       <c r="J249" t="s">
-        <v>2792</v>
+        <v>2793</v>
       </c>
       <c r="K249"/>
       <c r="L249" t="s">
-        <v>2793</v>
+        <v>2794</v>
       </c>
       <c r="M249" t="s">
-        <v>2794</v>
+        <v>2795</v>
       </c>
       <c r="N249" t="s">
         <v>33</v>
       </c>
       <c r="O249" t="s">
-        <v>2795</v>
+        <v>2796</v>
       </c>
       <c r="P249" t="s">
-        <v>2796</v>
+        <v>2797</v>
       </c>
       <c r="Q249" t="s">
         <v>36</v>
@@ -27275,13 +27282,13 @@
       <c r="R249"/>
       <c r="S249"/>
       <c r="T249" t="s">
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="U249" t="s">
-        <v>2663</v>
+        <v>2664</v>
       </c>
       <c r="V249" t="s">
-        <v>2664</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="250">
@@ -27289,7 +27296,7 @@
         <v>20184126</v>
       </c>
       <c r="B250" t="s">
-        <v>2797</v>
+        <v>2798</v>
       </c>
       <c r="C250" t="s">
         <v>87</v>
@@ -27299,7 +27306,7 @@
       </c>
       <c r="E250"/>
       <c r="F250" t="s">
-        <v>2798</v>
+        <v>2799</v>
       </c>
       <c r="G250" t="s">
         <v>27</v>
@@ -27308,28 +27315,28 @@
         <v>59</v>
       </c>
       <c r="I250" t="s">
-        <v>2799</v>
+        <v>2800</v>
       </c>
       <c r="J250" t="s">
-        <v>2800</v>
+        <v>2801</v>
       </c>
       <c r="K250" t="s">
-        <v>2801</v>
+        <v>2802</v>
       </c>
       <c r="L250" t="s">
-        <v>2802</v>
+        <v>2803</v>
       </c>
       <c r="M250" t="s">
-        <v>2803</v>
+        <v>2804</v>
       </c>
       <c r="N250" t="s">
         <v>33</v>
       </c>
       <c r="O250" t="s">
-        <v>2804</v>
+        <v>2805</v>
       </c>
       <c r="P250" t="s">
-        <v>2805</v>
+        <v>2806</v>
       </c>
       <c r="Q250" t="s">
         <v>98</v>
@@ -27337,13 +27344,13 @@
       <c r="R250"/>
       <c r="S250"/>
       <c r="T250" t="s">
-        <v>2806</v>
+        <v>2807</v>
       </c>
       <c r="U250" t="s">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="V250" t="s">
-        <v>2808</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="251">
@@ -27351,17 +27358,17 @@
         <v>20180469</v>
       </c>
       <c r="B251" t="s">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="C251" t="s">
         <v>119</v>
       </c>
       <c r="D251" t="s">
-        <v>2810</v>
+        <v>2811</v>
       </c>
       <c r="E251"/>
       <c r="F251" t="s">
-        <v>2811</v>
+        <v>2812</v>
       </c>
       <c r="G251" t="s">
         <v>27</v>
@@ -27370,28 +27377,28 @@
         <v>1415</v>
       </c>
       <c r="I251" t="s">
-        <v>2812</v>
+        <v>2813</v>
       </c>
       <c r="J251" t="s">
-        <v>2813</v>
+        <v>2814</v>
       </c>
       <c r="K251" t="s">
-        <v>2814</v>
+        <v>2815</v>
       </c>
       <c r="L251" t="s">
-        <v>2815</v>
+        <v>2816</v>
       </c>
       <c r="M251" t="s">
-        <v>2816</v>
+        <v>2817</v>
       </c>
       <c r="N251" t="s">
         <v>33</v>
       </c>
       <c r="O251" t="s">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="P251" t="s">
-        <v>2818</v>
+        <v>2819</v>
       </c>
       <c r="Q251" t="s">
         <v>36</v>
@@ -27399,13 +27406,13 @@
       <c r="R251"/>
       <c r="S251"/>
       <c r="T251" t="s">
-        <v>2819</v>
+        <v>2820</v>
       </c>
       <c r="U251" t="s">
-        <v>2820</v>
+        <v>2821</v>
       </c>
       <c r="V251" t="s">
-        <v>2821</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="252">
@@ -27413,19 +27420,19 @@
         <v>20184084</v>
       </c>
       <c r="B252" t="s">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="C252" t="s">
         <v>135</v>
       </c>
       <c r="D252" t="s">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="E252" t="s">
         <v>25</v>
       </c>
       <c r="F252" t="s">
-        <v>2824</v>
+        <v>2825</v>
       </c>
       <c r="G252" t="s">
         <v>164</v>
@@ -27434,28 +27441,28 @@
         <v>59</v>
       </c>
       <c r="I252" t="s">
-        <v>2825</v>
+        <v>2826</v>
       </c>
       <c r="J252" t="s">
-        <v>2826</v>
+        <v>2827</v>
       </c>
       <c r="K252" t="s">
-        <v>2827</v>
+        <v>2828</v>
       </c>
       <c r="L252" t="s">
-        <v>2828</v>
+        <v>2829</v>
       </c>
       <c r="M252" t="s">
-        <v>2829</v>
+        <v>2830</v>
       </c>
       <c r="N252" t="s">
         <v>33</v>
       </c>
       <c r="O252" t="s">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="P252" t="s">
-        <v>2831</v>
+        <v>2832</v>
       </c>
       <c r="Q252" t="s">
         <v>82</v>
@@ -27477,7 +27484,7 @@
         <v>20183897</v>
       </c>
       <c r="B253" t="s">
-        <v>2832</v>
+        <v>2833</v>
       </c>
       <c r="C253" t="s">
         <v>135</v>
@@ -27489,7 +27496,7 @@
         <v>183</v>
       </c>
       <c r="F253" t="s">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="G253" t="s">
         <v>27</v>
@@ -27498,28 +27505,28 @@
         <v>151</v>
       </c>
       <c r="I253" t="s">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="J253" t="s">
-        <v>2835</v>
+        <v>2836</v>
       </c>
       <c r="K253" t="s">
-        <v>2836</v>
+        <v>2837</v>
       </c>
       <c r="L253" t="s">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="M253" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="N253" t="s">
         <v>33</v>
       </c>
       <c r="O253" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="P253" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="Q253" t="s">
         <v>36</v>
@@ -27541,19 +27548,19 @@
         <v>20183940</v>
       </c>
       <c r="B254" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="C254" t="s">
         <v>87</v>
       </c>
       <c r="D254" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="E254" t="s">
         <v>25</v>
       </c>
       <c r="F254" t="s">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="G254" t="s">
         <v>27</v>
@@ -27562,28 +27569,28 @@
         <v>323</v>
       </c>
       <c r="I254" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="J254" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="K254" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="L254" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="M254" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="N254" t="s">
         <v>33</v>
       </c>
       <c r="O254" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="P254" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="Q254" t="s">
         <v>82</v>
@@ -27591,13 +27598,13 @@
       <c r="R254"/>
       <c r="S254"/>
       <c r="T254" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
       <c r="U254" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="V254" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="255">
@@ -27605,7 +27612,7 @@
         <v>20183951</v>
       </c>
       <c r="B255" t="s">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="C255" t="s">
         <v>135</v>
@@ -27617,7 +27624,7 @@
         <v>270</v>
       </c>
       <c r="F255" t="s">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="G255" t="s">
         <v>27</v>
@@ -27626,28 +27633,28 @@
         <v>59</v>
       </c>
       <c r="I255" t="s">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="J255" t="s">
-        <v>2855</v>
+        <v>2856</v>
       </c>
       <c r="K255" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="L255" t="s">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="M255" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
       <c r="N255" t="s">
         <v>33</v>
       </c>
       <c r="O255" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="P255" t="s">
-        <v>2860</v>
+        <v>2861</v>
       </c>
       <c r="Q255" t="s">
         <v>98</v>
@@ -27669,7 +27676,7 @@
         <v>20183952</v>
       </c>
       <c r="B256" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="C256" t="s">
         <v>135</v>
@@ -27681,7 +27688,7 @@
         <v>270</v>
       </c>
       <c r="F256" t="s">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="G256" t="s">
         <v>27</v>
@@ -27690,28 +27697,28 @@
         <v>59</v>
       </c>
       <c r="I256" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="J256" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="K256" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="L256" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="M256" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="N256" t="s">
         <v>33</v>
       </c>
       <c r="O256" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="P256" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="Q256" t="s">
         <v>98</v>
@@ -27733,19 +27740,19 @@
         <v>20183986</v>
       </c>
       <c r="B257" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="C257" t="s">
         <v>135</v>
       </c>
       <c r="D257" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="E257" t="s">
         <v>105</v>
       </c>
       <c r="F257" t="s">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="G257" t="s">
         <v>27</v>
@@ -27754,28 +27761,28 @@
         <v>59</v>
       </c>
       <c r="I257" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="J257" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="K257" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="L257" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="M257" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="N257" t="s">
         <v>33</v>
       </c>
       <c r="O257" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="P257" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Q257" t="s">
         <v>98</v>
@@ -27783,13 +27790,13 @@
       <c r="R257"/>
       <c r="S257"/>
       <c r="T257" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="U257" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="V257" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="258">
@@ -27797,19 +27804,19 @@
         <v>20183860</v>
       </c>
       <c r="B258" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="C258" t="s">
         <v>87</v>
       </c>
       <c r="D258" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="E258" t="s">
         <v>270</v>
       </c>
       <c r="F258" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="G258" t="s">
         <v>27</v>
@@ -27818,28 +27825,28 @@
         <v>28</v>
       </c>
       <c r="I258" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="J258" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="K258" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="L258" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="M258" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="N258" t="s">
         <v>33</v>
       </c>
       <c r="O258" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="P258" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Q258" t="s">
         <v>36</v>
@@ -27847,13 +27854,13 @@
       <c r="R258"/>
       <c r="S258"/>
       <c r="T258" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="U258" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="V258" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="259">
@@ -27861,7 +27868,7 @@
         <v>20183877</v>
       </c>
       <c r="B259" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="C259" t="s">
         <v>87</v>
@@ -27873,7 +27880,7 @@
         <v>105</v>
       </c>
       <c r="F259" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="G259" t="s">
         <v>27</v>
@@ -27882,28 +27889,28 @@
         <v>474</v>
       </c>
       <c r="I259" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="J259" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="K259" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="L259" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="M259" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="N259" t="s">
         <v>33</v>
       </c>
       <c r="O259" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="P259" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="Q259" t="s">
         <v>98</v>
@@ -27911,13 +27918,13 @@
       <c r="R259"/>
       <c r="S259"/>
       <c r="T259" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="U259" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="V259" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="260">
@@ -27925,19 +27932,19 @@
         <v>20183832</v>
       </c>
       <c r="B260" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="C260" t="s">
         <v>87</v>
       </c>
       <c r="D260" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="E260" t="s">
         <v>105</v>
       </c>
       <c r="F260" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="G260" t="s">
         <v>27</v>
@@ -27946,28 +27953,28 @@
         <v>45</v>
       </c>
       <c r="I260" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="J260" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="K260" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="L260" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="M260" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="N260" t="s">
         <v>33</v>
       </c>
       <c r="O260" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="P260" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="Q260" t="s">
         <v>82</v>
@@ -27975,13 +27982,13 @@
       <c r="R260"/>
       <c r="S260"/>
       <c r="T260" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="U260" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="V260" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="261">
@@ -27989,19 +27996,19 @@
         <v>20183792</v>
       </c>
       <c r="B261" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="C261" t="s">
         <v>135</v>
       </c>
       <c r="D261" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="E261" t="s">
         <v>25</v>
       </c>
       <c r="F261" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="G261" t="s">
         <v>27</v>
@@ -28010,28 +28017,28 @@
         <v>45</v>
       </c>
       <c r="I261" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="J261" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="K261" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="L261" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="M261" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="N261" t="s">
         <v>33</v>
       </c>
       <c r="O261" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="P261" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="Q261" t="s">
         <v>82</v>
@@ -28053,19 +28060,19 @@
         <v>20185571</v>
       </c>
       <c r="B262" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C262" t="s">
         <v>23</v>
       </c>
       <c r="D262" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="E262" t="s">
         <v>105</v>
       </c>
       <c r="F262" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="G262" t="s">
         <v>27</v>
@@ -28074,26 +28081,26 @@
         <v>45</v>
       </c>
       <c r="I262" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="J262" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="K262"/>
       <c r="L262" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="M262" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="N262" t="s">
         <v>33</v>
       </c>
       <c r="O262" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="P262" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="Q262" t="s">
         <v>82</v>
@@ -28101,13 +28108,13 @@
       <c r="R262"/>
       <c r="S262"/>
       <c r="T262" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="U262" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="V262" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="263">
@@ -28115,19 +28122,19 @@
         <v>20183766</v>
       </c>
       <c r="B263" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="C263" t="s">
         <v>87</v>
       </c>
       <c r="D263" t="s">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="E263" t="s">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="F263" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="G263" t="s">
         <v>27</v>
@@ -28136,28 +28143,28 @@
         <v>45</v>
       </c>
       <c r="I263" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="J263" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="K263" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="L263" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="M263" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="N263" t="s">
         <v>33</v>
       </c>
       <c r="O263" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="P263" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="Q263" t="s">
         <v>82</v>
@@ -28165,13 +28172,13 @@
       <c r="R263"/>
       <c r="S263"/>
       <c r="T263" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="U263" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="V263" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="264">
@@ -28179,7 +28186,7 @@
         <v>20183734</v>
       </c>
       <c r="B264" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="C264" t="s">
         <v>70</v>
@@ -28189,7 +28196,7 @@
       </c>
       <c r="E264"/>
       <c r="F264" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="G264" t="s">
         <v>27</v>
@@ -28198,28 +28205,28 @@
         <v>59</v>
       </c>
       <c r="I264" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="J264" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="K264" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="L264" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="M264" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="N264" t="s">
         <v>33</v>
       </c>
       <c r="O264" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
       <c r="P264" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="Q264" t="s">
         <v>82</v>
@@ -28241,17 +28248,17 @@
         <v>20183735</v>
       </c>
       <c r="B265" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="C265" t="s">
         <v>70</v>
       </c>
       <c r="D265" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="E265"/>
       <c r="F265" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="G265" t="s">
         <v>27</v>
@@ -28260,28 +28267,28 @@
         <v>59</v>
       </c>
       <c r="I265" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="J265" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="K265" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="L265" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="M265" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="N265" t="s">
         <v>33</v>
       </c>
       <c r="O265" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
       <c r="P265" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="Q265" t="s">
         <v>82</v>
@@ -28303,7 +28310,7 @@
         <v>20183736</v>
       </c>
       <c r="B266" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="C266" t="s">
         <v>70</v>
@@ -28313,7 +28320,7 @@
       </c>
       <c r="E266"/>
       <c r="F266" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="G266" t="s">
         <v>27</v>
@@ -28322,28 +28329,28 @@
         <v>59</v>
       </c>
       <c r="I266" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="J266" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="K266" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="L266" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="M266" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="N266" t="s">
         <v>33</v>
       </c>
       <c r="O266" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="P266" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="Q266" t="s">
         <v>82</v>
@@ -28365,7 +28372,7 @@
         <v>20183738</v>
       </c>
       <c r="B267" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="C267" t="s">
         <v>70</v>
@@ -28375,7 +28382,7 @@
       </c>
       <c r="E267"/>
       <c r="F267" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="G267" t="s">
         <v>27</v>
@@ -28384,28 +28391,28 @@
         <v>59</v>
       </c>
       <c r="I267" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="J267" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="K267" t="s">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="L267" t="s">
-        <v>2979</v>
+        <v>2980</v>
       </c>
       <c r="M267" t="s">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="N267" t="s">
         <v>33</v>
       </c>
       <c r="O267" t="s">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="P267" t="s">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="Q267" t="s">
         <v>82</v>
@@ -28427,17 +28434,17 @@
         <v>20183731</v>
       </c>
       <c r="B268" t="s">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="C268" t="s">
         <v>70</v>
       </c>
       <c r="D268" t="s">
-        <v>2984</v>
+        <v>2985</v>
       </c>
       <c r="E268"/>
       <c r="F268" t="s">
-        <v>2985</v>
+        <v>2986</v>
       </c>
       <c r="G268" t="s">
         <v>27</v>
@@ -28446,28 +28453,28 @@
         <v>59</v>
       </c>
       <c r="I268" t="s">
-        <v>2986</v>
+        <v>2987</v>
       </c>
       <c r="J268" t="s">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="K268" t="s">
-        <v>2988</v>
+        <v>2989</v>
       </c>
       <c r="L268" t="s">
-        <v>2989</v>
+        <v>2990</v>
       </c>
       <c r="M268" t="s">
-        <v>2990</v>
+        <v>2991</v>
       </c>
       <c r="N268" t="s">
         <v>33</v>
       </c>
       <c r="O268" t="s">
-        <v>2991</v>
+        <v>2992</v>
       </c>
       <c r="P268" t="s">
-        <v>2992</v>
+        <v>2993</v>
       </c>
       <c r="Q268" t="s">
         <v>82</v>
@@ -28475,13 +28482,13 @@
       <c r="R268"/>
       <c r="S268"/>
       <c r="T268" t="s">
-        <v>2993</v>
+        <v>2994</v>
       </c>
       <c r="U268" t="s">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="V268" t="s">
-        <v>2995</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="269">
@@ -28489,19 +28496,19 @@
         <v>20183620</v>
       </c>
       <c r="B269" t="s">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="C269" t="s">
         <v>87</v>
       </c>
       <c r="D269" t="s">
-        <v>2997</v>
+        <v>2998</v>
       </c>
       <c r="E269" t="s">
         <v>150</v>
       </c>
       <c r="F269" t="s">
-        <v>2998</v>
+        <v>2999</v>
       </c>
       <c r="G269" t="s">
         <v>27</v>
@@ -28510,28 +28517,28 @@
         <v>45</v>
       </c>
       <c r="I269" t="s">
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="J269" t="s">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="K269" t="s">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="L269" t="s">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="M269" t="s">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="N269" t="s">
         <v>33</v>
       </c>
       <c r="O269" t="s">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="P269" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="Q269" t="s">
         <v>36</v>
@@ -28553,19 +28560,19 @@
         <v>20183504</v>
       </c>
       <c r="B270" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C270" t="s">
         <v>87</v>
       </c>
       <c r="D270" t="s">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="E270" t="s">
         <v>270</v>
       </c>
       <c r="F270" t="s">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="G270" t="s">
         <v>27</v>
@@ -28574,28 +28581,28 @@
         <v>90</v>
       </c>
       <c r="I270" t="s">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="J270" t="s">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="K270" t="s">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="L270" t="s">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="M270" t="s">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="N270" t="s">
         <v>33</v>
       </c>
       <c r="O270" t="s">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="P270" t="s">
-        <v>3015</v>
+        <v>3016</v>
       </c>
       <c r="Q270" t="s">
         <v>98</v>
@@ -28603,13 +28610,13 @@
       <c r="R270"/>
       <c r="S270"/>
       <c r="T270" t="s">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="U270" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="V270" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="271">
@@ -28617,7 +28624,7 @@
         <v>20185412</v>
       </c>
       <c r="B271" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="C271" t="s">
         <v>23</v>
@@ -28629,7 +28636,7 @@
         <v>270</v>
       </c>
       <c r="F271" t="s">
-        <v>3020</v>
+        <v>3021</v>
       </c>
       <c r="G271" t="s">
         <v>27</v>
@@ -28638,26 +28645,26 @@
         <v>90</v>
       </c>
       <c r="I271" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="J271" t="s">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="K271"/>
       <c r="L271" t="s">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="M271" t="s">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="N271" t="s">
         <v>33</v>
       </c>
       <c r="O271" t="s">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="P271" t="s">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="Q271" t="s">
         <v>98</v>
@@ -28665,13 +28672,13 @@
       <c r="R271"/>
       <c r="S271"/>
       <c r="T271" t="s">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="U271" t="s">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="V271" t="s">
-        <v>3029</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="272">
@@ -28679,19 +28686,19 @@
         <v>20183372</v>
       </c>
       <c r="B272" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="C272" t="s">
         <v>87</v>
       </c>
       <c r="D272" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="E272" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="F272" t="s">
-        <v>3033</v>
+        <v>3034</v>
       </c>
       <c r="G272" t="s">
         <v>27</v>
@@ -28700,28 +28707,28 @@
         <v>45</v>
       </c>
       <c r="I272" t="s">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="J272" t="s">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="K272" t="s">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="L272" t="s">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="M272" t="s">
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="N272" t="s">
         <v>33</v>
       </c>
       <c r="O272" t="s">
-        <v>3039</v>
+        <v>3040</v>
       </c>
       <c r="P272" t="s">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="Q272" t="s">
         <v>98</v>
@@ -28729,13 +28736,13 @@
       <c r="R272"/>
       <c r="S272"/>
       <c r="T272" t="s">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="U272" t="s">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="V272" t="s">
-        <v>3043</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="273">
@@ -28743,7 +28750,7 @@
         <v>20181017</v>
       </c>
       <c r="B273" t="s">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="C273" t="s">
         <v>23</v>
@@ -28755,37 +28762,37 @@
         <v>183</v>
       </c>
       <c r="F273" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="G273" t="s">
         <v>27</v>
       </c>
       <c r="H273" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="I273" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="J273" t="s">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="K273" t="s">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="L273" t="s">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="M273" t="s">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="N273" t="s">
         <v>33</v>
       </c>
       <c r="O273" t="s">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="P273" t="s">
-        <v>3053</v>
+        <v>3054</v>
       </c>
       <c r="Q273" t="s">
         <v>36</v>
@@ -28793,13 +28800,13 @@
       <c r="R273"/>
       <c r="S273"/>
       <c r="T273" t="s">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="U273" t="s">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="V273" t="s">
-        <v>3056</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="274">
@@ -28807,7 +28814,7 @@
         <v>20183214</v>
       </c>
       <c r="B274" t="s">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C274" t="s">
         <v>135</v>
@@ -28819,7 +28826,7 @@
         <v>105</v>
       </c>
       <c r="F274" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="G274" t="s">
         <v>27</v>
@@ -28828,28 +28835,28 @@
         <v>474</v>
       </c>
       <c r="I274" t="s">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="J274" t="s">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="K274" t="s">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="L274" t="s">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="M274" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="N274" t="s">
         <v>33</v>
       </c>
       <c r="O274" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="P274" t="s">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="Q274" t="s">
         <v>98</v>
@@ -28871,7 +28878,7 @@
         <v>20183215</v>
       </c>
       <c r="B275" t="s">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C275" t="s">
         <v>87</v>
@@ -28883,7 +28890,7 @@
         <v>25</v>
       </c>
       <c r="F275" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="G275" t="s">
         <v>27</v>
@@ -28892,28 +28899,28 @@
         <v>45</v>
       </c>
       <c r="I275" t="s">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="J275" t="s">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="K275" t="s">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="L275" t="s">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="M275" t="s">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="N275" t="s">
         <v>33</v>
       </c>
       <c r="O275" t="s">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="P275" t="s">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="Q275" t="s">
         <v>98</v>
@@ -28921,13 +28928,13 @@
       <c r="R275"/>
       <c r="S275"/>
       <c r="T275" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="U275" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="V275" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="276">
@@ -28935,19 +28942,19 @@
         <v>20183226</v>
       </c>
       <c r="B276" t="s">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="C276" t="s">
         <v>87</v>
       </c>
       <c r="D276" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="E276" t="s">
         <v>105</v>
       </c>
       <c r="F276" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="G276" t="s">
         <v>27</v>
@@ -28956,28 +28963,28 @@
         <v>28</v>
       </c>
       <c r="I276" t="s">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="J276" t="s">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="K276" t="s">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="L276" t="s">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="M276" t="s">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="N276" t="s">
         <v>33</v>
       </c>
       <c r="O276" t="s">
-        <v>3082</v>
+        <v>3083</v>
       </c>
       <c r="P276" t="s">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="Q276" t="s">
         <v>82</v>
@@ -28985,13 +28992,13 @@
       <c r="R276"/>
       <c r="S276"/>
       <c r="T276" t="s">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="U276" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="V276" t="s">
-        <v>3086</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="277">
@@ -28999,7 +29006,7 @@
         <v>20183232</v>
       </c>
       <c r="B277" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="C277" t="s">
         <v>87</v>
@@ -29011,7 +29018,7 @@
         <v>270</v>
       </c>
       <c r="F277" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="G277" t="s">
         <v>27</v>
@@ -29020,28 +29027,28 @@
         <v>59</v>
       </c>
       <c r="I277" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="J277" t="s">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="K277" t="s">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="L277" t="s">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="M277" t="s">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="N277" t="s">
         <v>33</v>
       </c>
       <c r="O277" t="s">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="P277" t="s">
-        <v>3094</v>
+        <v>3095</v>
       </c>
       <c r="Q277" t="s">
         <v>36</v>
@@ -29049,13 +29056,13 @@
       <c r="R277"/>
       <c r="S277"/>
       <c r="T277" t="s">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="U277" t="s">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="V277" t="s">
-        <v>3097</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="278">
@@ -29063,7 +29070,7 @@
         <v>20183258</v>
       </c>
       <c r="B278" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="C278" t="s">
         <v>135</v>
@@ -29075,7 +29082,7 @@
         <v>270</v>
       </c>
       <c r="F278" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="G278" t="s">
         <v>27</v>
@@ -29084,28 +29091,28 @@
         <v>151</v>
       </c>
       <c r="I278" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="J278" t="s">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="K278" t="s">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="L278" t="s">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="M278" t="s">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="N278" t="s">
         <v>33</v>
       </c>
       <c r="O278" t="s">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="P278" t="s">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="Q278" t="s">
         <v>36</v>
@@ -29113,13 +29120,13 @@
       <c r="R278"/>
       <c r="S278"/>
       <c r="T278" t="s">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="U278" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="V278" t="s">
-        <v>3086</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="279">
@@ -29127,7 +29134,7 @@
         <v>20183301</v>
       </c>
       <c r="B279" t="s">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="C279" t="s">
         <v>87</v>
@@ -29139,7 +29146,7 @@
         <v>183</v>
       </c>
       <c r="F279" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="G279" t="s">
         <v>27</v>
@@ -29148,28 +29155,28 @@
         <v>1415</v>
       </c>
       <c r="I279" t="s">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="J279" t="s">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="K279" t="s">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="L279" t="s">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="M279" t="s">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="N279" t="s">
         <v>33</v>
       </c>
       <c r="O279" t="s">
-        <v>3112</v>
+        <v>3113</v>
       </c>
       <c r="P279" t="s">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="Q279" t="s">
         <v>98</v>
@@ -29177,13 +29184,13 @@
       <c r="R279"/>
       <c r="S279"/>
       <c r="T279" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
       <c r="U279" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="V279" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="280">
@@ -29191,7 +29198,7 @@
         <v>20181009</v>
       </c>
       <c r="B280" t="s">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="C280" t="s">
         <v>23</v>
@@ -29203,7 +29210,7 @@
         <v>270</v>
       </c>
       <c r="F280" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
       <c r="G280" t="s">
         <v>27</v>
@@ -29212,28 +29219,28 @@
         <v>28</v>
       </c>
       <c r="I280" t="s">
-        <v>3116</v>
+        <v>3117</v>
       </c>
       <c r="J280" t="s">
-        <v>3117</v>
+        <v>3118</v>
       </c>
       <c r="K280" t="s">
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="L280" t="s">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="M280" t="s">
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="N280" t="s">
         <v>33</v>
       </c>
       <c r="O280" t="s">
-        <v>3121</v>
+        <v>3122</v>
       </c>
       <c r="P280" t="s">
-        <v>3122</v>
+        <v>3123</v>
       </c>
       <c r="Q280" t="s">
         <v>98</v>
@@ -29255,19 +29262,19 @@
         <v>20183136</v>
       </c>
       <c r="B281" t="s">
-        <v>3123</v>
+        <v>3124</v>
       </c>
       <c r="C281" t="s">
         <v>87</v>
       </c>
       <c r="D281" t="s">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="E281" t="s">
         <v>105</v>
       </c>
       <c r="F281" t="s">
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="G281" t="s">
         <v>164</v>
@@ -29276,28 +29283,28 @@
         <v>28</v>
       </c>
       <c r="I281" t="s">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="J281" t="s">
-        <v>3126</v>
+        <v>3127</v>
       </c>
       <c r="K281" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="L281" t="s">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="M281" t="s">
-        <v>3129</v>
+        <v>3130</v>
       </c>
       <c r="N281" t="s">
         <v>33</v>
       </c>
       <c r="O281" t="s">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="P281" t="s">
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="Q281" t="s">
         <v>82</v>
@@ -29319,19 +29326,19 @@
         <v>20185168</v>
       </c>
       <c r="B282" t="s">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="C282" t="s">
         <v>23</v>
       </c>
       <c r="D282" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="E282" t="s">
         <v>270</v>
       </c>
       <c r="F282" t="s">
-        <v>3133</v>
+        <v>3134</v>
       </c>
       <c r="G282" t="s">
         <v>27</v>
@@ -29340,26 +29347,26 @@
         <v>28</v>
       </c>
       <c r="I282" t="s">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="J282" t="s">
-        <v>3135</v>
+        <v>3136</v>
       </c>
       <c r="K282"/>
       <c r="L282" t="s">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="M282" t="s">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="N282" t="s">
         <v>33</v>
       </c>
       <c r="O282" t="s">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="P282" t="s">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="Q282" t="s">
         <v>36</v>
@@ -29367,13 +29374,13 @@
       <c r="R282"/>
       <c r="S282"/>
       <c r="T282" t="s">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="U282" t="s">
-        <v>3141</v>
+        <v>3142</v>
       </c>
       <c r="V282" t="s">
-        <v>3142</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="283">
@@ -29381,19 +29388,19 @@
         <v>20185189</v>
       </c>
       <c r="B283" t="s">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="C283" t="s">
         <v>23</v>
       </c>
       <c r="D283" t="s">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="E283" t="s">
         <v>25</v>
       </c>
       <c r="F283" t="s">
-        <v>3133</v>
+        <v>3134</v>
       </c>
       <c r="G283" t="s">
         <v>27</v>
@@ -29402,26 +29409,26 @@
         <v>45</v>
       </c>
       <c r="I283" t="s">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="J283" t="s">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="K283"/>
       <c r="L283" t="s">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="M283" t="s">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="N283" t="s">
         <v>33</v>
       </c>
       <c r="O283" t="s">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="P283" t="s">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="Q283" t="s">
         <v>82</v>
@@ -29443,7 +29450,7 @@
         <v>20183073</v>
       </c>
       <c r="B284" t="s">
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="C284" t="s">
         <v>87</v>
@@ -29455,7 +29462,7 @@
         <v>270</v>
       </c>
       <c r="F284" t="s">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="G284" t="s">
         <v>27</v>
@@ -29464,28 +29471,28 @@
         <v>474</v>
       </c>
       <c r="I284" t="s">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="J284" t="s">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="K284" t="s">
-        <v>3155</v>
+        <v>3156</v>
       </c>
       <c r="L284" t="s">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="M284" t="s">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="N284" t="s">
         <v>33</v>
       </c>
       <c r="O284" t="s">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="P284" t="s">
-        <v>3159</v>
+        <v>3160</v>
       </c>
       <c r="Q284" t="s">
         <v>98</v>
@@ -29493,13 +29500,13 @@
       <c r="R284"/>
       <c r="S284"/>
       <c r="T284" t="s">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="U284" t="s">
-        <v>3161</v>
+        <v>3162</v>
       </c>
       <c r="V284" t="s">
-        <v>3162</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="285">
@@ -29507,17 +29514,17 @@
         <v>20183032</v>
       </c>
       <c r="B285" t="s">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="C285" t="s">
         <v>70</v>
       </c>
       <c r="D285" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="E285"/>
       <c r="F285" t="s">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="G285" t="s">
         <v>27</v>
@@ -29526,28 +29533,28 @@
         <v>45</v>
       </c>
       <c r="I285" t="s">
-        <v>3165</v>
+        <v>3166</v>
       </c>
       <c r="J285" t="s">
-        <v>3166</v>
+        <v>3167</v>
       </c>
       <c r="K285" t="s">
-        <v>3167</v>
+        <v>3168</v>
       </c>
       <c r="L285" t="s">
-        <v>3168</v>
+        <v>3169</v>
       </c>
       <c r="M285" t="s">
-        <v>3169</v>
+        <v>3170</v>
       </c>
       <c r="N285" t="s">
         <v>33</v>
       </c>
       <c r="O285" t="s">
-        <v>3170</v>
+        <v>3171</v>
       </c>
       <c r="P285" t="s">
-        <v>3171</v>
+        <v>3172</v>
       </c>
       <c r="Q285" t="s">
         <v>98</v>
@@ -29555,13 +29562,13 @@
       <c r="R285"/>
       <c r="S285"/>
       <c r="T285" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="U285" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="V285" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="286">
@@ -29569,7 +29576,7 @@
         <v>20183034</v>
       </c>
       <c r="B286" t="s">
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="C286" t="s">
         <v>70</v>
@@ -29579,7 +29586,7 @@
       </c>
       <c r="E286"/>
       <c r="F286" t="s">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="G286" t="s">
         <v>27</v>
@@ -29588,28 +29595,28 @@
         <v>45</v>
       </c>
       <c r="I286" t="s">
-        <v>3173</v>
+        <v>3174</v>
       </c>
       <c r="J286" t="s">
-        <v>3174</v>
+        <v>3175</v>
       </c>
       <c r="K286" t="s">
-        <v>3175</v>
+        <v>3176</v>
       </c>
       <c r="L286" t="s">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="M286" t="s">
-        <v>3177</v>
+        <v>3178</v>
       </c>
       <c r="N286" t="s">
         <v>33</v>
       </c>
       <c r="O286" t="s">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="P286" t="s">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="Q286" t="s">
         <v>82</v>
@@ -29617,13 +29624,13 @@
       <c r="R286"/>
       <c r="S286"/>
       <c r="T286" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="U286" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="V286" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="287">
@@ -29631,7 +29638,7 @@
         <v>20183036</v>
       </c>
       <c r="B287" t="s">
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="C287" t="s">
         <v>70</v>
@@ -29641,7 +29648,7 @@
       </c>
       <c r="E287"/>
       <c r="F287" t="s">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="G287" t="s">
         <v>27</v>
@@ -29650,28 +29657,28 @@
         <v>45</v>
       </c>
       <c r="I287" t="s">
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="J287" t="s">
-        <v>3182</v>
+        <v>3183</v>
       </c>
       <c r="K287" t="s">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="L287" t="s">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="M287" t="s">
-        <v>3185</v>
+        <v>3186</v>
       </c>
       <c r="N287" t="s">
         <v>33</v>
       </c>
       <c r="O287" t="s">
-        <v>3186</v>
+        <v>3187</v>
       </c>
       <c r="P287" t="s">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="Q287" t="s">
         <v>98</v>
@@ -29679,13 +29686,13 @@
       <c r="R287"/>
       <c r="S287"/>
       <c r="T287" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="U287" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="V287" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="288">
@@ -29693,19 +29700,19 @@
         <v>20183047</v>
       </c>
       <c r="B288" t="s">
-        <v>3188</v>
+        <v>3189</v>
       </c>
       <c r="C288" t="s">
         <v>87</v>
       </c>
       <c r="D288" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="E288" t="s">
         <v>723</v>
       </c>
       <c r="F288" t="s">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="G288" t="s">
         <v>27</v>
@@ -29714,28 +29721,28 @@
         <v>59</v>
       </c>
       <c r="I288" t="s">
-        <v>3189</v>
+        <v>3190</v>
       </c>
       <c r="J288" t="s">
-        <v>3190</v>
+        <v>3191</v>
       </c>
       <c r="K288" t="s">
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="L288" t="s">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="M288" t="s">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="N288" t="s">
         <v>33</v>
       </c>
       <c r="O288" t="s">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="P288" t="s">
-        <v>3195</v>
+        <v>3196</v>
       </c>
       <c r="Q288" t="s">
         <v>82</v>
@@ -29743,13 +29750,13 @@
       <c r="R288"/>
       <c r="S288"/>
       <c r="T288" t="s">
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="U288" t="s">
-        <v>3197</v>
+        <v>3198</v>
       </c>
       <c r="V288" t="s">
-        <v>3198</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="289">
@@ -29757,17 +29764,17 @@
         <v>20183022</v>
       </c>
       <c r="B289" t="s">
-        <v>3199</v>
+        <v>3200</v>
       </c>
       <c r="C289" t="s">
         <v>70</v>
       </c>
       <c r="D289" t="s">
-        <v>2984</v>
+        <v>2985</v>
       </c>
       <c r="E289"/>
       <c r="F289" t="s">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="G289" t="s">
         <v>27</v>
@@ -29776,28 +29783,28 @@
         <v>45</v>
       </c>
       <c r="I289" t="s">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="J289" t="s">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="K289" t="s">
-        <v>3203</v>
+        <v>3204</v>
       </c>
       <c r="L289" t="s">
-        <v>3204</v>
+        <v>3205</v>
       </c>
       <c r="M289" t="s">
-        <v>3205</v>
+        <v>3206</v>
       </c>
       <c r="N289" t="s">
         <v>33</v>
       </c>
       <c r="O289" t="s">
-        <v>3206</v>
+        <v>3207</v>
       </c>
       <c r="P289" t="s">
-        <v>3207</v>
+        <v>3208</v>
       </c>
       <c r="Q289" t="s">
         <v>98</v>
@@ -29805,13 +29812,13 @@
       <c r="R289"/>
       <c r="S289"/>
       <c r="T289" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="U289" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="V289" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="290">
@@ -29819,19 +29826,19 @@
         <v>20183012</v>
       </c>
       <c r="B290" t="s">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="C290" t="s">
         <v>87</v>
       </c>
       <c r="D290" t="s">
-        <v>3209</v>
+        <v>3210</v>
       </c>
       <c r="E290" t="s">
         <v>105</v>
       </c>
       <c r="F290" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="G290" t="s">
         <v>27</v>
@@ -29840,28 +29847,28 @@
         <v>28</v>
       </c>
       <c r="I290" t="s">
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="J290" t="s">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="K290" t="s">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="L290" t="s">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="M290" t="s">
-        <v>3215</v>
+        <v>3216</v>
       </c>
       <c r="N290" t="s">
         <v>33</v>
       </c>
       <c r="O290" t="s">
-        <v>3216</v>
+        <v>3217</v>
       </c>
       <c r="P290" t="s">
-        <v>3217</v>
+        <v>3218</v>
       </c>
       <c r="Q290" t="s">
         <v>82</v>
@@ -29869,13 +29876,13 @@
       <c r="R290"/>
       <c r="S290"/>
       <c r="T290" t="s">
-        <v>3218</v>
+        <v>3219</v>
       </c>
       <c r="U290" t="s">
-        <v>3219</v>
+        <v>3220</v>
       </c>
       <c r="V290" t="s">
-        <v>3220</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="291">
@@ -29883,7 +29890,7 @@
         <v>20185007</v>
       </c>
       <c r="B291" t="s">
-        <v>3221</v>
+        <v>3222</v>
       </c>
       <c r="C291" t="s">
         <v>23</v>
@@ -29895,7 +29902,7 @@
         <v>25</v>
       </c>
       <c r="F291" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="G291" t="s">
         <v>27</v>
@@ -29904,26 +29911,26 @@
         <v>45</v>
       </c>
       <c r="I291" t="s">
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="J291" t="s">
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="K291"/>
       <c r="L291" t="s">
-        <v>3224</v>
+        <v>3225</v>
       </c>
       <c r="M291" t="s">
-        <v>3225</v>
+        <v>3226</v>
       </c>
       <c r="N291" t="s">
         <v>33</v>
       </c>
       <c r="O291" t="s">
-        <v>3226</v>
+        <v>3227</v>
       </c>
       <c r="P291" t="s">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="Q291" t="s">
         <v>36</v>
@@ -29931,13 +29938,13 @@
       <c r="R291"/>
       <c r="S291"/>
       <c r="T291" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="U291" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="V291" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="292">
@@ -29945,19 +29952,19 @@
         <v>20174299</v>
       </c>
       <c r="B292" t="s">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="C292" t="s">
         <v>135</v>
       </c>
       <c r="D292" t="s">
-        <v>3229</v>
+        <v>3230</v>
       </c>
       <c r="E292" t="s">
         <v>183</v>
       </c>
       <c r="F292" t="s">
-        <v>3230</v>
+        <v>3231</v>
       </c>
       <c r="G292" t="s">
         <v>27</v>
@@ -29966,28 +29973,28 @@
         <v>45</v>
       </c>
       <c r="I292" t="s">
-        <v>3231</v>
+        <v>3232</v>
       </c>
       <c r="J292" t="s">
-        <v>3232</v>
+        <v>3233</v>
       </c>
       <c r="K292" t="s">
-        <v>3233</v>
+        <v>3234</v>
       </c>
       <c r="L292" t="s">
-        <v>3234</v>
+        <v>3235</v>
       </c>
       <c r="M292" t="s">
-        <v>3235</v>
+        <v>3236</v>
       </c>
       <c r="N292" t="s">
         <v>33</v>
       </c>
       <c r="O292" t="s">
-        <v>3236</v>
+        <v>3237</v>
       </c>
       <c r="P292" t="s">
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="Q292" t="s">
         <v>98</v>
@@ -29995,13 +30002,13 @@
       <c r="R292"/>
       <c r="S292"/>
       <c r="T292" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="U292" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="V292" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="293">
@@ -30009,19 +30016,19 @@
         <v>20174305</v>
       </c>
       <c r="B293" t="s">
-        <v>3238</v>
+        <v>3239</v>
       </c>
       <c r="C293" t="s">
         <v>135</v>
       </c>
       <c r="D293" t="s">
-        <v>3239</v>
+        <v>3240</v>
       </c>
       <c r="E293" t="s">
         <v>270</v>
       </c>
       <c r="F293" t="s">
-        <v>3230</v>
+        <v>3231</v>
       </c>
       <c r="G293" t="s">
         <v>27</v>
@@ -30030,28 +30037,28 @@
         <v>28</v>
       </c>
       <c r="I293" t="s">
-        <v>3240</v>
+        <v>3241</v>
       </c>
       <c r="J293" t="s">
-        <v>3241</v>
+        <v>3242</v>
       </c>
       <c r="K293" t="s">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="L293" t="s">
-        <v>3243</v>
+        <v>3244</v>
       </c>
       <c r="M293" t="s">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="N293" t="s">
         <v>33</v>
       </c>
       <c r="O293" t="s">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="P293" t="s">
-        <v>3246</v>
+        <v>3247</v>
       </c>
       <c r="Q293" t="s">
         <v>36</v>
@@ -30073,19 +30080,19 @@
         <v>20174083</v>
       </c>
       <c r="B294" t="s">
-        <v>3247</v>
+        <v>3248</v>
       </c>
       <c r="C294" t="s">
         <v>87</v>
       </c>
       <c r="D294" t="s">
-        <v>3248</v>
+        <v>3249</v>
       </c>
       <c r="E294" t="s">
         <v>270</v>
       </c>
       <c r="F294" t="s">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="G294" t="s">
         <v>27</v>
@@ -30094,28 +30101,28 @@
         <v>59</v>
       </c>
       <c r="I294" t="s">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="J294" t="s">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="K294" t="s">
-        <v>3252</v>
+        <v>3253</v>
       </c>
       <c r="L294" t="s">
-        <v>3253</v>
+        <v>3254</v>
       </c>
       <c r="M294" t="s">
-        <v>3254</v>
+        <v>3255</v>
       </c>
       <c r="N294" t="s">
         <v>33</v>
       </c>
       <c r="O294" t="s">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="P294" t="s">
-        <v>3256</v>
+        <v>3257</v>
       </c>
       <c r="Q294" t="s">
         <v>98</v>
@@ -30123,13 +30130,13 @@
       <c r="R294"/>
       <c r="S294"/>
       <c r="T294" t="s">
-        <v>3257</v>
+        <v>3258</v>
       </c>
       <c r="U294" t="s">
-        <v>3258</v>
+        <v>3259</v>
       </c>
       <c r="V294" t="s">
-        <v>3259</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="295">
@@ -30137,19 +30144,19 @@
         <v>20174099</v>
       </c>
       <c r="B295" t="s">
-        <v>3260</v>
+        <v>3261</v>
       </c>
       <c r="C295" t="s">
         <v>87</v>
       </c>
       <c r="D295" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="E295" t="s">
         <v>183</v>
       </c>
       <c r="F295" t="s">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="G295" t="s">
         <v>164</v>
@@ -30158,28 +30165,28 @@
         <v>28</v>
       </c>
       <c r="I295" t="s">
-        <v>3261</v>
+        <v>3262</v>
       </c>
       <c r="J295" t="s">
-        <v>3262</v>
+        <v>3263</v>
       </c>
       <c r="K295" t="s">
-        <v>3263</v>
+        <v>3264</v>
       </c>
       <c r="L295" t="s">
-        <v>3264</v>
+        <v>3265</v>
       </c>
       <c r="M295" t="s">
-        <v>3265</v>
+        <v>3266</v>
       </c>
       <c r="N295" t="s">
         <v>33</v>
       </c>
       <c r="O295" t="s">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="P295" t="s">
-        <v>3267</v>
+        <v>3268</v>
       </c>
       <c r="Q295" t="s">
         <v>98</v>
@@ -30187,13 +30194,13 @@
       <c r="R295"/>
       <c r="S295"/>
       <c r="T295" t="s">
-        <v>3268</v>
+        <v>3269</v>
       </c>
       <c r="U295" t="s">
-        <v>3269</v>
+        <v>3270</v>
       </c>
       <c r="V295" t="s">
-        <v>3270</v>
+        <v>3271</v>
       </c>
     </row>
     <row r="296">
@@ -30201,7 +30208,7 @@
         <v>20174034</v>
       </c>
       <c r="B296" t="s">
-        <v>3271</v>
+        <v>3272</v>
       </c>
       <c r="C296" t="s">
         <v>135</v>
@@ -30213,7 +30220,7 @@
         <v>270</v>
       </c>
       <c r="F296" t="s">
-        <v>3272</v>
+        <v>3273</v>
       </c>
       <c r="G296" t="s">
         <v>27</v>
@@ -30222,28 +30229,28 @@
         <v>90</v>
       </c>
       <c r="I296" t="s">
-        <v>3273</v>
+        <v>3274</v>
       </c>
       <c r="J296" t="s">
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="K296" t="s">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="L296" t="s">
-        <v>3276</v>
+        <v>3277</v>
       </c>
       <c r="M296" t="s">
-        <v>3277</v>
+        <v>3278</v>
       </c>
       <c r="N296" t="s">
         <v>33</v>
       </c>
       <c r="O296" t="s">
-        <v>3278</v>
+        <v>3279</v>
       </c>
       <c r="P296" t="s">
-        <v>3279</v>
+        <v>3280</v>
       </c>
       <c r="Q296" t="s">
         <v>98</v>
@@ -30265,19 +30272,19 @@
         <v>20175654</v>
       </c>
       <c r="B297" t="s">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="C297" t="s">
         <v>23</v>
       </c>
       <c r="D297" t="s">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="E297" t="s">
         <v>105</v>
       </c>
       <c r="F297" t="s">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="G297" t="s">
         <v>27</v>
@@ -30286,26 +30293,26 @@
         <v>474</v>
       </c>
       <c r="I297" t="s">
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="J297" t="s">
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="K297"/>
       <c r="L297" t="s">
-        <v>3285</v>
+        <v>3286</v>
       </c>
       <c r="M297" t="s">
-        <v>3286</v>
+        <v>3287</v>
       </c>
       <c r="N297" t="s">
         <v>33</v>
       </c>
       <c r="O297" t="s">
-        <v>3287</v>
+        <v>3288</v>
       </c>
       <c r="P297" t="s">
-        <v>3288</v>
+        <v>3289</v>
       </c>
       <c r="Q297" t="s">
         <v>98</v>
@@ -30313,13 +30320,13 @@
       <c r="R297"/>
       <c r="S297"/>
       <c r="T297" t="s">
-        <v>3289</v>
+        <v>3290</v>
       </c>
       <c r="U297" t="s">
-        <v>3290</v>
+        <v>3291</v>
       </c>
       <c r="V297" t="s">
-        <v>3291</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="298">
@@ -30327,19 +30334,19 @@
         <v>20175535</v>
       </c>
       <c r="B298" t="s">
-        <v>3292</v>
+        <v>3293</v>
       </c>
       <c r="C298" t="s">
         <v>23</v>
       </c>
       <c r="D298" t="s">
-        <v>3293</v>
+        <v>3294</v>
       </c>
       <c r="E298" t="s">
         <v>270</v>
       </c>
       <c r="F298" t="s">
-        <v>3294</v>
+        <v>3295</v>
       </c>
       <c r="G298" t="s">
         <v>27</v>
@@ -30348,26 +30355,26 @@
         <v>90</v>
       </c>
       <c r="I298" t="s">
-        <v>3295</v>
+        <v>3296</v>
       </c>
       <c r="J298" t="s">
-        <v>3296</v>
+        <v>3297</v>
       </c>
       <c r="K298"/>
       <c r="L298" t="s">
-        <v>3297</v>
+        <v>3298</v>
       </c>
       <c r="M298" t="s">
-        <v>3298</v>
+        <v>3299</v>
       </c>
       <c r="N298" t="s">
         <v>33</v>
       </c>
       <c r="O298" t="s">
-        <v>3299</v>
+        <v>3300</v>
       </c>
       <c r="P298" t="s">
-        <v>3300</v>
+        <v>3301</v>
       </c>
       <c r="Q298" t="s">
         <v>98</v>
@@ -30375,13 +30382,13 @@
       <c r="R298"/>
       <c r="S298"/>
       <c r="T298" t="s">
-        <v>3301</v>
+        <v>3302</v>
       </c>
       <c r="U298" t="s">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="V298" t="s">
-        <v>3303</v>
+        <v>3304</v>
       </c>
     </row>
     <row r="299">
@@ -30389,7 +30396,7 @@
         <v>20173881</v>
       </c>
       <c r="B299" t="s">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="C299" t="s">
         <v>87</v>
@@ -30401,7 +30408,7 @@
         <v>105</v>
       </c>
       <c r="F299" t="s">
-        <v>3305</v>
+        <v>3306</v>
       </c>
       <c r="G299" t="s">
         <v>27</v>
@@ -30410,28 +30417,28 @@
         <v>28</v>
       </c>
       <c r="I299" t="s">
-        <v>3306</v>
+        <v>3307</v>
       </c>
       <c r="J299" t="s">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="K299" t="s">
-        <v>3308</v>
+        <v>3309</v>
       </c>
       <c r="L299" t="s">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="M299" t="s">
-        <v>3310</v>
+        <v>3311</v>
       </c>
       <c r="N299" t="s">
         <v>33</v>
       </c>
       <c r="O299" t="s">
-        <v>3311</v>
+        <v>3312</v>
       </c>
       <c r="P299" t="s">
-        <v>3312</v>
+        <v>3313</v>
       </c>
       <c r="Q299" t="s">
         <v>98</v>
@@ -30453,7 +30460,7 @@
         <v>20173579</v>
       </c>
       <c r="B300" t="s">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="C300" t="s">
         <v>87</v>
@@ -30465,7 +30472,7 @@
         <v>105</v>
       </c>
       <c r="F300" t="s">
-        <v>3314</v>
+        <v>3315</v>
       </c>
       <c r="G300" t="s">
         <v>27</v>
@@ -30474,28 +30481,28 @@
         <v>28</v>
       </c>
       <c r="I300" t="s">
-        <v>3315</v>
+        <v>3316</v>
       </c>
       <c r="J300" t="s">
-        <v>3316</v>
+        <v>3317</v>
       </c>
       <c r="K300" t="s">
-        <v>3317</v>
+        <v>3318</v>
       </c>
       <c r="L300" t="s">
-        <v>3318</v>
+        <v>3319</v>
       </c>
       <c r="M300" t="s">
-        <v>3319</v>
+        <v>3320</v>
       </c>
       <c r="N300" t="s">
         <v>33</v>
       </c>
       <c r="O300" t="s">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="P300" t="s">
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="Q300" t="s">
         <v>98</v>
@@ -30517,19 +30524,19 @@
         <v>20173510</v>
       </c>
       <c r="B301" t="s">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="C301" t="s">
         <v>135</v>
       </c>
       <c r="D301" t="s">
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="E301" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="F301" t="s">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="G301" t="s">
         <v>164</v>
@@ -30538,28 +30545,28 @@
         <v>90</v>
       </c>
       <c r="I301" t="s">
-        <v>3325</v>
+        <v>3326</v>
       </c>
       <c r="J301" t="s">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="K301" t="s">
-        <v>3327</v>
+        <v>3328</v>
       </c>
       <c r="L301" t="s">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="M301" t="s">
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="N301" t="s">
         <v>33</v>
       </c>
       <c r="O301" t="s">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="P301" t="s">
-        <v>3331</v>
+        <v>3332</v>
       </c>
       <c r="Q301" t="s">
         <v>98</v>
@@ -30567,13 +30574,13 @@
       <c r="R301"/>
       <c r="S301"/>
       <c r="T301" t="s">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="U301" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="V301" t="s">
-        <v>3334</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="302">
@@ -30581,19 +30588,19 @@
         <v>20173460</v>
       </c>
       <c r="B302" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="C302" t="s">
         <v>87</v>
       </c>
       <c r="D302" t="s">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="E302" t="s">
         <v>105</v>
       </c>
       <c r="F302" t="s">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="G302" t="s">
         <v>27</v>
@@ -30602,28 +30609,28 @@
         <v>59</v>
       </c>
       <c r="I302" t="s">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="J302" t="s">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="K302" t="s">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="L302" t="s">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="M302" t="s">
-        <v>3342</v>
+        <v>3343</v>
       </c>
       <c r="N302" t="s">
         <v>33</v>
       </c>
       <c r="O302" t="s">
-        <v>3343</v>
+        <v>3344</v>
       </c>
       <c r="P302" t="s">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="Q302" t="s">
         <v>98</v>
@@ -30631,13 +30638,13 @@
       <c r="R302"/>
       <c r="S302"/>
       <c r="T302" t="s">
-        <v>3345</v>
+        <v>3346</v>
       </c>
       <c r="U302" t="s">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="V302" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="303">
@@ -30645,19 +30652,19 @@
         <v>20173412</v>
       </c>
       <c r="B303" t="s">
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="C303" t="s">
         <v>195</v>
       </c>
       <c r="D303" t="s">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="E303" t="s">
         <v>270</v>
       </c>
       <c r="F303" t="s">
-        <v>3349</v>
+        <v>3350</v>
       </c>
       <c r="G303" t="s">
         <v>27</v>
@@ -30666,28 +30673,28 @@
         <v>59</v>
       </c>
       <c r="I303" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="J303" t="s">
-        <v>3351</v>
+        <v>3352</v>
       </c>
       <c r="K303" t="s">
-        <v>3352</v>
+        <v>3353</v>
       </c>
       <c r="L303" t="s">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="M303" t="s">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="N303" t="s">
         <v>33</v>
       </c>
       <c r="O303" t="s">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="P303" t="s">
-        <v>3356</v>
+        <v>3357</v>
       </c>
       <c r="Q303" t="s">
         <v>98</v>
@@ -30695,13 +30702,13 @@
       <c r="R303"/>
       <c r="S303"/>
       <c r="T303" t="s">
-        <v>3357</v>
+        <v>3358</v>
       </c>
       <c r="U303" t="s">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="V303" t="s">
-        <v>3359</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="304">
@@ -30709,7 +30716,7 @@
         <v>20173376</v>
       </c>
       <c r="B304" t="s">
-        <v>3360</v>
+        <v>3361</v>
       </c>
       <c r="C304" t="s">
         <v>135</v>
@@ -30721,7 +30728,7 @@
         <v>105</v>
       </c>
       <c r="F304" t="s">
-        <v>3361</v>
+        <v>3362</v>
       </c>
       <c r="G304" t="s">
         <v>27</v>
@@ -30730,28 +30737,28 @@
         <v>28</v>
       </c>
       <c r="I304" t="s">
-        <v>3362</v>
+        <v>3363</v>
       </c>
       <c r="J304" t="s">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="K304" t="s">
-        <v>3364</v>
+        <v>3365</v>
       </c>
       <c r="L304" t="s">
-        <v>3365</v>
+        <v>3366</v>
       </c>
       <c r="M304" t="s">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="N304" t="s">
         <v>33</v>
       </c>
       <c r="O304" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="P304" t="s">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="Q304" t="s">
         <v>98</v>
@@ -30773,7 +30780,7 @@
         <v>20173365</v>
       </c>
       <c r="B305" t="s">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="C305" t="s">
         <v>87</v>
@@ -30785,7 +30792,7 @@
         <v>25</v>
       </c>
       <c r="F305" t="s">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="G305" t="s">
         <v>27</v>
@@ -30794,28 +30801,28 @@
         <v>151</v>
       </c>
       <c r="I305" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="J305" t="s">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="K305" t="s">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="L305" t="s">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="M305" t="s">
-        <v>3375</v>
+        <v>3376</v>
       </c>
       <c r="N305" t="s">
         <v>33</v>
       </c>
       <c r="O305" t="s">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="P305" t="s">
-        <v>3377</v>
+        <v>3378</v>
       </c>
       <c r="Q305" t="s">
         <v>98</v>
@@ -30837,19 +30844,19 @@
         <v>20171025</v>
       </c>
       <c r="B306" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C306" t="s">
         <v>23</v>
       </c>
       <c r="D306" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="E306" t="s">
         <v>105</v>
       </c>
       <c r="F306" t="s">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="G306" t="s">
         <v>27</v>
@@ -30858,28 +30865,28 @@
         <v>474</v>
       </c>
       <c r="I306" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="J306" t="s">
-        <v>3381</v>
+        <v>3382</v>
       </c>
       <c r="K306" t="s">
-        <v>3382</v>
+        <v>3383</v>
       </c>
       <c r="L306" t="s">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="M306" t="s">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="N306" t="s">
         <v>33</v>
       </c>
       <c r="O306" t="s">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="P306" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="Q306" t="s">
         <v>98</v>
@@ -30887,13 +30894,13 @@
       <c r="R306"/>
       <c r="S306"/>
       <c r="T306" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="U306" t="s">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="V306" t="s">
-        <v>3389</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="307">
@@ -30901,19 +30908,19 @@
         <v>20170417</v>
       </c>
       <c r="B307" t="s">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="C307" t="s">
         <v>119</v>
       </c>
       <c r="D307" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="E307" t="s">
         <v>270</v>
       </c>
       <c r="F307" t="s">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="G307" t="s">
         <v>27</v>
@@ -30922,28 +30929,28 @@
         <v>1415</v>
       </c>
       <c r="I307" t="s">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="J307" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="K307" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="L307" t="s">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="M307" t="s">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="N307" t="s">
         <v>33</v>
       </c>
       <c r="O307" t="s">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="P307" t="s">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="Q307" t="s">
         <v>36</v>
@@ -30965,19 +30972,19 @@
         <v>20175159</v>
       </c>
       <c r="B308" t="s">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="C308" t="s">
         <v>23</v>
       </c>
       <c r="D308" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="E308" t="s">
         <v>105</v>
       </c>
       <c r="F308" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="G308" t="s">
         <v>27</v>
@@ -30986,26 +30993,26 @@
         <v>474</v>
       </c>
       <c r="I308" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="J308" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="K308"/>
       <c r="L308" t="s">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="M308" t="s">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="N308" t="s">
         <v>33</v>
       </c>
       <c r="O308" t="s">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="P308" t="s">
-        <v>3406</v>
+        <v>3407</v>
       </c>
       <c r="Q308" t="s">
         <v>98</v>
@@ -31013,13 +31020,13 @@
       <c r="R308"/>
       <c r="S308"/>
       <c r="T308" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="U308" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="V308" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="309">
@@ -31027,7 +31034,7 @@
         <v>20175059</v>
       </c>
       <c r="B309" t="s">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="C309" t="s">
         <v>23</v>
@@ -31039,7 +31046,7 @@
         <v>105</v>
       </c>
       <c r="F309" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="G309" t="s">
         <v>27</v>
@@ -31048,26 +31055,26 @@
         <v>28</v>
       </c>
       <c r="I309" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="J309" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="K309"/>
       <c r="L309" t="s">
-        <v>3411</v>
+        <v>3412</v>
       </c>
       <c r="M309" t="s">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="N309" t="s">
         <v>33</v>
       </c>
       <c r="O309" t="s">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="P309" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="Q309" t="s">
         <v>82</v>
@@ -31089,19 +31096,19 @@
         <v>20173031</v>
       </c>
       <c r="B310" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="C310" t="s">
         <v>87</v>
       </c>
       <c r="D310" t="s">
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="E310" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="F310" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="G310" t="s">
         <v>164</v>
@@ -31110,28 +31117,28 @@
         <v>90</v>
       </c>
       <c r="I310" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="J310" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="K310" t="s">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="L310" t="s">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="M310" t="s">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="N310" t="s">
         <v>33</v>
       </c>
       <c r="O310" t="s">
-        <v>3422</v>
+        <v>3423</v>
       </c>
       <c r="P310" t="s">
-        <v>3423</v>
+        <v>3424</v>
       </c>
       <c r="Q310" t="s">
         <v>98</v>
@@ -31139,13 +31146,13 @@
       <c r="R310"/>
       <c r="S310"/>
       <c r="T310" t="s">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="U310" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="V310" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="311">
@@ -31153,19 +31160,19 @@
         <v>20164109</v>
       </c>
       <c r="B311" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="C311" t="s">
         <v>87</v>
       </c>
       <c r="D311" t="s">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="E311" t="s">
         <v>150</v>
       </c>
       <c r="F311" t="s">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="G311" t="s">
         <v>27</v>
@@ -31174,28 +31181,28 @@
         <v>151</v>
       </c>
       <c r="I311" t="s">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="J311" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="K311" t="s">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="L311" t="s">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="M311" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="N311" t="s">
         <v>33</v>
       </c>
       <c r="O311" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="P311" t="s">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="Q311" t="s">
         <v>82</v>
@@ -31203,13 +31210,13 @@
       <c r="R311"/>
       <c r="S311"/>
       <c r="T311" t="s">
-        <v>3437</v>
+        <v>3438</v>
       </c>
       <c r="U311" t="s">
-        <v>3438</v>
+        <v>3439</v>
       </c>
       <c r="V311" t="s">
-        <v>3439</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="312">
@@ -31217,19 +31224,19 @@
         <v>20163926</v>
       </c>
       <c r="B312" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="C312" t="s">
         <v>195</v>
       </c>
       <c r="D312" t="s">
-        <v>3441</v>
+        <v>3442</v>
       </c>
       <c r="E312" t="s">
         <v>270</v>
       </c>
       <c r="F312" t="s">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="G312" t="s">
         <v>27</v>
@@ -31238,28 +31245,28 @@
         <v>45</v>
       </c>
       <c r="I312" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="J312" t="s">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="K312" t="s">
-        <v>3445</v>
+        <v>3446</v>
       </c>
       <c r="L312" t="s">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="M312" t="s">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="N312" t="s">
         <v>33</v>
       </c>
       <c r="O312" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="P312" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="Q312" t="s">
         <v>36</v>
@@ -31267,13 +31274,13 @@
       <c r="R312"/>
       <c r="S312"/>
       <c r="T312" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="U312" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="V312" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="313">
@@ -31281,19 +31288,19 @@
         <v>20163898</v>
       </c>
       <c r="B313" t="s">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="C313" t="s">
         <v>87</v>
       </c>
       <c r="D313" t="s">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="E313" t="s">
         <v>105</v>
       </c>
       <c r="F313" t="s">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="G313" t="s">
         <v>27</v>
@@ -31302,28 +31309,28 @@
         <v>28</v>
       </c>
       <c r="I313" t="s">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="J313" t="s">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="K313" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="L313" t="s">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="M313" t="s">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="N313" t="s">
         <v>33</v>
       </c>
       <c r="O313" t="s">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="P313" t="s">
-        <v>3459</v>
+        <v>3460</v>
       </c>
       <c r="Q313" t="s">
         <v>36</v>
@@ -31345,19 +31352,19 @@
         <v>20163767</v>
       </c>
       <c r="B314" t="s">
-        <v>3460</v>
+        <v>3461</v>
       </c>
       <c r="C314" t="s">
         <v>195</v>
       </c>
       <c r="D314" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="E314" t="s">
         <v>270</v>
       </c>
       <c r="F314" t="s">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="G314" t="s">
         <v>27</v>
@@ -31366,28 +31373,28 @@
         <v>90</v>
       </c>
       <c r="I314" t="s">
-        <v>3462</v>
+        <v>3463</v>
       </c>
       <c r="J314" t="s">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="K314" t="s">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="L314" t="s">
-        <v>3465</v>
+        <v>3466</v>
       </c>
       <c r="M314" t="s">
-        <v>3466</v>
+        <v>3467</v>
       </c>
       <c r="N314" t="s">
         <v>33</v>
       </c>
       <c r="O314" t="s">
-        <v>3467</v>
+        <v>3468</v>
       </c>
       <c r="P314" t="s">
-        <v>3468</v>
+        <v>3469</v>
       </c>
       <c r="Q314" t="s">
         <v>36</v>
@@ -31409,19 +31416,19 @@
         <v>20163777</v>
       </c>
       <c r="B315" t="s">
-        <v>3469</v>
+        <v>3470</v>
       </c>
       <c r="C315" t="s">
         <v>87</v>
       </c>
       <c r="D315" t="s">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="E315" t="s">
         <v>25</v>
       </c>
       <c r="F315" t="s">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="G315" t="s">
         <v>27</v>
@@ -31430,28 +31437,28 @@
         <v>90</v>
       </c>
       <c r="I315" t="s">
-        <v>3471</v>
+        <v>3472</v>
       </c>
       <c r="J315" t="s">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="K315" t="s">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="L315" t="s">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="M315" t="s">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="N315" t="s">
         <v>33</v>
       </c>
       <c r="O315" t="s">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="P315" t="s">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="Q315" t="s">
         <v>98</v>
@@ -31459,13 +31466,13 @@
       <c r="R315"/>
       <c r="S315"/>
       <c r="T315" t="s">
-        <v>3478</v>
+        <v>3479</v>
       </c>
       <c r="U315" t="s">
-        <v>3479</v>
+        <v>3480</v>
       </c>
       <c r="V315" t="s">
-        <v>3480</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="316">
@@ -31473,19 +31480,19 @@
         <v>20163779</v>
       </c>
       <c r="B316" t="s">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="C316" t="s">
         <v>87</v>
       </c>
       <c r="D316" t="s">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="E316" t="s">
         <v>105</v>
       </c>
       <c r="F316" t="s">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="G316" t="s">
         <v>164</v>
@@ -31494,28 +31501,28 @@
         <v>45</v>
       </c>
       <c r="I316" t="s">
-        <v>3482</v>
+        <v>3483</v>
       </c>
       <c r="J316" t="s">
-        <v>3483</v>
+        <v>3484</v>
       </c>
       <c r="K316" t="s">
-        <v>3484</v>
+        <v>3485</v>
       </c>
       <c r="L316" t="s">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="M316" t="s">
-        <v>3486</v>
+        <v>3487</v>
       </c>
       <c r="N316" t="s">
         <v>33</v>
       </c>
       <c r="O316" t="s">
-        <v>3487</v>
+        <v>3488</v>
       </c>
       <c r="P316" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="Q316" t="s">
         <v>98</v>
@@ -31523,13 +31530,13 @@
       <c r="R316"/>
       <c r="S316"/>
       <c r="T316" t="s">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="U316" t="s">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="V316" t="s">
-        <v>3491</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="317">
@@ -31537,19 +31544,19 @@
         <v>20163814</v>
       </c>
       <c r="B317" t="s">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="C317" t="s">
         <v>87</v>
       </c>
       <c r="D317" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="E317" t="s">
         <v>270</v>
       </c>
       <c r="F317" t="s">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="G317" t="s">
         <v>27</v>
@@ -31558,28 +31565,28 @@
         <v>90</v>
       </c>
       <c r="I317" t="s">
-        <v>3493</v>
+        <v>3494</v>
       </c>
       <c r="J317" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="K317" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
       <c r="L317" t="s">
-        <v>3496</v>
+        <v>3497</v>
       </c>
       <c r="M317" t="s">
-        <v>3497</v>
+        <v>3498</v>
       </c>
       <c r="N317" t="s">
         <v>33</v>
       </c>
       <c r="O317" t="s">
-        <v>3498</v>
+        <v>3499</v>
       </c>
       <c r="P317" t="s">
-        <v>3499</v>
+        <v>3500</v>
       </c>
       <c r="Q317" t="s">
         <v>36</v>
@@ -31587,13 +31594,13 @@
       <c r="R317"/>
       <c r="S317"/>
       <c r="T317" t="s">
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="U317" t="s">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="V317" t="s">
-        <v>3502</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="318">
@@ -31601,7 +31608,7 @@
         <v>20163739</v>
       </c>
       <c r="B318" t="s">
-        <v>3503</v>
+        <v>3504</v>
       </c>
       <c r="C318" t="s">
         <v>87</v>
@@ -31613,7 +31620,7 @@
         <v>105</v>
       </c>
       <c r="F318" t="s">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="G318" t="s">
         <v>27</v>
@@ -31622,28 +31629,28 @@
         <v>28</v>
       </c>
       <c r="I318" t="s">
-        <v>3505</v>
+        <v>3506</v>
       </c>
       <c r="J318" t="s">
-        <v>3506</v>
+        <v>3507</v>
       </c>
       <c r="K318" t="s">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="L318" t="s">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="M318" t="s">
-        <v>3509</v>
+        <v>3510</v>
       </c>
       <c r="N318" t="s">
         <v>33</v>
       </c>
       <c r="O318" t="s">
-        <v>3510</v>
+        <v>3511</v>
       </c>
       <c r="P318" t="s">
-        <v>3511</v>
+        <v>3512</v>
       </c>
       <c r="Q318" t="s">
         <v>98</v>
@@ -31665,19 +31672,19 @@
         <v>20163690</v>
       </c>
       <c r="B319" t="s">
-        <v>3512</v>
+        <v>3513</v>
       </c>
       <c r="C319" t="s">
         <v>195</v>
       </c>
       <c r="D319" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="E319" t="s">
         <v>270</v>
       </c>
       <c r="F319" t="s">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="G319" t="s">
         <v>27</v>
@@ -31686,28 +31693,28 @@
         <v>151</v>
       </c>
       <c r="I319" t="s">
-        <v>3515</v>
+        <v>3516</v>
       </c>
       <c r="J319" t="s">
-        <v>3516</v>
+        <v>3517</v>
       </c>
       <c r="K319" t="s">
-        <v>3517</v>
+        <v>3518</v>
       </c>
       <c r="L319" t="s">
-        <v>3518</v>
+        <v>3519</v>
       </c>
       <c r="M319" t="s">
-        <v>3519</v>
+        <v>3520</v>
       </c>
       <c r="N319" t="s">
         <v>33</v>
       </c>
       <c r="O319" t="s">
-        <v>3520</v>
+        <v>3521</v>
       </c>
       <c r="P319" t="s">
-        <v>3521</v>
+        <v>3522</v>
       </c>
       <c r="Q319" t="s">
         <v>82</v>
@@ -31729,7 +31736,7 @@
         <v>20163639</v>
       </c>
       <c r="B320" t="s">
-        <v>3522</v>
+        <v>3523</v>
       </c>
       <c r="C320" t="s">
         <v>87</v>
@@ -31741,7 +31748,7 @@
         <v>25</v>
       </c>
       <c r="F320" t="s">
-        <v>3523</v>
+        <v>3524</v>
       </c>
       <c r="G320" t="s">
         <v>27</v>
@@ -31750,28 +31757,28 @@
         <v>151</v>
       </c>
       <c r="I320" t="s">
-        <v>3524</v>
+        <v>3525</v>
       </c>
       <c r="J320" t="s">
-        <v>3525</v>
+        <v>3526</v>
       </c>
       <c r="K320" t="s">
-        <v>3526</v>
+        <v>3527</v>
       </c>
       <c r="L320" t="s">
-        <v>3527</v>
+        <v>3528</v>
       </c>
       <c r="M320" t="s">
-        <v>3528</v>
+        <v>3529</v>
       </c>
       <c r="N320" t="s">
         <v>33</v>
       </c>
       <c r="O320" t="s">
-        <v>3529</v>
+        <v>3530</v>
       </c>
       <c r="P320" t="s">
-        <v>3530</v>
+        <v>3531</v>
       </c>
       <c r="Q320" t="s">
         <v>36</v>
@@ -31793,7 +31800,7 @@
         <v>20163588</v>
       </c>
       <c r="B321" t="s">
-        <v>3531</v>
+        <v>3532</v>
       </c>
       <c r="C321" t="s">
         <v>87</v>
@@ -31805,7 +31812,7 @@
         <v>150</v>
       </c>
       <c r="F321" t="s">
-        <v>3532</v>
+        <v>3533</v>
       </c>
       <c r="G321" t="s">
         <v>27</v>
@@ -31814,28 +31821,28 @@
         <v>151</v>
       </c>
       <c r="I321" t="s">
-        <v>3533</v>
+        <v>3534</v>
       </c>
       <c r="J321" t="s">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="K321" t="s">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="L321" t="s">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="M321" t="s">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="N321" t="s">
         <v>33</v>
       </c>
       <c r="O321" t="s">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="P321" t="s">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="Q321" t="s">
         <v>98</v>
@@ -31843,13 +31850,13 @@
       <c r="R321"/>
       <c r="S321"/>
       <c r="T321" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="U321" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="V321" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="322">
@@ -31857,19 +31864,19 @@
         <v>20163483</v>
       </c>
       <c r="B322" t="s">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="C322" t="s">
         <v>135</v>
       </c>
       <c r="D322" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="E322" t="s">
         <v>105</v>
       </c>
       <c r="F322" t="s">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="G322" t="s">
         <v>27</v>
@@ -31878,28 +31885,28 @@
         <v>45</v>
       </c>
       <c r="I322" t="s">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="J322" t="s">
-        <v>3543</v>
+        <v>3544</v>
       </c>
       <c r="K322" t="s">
-        <v>3544</v>
+        <v>3545</v>
       </c>
       <c r="L322" t="s">
-        <v>3545</v>
+        <v>3546</v>
       </c>
       <c r="M322" t="s">
-        <v>3546</v>
+        <v>3547</v>
       </c>
       <c r="N322" t="s">
         <v>33</v>
       </c>
       <c r="O322" t="s">
-        <v>3547</v>
+        <v>3548</v>
       </c>
       <c r="P322" t="s">
-        <v>3548</v>
+        <v>3549</v>
       </c>
       <c r="Q322" t="s">
         <v>98</v>
@@ -31907,13 +31914,13 @@
       <c r="R322"/>
       <c r="S322"/>
       <c r="T322" t="s">
-        <v>3549</v>
+        <v>3550</v>
       </c>
       <c r="U322" t="s">
-        <v>3550</v>
+        <v>3551</v>
       </c>
       <c r="V322" t="s">
-        <v>3551</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="323">
@@ -31921,7 +31928,7 @@
         <v>20163534</v>
       </c>
       <c r="B323" t="s">
-        <v>3552</v>
+        <v>3553</v>
       </c>
       <c r="C323" t="s">
         <v>87</v>
@@ -31933,7 +31940,7 @@
         <v>183</v>
       </c>
       <c r="F323" t="s">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="G323" t="s">
         <v>27</v>
@@ -31942,28 +31949,28 @@
         <v>151</v>
       </c>
       <c r="I323" t="s">
-        <v>3553</v>
+        <v>3554</v>
       </c>
       <c r="J323" t="s">
-        <v>3554</v>
+        <v>3555</v>
       </c>
       <c r="K323" t="s">
-        <v>3555</v>
+        <v>3556</v>
       </c>
       <c r="L323" t="s">
-        <v>3556</v>
+        <v>3557</v>
       </c>
       <c r="M323" t="s">
-        <v>3557</v>
+        <v>3558</v>
       </c>
       <c r="N323" t="s">
         <v>33</v>
       </c>
       <c r="O323" t="s">
-        <v>3558</v>
+        <v>3559</v>
       </c>
       <c r="P323" t="s">
-        <v>3559</v>
+        <v>3560</v>
       </c>
       <c r="Q323" t="s">
         <v>36</v>
@@ -31985,7 +31992,7 @@
         <v>20163539</v>
       </c>
       <c r="B324" t="s">
-        <v>3560</v>
+        <v>3561</v>
       </c>
       <c r="C324" t="s">
         <v>87</v>
@@ -31997,7 +32004,7 @@
         <v>25</v>
       </c>
       <c r="F324" t="s">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="G324" t="s">
         <v>27</v>
@@ -32006,28 +32013,28 @@
         <v>151</v>
       </c>
       <c r="I324" t="s">
-        <v>3561</v>
+        <v>3562</v>
       </c>
       <c r="J324" t="s">
-        <v>3562</v>
+        <v>3563</v>
       </c>
       <c r="K324" t="s">
-        <v>3563</v>
+        <v>3564</v>
       </c>
       <c r="L324" t="s">
-        <v>3564</v>
+        <v>3565</v>
       </c>
       <c r="M324" t="s">
-        <v>3565</v>
+        <v>3566</v>
       </c>
       <c r="N324" t="s">
         <v>33</v>
       </c>
       <c r="O324" t="s">
-        <v>3566</v>
+        <v>3567</v>
       </c>
       <c r="P324" t="s">
-        <v>3567</v>
+        <v>3568</v>
       </c>
       <c r="Q324" t="s">
         <v>98</v>
@@ -32049,7 +32056,7 @@
         <v>20161012</v>
       </c>
       <c r="B325" t="s">
-        <v>3568</v>
+        <v>3569</v>
       </c>
       <c r="C325" t="s">
         <v>23</v>
@@ -32061,7 +32068,7 @@
         <v>25</v>
       </c>
       <c r="F325" t="s">
-        <v>3569</v>
+        <v>3570</v>
       </c>
       <c r="G325" t="s">
         <v>27</v>
@@ -32070,28 +32077,28 @@
         <v>90</v>
       </c>
       <c r="I325" t="s">
-        <v>3570</v>
+        <v>3571</v>
       </c>
       <c r="J325" t="s">
-        <v>3571</v>
+        <v>3572</v>
       </c>
       <c r="K325" t="s">
-        <v>3572</v>
+        <v>3573</v>
       </c>
       <c r="L325" t="s">
-        <v>3573</v>
+        <v>3574</v>
       </c>
       <c r="M325" t="s">
-        <v>3574</v>
+        <v>3575</v>
       </c>
       <c r="N325" t="s">
         <v>33</v>
       </c>
       <c r="O325" t="s">
-        <v>3575</v>
+        <v>3576</v>
       </c>
       <c r="P325" t="s">
-        <v>3576</v>
+        <v>3577</v>
       </c>
       <c r="Q325" t="s">
         <v>98</v>
@@ -32099,13 +32106,13 @@
       <c r="R325"/>
       <c r="S325"/>
       <c r="T325" t="s">
-        <v>3577</v>
+        <v>3578</v>
       </c>
       <c r="U325" t="s">
-        <v>3578</v>
+        <v>3579</v>
       </c>
       <c r="V325" t="s">
-        <v>3579</v>
+        <v>3580</v>
       </c>
     </row>
   </sheetData>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -6870,7 +6870,7 @@
     <t xml:space="preserve">25.4836</t>
   </si>
   <si>
-    <t xml:space="preserve">Ermöglichen fehlende provisorische Steuerrechnungen NFA Optimierungen durch die Kantone?</t>
+    <t xml:space="preserve">Ermöglichen fehlende provisorische Steuerrechnungen NFA-Optimierungen durch die Kantone?</t>
   </si>
   <si>
     <t xml:space="preserve">Les facturations provisoires de l’impôt manquantes permettent-elles aux cantons d'optimiser la RPT ?</t>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -16724,9 +16724,7 @@
       <c r="D85" t="s">
         <v>1001</v>
       </c>
-      <c r="E85" t="s">
-        <v>44</v>
-      </c>
+      <c r="E85"/>
       <c r="F85" t="s">
         <v>1002</v>
       </c>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -410,7 +410,7 @@
     <t xml:space="preserve">2026-03-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Umgang des Bundes mit problematischen Stoffen - PFAS - Kohortenstudie</t>
+    <t xml:space="preserve">Umgang des Bundes mit problematischen Stoffen. PFAS. Kohortenstudie</t>
   </si>
   <si>
     <t xml:space="preserve">Gestion des substances problématiques par la Confédération. PFAS. Étude de cohorte</t>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -155,7 +155,7 @@
     <t xml:space="preserve">Un audit externe de l'OFDF pour restaurer la confiance du personnel et de l'économie</t>
   </si>
   <si>
-    <t xml:space="preserve">Una verifica esterna dell’UDSC per ristabilire la fiducia tra il personale e il mondo economico</t>
+    <t xml:space="preserve">Una verifica esterna dell'UDSC per ristabilire la fiducia tra il personale e il mondo economico</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de commander, avant que des décisions irréversibles ne soient prises, un audit externe de l’OFDF et de la transformation en cours portant notamment sur les points suivants&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Adéquation des moyens (budget et personnel) aux multiples tâches de l’OFDF, en particulier pour la surveillance de la frontière terrestre, le contrôle de la migration ou encore la lutte contre les trafics en tous genres (produits agricoles, animaux, plantes envahissantes)&lt;/li&gt;&lt;li&gt;Efficacité de DaziT dans l’encaissement des droits de douanes (recettes en recul en 2025), avec en particulier la fin du contrôle systématique des camions étrangers, et face aux attentes de l’économie (en écho aux critiques très dures du transporteur Marco Tepoorten parlant d’une «&amp;nbsp;désorganisation systémique&amp;nbsp;»)&lt;/li&gt;&lt;li&gt;Flexibiliser Allegra&lt;/li&gt;&lt;li&gt;Taux d’arrêts maladie et de départs de l’OFDF&lt;/li&gt;&lt;li&gt;Attractivité du statut des personnels OFDF&lt;/li&gt;&lt;li&gt;Formation (qui semble enregistrer un taux d’échec inusuel)&lt;/li&gt;&lt;li&gt;Taux de rotation inhabituel parmi les cadres supérieurs de l’OFDF&lt;/li&gt;&lt;li&gt;Avant de continuer à foncer dans une direction discutable, n’y a-t-il pas lieu de tirer les leçons de transformations analogues à l’étranger (Autriche, Canada), surtout de certains échecs ?&lt;/li&gt;&lt;li&gt;Quelles mesures pour restaurer la confiance du personnel et de l'économie et garantir l'efficacité de l'OFDF dans l'exécution de ses tâches ?&lt;/li&gt;&lt;/ul&gt;</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">Versucht das Pro-Komitee der SVP-Nachhaltigkeitsinitiative die Transparenzvorschriften zu umgehen?</t>
   </si>
   <si>
-    <t xml:space="preserve">Le comité en faveur de l’initiative de l’UDC pour la durabilité tente-t-il de contourner les règles de transparence ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iniziativa per la sostenibilità dell’UDC: il comitato promotore tenta di eludere le disposizioni in materia di trasparenza?</t>
+    <t xml:space="preserve">Le comité en faveur de l'initiative de l'UDC pour la durabilité tente-t-il de contourner les règles de transparence ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iniziativa per la sostenibilità dell'UDC: Il comitato promotore tenta di eludere le disposizioni in materia di trasparenza?</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;ol&gt;&lt;li&gt;Le Conseil fédéral ou le CDF ont-ils au courant des campagnes évoquées plus bas&amp;nbsp;? Lesquelles ont été portées à leur connaissance&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Savent-ils qui est derrière ces campagnes&amp;nbsp;? D’après certains médias, il pourrait s’agir de l’entourage des cadres de l’UDC. Le Conseil fédéral ou le CDF ont-ils des informations à ce sujet&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Le Conseil fédéral partage-t-il le soupçon qu’il s’agit d’une tentative de contourner les règles de transparence applicables aux campagnes de votation&amp;nbsp;? Estime-t-il aussi que les responsables de campagne utilisent une lacune manifeste de l’art.&amp;nbsp;8, al. 1, OFipo (inscription des communications) pour dissimuler l’origine des fonds destinés aux campagnes&amp;nbsp;? Compte-t-il combler cette lacune&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Le Conseil fédéral ou le CDF ont-ils demandé à l’UDC de cesser ses manœuvres visant à dissimuler le financement de ses campagnes&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -140,6 +140,102 @@
     <t xml:space="preserve">Media e comunicazione|Salute</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weichelt Manuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERT-E-S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umgang des Bundes mit problematischen Stoffen. PFAS. Kohortenstudie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestion des substances problématiques par la Confédération. PFAS. Étude de cohorte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestione di sostanze problematiche da parte della Confederazione, PFAS, studio di coorte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.efk.admin.ch%2Fwp-content%2Fuploads%2Fpublikationen%2Fberichte%2Fsicherheit_und_umwelt%2Fverkehr_und_umwelt%2F23489%2F23489be-endgueltige-fassung-v04.pdf&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418627523%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=IeMVU%2F1hFFBihhELV7SAmFjibLMt%2Fx2qsnlGzjc2IFI%3D&amp;amp;reserved=0"&gt;Le rapport 23489 du Contrôle fédéral des finances (CDF) sur la gestion des substances problématiques par la Confédération &lt;/a&gt;&amp;nbsp;a été publié en mai 2024. Il conclut à l’absence des bases qui permettraient de mesurer de manière exhaustive la présence de substances problématiques dans l’environnement et chez tous les êtres vivants, dont l’être humain. Le CDF recommande donc à la Confédération de mettre en place des structures minimales d’observation afin d’identifier les concentrations préoccupantes à un stade précoce. Cette recommandation a été réitérée dans la réponse à ma question 25.7601.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Et pourtant, le projet de biosurveillance humaine, prévu à grande échelle et de longue date, a été suspendu l’année dernière pour des raisons d’économies, les coûts étant estimés à 10 à 12 millions de francs par année.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Parmi les substances examinées dans le rapport figurent notamment les PFAS. Or, les auteurs du&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20224585&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418677476%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=z10Tv5jE3IpVBFh0o6UnY90TnVYXr2Y5Ndq3RmW5GVY%3D&amp;amp;reserved=0"&gt;rapport donnant suite au postulat Moser 22.4585&lt;/a&gt; estiment que la pollution due aux PFAS engendre à elle seule des coûts sanitaires estimés de 1 à 1,6 milliard de francs par année.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dans son avis de novembre 2024, le Conseil fédéral répond à mon&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20244132&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418722671%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=UBwnsioRhMw7aHxnliPc1mu3WpgRQV%2BO6IvjZOdi1ks%3D&amp;amp;reserved=0"&gt;postulat 24.4132 que « Les offices fédéraux concernés vont examiner de plus près et prioriser les recommandations formulées [dans le &lt;/a&gt;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.efk.admin.ch%2Fwp-content%2Fuploads%2Fpublikationen%2Fberichte%2Fsicherheit_und_umwelt%2Fverkehr_und_umwelt%2F23489%2F23489be-endgueltige-fassung-v04.pdf&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418760862%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=EgVyMNJbnjFXdus606rdIuOs7%2BpoM3PkpcFpJ3reOmA%3D&amp;amp;reserved=0"&gt;rapport 23489 du CDF]&lt;/a&gt;, en tenant compte notamment des moyens disponibles limités. »&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.efk.admin.ch%2Fwp-content%2Fuploads%2Fpublikationen%2Fberichte%2Fsicherheit_und_umwelt%2Fverkehr_und_umwelt%2F23489%2F23489be-endgueltige-fassung-v04.pdf&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418760862%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=EgVyMNJbnjFXdus606rdIuOs7%2BpoM3PkpcFpJ3reOmA%3D&amp;amp;reserved=0"&gt;&lt;/a&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie dès lors le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;p&gt;1. Est-il également d’avis que les mesures recommandées par le CDF doivent être examinées et mises en œuvre rapidement afin d’éviter des coûts élevés liés aux substances problématiques, en particulier les PFAS ? Si non, pourquoi ? Si oui, quand ces travaux seront-ils achevés ?&lt;br&gt;2.&amp;nbsp;Où en sont les offices fédéraux, près de deux ans après la publication du rapport, concernant l'examen, la priorisation et la mise en œuvre des recommandations ?&lt;br&gt;3.&amp;nbsp;Qu’entend-on par « structures minimales d’observation des substances problématiques » ? Quels progrès ont été réalisés depuis la publication du rapport ?&lt;br&gt;4.&amp;nbsp;Le Conseil fédéral est-il également d’avis qu’un projet de biosurveillance humaine tel que les pays voisins en mènent depuis des années pourrait apporter davantage de clarté sur l’exposition des différents groupes de population aux PFAS et permettre de prendre des décisions plus judicieuses ?&lt;br&gt;5.&amp;nbsp;Cette approche pourrait-elle contribuer à réduire les coûts générés par les PFAS et à mieux évaluer l’efficacité des mesures prises ? Dans l’affirmative, que représentent les coûts d’une étude de cohorte, selon le Conseil fédéral, au regard des coûts engendrés par les PFAS, qui se chiffrent en milliards de francs ? Si non, pourquoi ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Im Mai 2024 wurde der&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.efk.admin.ch%2Fwp-content%2Fuploads%2Fpublikationen%2Fberichte%2Fsicherheit_und_umwelt%2Fverkehr_und_umwelt%2F23489%2F23489be-endgueltige-fassung-v04.pdf&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418627523%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=IeMVU%2F1hFFBihhELV7SAmFjibLMt%2Fx2qsnlGzjc2IFI%3D&amp;amp;reserved=0"&gt;EFK-Bericht 23489&lt;/a&gt;&amp;nbsp;zum Umgangs des Bundes mit problematischen Stoffen publiziert. Er kommt zum Schluss, dass die Grundlagen fehlen, um das Ausmass des Vorkommens von problematischen Stoffen in der Umwelt und im Menschen umfassend festzustellen. Die EFK empfiehlt deshalb dem Bund, ein Mindestmass an Beobachtungsstrukturen für problematische Stoffe in der Umwelt und in allen Lebewesen aufzubauen, um frühzeitig besorgniserregende Konzentrationen zu identifizieren. Diese Empfehlung wurde in der Antwort auf meine Frage 25.7601 erneut herausgestrichen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Trotzdem wurde im vergangenen Jahr das lange geplante und grossangelegte Humanbiomonitoring-Projekt des Bundes aufgrund der prognostizierten Kosten von CHF 10–12 Mio. jährlich aus Spargründen gestoppt.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Zu den im EFK-Bericht untersuchten Stoffen gehören unter anderem die PFAS. Im&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20224585&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418677476%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=z10Tv5jE3IpVBFh0o6UnY90TnVYXr2Y5Ndq3RmW5GVY%3D&amp;amp;reserved=0"&gt;Postulatsbericht 22.4585 Moser&lt;/a&gt; werden allein die gesundheitlichen Folgekosten der PFAS-Belastung auf CHF 1-1,6 Mrd. jährlich geschätzt.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Im November 2024 schrieb der Bundesrat zu meinem&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20244132&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418722671%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=UBwnsioRhMw7aHxnliPc1mu3WpgRQV%2BO6IvjZOdi1ks%3D&amp;amp;reserved=0"&gt;Po. 24.4132&lt;/a&gt;, dass die Empfehlungen aus dem&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.efk.admin.ch%2Fwp-content%2Fuploads%2Fpublikationen%2Fberichte%2Fsicherheit_und_umwelt%2Fverkehr_und_umwelt%2F23489%2F23489be-endgueltige-fassung-v04.pdf&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418760862%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=EgVyMNJbnjFXdus606rdIuOs7%2BpoM3PkpcFpJ3reOmA%3D&amp;amp;reserved=0"&gt;EFK-Bericht 23489&lt;/a&gt; von den Bundesämtern vertieft geprüft und priorisiert würden, speziell vor dem Hintergrund der limitierten Ressourcen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich ersuche den Bundesrat um die Beantwortung folgender Fragen:&lt;/p&gt;&lt;p&gt;1. Ist er auch der Meinung, dass die von der EFK empfohlenen Massnahmen rasch geprüft und umgesetzt werden sollen, um hohen Folgekosten durch problematische Stoffe zu vermeiden, insbesondere zu PFAS? Falls nein, warum? Falls ja, wann ist der Prozess abgeschlossen?&lt;br&gt;2.&amp;nbsp;Wo stehen die Bundesämter konkret, fast zwei Jahre nach Veröffentlichung des Berichts und bezüglich der Prüfung, Priorisierung und Umsetzung&amp;nbsp;der Empfehlungen?&lt;br&gt;3.&amp;nbsp;Was ist unter einem «Mindestmass an Beobachtungsstrukturen für problematische Stoffe» zu verstehen? Welche Fortschritte wurden seit Publikation des Berichts erzielt?&lt;br&gt;4.&amp;nbsp;Teilt er die Ansicht, dass ein HBM, wie es umliegende Länder seit Jahren kennen, Klarheit in die PFAS-Belastung der Bevölkerungsgruppen bringen und so fundiertere Entscheidungen hätte ermöglichen können?&lt;br&gt;5.&amp;nbsp;Hätte dies helfen können, die Folgekosten von PFAS zu senken und die Wirksamkeit von Massnahmen besser beurteilen zu können? Falls ja, wie ordnet er die Kosten der Gesundheitsstudie im Verhältnis zu den milliardenschweren Gesundheitskosten von PFAS ein?&amp;nbsp;Falls nein, warum nicht?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wissenschaft und Forschung|Umwelt|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Science et recherche|Environnement|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scienza e ricerca|Ambiente|Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Po.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addor Jean-Luc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Externes Audit des Bundesamts für Zoll und Grenzsicherheit zur Wiederherstellung des Vertrauens des Personals und der Wirtschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un audit externe de l'OFDF pour restaurer la confiance du personnel et de l'économie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una verifica esterna dell'UDSC per ristabilire la fiducia tra il personale e il mondo economico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de commander, avant que des décisions irréversibles ne soient prises, un audit externe de l’OFDF et de la transformation en cours portant notamment sur les points suivants&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Adéquation des moyens (budget et personnel) aux multiples tâches de l’OFDF, en particulier pour la surveillance de la frontière terrestre, le contrôle de la migration ou encore la lutte contre les trafics en tous genres (produits agricoles, animaux, plantes envahissantes)&lt;/li&gt;&lt;li&gt;Efficacité de DaziT dans l’encaissement des droits de douanes (recettes en recul en 2025), avec en particulier la fin du contrôle systématique des camions étrangers, et face aux attentes de l’économie (en écho aux critiques très dures du transporteur Marco Tepoorten parlant d’une «&amp;nbsp;désorganisation systémique&amp;nbsp;»)&lt;/li&gt;&lt;li&gt;Flexibiliser Allegra&lt;/li&gt;&lt;li&gt;Taux d’arrêts maladie et de départs de l’OFDF&lt;/li&gt;&lt;li&gt;Attractivité du statut des personnels OFDF&lt;/li&gt;&lt;li&gt;Formation (qui semble enregistrer un taux d’échec inusuel)&lt;/li&gt;&lt;li&gt;Taux de rotation inhabituel parmi les cadres supérieurs de l’OFDF&lt;/li&gt;&lt;li&gt;Avant de continuer à foncer dans une direction discutable, n’y a-t-il pas lieu de tirer les leçons de transformations analogues à l’étranger (Autriche, Canada), surtout de certains échecs ?&lt;/li&gt;&lt;li&gt;Quelles mesures pour restaurer la confiance du personnel et de l'économie et garantir l'efficacité de l'OFDF dans l'exécution de ses tâches ?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Bevor irreversible Entscheide getroffen werden, wird der Bundesrat beauftragt, ein externes Audit des Bundesamts für Zoll und Grenzsicherheit (BAZG) und dessen laufender Umstrukturierung in Auftrag zu geben, das insbesondere folgende Punkte umfasst:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Angemessenheit der Mittel (Budget und Personal) für die vielfältigen Aufgaben des BAZG, insbesondere für die Überwachung der Landesgrenze, die Migrationskontrolle und die Bekämpfung von Schmuggel aller Art (landwirtschaftliche Produkte, Tiere, invasive Pflanzen);&lt;/li&gt;&lt;li&gt;Wirksamkeit des Programms Dazit bei der Zollerhebung (rückläufige Einnahmen&amp;nbsp;2025), insbesondere angesichts des Wegfalls der systematischen Kontrolle ausländischer Lastwagen und der Erwartungen der Wirtschaft (in Anlehnung an die sehr harte Kritik des Transportunternehmers Marco Tepoorten, der von einer «systemischen Desorganisation» sprach);&lt;/li&gt;&lt;li&gt;Flexibilisierung von Allegra;&lt;/li&gt;&lt;li&gt;Krankheitsabsenzen und Abgänge beim BAZG;&lt;/li&gt;&lt;li&gt;Attraktivität des BAZG-Personalstatus;&lt;/li&gt;&lt;li&gt;Ausbildung (mit offenbar ungewöhnlich hoher Durchfallquote);&lt;/li&gt;&lt;li&gt;untypische Fluktuationsrate bei den Führungskräften des BAZG;&lt;/li&gt;&lt;li&gt;Wäre es nicht angebracht, Lehren aus vergleichbaren Umstrukturierungen im Ausland (Österreich, Kanada) zu ziehen – insbesondere aus gewissen Misserfolgen –, bevor weiter in eine fragwürdige Richtung vorgeprescht wird?&lt;/li&gt;&lt;li&gt;Welche Massnahmen sind notwendig, um das Vertrauen des Personals und der Wirtschaft wiederherzustellen und die Wirksamkeit des BAZG bei der Aufgabenerfüllung zu gewährleisten?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eingereicht / Déposé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Beschäftigung und Arbeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Emploi et travail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Occupazione e lavoro</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3398</t>
   </si>
   <si>
@@ -152,12 +248,6 @@
     <t xml:space="preserve">pvl</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Einführung eines öffentlichen Registers der Subventionsempfänger</t>
   </si>
   <si>
@@ -173,18 +263,12 @@
     <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, ein öffentlich einsehbares, zentrales Register der &amp;nbsp;Empfängerinnen und Empfänger von Bundessubventionen einzuführen. Das Register soll als Ergänzung zur bestehenden Subventionsdatenbank ausgestaltet und durch Bund oder EFK geführt werden. Es hat mindestens den Namen oder Empfängertyp, Art und Zweck der Subvention, den jährlich ausbezahlten Betrag sowie das zuständige Bundesamt auszuweisen. Es soll bestehenden Daten der Bundesämter nutzen.&amp;nbsp;&lt;br&gt;Datenschutz- und sicherheitsrelevante Einschränkungen bleiben vorbehalten.&lt;/p&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Eingereicht / Déposé</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263398</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263398</t>
   </si>
   <si>
-    <t xml:space="preserve">Élu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Staatspolitik|Finanzwesen</t>
   </si>
   <si>
@@ -194,48 +278,6 @@
     <t xml:space="preserve">Politica nazionale|Finanze</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Po.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addor Jean-Luc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Externes Audit des Bundesamts für Zoll und Grenzsicherheit zur Wiederherstellung des Vertrauens des Personals und der Wirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Un audit externe de l'OFDF pour restaurer la confiance du personnel et de l'économie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una verifica esterna dell'UDSC per ristabilire la fiducia tra il personale e il mondo economico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de commander, avant que des décisions irréversibles ne soient prises, un audit externe de l’OFDF et de la transformation en cours portant notamment sur les points suivants&amp;nbsp;:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Adéquation des moyens (budget et personnel) aux multiples tâches de l’OFDF, en particulier pour la surveillance de la frontière terrestre, le contrôle de la migration ou encore la lutte contre les trafics en tous genres (produits agricoles, animaux, plantes envahissantes)&lt;/li&gt;&lt;li&gt;Efficacité de DaziT dans l’encaissement des droits de douanes (recettes en recul en 2025), avec en particulier la fin du contrôle systématique des camions étrangers, et face aux attentes de l’économie (en écho aux critiques très dures du transporteur Marco Tepoorten parlant d’une «&amp;nbsp;désorganisation systémique&amp;nbsp;»)&lt;/li&gt;&lt;li&gt;Flexibiliser Allegra&lt;/li&gt;&lt;li&gt;Taux d’arrêts maladie et de départs de l’OFDF&lt;/li&gt;&lt;li&gt;Attractivité du statut des personnels OFDF&lt;/li&gt;&lt;li&gt;Formation (qui semble enregistrer un taux d’échec inusuel)&lt;/li&gt;&lt;li&gt;Taux de rotation inhabituel parmi les cadres supérieurs de l’OFDF&lt;/li&gt;&lt;li&gt;Avant de continuer à foncer dans une direction discutable, n’y a-t-il pas lieu de tirer les leçons de transformations analogues à l’étranger (Autriche, Canada), surtout de certains échecs ?&lt;/li&gt;&lt;li&gt;Quelles mesures pour restaurer la confiance du personnel et de l'économie et garantir l'efficacité de l'OFDF dans l'exécution de ses tâches ?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Bevor irreversible Entscheide getroffen werden, wird der Bundesrat beauftragt, ein externes Audit des Bundesamts für Zoll und Grenzsicherheit (BAZG) und dessen laufender Umstrukturierung in Auftrag zu geben, das insbesondere folgende Punkte umfasst:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Angemessenheit der Mittel (Budget und Personal) für die vielfältigen Aufgaben des BAZG, insbesondere für die Überwachung der Landesgrenze, die Migrationskontrolle und die Bekämpfung von Schmuggel aller Art (landwirtschaftliche Produkte, Tiere, invasive Pflanzen);&lt;/li&gt;&lt;li&gt;Wirksamkeit des Programms Dazit bei der Zollerhebung (rückläufige Einnahmen&amp;nbsp;2025), insbesondere angesichts des Wegfalls der systematischen Kontrolle ausländischer Lastwagen und der Erwartungen der Wirtschaft (in Anlehnung an die sehr harte Kritik des Transportunternehmers Marco Tepoorten, der von einer «systemischen Desorganisation» sprach);&lt;/li&gt;&lt;li&gt;Flexibilisierung von Allegra;&lt;/li&gt;&lt;li&gt;Krankheitsabsenzen und Abgänge beim BAZG;&lt;/li&gt;&lt;li&gt;Attraktivität des BAZG-Personalstatus;&lt;/li&gt;&lt;li&gt;Ausbildung (mit offenbar ungewöhnlich hoher Durchfallquote);&lt;/li&gt;&lt;li&gt;untypische Fluktuationsrate bei den Führungskräften des BAZG;&lt;/li&gt;&lt;li&gt;Wäre es nicht angebracht, Lehren aus vergleichbaren Umstrukturierungen im Ausland (Österreich, Kanada) zu ziehen – insbesondere aus gewissen Misserfolgen –, bevor weiter in eine fragwürdige Richtung vorgeprescht wird?&lt;/li&gt;&lt;li&gt;Welche Massnahmen sind notwendig, um das Vertrauen des Personals und der Wirtschaft wiederherzustellen und die Wirksamkeit des BAZG bei der Aufgabenerfüllung zu gewährleisten?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Beschäftigung und Arbeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Emploi et travail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Occupazione e lavoro</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3487</t>
   </si>
   <si>
@@ -338,9 +380,6 @@
     <t xml:space="preserve">2025-12-18</t>
   </si>
   <si>
-    <t xml:space="preserve">UVEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Transparenz bei der Fördereffizienz aller erneuerbaren Technologien herstellen</t>
   </si>
   <si>
@@ -447,45 +486,6 @@
   </si>
   <si>
     <t xml:space="preserve">Economia|Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weichelt Manuela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERT-E-S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umgang des Bundes mit problematischen Stoffen. PFAS. Kohortenstudie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion des substances problématiques par la Confédération. PFAS. Étude de cohorte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestione di sostanze problematiche da parte della Confederazione, PFAS, studio di coorte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.efk.admin.ch%2Fwp-content%2Fuploads%2Fpublikationen%2Fberichte%2Fsicherheit_und_umwelt%2Fverkehr_und_umwelt%2F23489%2F23489be-endgueltige-fassung-v04.pdf&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418627523%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=IeMVU%2F1hFFBihhELV7SAmFjibLMt%2Fx2qsnlGzjc2IFI%3D&amp;amp;reserved=0"&gt;Le rapport 23489 du Contrôle fédéral des finances (CDF) sur la gestion des substances problématiques par la Confédération &lt;/a&gt;&amp;nbsp;a été publié en mai 2024. Il conclut à l’absence des bases qui permettraient de mesurer de manière exhaustive la présence de substances problématiques dans l’environnement et chez tous les êtres vivants, dont l’être humain. Le CDF recommande donc à la Confédération de mettre en place des structures minimales d’observation afin d’identifier les concentrations préoccupantes à un stade précoce. Cette recommandation a été réitérée dans la réponse à ma question 25.7601.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Et pourtant, le projet de biosurveillance humaine, prévu à grande échelle et de longue date, a été suspendu l’année dernière pour des raisons d’économies, les coûts étant estimés à 10 à 12 millions de francs par année.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Parmi les substances examinées dans le rapport figurent notamment les PFAS. Or, les auteurs du&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20224585&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418677476%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=z10Tv5jE3IpVBFh0o6UnY90TnVYXr2Y5Ndq3RmW5GVY%3D&amp;amp;reserved=0"&gt;rapport donnant suite au postulat Moser 22.4585&lt;/a&gt; estiment que la pollution due aux PFAS engendre à elle seule des coûts sanitaires estimés de 1 à 1,6 milliard de francs par année.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dans son avis de novembre 2024, le Conseil fédéral répond à mon&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20244132&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418722671%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=UBwnsioRhMw7aHxnliPc1mu3WpgRQV%2BO6IvjZOdi1ks%3D&amp;amp;reserved=0"&gt;postulat 24.4132 que « Les offices fédéraux concernés vont examiner de plus près et prioriser les recommandations formulées [dans le &lt;/a&gt;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.efk.admin.ch%2Fwp-content%2Fuploads%2Fpublikationen%2Fberichte%2Fsicherheit_und_umwelt%2Fverkehr_und_umwelt%2F23489%2F23489be-endgueltige-fassung-v04.pdf&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418760862%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=EgVyMNJbnjFXdus606rdIuOs7%2BpoM3PkpcFpJ3reOmA%3D&amp;amp;reserved=0"&gt;rapport 23489 du CDF]&lt;/a&gt;, en tenant compte notamment des moyens disponibles limités. »&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.efk.admin.ch%2Fwp-content%2Fuploads%2Fpublikationen%2Fberichte%2Fsicherheit_und_umwelt%2Fverkehr_und_umwelt%2F23489%2F23489be-endgueltige-fassung-v04.pdf&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418760862%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=EgVyMNJbnjFXdus606rdIuOs7%2BpoM3PkpcFpJ3reOmA%3D&amp;amp;reserved=0"&gt;&lt;/a&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je prie dès lors le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;p&gt;1. Est-il également d’avis que les mesures recommandées par le CDF doivent être examinées et mises en œuvre rapidement afin d’éviter des coûts élevés liés aux substances problématiques, en particulier les PFAS ? Si non, pourquoi ? Si oui, quand ces travaux seront-ils achevés ?&lt;br&gt;2.&amp;nbsp;Où en sont les offices fédéraux, près de deux ans après la publication du rapport, concernant l'examen, la priorisation et la mise en œuvre des recommandations ?&lt;br&gt;3.&amp;nbsp;Qu’entend-on par « structures minimales d’observation des substances problématiques » ? Quels progrès ont été réalisés depuis la publication du rapport ?&lt;br&gt;4.&amp;nbsp;Le Conseil fédéral est-il également d’avis qu’un projet de biosurveillance humaine tel que les pays voisins en mènent depuis des années pourrait apporter davantage de clarté sur l’exposition des différents groupes de population aux PFAS et permettre de prendre des décisions plus judicieuses ?&lt;br&gt;5.&amp;nbsp;Cette approche pourrait-elle contribuer à réduire les coûts générés par les PFAS et à mieux évaluer l’efficacité des mesures prises ? Dans l’affirmative, que représentent les coûts d’une étude de cohorte, selon le Conseil fédéral, au regard des coûts engendrés par les PFAS, qui se chiffrent en milliards de francs ? Si non, pourquoi ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Im Mai 2024 wurde der&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.efk.admin.ch%2Fwp-content%2Fuploads%2Fpublikationen%2Fberichte%2Fsicherheit_und_umwelt%2Fverkehr_und_umwelt%2F23489%2F23489be-endgueltige-fassung-v04.pdf&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418627523%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=IeMVU%2F1hFFBihhELV7SAmFjibLMt%2Fx2qsnlGzjc2IFI%3D&amp;amp;reserved=0"&gt;EFK-Bericht 23489&lt;/a&gt;&amp;nbsp;zum Umgangs des Bundes mit problematischen Stoffen publiziert. Er kommt zum Schluss, dass die Grundlagen fehlen, um das Ausmass des Vorkommens von problematischen Stoffen in der Umwelt und im Menschen umfassend festzustellen. Die EFK empfiehlt deshalb dem Bund, ein Mindestmass an Beobachtungsstrukturen für problematische Stoffe in der Umwelt und in allen Lebewesen aufzubauen, um frühzeitig besorgniserregende Konzentrationen zu identifizieren. Diese Empfehlung wurde in der Antwort auf meine Frage 25.7601 erneut herausgestrichen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Trotzdem wurde im vergangenen Jahr das lange geplante und grossangelegte Humanbiomonitoring-Projekt des Bundes aufgrund der prognostizierten Kosten von CHF 10–12 Mio. jährlich aus Spargründen gestoppt.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Zu den im EFK-Bericht untersuchten Stoffen gehören unter anderem die PFAS. Im&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20224585&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418677476%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=z10Tv5jE3IpVBFh0o6UnY90TnVYXr2Y5Ndq3RmW5GVY%3D&amp;amp;reserved=0"&gt;Postulatsbericht 22.4585 Moser&lt;/a&gt; werden allein die gesundheitlichen Folgekosten der PFAS-Belastung auf CHF 1-1,6 Mrd. jährlich geschätzt.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Im November 2024 schrieb der Bundesrat zu meinem&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.parlament.ch%2Fde%2Fratsbetrieb%2Fsuche-curia-vista%2Fgeschaeft%3FAffairId%3D20244132&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418722671%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=UBwnsioRhMw7aHxnliPc1mu3WpgRQV%2BO6IvjZOdi1ks%3D&amp;amp;reserved=0"&gt;Po. 24.4132&lt;/a&gt;, dass die Empfehlungen aus dem&amp;nbsp;&lt;a href="https://che01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.efk.admin.ch%2Fwp-content%2Fuploads%2Fpublikationen%2Fberichte%2Fsicherheit_und_umwelt%2Fverkehr_und_umwelt%2F23489%2F23489be-endgueltige-fassung-v04.pdf&amp;amp;data=05%7C02%7Cmanuela.weichelt%40parl.ch%7C88e06422cf774e5bd1f408de85c83fa3%7C0cf3ddc638a5480885f1cae22925a1b0%7C0%7C0%7C639095292418760862%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;amp;sdata=EgVyMNJbnjFXdus606rdIuOs7%2BpoM3PkpcFpJ3reOmA%3D&amp;amp;reserved=0"&gt;EFK-Bericht 23489&lt;/a&gt; von den Bundesämtern vertieft geprüft und priorisiert würden, speziell vor dem Hintergrund der limitierten Ressourcen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich ersuche den Bundesrat um die Beantwortung folgender Fragen:&lt;/p&gt;&lt;p&gt;1. Ist er auch der Meinung, dass die von der EFK empfohlenen Massnahmen rasch geprüft und umgesetzt werden sollen, um hohen Folgekosten durch problematische Stoffe zu vermeiden, insbesondere zu PFAS? Falls nein, warum? Falls ja, wann ist der Prozess abgeschlossen?&lt;br&gt;2.&amp;nbsp;Wo stehen die Bundesämter konkret, fast zwei Jahre nach Veröffentlichung des Berichts und bezüglich der Prüfung, Priorisierung und Umsetzung&amp;nbsp;der Empfehlungen?&lt;br&gt;3.&amp;nbsp;Was ist unter einem «Mindestmass an Beobachtungsstrukturen für problematische Stoffe» zu verstehen? Welche Fortschritte wurden seit Publikation des Berichts erzielt?&lt;br&gt;4.&amp;nbsp;Teilt er die Ansicht, dass ein HBM, wie es umliegende Länder seit Jahren kennen, Klarheit in die PFAS-Belastung der Bevölkerungsgruppen bringen und so fundiertere Entscheidungen hätte ermöglichen können?&lt;br&gt;5.&amp;nbsp;Hätte dies helfen können, die Folgekosten von PFAS zu senken und die Wirksamkeit von Massnahmen besser beurteilen zu können? Falls ja, wie ordnet er die Kosten der Gesundheitsstudie im Verhältnis zu den milliardenschweren Gesundheitskosten von PFAS ein?&amp;nbsp;Falls nein, warum nicht?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wissenschaft und Forschung|Umwelt|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Science et recherche|Environnement|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scienza e ricerca|Ambiente|Salute</t>
   </si>
   <si>
     <t xml:space="preserve">25.4594</t>
@@ -11407,68 +11407,68 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20263398</v>
+        <v>20263281</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>44</v>
       </c>
-      <c r="E3" t="s">
-        <v>45</v>
-      </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
         <v>27</v>
       </c>
       <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="s">
         <v>47</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>48</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>49</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>50</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" t="s">
         <v>51</v>
       </c>
-      <c r="M3" t="s">
+      <c r="P3" t="s">
         <v>52</v>
       </c>
-      <c r="N3" t="s">
+      <c r="Q3" t="s">
         <v>53</v>
       </c>
-      <c r="O3" t="s">
-        <v>54</v>
-      </c>
-      <c r="P3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>56</v>
-      </c>
       <c r="R3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="S3"/>
       <c r="T3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="U3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="V3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -11476,43 +11476,43 @@
         <v>20263485</v>
       </c>
       <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
         <v>60</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>61</v>
-      </c>
-      <c r="D4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" t="s">
-        <v>46</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" t="s">
         <v>64</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>65</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>66</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>67</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>68</v>
-      </c>
-      <c r="N4" t="s">
-        <v>53</v>
       </c>
       <c r="O4" t="s">
         <v>69</v>
@@ -11521,10 +11521,10 @@
         <v>70</v>
       </c>
       <c r="Q4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="S4"/>
       <c r="T4" t="s">
@@ -11539,79 +11539,79 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263487</v>
+        <v>20263398</v>
       </c>
       <c r="B5" t="s">
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" t="s">
+        <v>83</v>
+      </c>
+      <c r="P5" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q5" t="s">
         <v>53</v>
       </c>
-      <c r="O5" t="s">
-        <v>82</v>
-      </c>
-      <c r="P5" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>56</v>
-      </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="S5"/>
       <c r="T5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="V5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20263028</v>
+        <v>20263487</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
         <v>89</v>
@@ -11620,109 +11620,109 @@
         <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
       </c>
       <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" t="s">
         <v>92</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>93</v>
       </c>
-      <c r="J6" t="s">
+      <c r="L6" t="s">
         <v>94</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>95</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6" t="s">
         <v>96</v>
       </c>
-      <c r="M6" t="s">
+      <c r="P6" t="s">
         <v>97</v>
       </c>
-      <c r="N6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O6" t="s">
-        <v>99</v>
-      </c>
-      <c r="P6" t="s">
-        <v>100</v>
-      </c>
       <c r="Q6" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="R6" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="S6"/>
       <c r="T6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="U6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="V6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20254696</v>
+        <v>20263028</v>
       </c>
       <c r="B7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" t="s">
         <v>105</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
-        <v>107</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>
       </c>
       <c r="H7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" t="s">
         <v>108</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>109</v>
       </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
         <v>110</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>111</v>
       </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
         <v>112</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>113</v>
       </c>
-      <c r="N7" t="s">
-        <v>98</v>
-      </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>114</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>115</v>
       </c>
-      <c r="Q7" t="s">
-        <v>101</v>
-      </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="S7"/>
       <c r="T7" t="s">
@@ -11737,7 +11737,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20254582</v>
+        <v>20254696</v>
       </c>
       <c r="B8" t="s">
         <v>119</v>
@@ -11749,7 +11749,7 @@
         <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
         <v>121</v>
@@ -11758,139 +11758,139 @@
         <v>27</v>
       </c>
       <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
         <v>122</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>123</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>124</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>125</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>126</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
+        <v>112</v>
+      </c>
+      <c r="O8" t="s">
         <v>127</v>
       </c>
-      <c r="N8" t="s">
-        <v>98</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>128</v>
       </c>
-      <c r="P8" t="s">
-        <v>129</v>
-      </c>
       <c r="Q8" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="R8" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="S8"/>
       <c r="T8" t="s">
+        <v>129</v>
+      </c>
+      <c r="U8" t="s">
         <v>130</v>
       </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
         <v>131</v>
-      </c>
-      <c r="V8" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20254614</v>
+        <v>20254582</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
         <v>134</v>
-      </c>
-      <c r="E9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" t="s">
-        <v>121</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="I9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N9" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q9" t="s">
         <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="S9"/>
       <c r="T9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="V9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20263281</v>
+        <v>20254614</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
         <v>148</v>
@@ -11908,7 +11908,7 @@
         <v>152</v>
       </c>
       <c r="N10" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="O10" t="s">
         <v>153</v>
@@ -11917,14 +11917,12 @@
         <v>154</v>
       </c>
       <c r="Q10" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="R10" t="s">
-        <v>38</v>
-      </c>
-      <c r="S10" t="s">
-        <v>38</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="S10"/>
       <c r="T10" t="s">
         <v>155</v>
       </c>
@@ -11952,7 +11950,7 @@
         <v>160</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="G11" t="s">
         <v>161</v>
@@ -11976,7 +11974,7 @@
         <v>166</v>
       </c>
       <c r="N11" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O11" t="s">
         <v>167</v>
@@ -12009,7 +12007,7 @@
         <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
         <v>173</v>
@@ -12022,7 +12020,7 @@
         <v>27</v>
       </c>
       <c r="H12" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
         <v>175</v>
@@ -12040,7 +12038,7 @@
         <v>179</v>
       </c>
       <c r="N12" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O12" t="s">
         <v>180</v>
@@ -12088,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="H13" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I13" t="s">
         <v>190</v>
@@ -12104,7 +12102,7 @@
         <v>193</v>
       </c>
       <c r="N13" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O13" t="s">
         <v>194</v>
@@ -12113,7 +12111,7 @@
         <v>195</v>
       </c>
       <c r="Q13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R13" t="s">
         <v>196</v>
@@ -12152,7 +12150,7 @@
         <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
         <v>203</v>
@@ -12168,7 +12166,7 @@
         <v>206</v>
       </c>
       <c r="N14" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O14" t="s">
         <v>207</v>
@@ -12177,7 +12175,7 @@
         <v>208</v>
       </c>
       <c r="Q14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R14" t="s">
         <v>196</v>
@@ -12207,7 +12205,7 @@
         <v>213</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
         <v>214</v>
@@ -12216,7 +12214,7 @@
         <v>27</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I15" t="s">
         <v>215</v>
@@ -12232,7 +12230,7 @@
         <v>218</v>
       </c>
       <c r="N15" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O15" t="s">
         <v>219</v>
@@ -12241,7 +12239,7 @@
         <v>220</v>
       </c>
       <c r="Q15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R15" t="s">
         <v>214</v>
@@ -12271,7 +12269,7 @@
         <v>225</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
         <v>226</v>
@@ -12280,7 +12278,7 @@
         <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I16" t="s">
         <v>227</v>
@@ -12298,7 +12296,7 @@
         <v>231</v>
       </c>
       <c r="N16" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O16" t="s">
         <v>232</v>
@@ -12314,13 +12312,13 @@
       </c>
       <c r="S16"/>
       <c r="T16" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="U16" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="V16" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -12337,7 +12335,7 @@
         <v>237</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
         <v>238</v>
@@ -12346,7 +12344,7 @@
         <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I17" t="s">
         <v>239</v>
@@ -12373,7 +12371,7 @@
         <v>246</v>
       </c>
       <c r="Q17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R17" t="s">
         <v>247</v>
@@ -12397,7 +12395,7 @@
         <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
         <v>252</v>
@@ -12412,7 +12410,7 @@
         <v>27</v>
       </c>
       <c r="H18" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I18" t="s">
         <v>253</v>
@@ -12439,7 +12437,7 @@
         <v>260</v>
       </c>
       <c r="Q18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R18" t="s">
         <v>247</v>
@@ -12469,7 +12467,7 @@
         <v>265</v>
       </c>
       <c r="E19" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
         <v>238</v>
@@ -12505,7 +12503,7 @@
         <v>272</v>
       </c>
       <c r="Q19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R19" t="s">
         <v>247</v>
@@ -12529,7 +12527,7 @@
         <v>276</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>277</v>
@@ -12544,7 +12542,7 @@
         <v>161</v>
       </c>
       <c r="H20" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I20" t="s">
         <v>253</v>
@@ -12571,7 +12569,7 @@
         <v>281</v>
       </c>
       <c r="Q20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R20" t="s">
         <v>247</v>
@@ -12601,7 +12599,7 @@
         <v>283</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F21" t="s">
         <v>238</v>
@@ -12637,7 +12635,7 @@
         <v>290</v>
       </c>
       <c r="Q21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R21" t="s">
         <v>247</v>
@@ -12703,7 +12701,7 @@
         <v>303</v>
       </c>
       <c r="Q22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R22" t="s">
         <v>247</v>
@@ -12727,10 +12725,10 @@
         <v>307</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s">
         <v>25</v>
@@ -12769,7 +12767,7 @@
         <v>314</v>
       </c>
       <c r="Q23" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R23" t="s">
         <v>247</v>
@@ -12793,13 +12791,13 @@
         <v>318</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>319</v>
       </c>
       <c r="E24" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s">
         <v>320</v>
@@ -12808,7 +12806,7 @@
         <v>27</v>
       </c>
       <c r="H24" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I24" t="s">
         <v>321</v>
@@ -12874,7 +12872,7 @@
         <v>161</v>
       </c>
       <c r="H25" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I25" t="s">
         <v>334</v>
@@ -12892,7 +12890,7 @@
         <v>338</v>
       </c>
       <c r="N25" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O25" t="s">
         <v>339</v>
@@ -12901,7 +12899,7 @@
         <v>340</v>
       </c>
       <c r="Q25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R25" t="s">
         <v>247</v>
@@ -12925,7 +12923,7 @@
         <v>344</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>345</v>
@@ -12997,7 +12995,7 @@
         <v>357</v>
       </c>
       <c r="E27" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s">
         <v>358</v>
@@ -13006,7 +13004,7 @@
         <v>27</v>
       </c>
       <c r="H27" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I27" t="s">
         <v>359</v>
@@ -13022,7 +13020,7 @@
         <v>362</v>
       </c>
       <c r="N27" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O27" t="s">
         <v>363</v>
@@ -13061,7 +13059,7 @@
         <v>369</v>
       </c>
       <c r="E28" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F28" t="s">
         <v>358</v>
@@ -13070,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I28" t="s">
         <v>370</v>
@@ -13088,7 +13086,7 @@
         <v>374</v>
       </c>
       <c r="N28" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O28" t="s">
         <v>375</v>
@@ -13136,7 +13134,7 @@
         <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I29" t="s">
         <v>384</v>
@@ -13163,7 +13161,7 @@
         <v>390</v>
       </c>
       <c r="Q29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R29" t="s">
         <v>247</v>
@@ -13187,7 +13185,7 @@
         <v>394</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
         <v>395</v>
@@ -13202,7 +13200,7 @@
         <v>27</v>
       </c>
       <c r="H30" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I30" t="s">
         <v>397</v>
@@ -13229,7 +13227,7 @@
         <v>403</v>
       </c>
       <c r="Q30" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R30" t="s">
         <v>247</v>
@@ -13253,10 +13251,10 @@
         <v>407</v>
       </c>
       <c r="C31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" t="s">
         <v>43</v>
-      </c>
-      <c r="D31" t="s">
-        <v>146</v>
       </c>
       <c r="E31" t="s">
         <v>408</v>
@@ -13268,7 +13266,7 @@
         <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I31" t="s">
         <v>410</v>
@@ -13295,7 +13293,7 @@
         <v>416</v>
       </c>
       <c r="Q31" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R31" t="s">
         <v>247</v>
@@ -13334,7 +13332,7 @@
         <v>27</v>
       </c>
       <c r="H32" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I32" t="s">
         <v>422</v>
@@ -13361,7 +13359,7 @@
         <v>428</v>
       </c>
       <c r="Q32" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R32" t="s">
         <v>247</v>
@@ -13385,7 +13383,7 @@
         <v>432</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
         <v>433</v>
@@ -13451,13 +13449,13 @@
         <v>445</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
         <v>446</v>
       </c>
       <c r="E34" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F34" t="s">
         <v>409</v>
@@ -13523,7 +13521,7 @@
         <v>458</v>
       </c>
       <c r="E35" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F35" t="s">
         <v>459</v>
@@ -13532,7 +13530,7 @@
         <v>161</v>
       </c>
       <c r="H35" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I35" t="s">
         <v>460</v>
@@ -13550,7 +13548,7 @@
         <v>464</v>
       </c>
       <c r="N35" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O35" t="s">
         <v>465</v>
@@ -13616,7 +13614,7 @@
         <v>477</v>
       </c>
       <c r="N36" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O36" t="s">
         <v>478</v>
@@ -13682,7 +13680,7 @@
         <v>489</v>
       </c>
       <c r="N37" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O37" t="s">
         <v>490</v>
@@ -13691,7 +13689,7 @@
         <v>491</v>
       </c>
       <c r="Q37" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R37" t="s">
         <v>247</v>
@@ -13748,7 +13746,7 @@
         <v>501</v>
       </c>
       <c r="N38" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O38" t="s">
         <v>502</v>
@@ -13814,7 +13812,7 @@
         <v>512</v>
       </c>
       <c r="N39" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O39" t="s">
         <v>513</v>
@@ -13862,7 +13860,7 @@
         <v>27</v>
       </c>
       <c r="H40" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I40" t="s">
         <v>518</v>
@@ -13889,7 +13887,7 @@
         <v>524</v>
       </c>
       <c r="Q40" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R40" t="s">
         <v>247</v>
@@ -13928,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="H41" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I41" t="s">
         <v>530</v>
@@ -13944,7 +13942,7 @@
         <v>533</v>
       </c>
       <c r="N41" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O41" t="s">
         <v>534</v>
@@ -13953,7 +13951,7 @@
         <v>535</v>
       </c>
       <c r="Q41" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R41" t="s">
         <v>247</v>
@@ -13977,13 +13975,13 @@
         <v>539</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D42" t="s">
         <v>540</v>
       </c>
       <c r="E42" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F42" t="s">
         <v>541</v>
@@ -14058,7 +14056,7 @@
         <v>27</v>
       </c>
       <c r="H43" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I43" t="s">
         <v>554</v>
@@ -14074,7 +14072,7 @@
         <v>557</v>
       </c>
       <c r="N43" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O43" t="s">
         <v>558</v>
@@ -14122,7 +14120,7 @@
         <v>27</v>
       </c>
       <c r="H44" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I44" t="s">
         <v>564</v>
@@ -14138,7 +14136,7 @@
         <v>567</v>
       </c>
       <c r="N44" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O44" t="s">
         <v>568</v>
@@ -14147,7 +14145,7 @@
         <v>569</v>
       </c>
       <c r="Q44" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R44" t="s">
         <v>247</v>
@@ -14186,7 +14184,7 @@
         <v>27</v>
       </c>
       <c r="H45" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I45" t="s">
         <v>575</v>
@@ -14202,7 +14200,7 @@
         <v>578</v>
       </c>
       <c r="N45" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O45" t="s">
         <v>579</v>
@@ -14307,7 +14305,7 @@
         <v>597</v>
       </c>
       <c r="E47" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F47" t="s">
         <v>584</v>
@@ -14316,7 +14314,7 @@
         <v>27</v>
       </c>
       <c r="H47" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I47" t="s">
         <v>598</v>
@@ -14332,7 +14330,7 @@
         <v>601</v>
       </c>
       <c r="N47" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O47" t="s">
         <v>602</v>
@@ -14341,7 +14339,7 @@
         <v>603</v>
       </c>
       <c r="Q47" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R47" t="s">
         <v>247</v>
@@ -14365,7 +14363,7 @@
         <v>607</v>
       </c>
       <c r="C48" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D48" t="s">
         <v>608</v>
@@ -14396,7 +14394,7 @@
         <v>614</v>
       </c>
       <c r="N48" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O48" t="s">
         <v>615</v>
@@ -14462,7 +14460,7 @@
         <v>624</v>
       </c>
       <c r="N49" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O49" t="s">
         <v>625</v>
@@ -14528,7 +14526,7 @@
         <v>635</v>
       </c>
       <c r="N50" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O50" t="s">
         <v>636</v>
@@ -14576,7 +14574,7 @@
         <v>27</v>
       </c>
       <c r="H51" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I51" t="s">
         <v>644</v>
@@ -14592,7 +14590,7 @@
         <v>647</v>
       </c>
       <c r="N51" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O51" t="s">
         <v>648</v>
@@ -14601,7 +14599,7 @@
         <v>649</v>
       </c>
       <c r="Q51" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R51" t="s">
         <v>247</v>
@@ -14631,7 +14629,7 @@
         <v>654</v>
       </c>
       <c r="E52" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F52" t="s">
         <v>655</v>
@@ -14706,7 +14704,7 @@
         <v>27</v>
       </c>
       <c r="H53" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I53" t="s">
         <v>669</v>
@@ -14733,7 +14731,7 @@
         <v>675</v>
       </c>
       <c r="Q53" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R53" t="s">
         <v>247</v>
@@ -14763,7 +14761,7 @@
         <v>446</v>
       </c>
       <c r="E54" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F54" t="s">
         <v>680</v>
@@ -14829,7 +14827,7 @@
         <v>692</v>
       </c>
       <c r="E55" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F55" t="s">
         <v>680</v>
@@ -14838,7 +14836,7 @@
         <v>27</v>
       </c>
       <c r="H55" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I55" t="s">
         <v>693</v>
@@ -14865,7 +14863,7 @@
         <v>699</v>
       </c>
       <c r="Q55" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R55" t="s">
         <v>247</v>
@@ -14895,7 +14893,7 @@
         <v>701</v>
       </c>
       <c r="E56" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F56" t="s">
         <v>680</v>
@@ -14904,7 +14902,7 @@
         <v>27</v>
       </c>
       <c r="H56" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I56" t="s">
         <v>702</v>
@@ -14955,10 +14953,10 @@
         <v>709</v>
       </c>
       <c r="C57" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D57" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="E57" t="s">
         <v>408</v>
@@ -14970,7 +14968,7 @@
         <v>27</v>
       </c>
       <c r="H57" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I57" t="s">
         <v>710</v>
@@ -14997,7 +14995,7 @@
         <v>716</v>
       </c>
       <c r="Q57" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R57" t="s">
         <v>247</v>
@@ -15021,10 +15019,10 @@
         <v>720</v>
       </c>
       <c r="C58" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" t="s">
         <v>43</v>
-      </c>
-      <c r="D58" t="s">
-        <v>146</v>
       </c>
       <c r="E58" t="s">
         <v>408</v>
@@ -15036,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="H58" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I58" t="s">
         <v>721</v>
@@ -15063,7 +15061,7 @@
         <v>727</v>
       </c>
       <c r="Q58" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R58" t="s">
         <v>247</v>
@@ -15093,7 +15091,7 @@
         <v>729</v>
       </c>
       <c r="E59" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F59" t="s">
         <v>680</v>
@@ -15102,7 +15100,7 @@
         <v>27</v>
       </c>
       <c r="H59" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I59" t="s">
         <v>730</v>
@@ -15129,7 +15127,7 @@
         <v>736</v>
       </c>
       <c r="Q59" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R59" t="s">
         <v>247</v>
@@ -15159,7 +15157,7 @@
         <v>741</v>
       </c>
       <c r="E60" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F60" t="s">
         <v>742</v>
@@ -15186,7 +15184,7 @@
         <v>747</v>
       </c>
       <c r="N60" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O60" t="s">
         <v>748</v>
@@ -15250,7 +15248,7 @@
         <v>755</v>
       </c>
       <c r="N61" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O61" t="s">
         <v>756</v>
@@ -15259,7 +15257,7 @@
         <v>757</v>
       </c>
       <c r="Q61" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R61" t="s">
         <v>247</v>
@@ -15289,7 +15287,7 @@
         <v>446</v>
       </c>
       <c r="E62" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F62" t="s">
         <v>751</v>
@@ -15298,7 +15296,7 @@
         <v>27</v>
       </c>
       <c r="H62" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I62" t="s">
         <v>762</v>
@@ -15314,7 +15312,7 @@
         <v>765</v>
       </c>
       <c r="N62" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O62" t="s">
         <v>766</v>
@@ -15362,7 +15360,7 @@
         <v>27</v>
       </c>
       <c r="H63" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I63" t="s">
         <v>774</v>
@@ -15378,7 +15376,7 @@
         <v>777</v>
       </c>
       <c r="N63" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O63" t="s">
         <v>778</v>
@@ -15387,7 +15385,7 @@
         <v>779</v>
       </c>
       <c r="Q63" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R63" t="s">
         <v>247</v>
@@ -15426,7 +15424,7 @@
         <v>27</v>
       </c>
       <c r="H64" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I64" t="s">
         <v>784</v>
@@ -15442,7 +15440,7 @@
         <v>787</v>
       </c>
       <c r="N64" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O64" t="s">
         <v>788</v>
@@ -15451,7 +15449,7 @@
         <v>789</v>
       </c>
       <c r="Q64" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R64" t="s">
         <v>247</v>
@@ -15481,7 +15479,7 @@
         <v>794</v>
       </c>
       <c r="E65" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F65" t="s">
         <v>795</v>
@@ -15547,7 +15545,7 @@
         <v>701</v>
       </c>
       <c r="E66" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F66" t="s">
         <v>804</v>
@@ -15572,7 +15570,7 @@
         <v>808</v>
       </c>
       <c r="N66" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O66" t="s">
         <v>809</v>
@@ -15620,7 +15618,7 @@
         <v>27</v>
       </c>
       <c r="H67" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I67" t="s">
         <v>813</v>
@@ -15636,7 +15634,7 @@
         <v>816</v>
       </c>
       <c r="N67" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O67" t="s">
         <v>817</v>
@@ -15684,7 +15682,7 @@
         <v>27</v>
       </c>
       <c r="H68" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I68" t="s">
         <v>822</v>
@@ -15711,7 +15709,7 @@
         <v>828</v>
       </c>
       <c r="Q68" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R68" t="s">
         <v>247</v>
@@ -15741,7 +15739,7 @@
         <v>830</v>
       </c>
       <c r="E69" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F69" t="s">
         <v>821</v>
@@ -15750,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="H69" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I69" t="s">
         <v>831</v>
@@ -15801,13 +15799,13 @@
         <v>841</v>
       </c>
       <c r="C70" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D70" t="s">
         <v>830</v>
       </c>
       <c r="E70" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F70" t="s">
         <v>821</v>
@@ -15816,7 +15814,7 @@
         <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I70" t="s">
         <v>842</v>
@@ -15834,7 +15832,7 @@
         <v>846</v>
       </c>
       <c r="N70" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O70" t="s">
         <v>847</v>
@@ -15843,7 +15841,7 @@
         <v>848</v>
       </c>
       <c r="Q70" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R70" t="s">
         <v>247</v>
@@ -15900,7 +15898,7 @@
         <v>858</v>
       </c>
       <c r="N71" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O71" t="s">
         <v>859</v>
@@ -15909,7 +15907,7 @@
         <v>860</v>
       </c>
       <c r="Q71" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R71" t="s">
         <v>247</v>
@@ -15966,7 +15964,7 @@
         <v>868</v>
       </c>
       <c r="N72" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O72" t="s">
         <v>869</v>
@@ -15999,7 +15997,7 @@
         <v>871</v>
       </c>
       <c r="C73" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D73" t="s">
         <v>872</v>
@@ -16030,7 +16028,7 @@
         <v>878</v>
       </c>
       <c r="N73" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O73" t="s">
         <v>879</v>
@@ -16039,7 +16037,7 @@
         <v>880</v>
       </c>
       <c r="Q73" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R73" t="s">
         <v>247</v>
@@ -16063,7 +16061,7 @@
         <v>881</v>
       </c>
       <c r="C74" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D74" t="s">
         <v>882</v>
@@ -16076,7 +16074,7 @@
         <v>27</v>
       </c>
       <c r="H74" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I74" t="s">
         <v>884</v>
@@ -16130,10 +16128,10 @@
         <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="E75" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F75" t="s">
         <v>893</v>
@@ -16142,7 +16140,7 @@
         <v>27</v>
       </c>
       <c r="H75" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I75" t="s">
         <v>894</v>
@@ -16169,7 +16167,7 @@
         <v>900</v>
       </c>
       <c r="Q75" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R75" t="s">
         <v>247</v>
@@ -16193,13 +16191,13 @@
         <v>904</v>
       </c>
       <c r="C76" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D76" t="s">
         <v>446</v>
       </c>
       <c r="E76" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F76" t="s">
         <v>905</v>
@@ -16226,7 +16224,7 @@
         <v>910</v>
       </c>
       <c r="N76" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O76" t="s">
         <v>911</v>
@@ -16262,7 +16260,7 @@
         <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E77" t="s">
         <v>382</v>
@@ -16292,7 +16290,7 @@
         <v>918</v>
       </c>
       <c r="N77" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O77" t="s">
         <v>919</v>
@@ -16325,13 +16323,13 @@
         <v>924</v>
       </c>
       <c r="C78" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D78" t="s">
         <v>925</v>
       </c>
       <c r="E78" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F78" t="s">
         <v>926</v>
@@ -16358,7 +16356,7 @@
         <v>931</v>
       </c>
       <c r="N78" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O78" t="s">
         <v>932</v>
@@ -16397,7 +16395,7 @@
         <v>935</v>
       </c>
       <c r="E79" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F79" t="s">
         <v>936</v>
@@ -16406,7 +16404,7 @@
         <v>27</v>
       </c>
       <c r="H79" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I79" t="s">
         <v>937</v>
@@ -16422,7 +16420,7 @@
         <v>940</v>
       </c>
       <c r="N79" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O79" t="s">
         <v>941</v>
@@ -16431,7 +16429,7 @@
         <v>942</v>
       </c>
       <c r="Q79" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R79" t="s">
         <v>247</v>
@@ -16470,7 +16468,7 @@
         <v>27</v>
       </c>
       <c r="H80" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I80" t="s">
         <v>948</v>
@@ -16486,7 +16484,7 @@
         <v>951</v>
       </c>
       <c r="N80" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O80" t="s">
         <v>952</v>
@@ -16495,20 +16493,20 @@
         <v>953</v>
       </c>
       <c r="Q80" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R80" t="s">
         <v>247</v>
       </c>
       <c r="S80"/>
       <c r="T80" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="U80" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="V80" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81">
@@ -16525,7 +16523,7 @@
         <v>265</v>
       </c>
       <c r="E81" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F81" t="s">
         <v>955</v>
@@ -16534,7 +16532,7 @@
         <v>27</v>
       </c>
       <c r="H81" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I81" t="s">
         <v>956</v>
@@ -16552,7 +16550,7 @@
         <v>960</v>
       </c>
       <c r="N81" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O81" t="s">
         <v>961</v>
@@ -16561,7 +16559,7 @@
         <v>962</v>
       </c>
       <c r="Q81" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R81" t="s">
         <v>247</v>
@@ -16591,7 +16589,7 @@
         <v>967</v>
       </c>
       <c r="E82" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F82" t="s">
         <v>968</v>
@@ -16600,7 +16598,7 @@
         <v>27</v>
       </c>
       <c r="H82" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I82" t="s">
         <v>969</v>
@@ -16618,7 +16616,7 @@
         <v>973</v>
       </c>
       <c r="N82" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O82" t="s">
         <v>974</v>
@@ -16657,7 +16655,7 @@
         <v>980</v>
       </c>
       <c r="E83" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F83" t="s">
         <v>981</v>
@@ -16666,7 +16664,7 @@
         <v>27</v>
       </c>
       <c r="H83" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I83" t="s">
         <v>982</v>
@@ -16684,7 +16682,7 @@
         <v>986</v>
       </c>
       <c r="N83" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O83" t="s">
         <v>987</v>
@@ -16693,7 +16691,7 @@
         <v>988</v>
       </c>
       <c r="Q83" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R83" t="s">
         <v>247</v>
@@ -16723,7 +16721,7 @@
         <v>993</v>
       </c>
       <c r="E84" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F84" t="s">
         <v>994</v>
@@ -16750,7 +16748,7 @@
         <v>999</v>
       </c>
       <c r="N84" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O84" t="s">
         <v>1000</v>
@@ -16783,7 +16781,7 @@
         <v>1005</v>
       </c>
       <c r="C85" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D85" t="s">
         <v>1006</v>
@@ -16814,7 +16812,7 @@
         <v>1012</v>
       </c>
       <c r="N85" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O85" t="s">
         <v>1013</v>
@@ -16823,7 +16821,7 @@
         <v>1014</v>
       </c>
       <c r="Q85" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R85" t="s">
         <v>247</v>
@@ -16853,7 +16851,7 @@
         <v>1019</v>
       </c>
       <c r="E86" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F86" t="s">
         <v>1020</v>
@@ -16862,7 +16860,7 @@
         <v>27</v>
       </c>
       <c r="H86" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I86" t="s">
         <v>1021</v>
@@ -16880,7 +16878,7 @@
         <v>1025</v>
       </c>
       <c r="N86" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O86" t="s">
         <v>1026</v>
@@ -16889,7 +16887,7 @@
         <v>1027</v>
       </c>
       <c r="Q86" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R86" t="s">
         <v>247</v>
@@ -16913,7 +16911,7 @@
         <v>319</v>
       </c>
       <c r="E87" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F87" t="s">
         <v>1029</v>
@@ -16922,7 +16920,7 @@
         <v>27</v>
       </c>
       <c r="H87" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I87" t="s">
         <v>1030</v>
@@ -16938,7 +16936,7 @@
         <v>1033</v>
       </c>
       <c r="N87" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O87" t="s">
         <v>1034</v>
@@ -16947,7 +16945,7 @@
         <v>1035</v>
       </c>
       <c r="Q87" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R87" t="s">
         <v>247</v>
@@ -16971,13 +16969,13 @@
         <v>1039</v>
       </c>
       <c r="C88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D88" t="s">
         <v>597</v>
       </c>
       <c r="E88" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F88" t="s">
         <v>1040</v>
@@ -17004,7 +17002,7 @@
         <v>1045</v>
       </c>
       <c r="N88" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O88" t="s">
         <v>1046</v>
@@ -17013,7 +17011,7 @@
         <v>1047</v>
       </c>
       <c r="Q88" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R88" t="s">
         <v>247</v>
@@ -17043,7 +17041,7 @@
         <v>319</v>
       </c>
       <c r="E89" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F89" t="s">
         <v>1040</v>
@@ -17052,7 +17050,7 @@
         <v>27</v>
       </c>
       <c r="H89" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I89" t="s">
         <v>1049</v>
@@ -17070,7 +17068,7 @@
         <v>1053</v>
       </c>
       <c r="N89" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O89" t="s">
         <v>1054</v>
@@ -17079,7 +17077,7 @@
         <v>1055</v>
       </c>
       <c r="Q89" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R89" t="s">
         <v>247</v>
@@ -17109,7 +17107,7 @@
         <v>1057</v>
       </c>
       <c r="E90" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F90" t="s">
         <v>1058</v>
@@ -17136,7 +17134,7 @@
         <v>1063</v>
       </c>
       <c r="N90" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O90" t="s">
         <v>1064</v>
@@ -17145,7 +17143,7 @@
         <v>1065</v>
       </c>
       <c r="Q90" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R90" t="s">
         <v>247</v>
@@ -17169,7 +17167,7 @@
         <v>1069</v>
       </c>
       <c r="C91" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D91" t="s">
         <v>1070</v>
@@ -17211,7 +17209,7 @@
         <v>1078</v>
       </c>
       <c r="Q91" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R91" t="s">
         <v>247</v>
@@ -17235,13 +17233,13 @@
         <v>1082</v>
       </c>
       <c r="C92" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D92" t="s">
         <v>1083</v>
       </c>
       <c r="E92" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F92" t="s">
         <v>1071</v>
@@ -17250,7 +17248,7 @@
         <v>161</v>
       </c>
       <c r="H92" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I92" t="s">
         <v>1084</v>
@@ -17268,7 +17266,7 @@
         <v>1088</v>
       </c>
       <c r="N92" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O92" t="s">
         <v>1089</v>
@@ -17277,7 +17275,7 @@
         <v>1090</v>
       </c>
       <c r="Q92" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R92" t="s">
         <v>247</v>
@@ -17301,10 +17299,10 @@
         <v>1094</v>
       </c>
       <c r="C93" t="s">
+        <v>75</v>
+      </c>
+      <c r="D93" t="s">
         <v>43</v>
-      </c>
-      <c r="D93" t="s">
-        <v>146</v>
       </c>
       <c r="E93" t="s">
         <v>408</v>
@@ -17316,7 +17314,7 @@
         <v>27</v>
       </c>
       <c r="H93" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I93" t="s">
         <v>1096</v>
@@ -17334,7 +17332,7 @@
         <v>1100</v>
       </c>
       <c r="N93" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O93" t="s">
         <v>1101</v>
@@ -17343,20 +17341,20 @@
         <v>1102</v>
       </c>
       <c r="Q93" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R93" t="s">
         <v>247</v>
       </c>
       <c r="S93"/>
       <c r="T93" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="U93" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="V93" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="94">
@@ -17367,7 +17365,7 @@
         <v>1103</v>
       </c>
       <c r="C94" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D94" t="s">
         <v>1104</v>
@@ -17382,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="H94" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I94" t="s">
         <v>1105</v>
@@ -17400,7 +17398,7 @@
         <v>1109</v>
       </c>
       <c r="N94" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O94" t="s">
         <v>1110</v>
@@ -17409,7 +17407,7 @@
         <v>1111</v>
       </c>
       <c r="Q94" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R94" t="s">
         <v>247</v>
@@ -17439,7 +17437,7 @@
         <v>701</v>
       </c>
       <c r="E95" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F95" t="s">
         <v>1095</v>
@@ -17448,7 +17446,7 @@
         <v>27</v>
       </c>
       <c r="H95" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I95" t="s">
         <v>1116</v>
@@ -17466,7 +17464,7 @@
         <v>1120</v>
       </c>
       <c r="N95" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O95" t="s">
         <v>1121</v>
@@ -17475,7 +17473,7 @@
         <v>1122</v>
       </c>
       <c r="Q95" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R95" t="s">
         <v>247</v>
@@ -17499,7 +17497,7 @@
         <v>1126</v>
       </c>
       <c r="C96" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D96" t="s">
         <v>1127</v>
@@ -17532,7 +17530,7 @@
         <v>1132</v>
       </c>
       <c r="N96" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O96" t="s">
         <v>1133</v>
@@ -17580,7 +17578,7 @@
         <v>27</v>
       </c>
       <c r="H97" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I97" t="s">
         <v>1141</v>
@@ -17598,7 +17596,7 @@
         <v>1145</v>
       </c>
       <c r="N97" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O97" t="s">
         <v>1146</v>
@@ -17634,7 +17632,7 @@
         <v>23</v>
       </c>
       <c r="D98" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E98" t="s">
         <v>382</v>
@@ -17646,7 +17644,7 @@
         <v>27</v>
       </c>
       <c r="H98" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I98" t="s">
         <v>1153</v>
@@ -17664,7 +17662,7 @@
         <v>1157</v>
       </c>
       <c r="N98" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O98" t="s">
         <v>1158</v>
@@ -17673,7 +17671,7 @@
         <v>1159</v>
       </c>
       <c r="Q98" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R98" t="s">
         <v>247</v>
@@ -17703,7 +17701,7 @@
         <v>1164</v>
       </c>
       <c r="E99" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F99" t="s">
         <v>1152</v>
@@ -17730,7 +17728,7 @@
         <v>1169</v>
       </c>
       <c r="N99" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O99" t="s">
         <v>1170</v>
@@ -17739,7 +17737,7 @@
         <v>1171</v>
       </c>
       <c r="Q99" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R99" t="s">
         <v>247</v>
@@ -17778,7 +17776,7 @@
         <v>27</v>
       </c>
       <c r="H100" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I100" t="s">
         <v>1176</v>
@@ -17796,7 +17794,7 @@
         <v>1180</v>
       </c>
       <c r="N100" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O100" t="s">
         <v>1181</v>
@@ -17805,7 +17803,7 @@
         <v>1182</v>
       </c>
       <c r="Q100" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R100" t="s">
         <v>247</v>
@@ -17835,7 +17833,7 @@
         <v>1184</v>
       </c>
       <c r="E101" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F101" t="s">
         <v>1152</v>
@@ -17844,7 +17842,7 @@
         <v>27</v>
       </c>
       <c r="H101" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I101" t="s">
         <v>1185</v>
@@ -17862,7 +17860,7 @@
         <v>1189</v>
       </c>
       <c r="N101" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O101" t="s">
         <v>1190</v>
@@ -17895,13 +17893,13 @@
         <v>1192</v>
       </c>
       <c r="C102" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D102" t="s">
         <v>1193</v>
       </c>
       <c r="E102" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F102" t="s">
         <v>1194</v>
@@ -17910,7 +17908,7 @@
         <v>27</v>
       </c>
       <c r="H102" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I102" t="s">
         <v>1195</v>
@@ -17928,7 +17926,7 @@
         <v>1199</v>
       </c>
       <c r="N102" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O102" t="s">
         <v>1200</v>
@@ -17937,7 +17935,7 @@
         <v>1201</v>
       </c>
       <c r="Q102" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R102" t="s">
         <v>247</v>
@@ -17961,7 +17959,7 @@
         <v>1205</v>
       </c>
       <c r="C103" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D103" t="s">
         <v>213</v>
@@ -17976,7 +17974,7 @@
         <v>27</v>
       </c>
       <c r="H103" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I103" t="s">
         <v>1207</v>
@@ -17994,7 +17992,7 @@
         <v>1211</v>
       </c>
       <c r="N103" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O103" t="s">
         <v>1212</v>
@@ -18003,7 +18001,7 @@
         <v>1213</v>
       </c>
       <c r="Q103" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R103" t="s">
         <v>247</v>
@@ -18027,7 +18025,7 @@
         <v>1217</v>
       </c>
       <c r="C104" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D104" t="s">
         <v>213</v>
@@ -18042,7 +18040,7 @@
         <v>27</v>
       </c>
       <c r="H104" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I104" t="s">
         <v>1218</v>
@@ -18060,7 +18058,7 @@
         <v>1222</v>
       </c>
       <c r="N104" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O104" t="s">
         <v>1223</v>
@@ -18069,7 +18067,7 @@
         <v>1224</v>
       </c>
       <c r="Q104" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R104" t="s">
         <v>247</v>
@@ -18108,7 +18106,7 @@
         <v>27</v>
       </c>
       <c r="H105" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I105" t="s">
         <v>1231</v>
@@ -18126,7 +18124,7 @@
         <v>1235</v>
       </c>
       <c r="N105" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O105" t="s">
         <v>1236</v>
@@ -18135,7 +18133,7 @@
         <v>1237</v>
       </c>
       <c r="Q105" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R105" t="s">
         <v>247</v>
@@ -18165,7 +18163,7 @@
         <v>830</v>
       </c>
       <c r="E106" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F106" t="s">
         <v>1230</v>
@@ -18174,7 +18172,7 @@
         <v>27</v>
       </c>
       <c r="H106" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I106" t="s">
         <v>1242</v>
@@ -18192,7 +18190,7 @@
         <v>1246</v>
       </c>
       <c r="N106" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O106" t="s">
         <v>1247</v>
@@ -18225,13 +18223,13 @@
         <v>1252</v>
       </c>
       <c r="C107" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D107" t="s">
         <v>446</v>
       </c>
       <c r="E107" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F107" t="s">
         <v>1230</v>
@@ -18258,7 +18256,7 @@
         <v>1257</v>
       </c>
       <c r="N107" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O107" t="s">
         <v>1258</v>
@@ -18274,13 +18272,13 @@
       </c>
       <c r="S107"/>
       <c r="T107" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="U107" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="V107" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="108">
@@ -18306,7 +18304,7 @@
         <v>27</v>
       </c>
       <c r="H108" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I108" t="s">
         <v>1263</v>
@@ -18324,7 +18322,7 @@
         <v>1267</v>
       </c>
       <c r="N108" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O108" t="s">
         <v>1268</v>
@@ -18357,13 +18355,13 @@
         <v>1273</v>
       </c>
       <c r="C109" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D109" t="s">
         <v>967</v>
       </c>
       <c r="E109" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F109" t="s">
         <v>1262</v>
@@ -18372,7 +18370,7 @@
         <v>27</v>
       </c>
       <c r="H109" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I109" t="s">
         <v>1274</v>
@@ -18390,7 +18388,7 @@
         <v>1278</v>
       </c>
       <c r="N109" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O109" t="s">
         <v>1279</v>
@@ -18429,7 +18427,7 @@
         <v>967</v>
       </c>
       <c r="E110" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F110" t="s">
         <v>1262</v>
@@ -18438,7 +18436,7 @@
         <v>27</v>
       </c>
       <c r="H110" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I110" t="s">
         <v>1285</v>
@@ -18456,7 +18454,7 @@
         <v>1289</v>
       </c>
       <c r="N110" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O110" t="s">
         <v>1290</v>
@@ -18504,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="H111" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I111" t="s">
         <v>1294</v>
@@ -18522,7 +18520,7 @@
         <v>1298</v>
       </c>
       <c r="N111" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O111" t="s">
         <v>1299</v>
@@ -18531,7 +18529,7 @@
         <v>1300</v>
       </c>
       <c r="Q111" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R111" t="s">
         <v>247</v>
@@ -18555,13 +18553,13 @@
         <v>1301</v>
       </c>
       <c r="C112" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D112" t="s">
         <v>1302</v>
       </c>
       <c r="E112" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F112" t="s">
         <v>1293</v>
@@ -18597,7 +18595,7 @@
         <v>1309</v>
       </c>
       <c r="Q112" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R112" t="s">
         <v>247</v>
@@ -18636,7 +18634,7 @@
         <v>27</v>
       </c>
       <c r="H113" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I113" t="s">
         <v>1312</v>
@@ -18652,7 +18650,7 @@
         <v>1315</v>
       </c>
       <c r="N113" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O113" t="s">
         <v>1316</v>
@@ -18661,7 +18659,7 @@
         <v>1317</v>
       </c>
       <c r="Q113" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R113" t="s">
         <v>247</v>
@@ -18691,7 +18689,7 @@
         <v>1057</v>
       </c>
       <c r="E114" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F114" t="s">
         <v>1311</v>
@@ -18716,7 +18714,7 @@
         <v>1325</v>
       </c>
       <c r="N114" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O114" t="s">
         <v>1326</v>
@@ -18725,7 +18723,7 @@
         <v>1327</v>
       </c>
       <c r="Q114" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R114" t="s">
         <v>247</v>
@@ -18755,7 +18753,7 @@
         <v>1332</v>
       </c>
       <c r="E115" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F115" t="s">
         <v>1333</v>
@@ -18764,7 +18762,7 @@
         <v>27</v>
       </c>
       <c r="H115" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I115" t="s">
         <v>1334</v>
@@ -18782,7 +18780,7 @@
         <v>1338</v>
       </c>
       <c r="N115" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O115" t="s">
         <v>1339</v>
@@ -18791,7 +18789,7 @@
         <v>1340</v>
       </c>
       <c r="Q115" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R115" t="s">
         <v>247</v>
@@ -18830,7 +18828,7 @@
         <v>27</v>
       </c>
       <c r="H116" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I116" t="s">
         <v>1345</v>
@@ -18848,7 +18846,7 @@
         <v>1349</v>
       </c>
       <c r="N116" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O116" t="s">
         <v>1350</v>
@@ -18857,7 +18855,7 @@
         <v>1351</v>
       </c>
       <c r="Q116" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R116" t="s">
         <v>247</v>
@@ -18914,7 +18912,7 @@
         <v>1359</v>
       </c>
       <c r="N117" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O117" t="s">
         <v>1360</v>
@@ -18962,7 +18960,7 @@
         <v>27</v>
       </c>
       <c r="H118" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I118" t="s">
         <v>1364</v>
@@ -18980,7 +18978,7 @@
         <v>1368</v>
       </c>
       <c r="N118" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O118" t="s">
         <v>1369</v>
@@ -19013,13 +19011,13 @@
         <v>1374</v>
       </c>
       <c r="C119" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D119" t="s">
         <v>1375</v>
       </c>
       <c r="E119" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F119" t="s">
         <v>1376</v>
@@ -19028,7 +19026,7 @@
         <v>27</v>
       </c>
       <c r="H119" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I119" t="s">
         <v>1377</v>
@@ -19079,7 +19077,7 @@
         <v>1387</v>
       </c>
       <c r="C120" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D120" t="s">
         <v>1388</v>
@@ -19092,7 +19090,7 @@
         <v>27</v>
       </c>
       <c r="H120" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I120" t="s">
         <v>1389</v>
@@ -19110,7 +19108,7 @@
         <v>1393</v>
       </c>
       <c r="N120" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O120" t="s">
         <v>1394</v>
@@ -19158,7 +19156,7 @@
         <v>27</v>
       </c>
       <c r="H121" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I121" t="s">
         <v>1399</v>
@@ -19174,7 +19172,7 @@
         <v>1402</v>
       </c>
       <c r="N121" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O121" t="s">
         <v>1403</v>
@@ -19183,7 +19181,7 @@
         <v>1404</v>
       </c>
       <c r="Q121" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R121" t="s">
         <v>247</v>
@@ -19213,7 +19211,7 @@
         <v>1409</v>
       </c>
       <c r="E122" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F122" t="s">
         <v>1410</v>
@@ -19222,7 +19220,7 @@
         <v>27</v>
       </c>
       <c r="H122" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I122" t="s">
         <v>1411</v>
@@ -19238,7 +19236,7 @@
         <v>1414</v>
       </c>
       <c r="N122" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O122" t="s">
         <v>1415</v>
@@ -19247,7 +19245,7 @@
         <v>1416</v>
       </c>
       <c r="Q122" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R122" t="s">
         <v>247</v>
@@ -19271,13 +19269,13 @@
         <v>1417</v>
       </c>
       <c r="C123" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D123" t="s">
         <v>1418</v>
       </c>
       <c r="E123" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F123" t="s">
         <v>1419</v>
@@ -19286,7 +19284,7 @@
         <v>27</v>
       </c>
       <c r="H123" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I123" t="s">
         <v>1420</v>
@@ -19304,7 +19302,7 @@
         <v>1424</v>
       </c>
       <c r="N123" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O123" t="s">
         <v>1425</v>
@@ -19313,7 +19311,7 @@
         <v>1426</v>
       </c>
       <c r="Q123" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R123" t="s">
         <v>247</v>
@@ -19343,7 +19341,7 @@
         <v>729</v>
       </c>
       <c r="E124" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F124" t="s">
         <v>1431</v>
@@ -19352,7 +19350,7 @@
         <v>27</v>
       </c>
       <c r="H124" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I124" t="s">
         <v>1432</v>
@@ -19370,7 +19368,7 @@
         <v>1436</v>
       </c>
       <c r="N124" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O124" t="s">
         <v>1437</v>
@@ -19434,7 +19432,7 @@
         <v>1449</v>
       </c>
       <c r="N125" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O125" t="s">
         <v>1450</v>
@@ -19443,7 +19441,7 @@
         <v>1451</v>
       </c>
       <c r="Q125" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R125" t="s">
         <v>247</v>
@@ -19473,7 +19471,7 @@
         <v>1193</v>
       </c>
       <c r="E126" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F126" t="s">
         <v>1456</v>
@@ -19482,7 +19480,7 @@
         <v>27</v>
       </c>
       <c r="H126" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I126" t="s">
         <v>1457</v>
@@ -19498,7 +19496,7 @@
         <v>1460</v>
       </c>
       <c r="N126" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O126" t="s">
         <v>1461</v>
@@ -19507,7 +19505,7 @@
         <v>1462</v>
       </c>
       <c r="Q126" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R126" t="s">
         <v>247</v>
@@ -19564,7 +19562,7 @@
         <v>1473</v>
       </c>
       <c r="N127" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O127" t="s">
         <v>1474</v>
@@ -19573,7 +19571,7 @@
         <v>1475</v>
       </c>
       <c r="Q127" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R127" t="s">
         <v>247</v>
@@ -19603,7 +19601,7 @@
         <v>1480</v>
       </c>
       <c r="E128" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F128" t="s">
         <v>1481</v>
@@ -19612,7 +19610,7 @@
         <v>27</v>
       </c>
       <c r="H128" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I128" t="s">
         <v>1482</v>
@@ -19630,7 +19628,7 @@
         <v>1486</v>
       </c>
       <c r="N128" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O128" t="s">
         <v>1487</v>
@@ -19678,7 +19676,7 @@
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I129" t="s">
         <v>1495</v>
@@ -19694,7 +19692,7 @@
         <v>1498</v>
       </c>
       <c r="N129" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O129" t="s">
         <v>1499</v>
@@ -19733,7 +19731,7 @@
         <v>1505</v>
       </c>
       <c r="E130" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F130" t="s">
         <v>1506</v>
@@ -19760,7 +19758,7 @@
         <v>1511</v>
       </c>
       <c r="N130" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O130" t="s">
         <v>1512</v>
@@ -19826,7 +19824,7 @@
         <v>1524</v>
       </c>
       <c r="N131" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O131" t="s">
         <v>1525</v>
@@ -19835,7 +19833,7 @@
         <v>1526</v>
       </c>
       <c r="Q131" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R131" t="s">
         <v>247</v>
@@ -19874,7 +19872,7 @@
         <v>27</v>
       </c>
       <c r="H132" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I132" t="s">
         <v>1531</v>
@@ -19892,7 +19890,7 @@
         <v>1535</v>
       </c>
       <c r="N132" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O132" t="s">
         <v>1536</v>
@@ -19901,7 +19899,7 @@
         <v>1537</v>
       </c>
       <c r="Q132" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R132" t="s">
         <v>247</v>
@@ -19931,7 +19929,7 @@
         <v>1539</v>
       </c>
       <c r="E133" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F133" t="s">
         <v>1518</v>
@@ -19940,7 +19938,7 @@
         <v>27</v>
       </c>
       <c r="H133" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I133" t="s">
         <v>1540</v>
@@ -19958,7 +19956,7 @@
         <v>1544</v>
       </c>
       <c r="N133" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O133" t="s">
         <v>1545</v>
@@ -19967,7 +19965,7 @@
         <v>1546</v>
       </c>
       <c r="Q133" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R133" t="s">
         <v>247</v>
@@ -19991,7 +19989,7 @@
         <v>1550</v>
       </c>
       <c r="C134" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D134" t="s">
         <v>1551</v>
@@ -20024,7 +20022,7 @@
         <v>1557</v>
       </c>
       <c r="N134" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O134" t="s">
         <v>1558</v>
@@ -20063,7 +20061,7 @@
         <v>1564</v>
       </c>
       <c r="E135" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F135" t="s">
         <v>1552</v>
@@ -20072,7 +20070,7 @@
         <v>27</v>
       </c>
       <c r="H135" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I135" t="s">
         <v>1565</v>
@@ -20088,7 +20086,7 @@
         <v>1568</v>
       </c>
       <c r="N135" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O135" t="s">
         <v>1569</v>
@@ -20124,10 +20122,10 @@
         <v>187</v>
       </c>
       <c r="D136" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E136" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F136" t="s">
         <v>1575</v>
@@ -20136,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="H136" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I136" t="s">
         <v>1576</v>
@@ -20152,7 +20150,7 @@
         <v>1579</v>
       </c>
       <c r="N136" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O136" t="s">
         <v>1580</v>
@@ -20161,7 +20159,7 @@
         <v>1581</v>
       </c>
       <c r="Q136" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R136" t="s">
         <v>247</v>
@@ -20185,7 +20183,7 @@
         <v>1582</v>
       </c>
       <c r="C137" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D137" t="s">
         <v>872</v>
@@ -20264,7 +20262,7 @@
         <v>27</v>
       </c>
       <c r="H138" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I138" t="s">
         <v>1594</v>
@@ -20282,7 +20280,7 @@
         <v>1598</v>
       </c>
       <c r="N138" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O138" t="s">
         <v>1599</v>
@@ -20291,7 +20289,7 @@
         <v>1600</v>
       </c>
       <c r="Q138" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R138" t="s">
         <v>247</v>
@@ -20315,13 +20313,13 @@
         <v>1604</v>
       </c>
       <c r="C139" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D139" t="s">
         <v>967</v>
       </c>
       <c r="E139" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F139" t="s">
         <v>1605</v>
@@ -20330,7 +20328,7 @@
         <v>27</v>
       </c>
       <c r="H139" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I139" t="s">
         <v>1606</v>
@@ -20348,7 +20346,7 @@
         <v>1610</v>
       </c>
       <c r="N139" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O139" t="s">
         <v>1611</v>
@@ -20357,7 +20355,7 @@
         <v>1612</v>
       </c>
       <c r="Q139" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R139" t="s">
         <v>247</v>
@@ -20381,13 +20379,13 @@
         <v>1616</v>
       </c>
       <c r="C140" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D140" t="s">
         <v>1480</v>
       </c>
       <c r="E140" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F140" t="s">
         <v>1605</v>
@@ -20396,7 +20394,7 @@
         <v>27</v>
       </c>
       <c r="H140" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I140" t="s">
         <v>1617</v>
@@ -20414,7 +20412,7 @@
         <v>1621</v>
       </c>
       <c r="N140" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O140" t="s">
         <v>1622</v>
@@ -20453,7 +20451,7 @@
         <v>1628</v>
       </c>
       <c r="E141" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F141" t="s">
         <v>1605</v>
@@ -20480,7 +20478,7 @@
         <v>1633</v>
       </c>
       <c r="N141" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O141" t="s">
         <v>1634</v>
@@ -20489,7 +20487,7 @@
         <v>1635</v>
       </c>
       <c r="Q141" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R141" t="s">
         <v>247</v>
@@ -20513,13 +20511,13 @@
         <v>1639</v>
       </c>
       <c r="C142" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D142" t="s">
         <v>1640</v>
       </c>
       <c r="E142" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F142" t="s">
         <v>1641</v>
@@ -20528,7 +20526,7 @@
         <v>161</v>
       </c>
       <c r="H142" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I142" t="s">
         <v>1642</v>
@@ -20594,7 +20592,7 @@
         <v>27</v>
       </c>
       <c r="H143" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I143" t="s">
         <v>1654</v>
@@ -20612,7 +20610,7 @@
         <v>1658</v>
       </c>
       <c r="N143" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O143" t="s">
         <v>1659</v>
@@ -20621,7 +20619,7 @@
         <v>1660</v>
       </c>
       <c r="Q143" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R143" t="s">
         <v>247</v>
@@ -20651,7 +20649,7 @@
         <v>1302</v>
       </c>
       <c r="E144" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F144" t="s">
         <v>1665</v>
@@ -20678,7 +20676,7 @@
         <v>1670</v>
       </c>
       <c r="N144" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O144" t="s">
         <v>1671</v>
@@ -20687,7 +20685,7 @@
         <v>1672</v>
       </c>
       <c r="Q144" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R144" t="s">
         <v>247</v>
@@ -20717,7 +20715,7 @@
         <v>935</v>
       </c>
       <c r="E145" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F145" t="s">
         <v>1674</v>
@@ -20726,7 +20724,7 @@
         <v>27</v>
       </c>
       <c r="H145" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I145" t="s">
         <v>1675</v>
@@ -20744,7 +20742,7 @@
         <v>1679</v>
       </c>
       <c r="N145" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O145" t="s">
         <v>1680</v>
@@ -20753,7 +20751,7 @@
         <v>1681</v>
       </c>
       <c r="Q145" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R145" t="s">
         <v>247</v>
@@ -20783,7 +20781,7 @@
         <v>1683</v>
       </c>
       <c r="E146" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F146" t="s">
         <v>1684</v>
@@ -20792,7 +20790,7 @@
         <v>27</v>
       </c>
       <c r="H146" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I146" t="s">
         <v>1685</v>
@@ -20808,7 +20806,7 @@
         <v>1688</v>
       </c>
       <c r="N146" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O146" t="s">
         <v>1689</v>
@@ -20817,7 +20815,7 @@
         <v>1690</v>
       </c>
       <c r="Q146" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R146" t="s">
         <v>247</v>
@@ -20847,7 +20845,7 @@
         <v>1683</v>
       </c>
       <c r="E147" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F147" t="s">
         <v>1684</v>
@@ -20856,7 +20854,7 @@
         <v>27</v>
       </c>
       <c r="H147" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I147" t="s">
         <v>1692</v>
@@ -20872,7 +20870,7 @@
         <v>1695</v>
       </c>
       <c r="N147" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O147" t="s">
         <v>1696</v>
@@ -20881,7 +20879,7 @@
         <v>1697</v>
       </c>
       <c r="Q147" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R147" t="s">
         <v>247</v>
@@ -20938,7 +20936,7 @@
         <v>1704</v>
       </c>
       <c r="N148" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O148" t="s">
         <v>1705</v>
@@ -20947,7 +20945,7 @@
         <v>1706</v>
       </c>
       <c r="Q148" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R148" t="s">
         <v>247</v>
@@ -20971,7 +20969,7 @@
         <v>1710</v>
       </c>
       <c r="C149" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D149" t="s">
         <v>1711</v>
@@ -20986,7 +20984,7 @@
         <v>27</v>
       </c>
       <c r="H149" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I149" t="s">
         <v>1712</v>
@@ -21004,7 +21002,7 @@
         <v>1716</v>
       </c>
       <c r="N149" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O149" t="s">
         <v>1717</v>
@@ -21013,7 +21011,7 @@
         <v>1718</v>
       </c>
       <c r="Q149" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R149" t="s">
         <v>247</v>
@@ -21037,10 +21035,10 @@
         <v>1722</v>
       </c>
       <c r="C150" t="s">
+        <v>75</v>
+      </c>
+      <c r="D150" t="s">
         <v>43</v>
-      </c>
-      <c r="D150" t="s">
-        <v>146</v>
       </c>
       <c r="E150" t="s">
         <v>408</v>
@@ -21070,7 +21068,7 @@
         <v>1727</v>
       </c>
       <c r="N150" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O150" t="s">
         <v>1728</v>
@@ -21079,7 +21077,7 @@
         <v>1729</v>
       </c>
       <c r="Q150" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R150" t="s">
         <v>247</v>
@@ -21136,7 +21134,7 @@
         <v>1739</v>
       </c>
       <c r="N151" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O151" t="s">
         <v>1740</v>
@@ -21145,7 +21143,7 @@
         <v>1741</v>
       </c>
       <c r="Q151" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R151" t="s">
         <v>247</v>
@@ -21202,7 +21200,7 @@
         <v>1748</v>
       </c>
       <c r="N152" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O152" t="s">
         <v>1749</v>
@@ -21211,7 +21209,7 @@
         <v>1750</v>
       </c>
       <c r="Q152" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R152" t="s">
         <v>247</v>
@@ -21268,7 +21266,7 @@
         <v>1760</v>
       </c>
       <c r="N153" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O153" t="s">
         <v>1761</v>
@@ -21277,7 +21275,7 @@
         <v>1762</v>
       </c>
       <c r="Q153" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R153" t="s">
         <v>247</v>
@@ -21301,7 +21299,7 @@
         <v>1766</v>
       </c>
       <c r="C154" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D154" t="s">
         <v>1767</v>
@@ -21316,7 +21314,7 @@
         <v>27</v>
       </c>
       <c r="H154" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I154" t="s">
         <v>1768</v>
@@ -21334,7 +21332,7 @@
         <v>1772</v>
       </c>
       <c r="N154" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O154" t="s">
         <v>1773</v>
@@ -21382,7 +21380,7 @@
         <v>27</v>
       </c>
       <c r="H155" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I155" t="s">
         <v>1777</v>
@@ -21400,7 +21398,7 @@
         <v>1781</v>
       </c>
       <c r="N155" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O155" t="s">
         <v>1782</v>
@@ -21409,7 +21407,7 @@
         <v>1783</v>
       </c>
       <c r="Q155" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R155" t="s">
         <v>247</v>
@@ -21464,7 +21462,7 @@
         <v>1793</v>
       </c>
       <c r="N156" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O156" t="s">
         <v>1794</v>
@@ -21500,7 +21498,7 @@
         <v>187</v>
       </c>
       <c r="D157" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="E157" t="s">
         <v>408</v>
@@ -21528,7 +21526,7 @@
         <v>1804</v>
       </c>
       <c r="N157" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O157" t="s">
         <v>1805</v>
@@ -21537,7 +21535,7 @@
         <v>1806</v>
       </c>
       <c r="Q157" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R157" t="s">
         <v>247</v>
@@ -21592,7 +21590,7 @@
         <v>1811</v>
       </c>
       <c r="N158" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O158" t="s">
         <v>1812</v>
@@ -21601,7 +21599,7 @@
         <v>1813</v>
       </c>
       <c r="Q158" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R158" t="s">
         <v>247</v>
@@ -21625,7 +21623,7 @@
         <v>1814</v>
       </c>
       <c r="C159" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D159" t="s">
         <v>1815</v>
@@ -21665,7 +21663,7 @@
         <v>1824</v>
       </c>
       <c r="Q159" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R159" t="s">
         <v>247</v>
@@ -21689,7 +21687,7 @@
         <v>1825</v>
       </c>
       <c r="C160" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D160" t="s">
         <v>608</v>
@@ -21702,7 +21700,7 @@
         <v>27</v>
       </c>
       <c r="H160" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I160" t="s">
         <v>1827</v>
@@ -21720,7 +21718,7 @@
         <v>1831</v>
       </c>
       <c r="N160" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O160" t="s">
         <v>1832</v>
@@ -21729,7 +21727,7 @@
         <v>1833</v>
       </c>
       <c r="Q160" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R160" t="s">
         <v>247</v>
@@ -21759,7 +21757,7 @@
         <v>1683</v>
       </c>
       <c r="E161" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F161" t="s">
         <v>1838</v>
@@ -21768,7 +21766,7 @@
         <v>27</v>
       </c>
       <c r="H161" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I161" t="s">
         <v>1839</v>
@@ -21786,7 +21784,7 @@
         <v>1843</v>
       </c>
       <c r="N161" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O161" t="s">
         <v>1844</v>
@@ -21819,7 +21817,7 @@
         <v>1849</v>
       </c>
       <c r="C162" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D162" t="s">
         <v>1104</v>
@@ -21834,7 +21832,7 @@
         <v>27</v>
       </c>
       <c r="H162" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I162" t="s">
         <v>1851</v>
@@ -21852,7 +21850,7 @@
         <v>1855</v>
       </c>
       <c r="N162" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O162" t="s">
         <v>1856</v>
@@ -21885,7 +21883,7 @@
         <v>1861</v>
       </c>
       <c r="C163" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D163" t="s">
         <v>1862</v>
@@ -21918,7 +21916,7 @@
         <v>1868</v>
       </c>
       <c r="N163" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O163" t="s">
         <v>1869</v>
@@ -21927,7 +21925,7 @@
         <v>1870</v>
       </c>
       <c r="Q163" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R163" t="s">
         <v>247</v>
@@ -21966,7 +21964,7 @@
         <v>27</v>
       </c>
       <c r="H164" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I164" t="s">
         <v>1874</v>
@@ -21982,7 +21980,7 @@
         <v>1877</v>
       </c>
       <c r="N164" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O164" t="s">
         <v>1878</v>
@@ -22048,7 +22046,7 @@
         <v>1890</v>
       </c>
       <c r="N165" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O165" t="s">
         <v>1891</v>
@@ -22057,7 +22055,7 @@
         <v>1892</v>
       </c>
       <c r="Q165" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R165" t="s">
         <v>247</v>
@@ -22087,7 +22085,7 @@
         <v>1897</v>
       </c>
       <c r="E166" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F166" t="s">
         <v>1885</v>
@@ -22114,7 +22112,7 @@
         <v>1902</v>
       </c>
       <c r="N166" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O166" t="s">
         <v>1903</v>
@@ -22147,7 +22145,7 @@
         <v>1908</v>
       </c>
       <c r="C167" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D167" t="s">
         <v>1909</v>
@@ -22180,7 +22178,7 @@
         <v>1914</v>
       </c>
       <c r="N167" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O167" t="s">
         <v>1915</v>
@@ -22228,7 +22226,7 @@
         <v>27</v>
       </c>
       <c r="H168" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I168" t="s">
         <v>1922</v>
@@ -22246,7 +22244,7 @@
         <v>1926</v>
       </c>
       <c r="N168" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O168" t="s">
         <v>1927</v>
@@ -22285,7 +22283,7 @@
         <v>830</v>
       </c>
       <c r="E169" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F169" t="s">
         <v>1921</v>
@@ -22294,7 +22292,7 @@
         <v>27</v>
       </c>
       <c r="H169" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I169" t="s">
         <v>1933</v>
@@ -22312,7 +22310,7 @@
         <v>1937</v>
       </c>
       <c r="N169" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O169" t="s">
         <v>1938</v>
@@ -22321,7 +22319,7 @@
         <v>1939</v>
       </c>
       <c r="Q169" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R169" t="s">
         <v>247</v>
@@ -22345,7 +22343,7 @@
         <v>1943</v>
       </c>
       <c r="C170" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D170" t="s">
         <v>862</v>
@@ -22360,7 +22358,7 @@
         <v>27</v>
       </c>
       <c r="H170" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I170" t="s">
         <v>1944</v>
@@ -22378,7 +22376,7 @@
         <v>1948</v>
       </c>
       <c r="N170" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O170" t="s">
         <v>1949</v>
@@ -22387,7 +22385,7 @@
         <v>1950</v>
       </c>
       <c r="Q170" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R170" t="s">
         <v>247</v>
@@ -22414,7 +22412,7 @@
         <v>23</v>
       </c>
       <c r="D171" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="E171" t="s">
         <v>408</v>
@@ -22426,7 +22424,7 @@
         <v>27</v>
       </c>
       <c r="H171" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I171" t="s">
         <v>1953</v>
@@ -22444,7 +22442,7 @@
         <v>1957</v>
       </c>
       <c r="N171" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O171" t="s">
         <v>1958</v>
@@ -22453,20 +22451,20 @@
         <v>1959</v>
       </c>
       <c r="Q171" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R171" t="s">
         <v>247</v>
       </c>
       <c r="S171"/>
       <c r="T171" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="U171" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="V171" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="172">
@@ -22483,7 +22481,7 @@
         <v>1961</v>
       </c>
       <c r="E172" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F172" t="s">
         <v>1962</v>
@@ -22510,7 +22508,7 @@
         <v>1967</v>
       </c>
       <c r="N172" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O172" t="s">
         <v>1968</v>
@@ -22519,7 +22517,7 @@
         <v>1969</v>
       </c>
       <c r="Q172" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R172" t="s">
         <v>247</v>
@@ -22558,7 +22556,7 @@
         <v>27</v>
       </c>
       <c r="H173" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I173" t="s">
         <v>1975</v>
@@ -22576,7 +22574,7 @@
         <v>1979</v>
       </c>
       <c r="N173" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O173" t="s">
         <v>1980</v>
@@ -22609,7 +22607,7 @@
         <v>1985</v>
       </c>
       <c r="C174" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D174" t="s">
         <v>1986</v>
@@ -22642,7 +22640,7 @@
         <v>1991</v>
       </c>
       <c r="N174" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O174" t="s">
         <v>1992</v>
@@ -22651,7 +22649,7 @@
         <v>1993</v>
       </c>
       <c r="Q174" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R174" t="s">
         <v>247</v>
@@ -22678,7 +22676,7 @@
         <v>23</v>
       </c>
       <c r="D175" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="E175" t="s">
         <v>408</v>
@@ -22690,7 +22688,7 @@
         <v>27</v>
       </c>
       <c r="H175" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I175" t="s">
         <v>1996</v>
@@ -22708,7 +22706,7 @@
         <v>2000</v>
       </c>
       <c r="N175" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O175" t="s">
         <v>2001</v>
@@ -22717,7 +22715,7 @@
         <v>2002</v>
       </c>
       <c r="Q175" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R175" t="s">
         <v>247</v>
@@ -22741,7 +22739,7 @@
         <v>2003</v>
       </c>
       <c r="C176" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D176" t="s">
         <v>2004</v>
@@ -22756,7 +22754,7 @@
         <v>27</v>
       </c>
       <c r="H176" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I176" t="s">
         <v>2005</v>
@@ -22774,7 +22772,7 @@
         <v>2009</v>
       </c>
       <c r="N176" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O176" t="s">
         <v>2010</v>
@@ -22840,7 +22838,7 @@
         <v>2022</v>
       </c>
       <c r="N177" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O177" t="s">
         <v>2023</v>
@@ -22906,7 +22904,7 @@
         <v>2034</v>
       </c>
       <c r="N178" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O178" t="s">
         <v>2035</v>
@@ -22915,7 +22913,7 @@
         <v>2036</v>
       </c>
       <c r="Q178" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R178" t="s">
         <v>247</v>
@@ -22954,7 +22952,7 @@
         <v>27</v>
       </c>
       <c r="H179" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I179" t="s">
         <v>2042</v>
@@ -22972,7 +22970,7 @@
         <v>2046</v>
       </c>
       <c r="N179" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O179" t="s">
         <v>2047</v>
@@ -23011,7 +23009,7 @@
         <v>2053</v>
       </c>
       <c r="E180" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F180" t="s">
         <v>2029</v>
@@ -23020,7 +23018,7 @@
         <v>27</v>
       </c>
       <c r="H180" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I180" t="s">
         <v>2054</v>
@@ -23038,7 +23036,7 @@
         <v>2058</v>
       </c>
       <c r="N180" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O180" t="s">
         <v>2059</v>
@@ -23047,7 +23045,7 @@
         <v>2060</v>
       </c>
       <c r="Q180" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R180" t="s">
         <v>247</v>
@@ -23104,7 +23102,7 @@
         <v>2070</v>
       </c>
       <c r="N181" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O181" t="s">
         <v>2071</v>
@@ -23113,7 +23111,7 @@
         <v>2072</v>
       </c>
       <c r="Q181" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R181" t="s">
         <v>247</v>
@@ -23152,7 +23150,7 @@
         <v>27</v>
       </c>
       <c r="H182" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I182" t="s">
         <v>2076</v>
@@ -23170,7 +23168,7 @@
         <v>2080</v>
       </c>
       <c r="N182" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O182" t="s">
         <v>2081</v>
@@ -23179,7 +23177,7 @@
         <v>2082</v>
       </c>
       <c r="Q182" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R182" t="s">
         <v>247</v>
@@ -23218,7 +23216,7 @@
         <v>27</v>
       </c>
       <c r="H183" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I183" t="s">
         <v>2085</v>
@@ -23234,7 +23232,7 @@
         <v>2088</v>
       </c>
       <c r="N183" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O183" t="s">
         <v>2089</v>
@@ -23243,7 +23241,7 @@
         <v>2090</v>
       </c>
       <c r="Q183" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R183" t="s">
         <v>247</v>
@@ -23282,7 +23280,7 @@
         <v>27</v>
       </c>
       <c r="H184" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I184" t="s">
         <v>2096</v>
@@ -23298,7 +23296,7 @@
         <v>2099</v>
       </c>
       <c r="N184" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O184" t="s">
         <v>2100</v>
@@ -23307,7 +23305,7 @@
         <v>2101</v>
       </c>
       <c r="Q184" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R184" t="s">
         <v>247</v>
@@ -23331,7 +23329,7 @@
         <v>2105</v>
       </c>
       <c r="C185" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D185" t="s">
         <v>1397</v>
@@ -23346,7 +23344,7 @@
         <v>27</v>
       </c>
       <c r="H185" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I185" t="s">
         <v>2107</v>
@@ -23364,7 +23362,7 @@
         <v>2111</v>
       </c>
       <c r="N185" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O185" t="s">
         <v>2112</v>
@@ -23373,7 +23371,7 @@
         <v>2113</v>
       </c>
       <c r="Q185" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R185" t="s">
         <v>247</v>
@@ -23412,7 +23410,7 @@
         <v>27</v>
       </c>
       <c r="H186" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I186" t="s">
         <v>2119</v>
@@ -23430,7 +23428,7 @@
         <v>2123</v>
       </c>
       <c r="N186" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O186" t="s">
         <v>2124</v>
@@ -23478,7 +23476,7 @@
         <v>27</v>
       </c>
       <c r="H187" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I187" t="s">
         <v>2133</v>
@@ -23496,7 +23494,7 @@
         <v>2137</v>
       </c>
       <c r="N187" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O187" t="s">
         <v>2138</v>
@@ -23512,13 +23510,13 @@
       </c>
       <c r="S187"/>
       <c r="T187" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="U187" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="V187" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="188">
@@ -23544,7 +23542,7 @@
         <v>27</v>
       </c>
       <c r="H188" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I188" t="s">
         <v>2141</v>
@@ -23562,7 +23560,7 @@
         <v>2145</v>
       </c>
       <c r="N188" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O188" t="s">
         <v>2146</v>
@@ -23571,7 +23569,7 @@
         <v>2147</v>
       </c>
       <c r="Q188" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R188" t="s">
         <v>247</v>
@@ -23595,13 +23593,13 @@
         <v>2151</v>
       </c>
       <c r="C189" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D189" t="s">
         <v>2152</v>
       </c>
       <c r="E189" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F189" t="s">
         <v>2153</v>
@@ -23610,7 +23608,7 @@
         <v>27</v>
       </c>
       <c r="H189" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I189" t="s">
         <v>2154</v>
@@ -23628,7 +23626,7 @@
         <v>2158</v>
       </c>
       <c r="N189" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O189" t="s">
         <v>2159</v>
@@ -23637,7 +23635,7 @@
         <v>2160</v>
       </c>
       <c r="Q189" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R189" t="s">
         <v>247</v>
@@ -23667,7 +23665,7 @@
         <v>2165</v>
       </c>
       <c r="E190" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F190" t="s">
         <v>2166</v>
@@ -23676,7 +23674,7 @@
         <v>27</v>
       </c>
       <c r="H190" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I190" t="s">
         <v>2167</v>
@@ -23692,7 +23690,7 @@
         <v>2170</v>
       </c>
       <c r="N190" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O190" t="s">
         <v>2171</v>
@@ -23701,7 +23699,7 @@
         <v>2172</v>
       </c>
       <c r="Q190" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R190" t="s">
         <v>247</v>
@@ -23740,7 +23738,7 @@
         <v>27</v>
       </c>
       <c r="H191" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I191" t="s">
         <v>2178</v>
@@ -23758,7 +23756,7 @@
         <v>2182</v>
       </c>
       <c r="N191" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O191" t="s">
         <v>2183</v>
@@ -23797,7 +23795,7 @@
         <v>1628</v>
       </c>
       <c r="E192" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F192" t="s">
         <v>2189</v>
@@ -23806,7 +23804,7 @@
         <v>27</v>
       </c>
       <c r="H192" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I192" t="s">
         <v>2190</v>
@@ -23824,7 +23822,7 @@
         <v>2194</v>
       </c>
       <c r="N192" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O192" t="s">
         <v>2195</v>
@@ -23857,7 +23855,7 @@
         <v>2197</v>
       </c>
       <c r="C193" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D193" t="s">
         <v>608</v>
@@ -23870,7 +23868,7 @@
         <v>27</v>
       </c>
       <c r="H193" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I193" t="s">
         <v>2199</v>
@@ -23888,7 +23886,7 @@
         <v>2203</v>
       </c>
       <c r="N193" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O193" t="s">
         <v>2204</v>
@@ -23936,7 +23934,7 @@
         <v>27</v>
       </c>
       <c r="H194" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I194" t="s">
         <v>2212</v>
@@ -23954,7 +23952,7 @@
         <v>2216</v>
       </c>
       <c r="N194" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O194" t="s">
         <v>2217</v>
@@ -24002,7 +24000,7 @@
         <v>27</v>
       </c>
       <c r="H195" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I195" t="s">
         <v>2225</v>
@@ -24020,7 +24018,7 @@
         <v>2229</v>
       </c>
       <c r="N195" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O195" t="s">
         <v>2230</v>
@@ -24068,7 +24066,7 @@
         <v>27</v>
       </c>
       <c r="H196" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I196" t="s">
         <v>2237</v>
@@ -24084,7 +24082,7 @@
         <v>2240</v>
       </c>
       <c r="N196" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O196" t="s">
         <v>2241</v>
@@ -24117,13 +24115,13 @@
         <v>2246</v>
       </c>
       <c r="C197" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D197" t="s">
         <v>446</v>
       </c>
       <c r="E197" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F197" t="s">
         <v>2247</v>
@@ -24132,7 +24130,7 @@
         <v>27</v>
       </c>
       <c r="H197" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I197" t="s">
         <v>2248</v>
@@ -24150,7 +24148,7 @@
         <v>2252</v>
       </c>
       <c r="N197" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O197" t="s">
         <v>2253</v>
@@ -24183,7 +24181,7 @@
         <v>2258</v>
       </c>
       <c r="C198" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D198" t="s">
         <v>2259</v>
@@ -24214,7 +24212,7 @@
         <v>2265</v>
       </c>
       <c r="N198" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O198" t="s">
         <v>2266</v>
@@ -24223,7 +24221,7 @@
         <v>2267</v>
       </c>
       <c r="Q198" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R198" t="s">
         <v>247</v>
@@ -24247,7 +24245,7 @@
         <v>2271</v>
       </c>
       <c r="C199" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D199" t="s">
         <v>2272</v>
@@ -24260,7 +24258,7 @@
         <v>161</v>
       </c>
       <c r="H199" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I199" t="s">
         <v>2274</v>
@@ -24278,7 +24276,7 @@
         <v>2278</v>
       </c>
       <c r="N199" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O199" t="s">
         <v>2279</v>
@@ -24287,7 +24285,7 @@
         <v>2280</v>
       </c>
       <c r="Q199" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R199" t="s">
         <v>247</v>
@@ -24311,7 +24309,7 @@
         <v>2284</v>
       </c>
       <c r="C200" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D200" t="s">
         <v>2272</v>
@@ -24324,7 +24322,7 @@
         <v>161</v>
       </c>
       <c r="H200" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I200" t="s">
         <v>2285</v>
@@ -24342,7 +24340,7 @@
         <v>2289</v>
       </c>
       <c r="N200" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O200" t="s">
         <v>2290</v>
@@ -24351,7 +24349,7 @@
         <v>2291</v>
       </c>
       <c r="Q200" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R200" t="s">
         <v>247</v>
@@ -24375,13 +24373,13 @@
         <v>2295</v>
       </c>
       <c r="C201" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D201" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E201" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F201" t="s">
         <v>226</v>
@@ -24390,7 +24388,7 @@
         <v>27</v>
       </c>
       <c r="H201" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I201" t="s">
         <v>2296</v>
@@ -24417,7 +24415,7 @@
         <v>2302</v>
       </c>
       <c r="Q201" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R201"/>
       <c r="S201"/>
@@ -24445,7 +24443,7 @@
         <v>830</v>
       </c>
       <c r="E202" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F202" t="s">
         <v>226</v>
@@ -24454,7 +24452,7 @@
         <v>27</v>
       </c>
       <c r="H202" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I202" t="s">
         <v>2307</v>
@@ -24503,7 +24501,7 @@
         <v>2314</v>
       </c>
       <c r="C203" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D203" t="s">
         <v>2315</v>
@@ -24512,7 +24510,7 @@
         <v>25</v>
       </c>
       <c r="F203" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G203" t="s">
         <v>161</v>
@@ -24545,7 +24543,7 @@
         <v>2323</v>
       </c>
       <c r="Q203" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R203"/>
       <c r="S203"/>
@@ -24567,7 +24565,7 @@
         <v>2327</v>
       </c>
       <c r="C204" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D204" t="s">
         <v>484</v>
@@ -24576,13 +24574,13 @@
         <v>160</v>
       </c>
       <c r="F204" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="G204" t="s">
         <v>27</v>
       </c>
       <c r="H204" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I204" t="s">
         <v>2328</v>
@@ -24637,7 +24635,7 @@
         <v>2339</v>
       </c>
       <c r="E205" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F205" t="s">
         <v>2340</v>
@@ -24662,7 +24660,7 @@
         <v>2344</v>
       </c>
       <c r="N205" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O205" t="s">
         <v>2345</v>
@@ -24699,7 +24697,7 @@
         <v>701</v>
       </c>
       <c r="E206" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F206" t="s">
         <v>2340</v>
@@ -24724,7 +24722,7 @@
         <v>2351</v>
       </c>
       <c r="N206" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O206" t="s">
         <v>2352</v>
@@ -24733,7 +24731,7 @@
         <v>2353</v>
       </c>
       <c r="Q206" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R206"/>
       <c r="S206"/>
@@ -24755,13 +24753,13 @@
         <v>2357</v>
       </c>
       <c r="C207" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D207" t="s">
         <v>1057</v>
       </c>
       <c r="E207" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F207" t="s">
         <v>2358</v>
@@ -24770,7 +24768,7 @@
         <v>27</v>
       </c>
       <c r="H207" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I207" t="s">
         <v>2359</v>
@@ -24788,7 +24786,7 @@
         <v>2363</v>
       </c>
       <c r="N207" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O207" t="s">
         <v>2364</v>
@@ -24797,18 +24795,18 @@
         <v>2365</v>
       </c>
       <c r="Q207" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R207"/>
       <c r="S207"/>
       <c r="T207" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="U207" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="V207" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="208">
@@ -24819,13 +24817,13 @@
         <v>2366</v>
       </c>
       <c r="C208" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D208" t="s">
         <v>2367</v>
       </c>
       <c r="E208" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F208" t="s">
         <v>2368</v>
@@ -24834,7 +24832,7 @@
         <v>27</v>
       </c>
       <c r="H208" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I208" t="s">
         <v>2369</v>
@@ -24861,7 +24859,7 @@
         <v>2375</v>
       </c>
       <c r="Q208" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R208"/>
       <c r="S208"/>
@@ -24883,7 +24881,7 @@
         <v>2376</v>
       </c>
       <c r="C209" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D209" t="s">
         <v>188</v>
@@ -24898,7 +24896,7 @@
         <v>27</v>
       </c>
       <c r="H209" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I209" t="s">
         <v>2377</v>
@@ -24925,7 +24923,7 @@
         <v>2383</v>
       </c>
       <c r="Q209" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R209"/>
       <c r="S209"/>
@@ -24947,7 +24945,7 @@
         <v>2387</v>
       </c>
       <c r="C210" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D210" t="s">
         <v>2388</v>
@@ -24962,7 +24960,7 @@
         <v>161</v>
       </c>
       <c r="H210" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I210" t="s">
         <v>175</v>
@@ -24980,7 +24978,7 @@
         <v>2391</v>
       </c>
       <c r="N210" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O210" t="s">
         <v>2392</v>
@@ -24994,13 +24992,13 @@
       <c r="R210"/>
       <c r="S210"/>
       <c r="T210" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="U210" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="V210" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="211">
@@ -25011,7 +25009,7 @@
         <v>2394</v>
       </c>
       <c r="C211" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D211" t="s">
         <v>2395</v>
@@ -25081,7 +25079,7 @@
         <v>967</v>
       </c>
       <c r="E212" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F212" t="s">
         <v>2389</v>
@@ -25117,7 +25115,7 @@
         <v>2410</v>
       </c>
       <c r="Q212" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R212"/>
       <c r="S212"/>
@@ -25139,13 +25137,13 @@
         <v>2414</v>
       </c>
       <c r="C213" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D213" t="s">
         <v>2415</v>
       </c>
       <c r="E213" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F213" t="s">
         <v>2389</v>
@@ -25172,7 +25170,7 @@
         <v>2420</v>
       </c>
       <c r="N213" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O213" t="s">
         <v>2421</v>
@@ -25181,7 +25179,7 @@
         <v>2422</v>
       </c>
       <c r="Q213" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R213"/>
       <c r="S213"/>
@@ -25236,7 +25234,7 @@
         <v>2433</v>
       </c>
       <c r="N214" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O214" t="s">
         <v>2434</v>
@@ -25273,7 +25271,7 @@
         <v>553</v>
       </c>
       <c r="E215" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F215" t="s">
         <v>2440</v>
@@ -25282,7 +25280,7 @@
         <v>27</v>
       </c>
       <c r="H215" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I215" t="s">
         <v>2441</v>
@@ -25309,7 +25307,7 @@
         <v>2447</v>
       </c>
       <c r="Q215" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R215"/>
       <c r="S215"/>
@@ -25346,7 +25344,7 @@
         <v>27</v>
       </c>
       <c r="H216" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I216" t="s">
         <v>2449</v>
@@ -25362,7 +25360,7 @@
         <v>2452</v>
       </c>
       <c r="N216" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O216" t="s">
         <v>2453</v>
@@ -25396,10 +25394,10 @@
         <v>187</v>
       </c>
       <c r="D217" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="E217" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F217" t="s">
         <v>2440</v>
@@ -25408,7 +25406,7 @@
         <v>27</v>
       </c>
       <c r="H217" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I217" t="s">
         <v>2456</v>
@@ -25424,7 +25422,7 @@
         <v>2459</v>
       </c>
       <c r="N217" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O217" t="s">
         <v>2460</v>
@@ -25433,7 +25431,7 @@
         <v>2461</v>
       </c>
       <c r="Q217" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R217"/>
       <c r="S217"/>
@@ -25461,7 +25459,7 @@
         <v>265</v>
       </c>
       <c r="E218" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F218" t="s">
         <v>2440</v>
@@ -25470,7 +25468,7 @@
         <v>27</v>
       </c>
       <c r="H218" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I218" t="s">
         <v>2466</v>
@@ -25486,7 +25484,7 @@
         <v>2469</v>
       </c>
       <c r="N218" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O218" t="s">
         <v>2470</v>
@@ -25495,7 +25493,7 @@
         <v>2471</v>
       </c>
       <c r="Q218" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R218"/>
       <c r="S218"/>
@@ -25517,7 +25515,7 @@
         <v>2472</v>
       </c>
       <c r="C219" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D219" t="s">
         <v>2473</v>
@@ -25530,7 +25528,7 @@
         <v>27</v>
       </c>
       <c r="H219" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I219" t="s">
         <v>2475</v>
@@ -25582,10 +25580,10 @@
         <v>187</v>
       </c>
       <c r="D220" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E220" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F220" t="s">
         <v>174</v>
@@ -25594,7 +25592,7 @@
         <v>27</v>
       </c>
       <c r="H220" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I220" t="s">
         <v>2486</v>
@@ -25610,7 +25608,7 @@
         <v>2489</v>
       </c>
       <c r="N220" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O220" t="s">
         <v>2490</v>
@@ -25647,7 +25645,7 @@
         <v>2496</v>
       </c>
       <c r="E221" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F221" t="s">
         <v>174</v>
@@ -25656,7 +25654,7 @@
         <v>27</v>
       </c>
       <c r="H221" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I221" t="s">
         <v>2497</v>
@@ -25672,7 +25670,7 @@
         <v>2500</v>
       </c>
       <c r="N221" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O221" t="s">
         <v>2501</v>
@@ -25718,7 +25716,7 @@
         <v>161</v>
       </c>
       <c r="H222" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I222" t="s">
         <v>2506</v>
@@ -25736,7 +25734,7 @@
         <v>2510</v>
       </c>
       <c r="N222" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O222" t="s">
         <v>2511</v>
@@ -25745,7 +25743,7 @@
         <v>2512</v>
       </c>
       <c r="Q222" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R222"/>
       <c r="S222"/>
@@ -25770,10 +25768,10 @@
         <v>187</v>
       </c>
       <c r="D223" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="E223" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F223" t="s">
         <v>2514</v>
@@ -25798,7 +25796,7 @@
         <v>2518</v>
       </c>
       <c r="N223" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O223" t="s">
         <v>2519</v>
@@ -25807,7 +25805,7 @@
         <v>2520</v>
       </c>
       <c r="Q223" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R223"/>
       <c r="S223"/>
@@ -25829,7 +25827,7 @@
         <v>2521</v>
       </c>
       <c r="C224" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D224" t="s">
         <v>2522</v>
@@ -25891,7 +25889,7 @@
         <v>2531</v>
       </c>
       <c r="C225" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D225" t="s">
         <v>2532</v>
@@ -25906,7 +25904,7 @@
         <v>161</v>
       </c>
       <c r="H225" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I225" t="s">
         <v>2534</v>
@@ -25924,7 +25922,7 @@
         <v>2538</v>
       </c>
       <c r="N225" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O225" t="s">
         <v>2539</v>
@@ -25933,7 +25931,7 @@
         <v>2540</v>
       </c>
       <c r="Q225" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R225"/>
       <c r="S225"/>
@@ -25961,7 +25959,7 @@
         <v>1302</v>
       </c>
       <c r="E226" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F226" t="s">
         <v>2545</v>
@@ -25988,7 +25986,7 @@
         <v>2550</v>
       </c>
       <c r="N226" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O226" t="s">
         <v>2551</v>
@@ -25997,7 +25995,7 @@
         <v>2552</v>
       </c>
       <c r="Q226" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R226"/>
       <c r="S226"/>
@@ -26025,7 +26023,7 @@
         <v>2557</v>
       </c>
       <c r="E227" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F227" t="s">
         <v>2558</v>
@@ -26034,7 +26032,7 @@
         <v>27</v>
       </c>
       <c r="H227" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I227" t="s">
         <v>2559</v>
@@ -26052,7 +26050,7 @@
         <v>2563</v>
       </c>
       <c r="N227" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O227" t="s">
         <v>2564</v>
@@ -26061,7 +26059,7 @@
         <v>2565</v>
       </c>
       <c r="Q227" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R227"/>
       <c r="S227"/>
@@ -26098,7 +26096,7 @@
         <v>27</v>
       </c>
       <c r="H228" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I228" t="s">
         <v>2571</v>
@@ -26114,7 +26112,7 @@
         <v>2574</v>
       </c>
       <c r="N228" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O228" t="s">
         <v>2575</v>
@@ -26123,7 +26121,7 @@
         <v>2576</v>
       </c>
       <c r="Q228" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R228"/>
       <c r="S228"/>
@@ -26151,7 +26149,7 @@
         <v>2578</v>
       </c>
       <c r="E229" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F229" t="s">
         <v>2579</v>
@@ -26160,7 +26158,7 @@
         <v>27</v>
       </c>
       <c r="H229" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I229" t="s">
         <v>2580</v>
@@ -26178,7 +26176,7 @@
         <v>2584</v>
       </c>
       <c r="N229" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O229" t="s">
         <v>2585</v>
@@ -26212,10 +26210,10 @@
         <v>23</v>
       </c>
       <c r="D230" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E230" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F230" t="s">
         <v>2579</v>
@@ -26224,7 +26222,7 @@
         <v>27</v>
       </c>
       <c r="H230" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I230" t="s">
         <v>2591</v>
@@ -26242,7 +26240,7 @@
         <v>2595</v>
       </c>
       <c r="N230" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O230" t="s">
         <v>2596</v>
@@ -26251,18 +26249,18 @@
         <v>2597</v>
       </c>
       <c r="Q230" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R230"/>
       <c r="S230"/>
       <c r="T230" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="U230" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="V230" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="231">
@@ -26306,7 +26304,7 @@
         <v>2604</v>
       </c>
       <c r="N231" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O231" t="s">
         <v>2605</v>
@@ -26343,7 +26341,7 @@
         <v>1628</v>
       </c>
       <c r="E232" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F232" t="s">
         <v>2611</v>
@@ -26352,7 +26350,7 @@
         <v>27</v>
       </c>
       <c r="H232" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I232" t="s">
         <v>2612</v>
@@ -26370,7 +26368,7 @@
         <v>2616</v>
       </c>
       <c r="N232" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O232" t="s">
         <v>2617</v>
@@ -26416,7 +26414,7 @@
         <v>27</v>
       </c>
       <c r="H233" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I233" t="s">
         <v>2621</v>
@@ -26434,7 +26432,7 @@
         <v>2625</v>
       </c>
       <c r="N233" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O233" t="s">
         <v>2626</v>
@@ -26443,18 +26441,18 @@
         <v>2627</v>
       </c>
       <c r="Q233" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R233"/>
       <c r="S233"/>
       <c r="T233" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="U233" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="V233" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="234">
@@ -26480,7 +26478,7 @@
         <v>27</v>
       </c>
       <c r="H234" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I234" t="s">
         <v>2630</v>
@@ -26498,7 +26496,7 @@
         <v>2634</v>
       </c>
       <c r="N234" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O234" t="s">
         <v>2635</v>
@@ -26544,7 +26542,7 @@
         <v>161</v>
       </c>
       <c r="H235" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I235" t="s">
         <v>2642</v>
@@ -26562,7 +26560,7 @@
         <v>2646</v>
       </c>
       <c r="N235" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O235" t="s">
         <v>2647</v>
@@ -26608,7 +26606,7 @@
         <v>27</v>
       </c>
       <c r="H236" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I236" t="s">
         <v>2651</v>
@@ -26626,7 +26624,7 @@
         <v>2655</v>
       </c>
       <c r="N236" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O236" t="s">
         <v>2656</v>
@@ -26635,18 +26633,18 @@
         <v>2657</v>
       </c>
       <c r="Q236" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R236"/>
       <c r="S236"/>
       <c r="T236" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="U236" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="V236" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="237">
@@ -26657,7 +26655,7 @@
         <v>2658</v>
       </c>
       <c r="C237" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D237" t="s">
         <v>2659</v>
@@ -26690,7 +26688,7 @@
         <v>2665</v>
       </c>
       <c r="N237" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O237" t="s">
         <v>2666</v>
@@ -26736,7 +26734,7 @@
         <v>27</v>
       </c>
       <c r="H238" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I238" t="s">
         <v>2673</v>
@@ -26752,7 +26750,7 @@
         <v>2676</v>
       </c>
       <c r="N238" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O238" t="s">
         <v>2677</v>
@@ -26761,7 +26759,7 @@
         <v>2678</v>
       </c>
       <c r="Q238" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R238"/>
       <c r="S238"/>
@@ -26816,7 +26814,7 @@
         <v>2688</v>
       </c>
       <c r="N239" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O239" t="s">
         <v>2689</v>
@@ -26853,7 +26851,7 @@
         <v>2695</v>
       </c>
       <c r="E240" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F240" t="s">
         <v>2696</v>
@@ -26862,7 +26860,7 @@
         <v>27</v>
       </c>
       <c r="H240" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I240" t="s">
         <v>2697</v>
@@ -26880,7 +26878,7 @@
         <v>2701</v>
       </c>
       <c r="N240" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O240" t="s">
         <v>2702</v>
@@ -26889,7 +26887,7 @@
         <v>2703</v>
       </c>
       <c r="Q240" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R240"/>
       <c r="S240"/>
@@ -26911,13 +26909,13 @@
         <v>2707</v>
       </c>
       <c r="C241" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D241" t="s">
         <v>1302</v>
       </c>
       <c r="E241" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F241" t="s">
         <v>2696</v>
@@ -26926,7 +26924,7 @@
         <v>27</v>
       </c>
       <c r="H241" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I241" t="s">
         <v>2708</v>
@@ -26944,7 +26942,7 @@
         <v>2712</v>
       </c>
       <c r="N241" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O241" t="s">
         <v>2713</v>
@@ -26953,7 +26951,7 @@
         <v>2714</v>
       </c>
       <c r="Q241" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R241"/>
       <c r="S241"/>
@@ -26978,10 +26976,10 @@
         <v>23</v>
       </c>
       <c r="D242" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E242" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F242" t="s">
         <v>2696</v>
@@ -26990,7 +26988,7 @@
         <v>27</v>
       </c>
       <c r="H242" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I242" t="s">
         <v>2719</v>
@@ -27008,7 +27006,7 @@
         <v>2723</v>
       </c>
       <c r="N242" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O242" t="s">
         <v>2724</v>
@@ -27017,7 +27015,7 @@
         <v>2725</v>
       </c>
       <c r="Q242" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R242"/>
       <c r="S242"/>
@@ -27039,7 +27037,7 @@
         <v>2729</v>
       </c>
       <c r="C243" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D243" t="s">
         <v>2599</v>
@@ -27072,7 +27070,7 @@
         <v>2735</v>
       </c>
       <c r="N243" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O243" t="s">
         <v>2736</v>
@@ -27081,7 +27079,7 @@
         <v>2737</v>
       </c>
       <c r="Q243" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R243"/>
       <c r="S243"/>
@@ -27109,7 +27107,7 @@
         <v>2742</v>
       </c>
       <c r="E244" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F244" t="s">
         <v>2730</v>
@@ -27118,7 +27116,7 @@
         <v>161</v>
       </c>
       <c r="H244" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I244" t="s">
         <v>2743</v>
@@ -27136,7 +27134,7 @@
         <v>2747</v>
       </c>
       <c r="N244" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O244" t="s">
         <v>2748</v>
@@ -27145,7 +27143,7 @@
         <v>2749</v>
       </c>
       <c r="Q244" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R244"/>
       <c r="S244"/>
@@ -27200,7 +27198,7 @@
         <v>2760</v>
       </c>
       <c r="N245" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O245" t="s">
         <v>2761</v>
@@ -27209,7 +27207,7 @@
         <v>2762</v>
       </c>
       <c r="Q245" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R245"/>
       <c r="S245"/>
@@ -27231,7 +27229,7 @@
         <v>2766</v>
       </c>
       <c r="C246" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D246" t="s">
         <v>2767</v>
@@ -27246,7 +27244,7 @@
         <v>27</v>
       </c>
       <c r="H246" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I246" t="s">
         <v>2770</v>
@@ -27264,7 +27262,7 @@
         <v>2774</v>
       </c>
       <c r="N246" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O246" t="s">
         <v>2775</v>
@@ -27273,7 +27271,7 @@
         <v>2776</v>
       </c>
       <c r="Q246" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R246"/>
       <c r="S246"/>
@@ -27310,7 +27308,7 @@
         <v>27</v>
       </c>
       <c r="H247" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I247" t="s">
         <v>2780</v>
@@ -27326,7 +27324,7 @@
         <v>2783</v>
       </c>
       <c r="N247" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O247" t="s">
         <v>2784</v>
@@ -27372,7 +27370,7 @@
         <v>27</v>
       </c>
       <c r="H248" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I248" t="s">
         <v>2787</v>
@@ -27388,7 +27386,7 @@
         <v>2790</v>
       </c>
       <c r="N248" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O248" t="s">
         <v>2791</v>
@@ -27419,13 +27417,13 @@
         <v>2793</v>
       </c>
       <c r="C249" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D249" t="s">
         <v>2794</v>
       </c>
       <c r="E249" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F249" t="s">
         <v>2795</v>
@@ -27434,7 +27432,7 @@
         <v>27</v>
       </c>
       <c r="H249" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I249" t="s">
         <v>2796</v>
@@ -27452,7 +27450,7 @@
         <v>2800</v>
       </c>
       <c r="N249" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O249" t="s">
         <v>2801</v>
@@ -27461,7 +27459,7 @@
         <v>2802</v>
       </c>
       <c r="Q249" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R249"/>
       <c r="S249"/>
@@ -27498,7 +27496,7 @@
         <v>27</v>
       </c>
       <c r="H250" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I250" t="s">
         <v>2806</v>
@@ -27516,7 +27514,7 @@
         <v>2810</v>
       </c>
       <c r="N250" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O250" t="s">
         <v>2811</v>
@@ -27525,7 +27523,7 @@
         <v>2812</v>
       </c>
       <c r="Q250" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R250"/>
       <c r="S250"/>
@@ -27547,13 +27545,13 @@
         <v>2813</v>
       </c>
       <c r="C251" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D251" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E251" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F251" t="s">
         <v>2805</v>
@@ -27562,7 +27560,7 @@
         <v>27</v>
       </c>
       <c r="H251" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I251" t="s">
         <v>2814</v>
@@ -27580,7 +27578,7 @@
         <v>2818</v>
       </c>
       <c r="N251" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O251" t="s">
         <v>2819</v>
@@ -27589,7 +27587,7 @@
         <v>2820</v>
       </c>
       <c r="Q251" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R251"/>
       <c r="S251"/>
@@ -27617,7 +27615,7 @@
         <v>2794</v>
       </c>
       <c r="E252" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F252" t="s">
         <v>2825</v>
@@ -27626,7 +27624,7 @@
         <v>27</v>
       </c>
       <c r="H252" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I252" t="s">
         <v>2826</v>
@@ -27642,7 +27640,7 @@
         <v>2829</v>
       </c>
       <c r="N252" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O252" t="s">
         <v>2830</v>
@@ -27651,7 +27649,7 @@
         <v>2831</v>
       </c>
       <c r="Q252" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R252"/>
       <c r="S252"/>
@@ -27688,7 +27686,7 @@
         <v>27</v>
       </c>
       <c r="H253" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I253" t="s">
         <v>2834</v>
@@ -27704,7 +27702,7 @@
         <v>2837</v>
       </c>
       <c r="N253" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O253" t="s">
         <v>2838</v>
@@ -27713,7 +27711,7 @@
         <v>2839</v>
       </c>
       <c r="Q253" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R253"/>
       <c r="S253"/>
@@ -27750,7 +27748,7 @@
         <v>27</v>
       </c>
       <c r="H254" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I254" t="s">
         <v>2844</v>
@@ -27766,7 +27764,7 @@
         <v>2847</v>
       </c>
       <c r="N254" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O254" t="s">
         <v>2848</v>
@@ -27775,7 +27773,7 @@
         <v>2849</v>
       </c>
       <c r="Q254" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R254"/>
       <c r="S254"/>
@@ -27810,7 +27808,7 @@
         <v>27</v>
       </c>
       <c r="H255" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I255" t="s">
         <v>2852</v>
@@ -27828,7 +27826,7 @@
         <v>2856</v>
       </c>
       <c r="N255" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O255" t="s">
         <v>2857</v>
@@ -27890,7 +27888,7 @@
         <v>2869</v>
       </c>
       <c r="N256" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O256" t="s">
         <v>2870</v>
@@ -27899,7 +27897,7 @@
         <v>2871</v>
       </c>
       <c r="Q256" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R256"/>
       <c r="S256"/>
@@ -27921,7 +27919,7 @@
         <v>2875</v>
       </c>
       <c r="C257" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D257" t="s">
         <v>2876</v>
@@ -27936,7 +27934,7 @@
         <v>161</v>
       </c>
       <c r="H257" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I257" t="s">
         <v>2878</v>
@@ -27954,7 +27952,7 @@
         <v>2882</v>
       </c>
       <c r="N257" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O257" t="s">
         <v>2883</v>
@@ -27963,7 +27961,7 @@
         <v>2884</v>
       </c>
       <c r="Q257" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R257"/>
       <c r="S257"/>
@@ -27985,7 +27983,7 @@
         <v>2885</v>
       </c>
       <c r="C258" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D258" t="s">
         <v>1711</v>
@@ -28018,7 +28016,7 @@
         <v>2891</v>
       </c>
       <c r="N258" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O258" t="s">
         <v>2892</v>
@@ -28027,7 +28025,7 @@
         <v>2893</v>
       </c>
       <c r="Q258" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R258"/>
       <c r="S258"/>
@@ -28082,7 +28080,7 @@
         <v>2900</v>
       </c>
       <c r="N259" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O259" t="s">
         <v>2901</v>
@@ -28091,7 +28089,7 @@
         <v>2902</v>
       </c>
       <c r="Q259" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R259"/>
       <c r="S259"/>
@@ -28113,7 +28111,7 @@
         <v>2906</v>
       </c>
       <c r="C260" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D260" t="s">
         <v>574</v>
@@ -28128,7 +28126,7 @@
         <v>27</v>
       </c>
       <c r="H260" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I260" t="s">
         <v>2907</v>
@@ -28146,7 +28144,7 @@
         <v>2911</v>
       </c>
       <c r="N260" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O260" t="s">
         <v>2912</v>
@@ -28177,7 +28175,7 @@
         <v>2914</v>
       </c>
       <c r="C261" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D261" t="s">
         <v>574</v>
@@ -28192,7 +28190,7 @@
         <v>27</v>
       </c>
       <c r="H261" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I261" t="s">
         <v>2915</v>
@@ -28210,7 +28208,7 @@
         <v>2919</v>
       </c>
       <c r="N261" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O261" t="s">
         <v>2920</v>
@@ -28241,13 +28239,13 @@
         <v>2922</v>
       </c>
       <c r="C262" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D262" t="s">
         <v>2923</v>
       </c>
       <c r="E262" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F262" t="s">
         <v>2886</v>
@@ -28256,7 +28254,7 @@
         <v>27</v>
       </c>
       <c r="H262" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I262" t="s">
         <v>2924</v>
@@ -28274,7 +28272,7 @@
         <v>2928</v>
       </c>
       <c r="N262" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O262" t="s">
         <v>2929</v>
@@ -28320,7 +28318,7 @@
         <v>27</v>
       </c>
       <c r="H263" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I263" t="s">
         <v>2937</v>
@@ -28338,7 +28336,7 @@
         <v>2941</v>
       </c>
       <c r="N263" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O263" t="s">
         <v>2942</v>
@@ -28347,7 +28345,7 @@
         <v>2943</v>
       </c>
       <c r="Q263" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R263"/>
       <c r="S263"/>
@@ -28375,7 +28373,7 @@
         <v>1019</v>
       </c>
       <c r="E264" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F264" t="s">
         <v>2936</v>
@@ -28402,7 +28400,7 @@
         <v>2952</v>
       </c>
       <c r="N264" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O264" t="s">
         <v>2953</v>
@@ -28439,7 +28437,7 @@
         <v>2959</v>
       </c>
       <c r="E265" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F265" t="s">
         <v>2960</v>
@@ -28448,7 +28446,7 @@
         <v>27</v>
       </c>
       <c r="H265" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I265" t="s">
         <v>2961</v>
@@ -28466,7 +28464,7 @@
         <v>2965</v>
       </c>
       <c r="N265" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O265" t="s">
         <v>2966</v>
@@ -28475,7 +28473,7 @@
         <v>2967</v>
       </c>
       <c r="Q265" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R265"/>
       <c r="S265"/>
@@ -28497,7 +28495,7 @@
         <v>2971</v>
       </c>
       <c r="C266" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D266" t="s">
         <v>2895</v>
@@ -28512,7 +28510,7 @@
         <v>27</v>
       </c>
       <c r="H266" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I266" t="s">
         <v>2973</v>
@@ -28530,7 +28528,7 @@
         <v>2977</v>
       </c>
       <c r="N266" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O266" t="s">
         <v>2978</v>
@@ -28539,7 +28537,7 @@
         <v>2979</v>
       </c>
       <c r="Q266" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R266"/>
       <c r="S266"/>
@@ -28567,7 +28565,7 @@
         <v>2959</v>
       </c>
       <c r="E267" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F267" t="s">
         <v>2972</v>
@@ -28576,7 +28574,7 @@
         <v>27</v>
       </c>
       <c r="H267" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I267" t="s">
         <v>2981</v>
@@ -28592,7 +28590,7 @@
         <v>2984</v>
       </c>
       <c r="N267" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O267" t="s">
         <v>2985</v>
@@ -28601,7 +28599,7 @@
         <v>2986</v>
       </c>
       <c r="Q267" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R267"/>
       <c r="S267"/>
@@ -28638,7 +28636,7 @@
         <v>27</v>
       </c>
       <c r="H268" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I268" t="s">
         <v>2992</v>
@@ -28656,7 +28654,7 @@
         <v>2996</v>
       </c>
       <c r="N268" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O268" t="s">
         <v>2997</v>
@@ -28665,7 +28663,7 @@
         <v>2998</v>
       </c>
       <c r="Q268" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R268"/>
       <c r="S268"/>
@@ -28687,7 +28685,7 @@
         <v>3002</v>
       </c>
       <c r="C269" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D269" t="s">
         <v>173</v>
@@ -28700,7 +28698,7 @@
         <v>27</v>
       </c>
       <c r="H269" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I269" t="s">
         <v>3004</v>
@@ -28718,7 +28716,7 @@
         <v>3008</v>
       </c>
       <c r="N269" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O269" t="s">
         <v>3009</v>
@@ -28727,18 +28725,18 @@
         <v>3010</v>
       </c>
       <c r="Q269" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R269"/>
       <c r="S269"/>
       <c r="T269" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="U269" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="V269" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="270">
@@ -28749,7 +28747,7 @@
         <v>3011</v>
       </c>
       <c r="C270" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D270" t="s">
         <v>3012</v>
@@ -28762,7 +28760,7 @@
         <v>27</v>
       </c>
       <c r="H270" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I270" t="s">
         <v>3013</v>
@@ -28780,7 +28778,7 @@
         <v>3017</v>
       </c>
       <c r="N270" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O270" t="s">
         <v>3018</v>
@@ -28789,18 +28787,18 @@
         <v>3019</v>
       </c>
       <c r="Q270" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R270"/>
       <c r="S270"/>
       <c r="T270" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="U270" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="V270" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="271">
@@ -28811,7 +28809,7 @@
         <v>3020</v>
       </c>
       <c r="C271" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D271" t="s">
         <v>1388</v>
@@ -28824,7 +28822,7 @@
         <v>27</v>
       </c>
       <c r="H271" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I271" t="s">
         <v>3021</v>
@@ -28842,7 +28840,7 @@
         <v>3025</v>
       </c>
       <c r="N271" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O271" t="s">
         <v>3026</v>
@@ -28851,7 +28849,7 @@
         <v>3027</v>
       </c>
       <c r="Q271" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R271"/>
       <c r="S271"/>
@@ -28873,7 +28871,7 @@
         <v>3028</v>
       </c>
       <c r="C272" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D272" t="s">
         <v>1443</v>
@@ -28886,7 +28884,7 @@
         <v>27</v>
       </c>
       <c r="H272" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I272" t="s">
         <v>3029</v>
@@ -28904,7 +28902,7 @@
         <v>3033</v>
       </c>
       <c r="N272" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O272" t="s">
         <v>3034</v>
@@ -28913,18 +28911,18 @@
         <v>3035</v>
       </c>
       <c r="Q272" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R272"/>
       <c r="S272"/>
       <c r="T272" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="U272" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="V272" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="273">
@@ -28935,7 +28933,7 @@
         <v>3036</v>
       </c>
       <c r="C273" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D273" t="s">
         <v>3037</v>
@@ -28948,7 +28946,7 @@
         <v>27</v>
       </c>
       <c r="H273" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I273" t="s">
         <v>3039</v>
@@ -28966,7 +28964,7 @@
         <v>3043</v>
       </c>
       <c r="N273" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O273" t="s">
         <v>3044</v>
@@ -28975,7 +28973,7 @@
         <v>3045</v>
       </c>
       <c r="Q273" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R273"/>
       <c r="S273"/>
@@ -29003,7 +29001,7 @@
         <v>3050</v>
       </c>
       <c r="E274" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F274" t="s">
         <v>3051</v>
@@ -29012,7 +29010,7 @@
         <v>27</v>
       </c>
       <c r="H274" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I274" t="s">
         <v>3052</v>
@@ -29030,7 +29028,7 @@
         <v>3056</v>
       </c>
       <c r="N274" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O274" t="s">
         <v>3057</v>
@@ -29039,18 +29037,18 @@
         <v>3058</v>
       </c>
       <c r="Q274" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R274"/>
       <c r="S274"/>
       <c r="T274" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="U274" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="V274" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="275">
@@ -29076,7 +29074,7 @@
         <v>27</v>
       </c>
       <c r="H275" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I275" t="s">
         <v>3062</v>
@@ -29094,7 +29092,7 @@
         <v>3066</v>
       </c>
       <c r="N275" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O275" t="s">
         <v>3067</v>
@@ -29140,7 +29138,7 @@
         <v>27</v>
       </c>
       <c r="H276" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I276" t="s">
         <v>3074</v>
@@ -29156,7 +29154,7 @@
         <v>3077</v>
       </c>
       <c r="N276" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O276" t="s">
         <v>3078</v>
@@ -29202,7 +29200,7 @@
         <v>27</v>
       </c>
       <c r="H277" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I277" t="s">
         <v>3087</v>
@@ -29220,7 +29218,7 @@
         <v>3091</v>
       </c>
       <c r="N277" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O277" t="s">
         <v>3092</v>
@@ -29284,7 +29282,7 @@
         <v>3104</v>
       </c>
       <c r="N278" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O278" t="s">
         <v>3105</v>
@@ -29293,7 +29291,7 @@
         <v>3106</v>
       </c>
       <c r="Q278" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R278"/>
       <c r="S278"/>
@@ -29315,13 +29313,13 @@
         <v>3110</v>
       </c>
       <c r="C279" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D279" t="s">
         <v>1083</v>
       </c>
       <c r="E279" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F279" t="s">
         <v>3098</v>
@@ -29348,7 +29346,7 @@
         <v>3115</v>
       </c>
       <c r="N279" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O279" t="s">
         <v>3116</v>
@@ -29394,7 +29392,7 @@
         <v>27</v>
       </c>
       <c r="H280" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I280" t="s">
         <v>3119</v>
@@ -29412,7 +29410,7 @@
         <v>3123</v>
       </c>
       <c r="N280" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O280" t="s">
         <v>3124</v>
@@ -29449,7 +29447,7 @@
         <v>2578</v>
       </c>
       <c r="E281" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F281" t="s">
         <v>3098</v>
@@ -29458,7 +29456,7 @@
         <v>27</v>
       </c>
       <c r="H281" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I281" t="s">
         <v>3130</v>
@@ -29476,7 +29474,7 @@
         <v>3134</v>
       </c>
       <c r="N281" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O281" t="s">
         <v>3135</v>
@@ -29485,7 +29483,7 @@
         <v>3136</v>
       </c>
       <c r="Q281" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R281"/>
       <c r="S281"/>
@@ -29522,7 +29520,7 @@
         <v>27</v>
       </c>
       <c r="H282" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I282" t="s">
         <v>3141</v>
@@ -29540,7 +29538,7 @@
         <v>3145</v>
       </c>
       <c r="N282" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O282" t="s">
         <v>3146</v>
@@ -29549,7 +29547,7 @@
         <v>3147</v>
       </c>
       <c r="Q282" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R282"/>
       <c r="S282"/>
@@ -29571,7 +29569,7 @@
         <v>3151</v>
       </c>
       <c r="C283" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D283" t="s">
         <v>1353</v>
@@ -29604,7 +29602,7 @@
         <v>3156</v>
       </c>
       <c r="N283" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O283" t="s">
         <v>3157</v>
@@ -29613,7 +29611,7 @@
         <v>3158</v>
       </c>
       <c r="Q283" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R283"/>
       <c r="S283"/>
@@ -29668,7 +29666,7 @@
         <v>3164</v>
       </c>
       <c r="N284" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O284" t="s">
         <v>3165</v>
@@ -29714,7 +29712,7 @@
         <v>27</v>
       </c>
       <c r="H285" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I285" t="s">
         <v>3169</v>
@@ -29732,7 +29730,7 @@
         <v>3173</v>
       </c>
       <c r="N285" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O285" t="s">
         <v>3174</v>
@@ -29769,7 +29767,7 @@
         <v>2742</v>
       </c>
       <c r="E286" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F286" t="s">
         <v>3177</v>
@@ -29778,7 +29776,7 @@
         <v>161</v>
       </c>
       <c r="H286" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I286" t="s">
         <v>3178</v>
@@ -29796,7 +29794,7 @@
         <v>3182</v>
       </c>
       <c r="N286" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O286" t="s">
         <v>3183</v>
@@ -29805,18 +29803,18 @@
         <v>3184</v>
       </c>
       <c r="Q286" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R286"/>
       <c r="S286"/>
       <c r="T286" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="U286" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="V286" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="287">
@@ -29842,7 +29840,7 @@
         <v>27</v>
       </c>
       <c r="H287" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I287" t="s">
         <v>3187</v>
@@ -29858,7 +29856,7 @@
         <v>3190</v>
       </c>
       <c r="N287" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O287" t="s">
         <v>3191</v>
@@ -29867,7 +29865,7 @@
         <v>3192</v>
       </c>
       <c r="Q287" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R287"/>
       <c r="S287"/>
@@ -29904,7 +29902,7 @@
         <v>27</v>
       </c>
       <c r="H288" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I288" t="s">
         <v>3198</v>
@@ -29920,7 +29918,7 @@
         <v>3201</v>
       </c>
       <c r="N288" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O288" t="s">
         <v>3202</v>
@@ -29929,7 +29927,7 @@
         <v>3203</v>
       </c>
       <c r="Q288" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R288"/>
       <c r="S288"/>
@@ -29984,7 +29982,7 @@
         <v>3210</v>
       </c>
       <c r="N289" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O289" t="s">
         <v>3211</v>
@@ -30015,7 +30013,7 @@
         <v>3216</v>
       </c>
       <c r="C290" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D290" t="s">
         <v>3012</v>
@@ -30028,7 +30026,7 @@
         <v>27</v>
       </c>
       <c r="H290" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I290" t="s">
         <v>3218</v>
@@ -30046,7 +30044,7 @@
         <v>3222</v>
       </c>
       <c r="N290" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O290" t="s">
         <v>3223</v>
@@ -30077,7 +30075,7 @@
         <v>3225</v>
       </c>
       <c r="C291" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D291" t="s">
         <v>1388</v>
@@ -30090,7 +30088,7 @@
         <v>27</v>
       </c>
       <c r="H291" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I291" t="s">
         <v>3226</v>
@@ -30108,7 +30106,7 @@
         <v>3230</v>
       </c>
       <c r="N291" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O291" t="s">
         <v>3231</v>
@@ -30117,7 +30115,7 @@
         <v>3232</v>
       </c>
       <c r="Q291" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R291"/>
       <c r="S291"/>
@@ -30139,7 +30137,7 @@
         <v>3233</v>
       </c>
       <c r="C292" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D292" t="s">
         <v>1443</v>
@@ -30152,7 +30150,7 @@
         <v>27</v>
       </c>
       <c r="H292" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I292" t="s">
         <v>3234</v>
@@ -30170,7 +30168,7 @@
         <v>3238</v>
       </c>
       <c r="N292" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O292" t="s">
         <v>3239</v>
@@ -30207,7 +30205,7 @@
         <v>2557</v>
       </c>
       <c r="E293" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F293" t="s">
         <v>3217</v>
@@ -30216,7 +30214,7 @@
         <v>27</v>
       </c>
       <c r="H293" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I293" t="s">
         <v>3242</v>
@@ -30234,7 +30232,7 @@
         <v>3246</v>
       </c>
       <c r="N293" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O293" t="s">
         <v>3247</v>
@@ -30243,7 +30241,7 @@
         <v>3248</v>
       </c>
       <c r="Q293" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R293"/>
       <c r="S293"/>
@@ -30265,7 +30263,7 @@
         <v>3252</v>
       </c>
       <c r="C294" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D294" t="s">
         <v>3037</v>
@@ -30278,7 +30276,7 @@
         <v>27</v>
       </c>
       <c r="H294" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I294" t="s">
         <v>3254</v>
@@ -30296,7 +30294,7 @@
         <v>3258</v>
       </c>
       <c r="N294" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O294" t="s">
         <v>3259</v>
@@ -30333,7 +30331,7 @@
         <v>3262</v>
       </c>
       <c r="E295" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F295" t="s">
         <v>3263</v>
@@ -30342,7 +30340,7 @@
         <v>27</v>
       </c>
       <c r="H295" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I295" t="s">
         <v>3264</v>
@@ -30360,7 +30358,7 @@
         <v>3268</v>
       </c>
       <c r="N295" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O295" t="s">
         <v>3269</v>
@@ -30369,7 +30367,7 @@
         <v>3270</v>
       </c>
       <c r="Q295" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R295"/>
       <c r="S295"/>
@@ -30406,7 +30404,7 @@
         <v>27</v>
       </c>
       <c r="H296" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I296" t="s">
         <v>3275</v>
@@ -30422,7 +30420,7 @@
         <v>3278</v>
       </c>
       <c r="N296" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O296" t="s">
         <v>3279</v>
@@ -30431,7 +30429,7 @@
         <v>3280</v>
       </c>
       <c r="Q296" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R296"/>
       <c r="S296"/>
@@ -30453,7 +30451,7 @@
         <v>3281</v>
       </c>
       <c r="C297" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D297" t="s">
         <v>3282</v>
@@ -30468,7 +30466,7 @@
         <v>27</v>
       </c>
       <c r="H297" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I297" t="s">
         <v>3284</v>
@@ -30486,7 +30484,7 @@
         <v>3288</v>
       </c>
       <c r="N297" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O297" t="s">
         <v>3289</v>
@@ -30517,7 +30515,7 @@
         <v>3291</v>
       </c>
       <c r="C298" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D298" t="s">
         <v>3292</v>
@@ -30532,7 +30530,7 @@
         <v>27</v>
       </c>
       <c r="H298" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I298" t="s">
         <v>3293</v>
@@ -30550,7 +30548,7 @@
         <v>3297</v>
       </c>
       <c r="N298" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O298" t="s">
         <v>3298</v>
@@ -30559,7 +30557,7 @@
         <v>3299</v>
       </c>
       <c r="Q298" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R298"/>
       <c r="S298"/>
@@ -30596,7 +30594,7 @@
         <v>27</v>
       </c>
       <c r="H299" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I299" t="s">
         <v>3303</v>
@@ -30614,7 +30612,7 @@
         <v>3307</v>
       </c>
       <c r="N299" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O299" t="s">
         <v>3308</v>
@@ -30660,7 +30658,7 @@
         <v>161</v>
       </c>
       <c r="H300" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I300" t="s">
         <v>3314</v>
@@ -30678,7 +30676,7 @@
         <v>3318</v>
       </c>
       <c r="N300" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O300" t="s">
         <v>3319</v>
@@ -30709,7 +30707,7 @@
         <v>3324</v>
       </c>
       <c r="C301" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D301" t="s">
         <v>1884</v>
@@ -30724,7 +30722,7 @@
         <v>27</v>
       </c>
       <c r="H301" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I301" t="s">
         <v>3326</v>
@@ -30742,7 +30740,7 @@
         <v>3330</v>
       </c>
       <c r="N301" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O301" t="s">
         <v>3331</v>
@@ -30779,7 +30777,7 @@
         <v>3334</v>
       </c>
       <c r="E302" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F302" t="s">
         <v>3335</v>
@@ -30804,7 +30802,7 @@
         <v>3339</v>
       </c>
       <c r="N302" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O302" t="s">
         <v>3340</v>
@@ -30850,7 +30848,7 @@
         <v>27</v>
       </c>
       <c r="H303" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I303" t="s">
         <v>3348</v>
@@ -30866,7 +30864,7 @@
         <v>3351</v>
       </c>
       <c r="N303" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O303" t="s">
         <v>3352</v>
@@ -30903,7 +30901,7 @@
         <v>1564</v>
       </c>
       <c r="E304" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F304" t="s">
         <v>3358</v>
@@ -30912,7 +30910,7 @@
         <v>27</v>
       </c>
       <c r="H304" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I304" t="s">
         <v>3359</v>
@@ -30930,7 +30928,7 @@
         <v>3363</v>
       </c>
       <c r="N304" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O304" t="s">
         <v>3364</v>
@@ -30944,13 +30942,13 @@
       <c r="R304"/>
       <c r="S304"/>
       <c r="T304" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="U304" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="V304" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="305">
@@ -30967,7 +30965,7 @@
         <v>1897</v>
       </c>
       <c r="E305" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F305" t="s">
         <v>3367</v>
@@ -30976,7 +30974,7 @@
         <v>27</v>
       </c>
       <c r="H305" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I305" t="s">
         <v>3368</v>
@@ -30994,7 +30992,7 @@
         <v>3372</v>
       </c>
       <c r="N305" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O305" t="s">
         <v>3373</v>
@@ -31025,7 +31023,7 @@
         <v>3375</v>
       </c>
       <c r="C306" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D306" t="s">
         <v>3376</v>
@@ -31040,7 +31038,7 @@
         <v>161</v>
       </c>
       <c r="H306" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I306" t="s">
         <v>3378</v>
@@ -31058,7 +31056,7 @@
         <v>3382</v>
       </c>
       <c r="N306" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O306" t="s">
         <v>3383</v>
@@ -31095,7 +31093,7 @@
         <v>3389</v>
       </c>
       <c r="E307" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F307" t="s">
         <v>3390</v>
@@ -31104,7 +31102,7 @@
         <v>27</v>
       </c>
       <c r="H307" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I307" t="s">
         <v>3391</v>
@@ -31122,7 +31120,7 @@
         <v>3395</v>
       </c>
       <c r="N307" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O307" t="s">
         <v>3396</v>
@@ -31153,7 +31151,7 @@
         <v>3401</v>
       </c>
       <c r="C308" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D308" t="s">
         <v>2804</v>
@@ -31168,7 +31166,7 @@
         <v>27</v>
       </c>
       <c r="H308" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I308" t="s">
         <v>3403</v>
@@ -31186,7 +31184,7 @@
         <v>3407</v>
       </c>
       <c r="N308" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O308" t="s">
         <v>3408</v>
@@ -31217,13 +31215,13 @@
         <v>3413</v>
       </c>
       <c r="C309" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D309" t="s">
         <v>1628</v>
       </c>
       <c r="E309" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F309" t="s">
         <v>3414</v>
@@ -31232,7 +31230,7 @@
         <v>27</v>
       </c>
       <c r="H309" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I309" t="s">
         <v>3415</v>
@@ -31250,7 +31248,7 @@
         <v>3419</v>
       </c>
       <c r="N309" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O309" t="s">
         <v>3420</v>
@@ -31314,7 +31312,7 @@
         <v>3428</v>
       </c>
       <c r="N310" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O310" t="s">
         <v>3429</v>
@@ -31351,7 +31349,7 @@
         <v>2695</v>
       </c>
       <c r="E311" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F311" t="s">
         <v>3432</v>
@@ -31378,7 +31376,7 @@
         <v>3437</v>
       </c>
       <c r="N311" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O311" t="s">
         <v>3438</v>
@@ -31442,7 +31440,7 @@
         <v>3449</v>
       </c>
       <c r="N312" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O312" t="s">
         <v>3450</v>
@@ -31451,7 +31449,7 @@
         <v>3451</v>
       </c>
       <c r="Q312" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R312"/>
       <c r="S312"/>
@@ -31479,7 +31477,7 @@
         <v>2578</v>
       </c>
       <c r="E313" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F313" t="s">
         <v>3453</v>
@@ -31504,7 +31502,7 @@
         <v>3457</v>
       </c>
       <c r="N313" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O313" t="s">
         <v>3458</v>
@@ -31518,13 +31516,13 @@
       <c r="R313"/>
       <c r="S313"/>
       <c r="T313" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="U313" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="V313" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="314">
@@ -31541,7 +31539,7 @@
         <v>1564</v>
       </c>
       <c r="E314" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F314" t="s">
         <v>3461</v>
@@ -31550,7 +31548,7 @@
         <v>27</v>
       </c>
       <c r="H314" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I314" t="s">
         <v>3462</v>
@@ -31566,7 +31564,7 @@
         <v>3465</v>
       </c>
       <c r="N314" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O314" t="s">
         <v>3466</v>
@@ -31575,7 +31573,7 @@
         <v>3467</v>
       </c>
       <c r="Q314" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R314"/>
       <c r="S314"/>
@@ -31612,7 +31610,7 @@
         <v>161</v>
       </c>
       <c r="H315" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I315" t="s">
         <v>3470</v>
@@ -31630,7 +31628,7 @@
         <v>3474</v>
       </c>
       <c r="N315" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O315" t="s">
         <v>3475</v>
@@ -31667,7 +31665,7 @@
         <v>3481</v>
       </c>
       <c r="E316" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F316" t="s">
         <v>3482</v>
@@ -31694,7 +31692,7 @@
         <v>3487</v>
       </c>
       <c r="N316" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O316" t="s">
         <v>3488</v>
@@ -31703,7 +31701,7 @@
         <v>3489</v>
       </c>
       <c r="Q316" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R316"/>
       <c r="S316"/>
@@ -31725,7 +31723,7 @@
         <v>3493</v>
       </c>
       <c r="C317" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D317" t="s">
         <v>3494</v>
@@ -31740,7 +31738,7 @@
         <v>27</v>
       </c>
       <c r="H317" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I317" t="s">
         <v>3496</v>
@@ -31758,7 +31756,7 @@
         <v>3500</v>
       </c>
       <c r="N317" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O317" t="s">
         <v>3501</v>
@@ -31767,7 +31765,7 @@
         <v>3502</v>
       </c>
       <c r="Q317" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R317"/>
       <c r="S317"/>
@@ -31795,7 +31793,7 @@
         <v>3504</v>
       </c>
       <c r="E318" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F318" t="s">
         <v>3505</v>
@@ -31804,7 +31802,7 @@
         <v>27</v>
       </c>
       <c r="H318" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I318" t="s">
         <v>3506</v>
@@ -31822,7 +31820,7 @@
         <v>3510</v>
       </c>
       <c r="N318" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O318" t="s">
         <v>3511</v>
@@ -31831,7 +31829,7 @@
         <v>3512</v>
       </c>
       <c r="Q318" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R318"/>
       <c r="S318"/>
@@ -31853,7 +31851,7 @@
         <v>3513</v>
       </c>
       <c r="C319" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D319" t="s">
         <v>2599</v>
@@ -31868,7 +31866,7 @@
         <v>27</v>
       </c>
       <c r="H319" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I319" t="s">
         <v>3515</v>
@@ -31886,7 +31884,7 @@
         <v>3519</v>
       </c>
       <c r="N319" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O319" t="s">
         <v>3520</v>
@@ -31895,18 +31893,18 @@
         <v>3521</v>
       </c>
       <c r="Q319" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R319"/>
       <c r="S319"/>
       <c r="T319" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="U319" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="V319" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="320">
@@ -31932,7 +31930,7 @@
         <v>27</v>
       </c>
       <c r="H320" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I320" t="s">
         <v>3524</v>
@@ -31950,7 +31948,7 @@
         <v>3528</v>
       </c>
       <c r="N320" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O320" t="s">
         <v>3529</v>
@@ -31987,7 +31985,7 @@
         <v>2742</v>
       </c>
       <c r="E321" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F321" t="s">
         <v>3514</v>
@@ -31996,7 +31994,7 @@
         <v>161</v>
       </c>
       <c r="H321" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I321" t="s">
         <v>3535</v>
@@ -32014,7 +32012,7 @@
         <v>3539</v>
       </c>
       <c r="N321" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O321" t="s">
         <v>3540</v>
@@ -32060,7 +32058,7 @@
         <v>27</v>
       </c>
       <c r="H322" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I322" t="s">
         <v>3546</v>
@@ -32078,7 +32076,7 @@
         <v>3550</v>
       </c>
       <c r="N322" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O322" t="s">
         <v>3551</v>
@@ -32087,7 +32085,7 @@
         <v>3552</v>
       </c>
       <c r="Q322" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R322"/>
       <c r="S322"/>
@@ -32115,7 +32113,7 @@
         <v>1409</v>
       </c>
       <c r="E323" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F323" t="s">
         <v>3557</v>
@@ -32124,7 +32122,7 @@
         <v>27</v>
       </c>
       <c r="H323" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I323" t="s">
         <v>3558</v>
@@ -32142,7 +32140,7 @@
         <v>3562</v>
       </c>
       <c r="N323" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O323" t="s">
         <v>3563</v>
@@ -32156,13 +32154,13 @@
       <c r="R323"/>
       <c r="S323"/>
       <c r="T323" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="U323" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="V323" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="324">
@@ -32173,7 +32171,7 @@
         <v>3565</v>
       </c>
       <c r="C324" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D324" t="s">
         <v>3566</v>
@@ -32206,7 +32204,7 @@
         <v>3572</v>
       </c>
       <c r="N324" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O324" t="s">
         <v>3573</v>
@@ -32215,18 +32213,18 @@
         <v>3574</v>
       </c>
       <c r="Q324" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R324"/>
       <c r="S324"/>
       <c r="T324" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="U324" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="V324" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="325">
@@ -32270,7 +32268,7 @@
         <v>3581</v>
       </c>
       <c r="N325" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O325" t="s">
         <v>3582</v>
@@ -32279,7 +32277,7 @@
         <v>3583</v>
       </c>
       <c r="Q325" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R325"/>
       <c r="S325"/>
@@ -32307,7 +32305,7 @@
         <v>1683</v>
       </c>
       <c r="E326" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="F326" t="s">
         <v>3585</v>
@@ -32334,7 +32332,7 @@
         <v>3590</v>
       </c>
       <c r="N326" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O326" t="s">
         <v>3591</v>
@@ -32365,13 +32363,13 @@
         <v>3593</v>
       </c>
       <c r="C327" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D327" t="s">
         <v>2959</v>
       </c>
       <c r="E327" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F327" t="s">
         <v>3594</v>
@@ -32380,7 +32378,7 @@
         <v>27</v>
       </c>
       <c r="H327" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="I327" t="s">
         <v>3595</v>
@@ -32398,7 +32396,7 @@
         <v>3599</v>
       </c>
       <c r="N327" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O327" t="s">
         <v>3600</v>
@@ -32462,7 +32460,7 @@
         <v>3610</v>
       </c>
       <c r="N328" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O328" t="s">
         <v>3611</v>
@@ -32471,7 +32469,7 @@
         <v>3612</v>
       </c>
       <c r="Q328" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R328"/>
       <c r="S328"/>
@@ -32526,7 +32524,7 @@
         <v>3618</v>
       </c>
       <c r="N329" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O329" t="s">
         <v>3619</v>
@@ -32572,7 +32570,7 @@
         <v>27</v>
       </c>
       <c r="H330" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I330" t="s">
         <v>3623</v>
@@ -32590,7 +32588,7 @@
         <v>3627</v>
       </c>
       <c r="N330" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O330" t="s">
         <v>3628</v>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -185,6 +185,57 @@
     <t xml:space="preserve">Scienza e ricerca|Ambiente|Salute</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gredig Corina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pvl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einführung eines öffentlichen Registers der Subventionsempfänger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer un registre public des bénéficiaires de subventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduzione di un registro pubblico dei beneficiari di sussidi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de créer un registre central public des bénéficiaires de subventions fédérales. Ce registre sera conçu pour compléter la banque de données sur les subventions et sa tenue sera confiée à la Confédération ou au Contrôle fédéral des finances. Il indiquera au minimum le nom du bénéficiaire ou son type, la nature et l’objet de la subvention, le montant annuel versé et l’office fédéral compétent et utilisera les données dont disposent les offices fédéraux.&amp;nbsp;&lt;br&gt;Les restrictions dictées par la protection des données et par la sécurité seront réservées.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, ein öffentlich einsehbares, zentrales Register der &amp;nbsp;Empfängerinnen und Empfänger von Bundessubventionen einzuführen. Das Register soll als Ergänzung zur bestehenden Subventionsdatenbank ausgestaltet und durch Bund oder EFK geführt werden. Es hat mindestens den Namen oder Empfängertyp, Art und Zweck der Subvention, den jährlich ausbezahlten Betrag sowie das zuständige Bundesamt auszuweisen. Es soll bestehenden Daten der Bundesämter nutzen.&amp;nbsp;&lt;br&gt;Datenschutz- und sicherheitsrelevante Einschränkungen bleiben vorbehalten.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eingereicht / Déposé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3485</t>
   </si>
   <si>
@@ -197,12 +248,6 @@
     <t xml:space="preserve">UDC</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Externes Audit des Bundesamts für Zoll und Grenzsicherheit zur Wiederherstellung des Vertrauens des Personals und der Wirtschaft</t>
   </si>
   <si>
@@ -218,9 +263,6 @@
     <t xml:space="preserve">&lt;p&gt;Bevor irreversible Entscheide getroffen werden, wird der Bundesrat beauftragt, ein externes Audit des Bundesamts für Zoll und Grenzsicherheit (BAZG) und dessen laufender Umstrukturierung in Auftrag zu geben, das insbesondere folgende Punkte umfasst:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Angemessenheit der Mittel (Budget und Personal) für die vielfältigen Aufgaben des BAZG, insbesondere für die Überwachung der Landesgrenze, die Migrationskontrolle und die Bekämpfung von Schmuggel aller Art (landwirtschaftliche Produkte, Tiere, invasive Pflanzen);&lt;/li&gt;&lt;li&gt;Wirksamkeit des Programms Dazit bei der Zollerhebung (rückläufige Einnahmen&amp;nbsp;2025), insbesondere angesichts des Wegfalls der systematischen Kontrolle ausländischer Lastwagen und der Erwartungen der Wirtschaft (in Anlehnung an die sehr harte Kritik des Transportunternehmers Marco Tepoorten, der von einer «systemischen Desorganisation» sprach);&lt;/li&gt;&lt;li&gt;Flexibilisierung von Allegra;&lt;/li&gt;&lt;li&gt;Krankheitsabsenzen und Abgänge beim BAZG;&lt;/li&gt;&lt;li&gt;Attraktivität des BAZG-Personalstatus;&lt;/li&gt;&lt;li&gt;Ausbildung (mit offenbar ungewöhnlich hoher Durchfallquote);&lt;/li&gt;&lt;li&gt;untypische Fluktuationsrate bei den Führungskräften des BAZG;&lt;/li&gt;&lt;li&gt;Wäre es nicht angebracht, Lehren aus vergleichbaren Umstrukturierungen im Ausland (Österreich, Kanada) zu ziehen – insbesondere aus gewissen Misserfolgen –, bevor weiter in eine fragwürdige Richtung vorgeprescht wird?&lt;/li&gt;&lt;li&gt;Welche Massnahmen sind notwendig, um das Vertrauen des Personals und der Wirtschaft wiederherzustellen und die Wirksamkeit des BAZG bei der Aufgabenerfüllung zu gewährleisten?&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Eingereicht / Déposé</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263485</t>
   </si>
   <si>
@@ -234,48 +276,6 @@
   </si>
   <si>
     <t xml:space="preserve">Politica nazionale|Finanze|Occupazione e lavoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gredig Corina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pvl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einführung eines öffentlichen Registers der Subventionsempfänger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Créer un registre public des bénéficiaires de subventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introduzione di un registro pubblico dei beneficiari di sussidi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de créer un registre central public des bénéficiaires de subventions fédérales. Ce registre sera conçu pour compléter la banque de données sur les subventions et sa tenue sera confiée à la Confédération ou au Contrôle fédéral des finances. Il indiquera au minimum le nom du bénéficiaire ou son type, la nature et l’objet de la subvention, le montant annuel versé et l’office fédéral compétent et utilisera les données dont disposent les offices fédéraux.&amp;nbsp;&lt;br&gt;Les restrictions dictées par la protection des données et par la sécurité seront réservées.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, ein öffentlich einsehbares, zentrales Register der &amp;nbsp;Empfängerinnen und Empfänger von Bundessubventionen einzuführen. Das Register soll als Ergänzung zur bestehenden Subventionsdatenbank ausgestaltet und durch Bund oder EFK geführt werden. Es hat mindestens den Namen oder Empfängertyp, Art und Zweck der Subvention, den jährlich ausbezahlten Betrag sowie das zuständige Bundesamt auszuweisen. Es soll bestehenden Daten der Bundesämter nutzen.&amp;nbsp;&lt;br&gt;Datenschutz- und sicherheitsrelevante Einschränkungen bleiben vorbehalten.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze</t>
   </si>
   <si>
     <t xml:space="preserve">26.3487</t>
@@ -11473,7 +11473,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263485</v>
+        <v>20263398</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -11539,7 +11539,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263398</v>
+        <v>20263485</v>
       </c>
       <c r="B5" t="s">
         <v>74</v>
@@ -11749,7 +11749,7 @@
         <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
         <v>121</v>
@@ -12007,7 +12007,7 @@
         <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
         <v>173</v>
@@ -12269,7 +12269,7 @@
         <v>225</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F16" t="s">
         <v>226</v>
@@ -12312,13 +12312,13 @@
       </c>
       <c r="S16"/>
       <c r="T16" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="U16" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="V16" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -12335,7 +12335,7 @@
         <v>237</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s">
         <v>238</v>
@@ -12395,7 +12395,7 @@
         <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
         <v>252</v>
@@ -12527,7 +12527,7 @@
         <v>276</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
         <v>277</v>
@@ -12599,7 +12599,7 @@
         <v>283</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
         <v>238</v>
@@ -12725,7 +12725,7 @@
         <v>307</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
         <v>133</v>
@@ -12791,7 +12791,7 @@
         <v>318</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
         <v>319</v>
@@ -12923,7 +12923,7 @@
         <v>344</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
         <v>345</v>
@@ -12995,7 +12995,7 @@
         <v>357</v>
       </c>
       <c r="E27" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F27" t="s">
         <v>358</v>
@@ -13059,7 +13059,7 @@
         <v>369</v>
       </c>
       <c r="E28" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s">
         <v>358</v>
@@ -13185,7 +13185,7 @@
         <v>394</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
         <v>395</v>
@@ -13251,7 +13251,7 @@
         <v>407</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
         <v>43</v>
@@ -13383,7 +13383,7 @@
         <v>432</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D33" t="s">
         <v>433</v>
@@ -13449,13 +13449,13 @@
         <v>445</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
         <v>446</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F34" t="s">
         <v>409</v>
@@ -13975,7 +13975,7 @@
         <v>539</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D42" t="s">
         <v>540</v>
@@ -14305,7 +14305,7 @@
         <v>597</v>
       </c>
       <c r="E47" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F47" t="s">
         <v>584</v>
@@ -14363,7 +14363,7 @@
         <v>607</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D48" t="s">
         <v>608</v>
@@ -14761,7 +14761,7 @@
         <v>446</v>
       </c>
       <c r="E54" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F54" t="s">
         <v>680</v>
@@ -14953,7 +14953,7 @@
         <v>709</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D57" t="s">
         <v>43</v>
@@ -15019,7 +15019,7 @@
         <v>720</v>
       </c>
       <c r="C58" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D58" t="s">
         <v>43</v>
@@ -15287,7 +15287,7 @@
         <v>446</v>
       </c>
       <c r="E62" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F62" t="s">
         <v>751</v>
@@ -15479,7 +15479,7 @@
         <v>794</v>
       </c>
       <c r="E65" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F65" t="s">
         <v>795</v>
@@ -15739,7 +15739,7 @@
         <v>830</v>
       </c>
       <c r="E69" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F69" t="s">
         <v>821</v>
@@ -15799,13 +15799,13 @@
         <v>841</v>
       </c>
       <c r="C70" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D70" t="s">
         <v>830</v>
       </c>
       <c r="E70" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F70" t="s">
         <v>821</v>
@@ -15997,7 +15997,7 @@
         <v>871</v>
       </c>
       <c r="C73" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D73" t="s">
         <v>872</v>
@@ -16061,7 +16061,7 @@
         <v>881</v>
       </c>
       <c r="C74" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D74" t="s">
         <v>882</v>
@@ -16128,10 +16128,10 @@
         <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="E75" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F75" t="s">
         <v>893</v>
@@ -16191,13 +16191,13 @@
         <v>904</v>
       </c>
       <c r="C76" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D76" t="s">
         <v>446</v>
       </c>
       <c r="E76" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F76" t="s">
         <v>905</v>
@@ -16323,13 +16323,13 @@
         <v>924</v>
       </c>
       <c r="C78" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D78" t="s">
         <v>925</v>
       </c>
       <c r="E78" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F78" t="s">
         <v>926</v>
@@ -16500,13 +16500,13 @@
       </c>
       <c r="S80"/>
       <c r="T80" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="U80" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="V80" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81">
@@ -16655,7 +16655,7 @@
         <v>980</v>
       </c>
       <c r="E83" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F83" t="s">
         <v>981</v>
@@ -16721,7 +16721,7 @@
         <v>993</v>
       </c>
       <c r="E84" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F84" t="s">
         <v>994</v>
@@ -16781,7 +16781,7 @@
         <v>1005</v>
       </c>
       <c r="C85" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D85" t="s">
         <v>1006</v>
@@ -16851,7 +16851,7 @@
         <v>1019</v>
       </c>
       <c r="E86" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F86" t="s">
         <v>1020</v>
@@ -16969,13 +16969,13 @@
         <v>1039</v>
       </c>
       <c r="C88" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D88" t="s">
         <v>597</v>
       </c>
       <c r="E88" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F88" t="s">
         <v>1040</v>
@@ -17167,7 +17167,7 @@
         <v>1069</v>
       </c>
       <c r="C91" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D91" t="s">
         <v>1070</v>
@@ -17233,13 +17233,13 @@
         <v>1082</v>
       </c>
       <c r="C92" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D92" t="s">
         <v>1083</v>
       </c>
       <c r="E92" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F92" t="s">
         <v>1071</v>
@@ -17299,7 +17299,7 @@
         <v>1094</v>
       </c>
       <c r="C93" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D93" t="s">
         <v>43</v>
@@ -17348,13 +17348,13 @@
       </c>
       <c r="S93"/>
       <c r="T93" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="U93" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="V93" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="94">
@@ -17365,7 +17365,7 @@
         <v>1103</v>
       </c>
       <c r="C94" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D94" t="s">
         <v>1104</v>
@@ -17497,7 +17497,7 @@
         <v>1126</v>
       </c>
       <c r="C96" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D96" t="s">
         <v>1127</v>
@@ -17701,7 +17701,7 @@
         <v>1164</v>
       </c>
       <c r="E99" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F99" t="s">
         <v>1152</v>
@@ -17893,7 +17893,7 @@
         <v>1192</v>
       </c>
       <c r="C102" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D102" t="s">
         <v>1193</v>
@@ -17959,7 +17959,7 @@
         <v>1205</v>
       </c>
       <c r="C103" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D103" t="s">
         <v>213</v>
@@ -18025,7 +18025,7 @@
         <v>1217</v>
       </c>
       <c r="C104" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D104" t="s">
         <v>213</v>
@@ -18163,7 +18163,7 @@
         <v>830</v>
       </c>
       <c r="E106" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F106" t="s">
         <v>1230</v>
@@ -18223,13 +18223,13 @@
         <v>1252</v>
       </c>
       <c r="C107" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D107" t="s">
         <v>446</v>
       </c>
       <c r="E107" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F107" t="s">
         <v>1230</v>
@@ -18272,13 +18272,13 @@
       </c>
       <c r="S107"/>
       <c r="T107" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="U107" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="V107" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="108">
@@ -18355,7 +18355,7 @@
         <v>1273</v>
       </c>
       <c r="C109" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D109" t="s">
         <v>967</v>
@@ -18553,13 +18553,13 @@
         <v>1301</v>
       </c>
       <c r="C112" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D112" t="s">
         <v>1302</v>
       </c>
       <c r="E112" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F112" t="s">
         <v>1293</v>
@@ -19011,13 +19011,13 @@
         <v>1374</v>
       </c>
       <c r="C119" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D119" t="s">
         <v>1375</v>
       </c>
       <c r="E119" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F119" t="s">
         <v>1376</v>
@@ -19077,7 +19077,7 @@
         <v>1387</v>
       </c>
       <c r="C120" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D120" t="s">
         <v>1388</v>
@@ -19211,7 +19211,7 @@
         <v>1409</v>
       </c>
       <c r="E122" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F122" t="s">
         <v>1410</v>
@@ -19269,7 +19269,7 @@
         <v>1417</v>
       </c>
       <c r="C123" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D123" t="s">
         <v>1418</v>
@@ -19601,7 +19601,7 @@
         <v>1480</v>
       </c>
       <c r="E128" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F128" t="s">
         <v>1481</v>
@@ -19989,7 +19989,7 @@
         <v>1550</v>
       </c>
       <c r="C134" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D134" t="s">
         <v>1551</v>
@@ -20061,7 +20061,7 @@
         <v>1564</v>
       </c>
       <c r="E135" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F135" t="s">
         <v>1552</v>
@@ -20125,7 +20125,7 @@
         <v>120</v>
       </c>
       <c r="E136" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F136" t="s">
         <v>1575</v>
@@ -20183,7 +20183,7 @@
         <v>1582</v>
       </c>
       <c r="C137" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D137" t="s">
         <v>872</v>
@@ -20313,7 +20313,7 @@
         <v>1604</v>
       </c>
       <c r="C139" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D139" t="s">
         <v>967</v>
@@ -20379,13 +20379,13 @@
         <v>1616</v>
       </c>
       <c r="C140" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D140" t="s">
         <v>1480</v>
       </c>
       <c r="E140" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F140" t="s">
         <v>1605</v>
@@ -20451,7 +20451,7 @@
         <v>1628</v>
       </c>
       <c r="E141" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F141" t="s">
         <v>1605</v>
@@ -20511,13 +20511,13 @@
         <v>1639</v>
       </c>
       <c r="C142" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D142" t="s">
         <v>1640</v>
       </c>
       <c r="E142" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F142" t="s">
         <v>1641</v>
@@ -20649,7 +20649,7 @@
         <v>1302</v>
       </c>
       <c r="E144" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F144" t="s">
         <v>1665</v>
@@ -20969,7 +20969,7 @@
         <v>1710</v>
       </c>
       <c r="C149" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D149" t="s">
         <v>1711</v>
@@ -21035,7 +21035,7 @@
         <v>1722</v>
       </c>
       <c r="C150" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D150" t="s">
         <v>43</v>
@@ -21299,7 +21299,7 @@
         <v>1766</v>
       </c>
       <c r="C154" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D154" t="s">
         <v>1767</v>
@@ -21623,7 +21623,7 @@
         <v>1814</v>
       </c>
       <c r="C159" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D159" t="s">
         <v>1815</v>
@@ -21687,7 +21687,7 @@
         <v>1825</v>
       </c>
       <c r="C160" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D160" t="s">
         <v>608</v>
@@ -21817,7 +21817,7 @@
         <v>1849</v>
       </c>
       <c r="C162" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D162" t="s">
         <v>1104</v>
@@ -21883,7 +21883,7 @@
         <v>1861</v>
       </c>
       <c r="C163" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D163" t="s">
         <v>1862</v>
@@ -22085,7 +22085,7 @@
         <v>1897</v>
       </c>
       <c r="E166" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F166" t="s">
         <v>1885</v>
@@ -22145,7 +22145,7 @@
         <v>1908</v>
       </c>
       <c r="C167" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D167" t="s">
         <v>1909</v>
@@ -22283,7 +22283,7 @@
         <v>830</v>
       </c>
       <c r="E169" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F169" t="s">
         <v>1921</v>
@@ -22343,7 +22343,7 @@
         <v>1943</v>
       </c>
       <c r="C170" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D170" t="s">
         <v>862</v>
@@ -22481,7 +22481,7 @@
         <v>1961</v>
       </c>
       <c r="E172" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F172" t="s">
         <v>1962</v>
@@ -22607,7 +22607,7 @@
         <v>1985</v>
       </c>
       <c r="C174" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D174" t="s">
         <v>1986</v>
@@ -22739,7 +22739,7 @@
         <v>2003</v>
       </c>
       <c r="C176" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D176" t="s">
         <v>2004</v>
@@ -23329,7 +23329,7 @@
         <v>2105</v>
       </c>
       <c r="C185" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D185" t="s">
         <v>1397</v>
@@ -23593,13 +23593,13 @@
         <v>2151</v>
       </c>
       <c r="C189" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D189" t="s">
         <v>2152</v>
       </c>
       <c r="E189" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F189" t="s">
         <v>2153</v>
@@ -23795,7 +23795,7 @@
         <v>1628</v>
       </c>
       <c r="E192" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F192" t="s">
         <v>2189</v>
@@ -23855,7 +23855,7 @@
         <v>2197</v>
       </c>
       <c r="C193" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D193" t="s">
         <v>608</v>
@@ -24115,13 +24115,13 @@
         <v>2246</v>
       </c>
       <c r="C197" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D197" t="s">
         <v>446</v>
       </c>
       <c r="E197" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F197" t="s">
         <v>2247</v>
@@ -24181,7 +24181,7 @@
         <v>2258</v>
       </c>
       <c r="C198" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D198" t="s">
         <v>2259</v>
@@ -24245,7 +24245,7 @@
         <v>2271</v>
       </c>
       <c r="C199" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D199" t="s">
         <v>2272</v>
@@ -24309,7 +24309,7 @@
         <v>2284</v>
       </c>
       <c r="C200" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D200" t="s">
         <v>2272</v>
@@ -24373,13 +24373,13 @@
         <v>2295</v>
       </c>
       <c r="C201" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D201" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E201" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F201" t="s">
         <v>226</v>
@@ -24443,7 +24443,7 @@
         <v>830</v>
       </c>
       <c r="E202" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F202" t="s">
         <v>226</v>
@@ -24501,7 +24501,7 @@
         <v>2314</v>
       </c>
       <c r="C203" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D203" t="s">
         <v>2315</v>
@@ -24565,7 +24565,7 @@
         <v>2327</v>
       </c>
       <c r="C204" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D204" t="s">
         <v>484</v>
@@ -24635,7 +24635,7 @@
         <v>2339</v>
       </c>
       <c r="E205" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F205" t="s">
         <v>2340</v>
@@ -24753,7 +24753,7 @@
         <v>2357</v>
       </c>
       <c r="C207" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D207" t="s">
         <v>1057</v>
@@ -24800,13 +24800,13 @@
       <c r="R207"/>
       <c r="S207"/>
       <c r="T207" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="U207" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="V207" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="208">
@@ -24817,7 +24817,7 @@
         <v>2366</v>
       </c>
       <c r="C208" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D208" t="s">
         <v>2367</v>
@@ -24881,7 +24881,7 @@
         <v>2376</v>
       </c>
       <c r="C209" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D209" t="s">
         <v>188</v>
@@ -24945,7 +24945,7 @@
         <v>2387</v>
       </c>
       <c r="C210" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D210" t="s">
         <v>2388</v>
@@ -24992,13 +24992,13 @@
       <c r="R210"/>
       <c r="S210"/>
       <c r="T210" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="U210" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="V210" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="211">
@@ -25009,7 +25009,7 @@
         <v>2394</v>
       </c>
       <c r="C211" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D211" t="s">
         <v>2395</v>
@@ -25137,7 +25137,7 @@
         <v>2414</v>
       </c>
       <c r="C213" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D213" t="s">
         <v>2415</v>
@@ -25515,7 +25515,7 @@
         <v>2472</v>
       </c>
       <c r="C219" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D219" t="s">
         <v>2473</v>
@@ -25580,10 +25580,10 @@
         <v>187</v>
       </c>
       <c r="D220" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E220" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F220" t="s">
         <v>174</v>
@@ -25827,7 +25827,7 @@
         <v>2521</v>
       </c>
       <c r="C224" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D224" t="s">
         <v>2522</v>
@@ -25889,7 +25889,7 @@
         <v>2531</v>
       </c>
       <c r="C225" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D225" t="s">
         <v>2532</v>
@@ -25959,7 +25959,7 @@
         <v>1302</v>
       </c>
       <c r="E226" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F226" t="s">
         <v>2545</v>
@@ -26023,7 +26023,7 @@
         <v>2557</v>
       </c>
       <c r="E227" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F227" t="s">
         <v>2558</v>
@@ -26149,7 +26149,7 @@
         <v>2578</v>
       </c>
       <c r="E229" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F229" t="s">
         <v>2579</v>
@@ -26210,10 +26210,10 @@
         <v>23</v>
       </c>
       <c r="D230" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E230" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F230" t="s">
         <v>2579</v>
@@ -26341,7 +26341,7 @@
         <v>1628</v>
       </c>
       <c r="E232" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F232" t="s">
         <v>2611</v>
@@ -26655,7 +26655,7 @@
         <v>2658</v>
       </c>
       <c r="C237" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D237" t="s">
         <v>2659</v>
@@ -26851,7 +26851,7 @@
         <v>2695</v>
       </c>
       <c r="E240" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F240" t="s">
         <v>2696</v>
@@ -26909,13 +26909,13 @@
         <v>2707</v>
       </c>
       <c r="C241" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D241" t="s">
         <v>1302</v>
       </c>
       <c r="E241" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F241" t="s">
         <v>2696</v>
@@ -26979,7 +26979,7 @@
         <v>120</v>
       </c>
       <c r="E242" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F242" t="s">
         <v>2696</v>
@@ -27037,7 +27037,7 @@
         <v>2729</v>
       </c>
       <c r="C243" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D243" t="s">
         <v>2599</v>
@@ -27107,7 +27107,7 @@
         <v>2742</v>
       </c>
       <c r="E244" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F244" t="s">
         <v>2730</v>
@@ -27229,7 +27229,7 @@
         <v>2766</v>
       </c>
       <c r="C246" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D246" t="s">
         <v>2767</v>
@@ -27417,13 +27417,13 @@
         <v>2793</v>
       </c>
       <c r="C249" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D249" t="s">
         <v>2794</v>
       </c>
       <c r="E249" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F249" t="s">
         <v>2795</v>
@@ -27545,13 +27545,13 @@
         <v>2813</v>
       </c>
       <c r="C251" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D251" t="s">
         <v>120</v>
       </c>
       <c r="E251" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F251" t="s">
         <v>2805</v>
@@ -27615,7 +27615,7 @@
         <v>2794</v>
       </c>
       <c r="E252" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F252" t="s">
         <v>2825</v>
@@ -27919,7 +27919,7 @@
         <v>2875</v>
       </c>
       <c r="C257" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D257" t="s">
         <v>2876</v>
@@ -27983,7 +27983,7 @@
         <v>2885</v>
       </c>
       <c r="C258" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D258" t="s">
         <v>1711</v>
@@ -28111,7 +28111,7 @@
         <v>2906</v>
       </c>
       <c r="C260" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D260" t="s">
         <v>574</v>
@@ -28175,7 +28175,7 @@
         <v>2914</v>
       </c>
       <c r="C261" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D261" t="s">
         <v>574</v>
@@ -28239,13 +28239,13 @@
         <v>2922</v>
       </c>
       <c r="C262" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D262" t="s">
         <v>2923</v>
       </c>
       <c r="E262" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F262" t="s">
         <v>2886</v>
@@ -28373,7 +28373,7 @@
         <v>1019</v>
       </c>
       <c r="E264" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F264" t="s">
         <v>2936</v>
@@ -28437,7 +28437,7 @@
         <v>2959</v>
       </c>
       <c r="E265" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F265" t="s">
         <v>2960</v>
@@ -28495,7 +28495,7 @@
         <v>2971</v>
       </c>
       <c r="C266" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D266" t="s">
         <v>2895</v>
@@ -28565,7 +28565,7 @@
         <v>2959</v>
       </c>
       <c r="E267" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F267" t="s">
         <v>2972</v>
@@ -29313,13 +29313,13 @@
         <v>3110</v>
       </c>
       <c r="C279" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D279" t="s">
         <v>1083</v>
       </c>
       <c r="E279" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F279" t="s">
         <v>3098</v>
@@ -29447,7 +29447,7 @@
         <v>2578</v>
       </c>
       <c r="E281" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F281" t="s">
         <v>3098</v>
@@ -29569,7 +29569,7 @@
         <v>3151</v>
       </c>
       <c r="C283" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D283" t="s">
         <v>1353</v>
@@ -29767,7 +29767,7 @@
         <v>2742</v>
       </c>
       <c r="E286" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F286" t="s">
         <v>3177</v>
@@ -29808,13 +29808,13 @@
       <c r="R286"/>
       <c r="S286"/>
       <c r="T286" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="U286" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="V286" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="287">
@@ -30205,7 +30205,7 @@
         <v>2557</v>
       </c>
       <c r="E293" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F293" t="s">
         <v>3217</v>
@@ -30331,7 +30331,7 @@
         <v>3262</v>
       </c>
       <c r="E295" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F295" t="s">
         <v>3263</v>
@@ -30451,7 +30451,7 @@
         <v>3281</v>
       </c>
       <c r="C297" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D297" t="s">
         <v>3282</v>
@@ -30515,7 +30515,7 @@
         <v>3291</v>
       </c>
       <c r="C298" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D298" t="s">
         <v>3292</v>
@@ -30707,7 +30707,7 @@
         <v>3324</v>
       </c>
       <c r="C301" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D301" t="s">
         <v>1884</v>
@@ -30777,7 +30777,7 @@
         <v>3334</v>
       </c>
       <c r="E302" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F302" t="s">
         <v>3335</v>
@@ -30901,7 +30901,7 @@
         <v>1564</v>
       </c>
       <c r="E304" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F304" t="s">
         <v>3358</v>
@@ -30942,13 +30942,13 @@
       <c r="R304"/>
       <c r="S304"/>
       <c r="T304" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="U304" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="V304" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="305">
@@ -30965,7 +30965,7 @@
         <v>1897</v>
       </c>
       <c r="E305" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F305" t="s">
         <v>3367</v>
@@ -31023,7 +31023,7 @@
         <v>3375</v>
       </c>
       <c r="C306" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D306" t="s">
         <v>3376</v>
@@ -31093,7 +31093,7 @@
         <v>3389</v>
       </c>
       <c r="E307" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F307" t="s">
         <v>3390</v>
@@ -31151,7 +31151,7 @@
         <v>3401</v>
       </c>
       <c r="C308" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D308" t="s">
         <v>2804</v>
@@ -31215,13 +31215,13 @@
         <v>3413</v>
       </c>
       <c r="C309" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D309" t="s">
         <v>1628</v>
       </c>
       <c r="E309" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F309" t="s">
         <v>3414</v>
@@ -31349,7 +31349,7 @@
         <v>2695</v>
       </c>
       <c r="E311" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F311" t="s">
         <v>3432</v>
@@ -31477,7 +31477,7 @@
         <v>2578</v>
       </c>
       <c r="E313" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F313" t="s">
         <v>3453</v>
@@ -31539,7 +31539,7 @@
         <v>1564</v>
       </c>
       <c r="E314" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F314" t="s">
         <v>3461</v>
@@ -31723,7 +31723,7 @@
         <v>3493</v>
       </c>
       <c r="C317" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D317" t="s">
         <v>3494</v>
@@ -31793,7 +31793,7 @@
         <v>3504</v>
       </c>
       <c r="E318" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F318" t="s">
         <v>3505</v>
@@ -31851,7 +31851,7 @@
         <v>3513</v>
       </c>
       <c r="C319" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D319" t="s">
         <v>2599</v>
@@ -31985,7 +31985,7 @@
         <v>2742</v>
       </c>
       <c r="E321" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F321" t="s">
         <v>3514</v>
@@ -32113,7 +32113,7 @@
         <v>1409</v>
       </c>
       <c r="E323" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F323" t="s">
         <v>3557</v>
@@ -32154,13 +32154,13 @@
       <c r="R323"/>
       <c r="S323"/>
       <c r="T323" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="U323" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="V323" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="324">
@@ -32171,7 +32171,7 @@
         <v>3565</v>
       </c>
       <c r="C324" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D324" t="s">
         <v>3566</v>
@@ -32363,13 +32363,13 @@
         <v>3593</v>
       </c>
       <c r="C327" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D327" t="s">
         <v>2959</v>
       </c>
       <c r="E327" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F327" t="s">
         <v>3594</v>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -983,7 +983,7 @@
     <t xml:space="preserve">Verwaltungspraxis bei Fintech-Lizenzen</t>
   </si>
   <si>
-    <t xml:space="preserve">Pratique administrative relative aux autorisations Fintech</t>
+    <t xml:space="preserve">Pratique administrative relative aux autorisations fintech</t>
   </si>
   <si>
     <t xml:space="preserve">Prassi amministrativa per le licenze fintech</t>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -17747,9 +17747,15 @@
         <v>354</v>
       </c>
       <c r="S95"/>
-      <c r="T95"/>
-      <c r="U95"/>
-      <c r="V95"/>
+      <c r="T95" t="s">
+        <v>294</v>
+      </c>
+      <c r="U95" t="s">
+        <v>295</v>
+      </c>
+      <c r="V95" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -179,21 +179,54 @@
     <t xml:space="preserve">Politica nazionale|Media e comunicazione|Protezione sociale</t>
   </si>
   <si>
+    <t xml:space="preserve">26.7321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de Quattro Jacqueline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgische Staatsangehörige: überdurchschnittlich hohe Gesundheitskosten </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Géorgiens : des coûts médicaux supérieurs à la moyenne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Un audit du Contrôle fédéral des finances confirme des coûts médicaux très supérieurs à la moyenne pour les requérants géorgiens, soit 44,40&amp;nbsp;fr par jour et par personne. Entre 2022 et 2025, 26 d’entre eux ont été pris en charge par le SEM pour des traitements lourds. Parmi eux, 17 cas ont bénéficié d’un soutien financier total ou partiel du SEM pour 2,5&amp;nbsp;millions. Avec un cas allant jusqu’à 1,37&amp;nbsp;million. Quand et comment le Conseil fédéral va-t-il enrayer ce tourisme médical ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Eine Prüfung der Eidgenössischen Finanzkontrolle zeigt, dass die medizinischen Kosten für georgische Asylsuchende mit Fr.&amp;nbsp;44.40 pro Tag und Person deutlich über dem Durchschnitt liegen. Zwischen 2022 und 2025 benötigten 26&amp;nbsp;Asylsuchende Kostengutsprachen des Staatssekretariats für Migration&amp;nbsp;(SEM) für aufwändige Behandlungen. 17 von ihnen erhielten eine vollständige oder teilweise finanzielle Unterstützung durch das SEM im Gesamtumfang von 2,5&amp;nbsp;Millionen&amp;nbsp;Franken. In einem Fall lagen die Kosten bei bis zu 1,37&amp;nbsp;Millionen&amp;nbsp;Franken. Wann und wie wird der Bundesrat diesem Medizintourismus Einhalt gebieten?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen|Migration|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances|Politique migratoire|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze|Migrazione|Salute</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.7324</t>
   </si>
   <si>
-    <t xml:space="preserve">de Quattro Jacqueline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EJPD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Schwachstellen im Staatssekretariat für Migration </t>
   </si>
   <si>
@@ -267,39 +300,6 @@
   </si>
   <si>
     <t xml:space="preserve">Politica nazionale|Finanze|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georgische Staatsangehörige: überdurchschnittlich hohe Gesundheitskosten </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Géorgiens : des coûts médicaux supérieurs à la moyenne </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Un audit du Contrôle fédéral des finances confirme des coûts médicaux très supérieurs à la moyenne pour les requérants géorgiens, soit 44,40&amp;nbsp;fr par jour et par personne. Entre 2022 et 2025, 26 d’entre eux ont été pris en charge par le SEM pour des traitements lourds. Parmi eux, 17 cas ont bénéficié d’un soutien financier total ou partiel du SEM pour 2,5&amp;nbsp;millions. Avec un cas allant jusqu’à 1,37&amp;nbsp;million. Quand et comment le Conseil fédéral va-t-il enrayer ce tourisme médical ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Eine Prüfung der Eidgenössischen Finanzkontrolle zeigt, dass die medizinischen Kosten für georgische Asylsuchende mit Fr.&amp;nbsp;44.40 pro Tag und Person deutlich über dem Durchschnitt liegen. Zwischen 2022 und 2025 benötigten 26&amp;nbsp;Asylsuchende Kostengutsprachen des Staatssekretariats für Migration&amp;nbsp;(SEM) für aufwändige Behandlungen. 17 von ihnen erhielten eine vollständige oder teilweise finanzielle Unterstützung durch das SEM im Gesamtumfang von 2,5&amp;nbsp;Millionen&amp;nbsp;Franken. In einem Fall lagen die Kosten bei bis zu 1,37&amp;nbsp;Millionen&amp;nbsp;Franken. Wann und wie wird der Bundesrat diesem Medizintourismus Einhalt gebieten?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen|Migration|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances|Politique migratoire|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze|Migrazione|Salute</t>
   </si>
   <si>
     <t xml:space="preserve">26.3335</t>
@@ -11838,7 +11838,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20267324</v>
+        <v>20267321</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -11884,124 +11884,124 @@
         <v>65</v>
       </c>
       <c r="Q4" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="R4" t="s">
         <v>37</v>
       </c>
       <c r="S4"/>
       <c r="T4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263550</v>
+        <v>20267324</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" t="s">
         <v>71</v>
       </c>
-      <c r="E5" t="s">
+      <c r="J5" t="s">
         <v>72</v>
       </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="K5"/>
+      <c r="L5" t="s">
         <v>73</v>
       </c>
-      <c r="H5"/>
-      <c r="I5" t="s">
+      <c r="M5" t="s">
         <v>74</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" t="s">
         <v>75</v>
       </c>
-      <c r="K5" t="s">
+      <c r="P5" t="s">
         <v>76</v>
       </c>
-      <c r="L5"/>
-      <c r="M5" t="s">
-        <v>77</v>
-      </c>
-      <c r="N5" t="s">
-        <v>78</v>
-      </c>
-      <c r="O5" t="s">
-        <v>79</v>
-      </c>
-      <c r="P5" t="s">
-        <v>80</v>
-      </c>
       <c r="Q5" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="R5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S5"/>
       <c r="T5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="V5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20267321</v>
+        <v>20263550</v>
       </c>
       <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6"/>
+      <c r="I6" t="s">
         <v>85</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>86</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>87</v>
       </c>
-      <c r="K6"/>
-      <c r="L6" t="s">
+      <c r="L6"/>
+      <c r="M6" t="s">
         <v>88</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>89</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
       </c>
       <c r="O6" t="s">
         <v>90</v>
@@ -12013,11 +12013,9 @@
         <v>92</v>
       </c>
       <c r="R6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S6" t="s">
-        <v>37</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="S6"/>
       <c r="T6" t="s">
         <v>93</v>
       </c>
@@ -12036,7 +12034,7 @@
         <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
         <v>97</v>
@@ -12180,7 +12178,7 @@
         <v>99</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -12246,7 +12244,7 @@
         <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s">
         <v>145</v>
@@ -12300,19 +12298,19 @@
         <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
         <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F11" t="s">
         <v>155</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s">
         <v>156</v>
@@ -12408,7 +12406,7 @@
         <v>177</v>
       </c>
       <c r="Q12" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R12" t="s">
         <v>178</v>
@@ -12438,7 +12436,7 @@
         <v>183</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F13" t="s">
         <v>170</v>
@@ -12474,7 +12472,7 @@
         <v>190</v>
       </c>
       <c r="Q13" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R13" t="s">
         <v>178</v>
@@ -12498,7 +12496,7 @@
         <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>195</v>
@@ -12540,7 +12538,7 @@
         <v>202</v>
       </c>
       <c r="Q14" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R14" t="s">
         <v>178</v>
@@ -12564,13 +12562,13 @@
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
         <v>207</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F15" t="s">
         <v>155</v>
@@ -12630,7 +12628,7 @@
         <v>218</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
         <v>219</v>
@@ -12696,7 +12694,7 @@
         <v>231</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
         <v>232</v>
@@ -12762,7 +12760,7 @@
         <v>245</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
         <v>246</v>
@@ -12804,7 +12802,7 @@
         <v>254</v>
       </c>
       <c r="Q18" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R18" t="s">
         <v>241</v>
@@ -12870,7 +12868,7 @@
         <v>266</v>
       </c>
       <c r="Q19" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R19" t="s">
         <v>170</v>
@@ -12894,7 +12892,7 @@
         <v>270</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>271</v>
@@ -12936,7 +12934,7 @@
         <v>279</v>
       </c>
       <c r="Q20" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R20" t="s">
         <v>170</v>
@@ -12960,7 +12958,7 @@
         <v>283</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
         <v>284</v>
@@ -13026,7 +13024,7 @@
         <v>296</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
         <v>297</v>
@@ -13092,7 +13090,7 @@
         <v>308</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
         <v>309</v>
@@ -13104,7 +13102,7 @@
         <v>285</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s">
         <v>233</v>
@@ -13262,7 +13260,7 @@
         <v>341</v>
       </c>
       <c r="Q25" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R25" t="s">
         <v>342</v>
@@ -13326,7 +13324,7 @@
         <v>351</v>
       </c>
       <c r="Q26" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R26" t="s">
         <v>342</v>
@@ -13390,7 +13388,7 @@
         <v>363</v>
       </c>
       <c r="Q27" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R27" t="s">
         <v>357</v>
@@ -13420,7 +13418,7 @@
         <v>368</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F28" t="s">
         <v>369</v>
@@ -13486,7 +13484,7 @@
         <v>380</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F29" t="s">
         <v>381</v>
@@ -13522,7 +13520,7 @@
         <v>389</v>
       </c>
       <c r="Q29" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R29" t="s">
         <v>390</v>
@@ -13588,7 +13586,7 @@
         <v>403</v>
       </c>
       <c r="Q30" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R30" t="s">
         <v>390</v>
@@ -13612,7 +13610,7 @@
         <v>407</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
@@ -13654,7 +13652,7 @@
         <v>414</v>
       </c>
       <c r="Q31" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R31" t="s">
         <v>390</v>
@@ -13690,7 +13688,7 @@
         <v>381</v>
       </c>
       <c r="G32" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s">
         <v>247</v>
@@ -13720,7 +13718,7 @@
         <v>423</v>
       </c>
       <c r="Q32" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R32" t="s">
         <v>390</v>
@@ -13744,13 +13742,13 @@
         <v>424</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
         <v>425</v>
       </c>
       <c r="E33" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s">
         <v>381</v>
@@ -13786,7 +13784,7 @@
         <v>432</v>
       </c>
       <c r="Q33" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R33" t="s">
         <v>390</v>
@@ -13810,7 +13808,7 @@
         <v>436</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
         <v>437</v>
@@ -13852,7 +13850,7 @@
         <v>445</v>
       </c>
       <c r="Q34" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R34" t="s">
         <v>390</v>
@@ -13918,7 +13916,7 @@
         <v>456</v>
       </c>
       <c r="Q35" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R35" t="s">
         <v>390</v>
@@ -14008,7 +14006,7 @@
         <v>473</v>
       </c>
       <c r="C37" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
         <v>474</v>
@@ -14020,7 +14018,7 @@
         <v>475</v>
       </c>
       <c r="G37" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s">
         <v>247</v>
@@ -14050,7 +14048,7 @@
         <v>482</v>
       </c>
       <c r="Q37" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R37" t="s">
         <v>390</v>
@@ -14086,7 +14084,7 @@
         <v>475</v>
       </c>
       <c r="G38" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s">
         <v>233</v>
@@ -14146,7 +14144,7 @@
         <v>499</v>
       </c>
       <c r="E39" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F39" t="s">
         <v>500</v>
@@ -14210,7 +14208,7 @@
         <v>511</v>
       </c>
       <c r="E40" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F40" t="s">
         <v>500</v>
@@ -14228,7 +14226,7 @@
         <v>513</v>
       </c>
       <c r="K40" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L40" t="s">
         <v>514</v>
@@ -14270,7 +14268,7 @@
         <v>521</v>
       </c>
       <c r="C41" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D41" t="s">
         <v>522</v>
@@ -14312,7 +14310,7 @@
         <v>531</v>
       </c>
       <c r="Q41" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R41" t="s">
         <v>390</v>
@@ -14378,7 +14376,7 @@
         <v>544</v>
       </c>
       <c r="Q42" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R42" t="s">
         <v>390</v>
@@ -14444,7 +14442,7 @@
         <v>557</v>
       </c>
       <c r="Q43" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R43" t="s">
         <v>390</v>
@@ -14468,7 +14466,7 @@
         <v>561</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D44" t="s">
         <v>562</v>
@@ -14510,7 +14508,7 @@
         <v>569</v>
       </c>
       <c r="Q44" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R44" t="s">
         <v>390</v>
@@ -14606,7 +14604,7 @@
         <v>586</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F46" t="s">
         <v>550</v>
@@ -14678,7 +14676,7 @@
         <v>599</v>
       </c>
       <c r="G47" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s">
         <v>145</v>
@@ -14732,7 +14730,7 @@
         <v>610</v>
       </c>
       <c r="C48" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
         <v>611</v>
@@ -14744,7 +14742,7 @@
         <v>599</v>
       </c>
       <c r="G48" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s">
         <v>59</v>
@@ -14798,7 +14796,7 @@
         <v>622</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D49" t="s">
         <v>623</v>
@@ -14840,7 +14838,7 @@
         <v>630</v>
       </c>
       <c r="Q49" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R49" t="s">
         <v>390</v>
@@ -14864,7 +14862,7 @@
         <v>634</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D50" t="s">
         <v>143</v>
@@ -14876,7 +14874,7 @@
         <v>599</v>
       </c>
       <c r="G50" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s">
         <v>59</v>
@@ -14930,7 +14928,7 @@
         <v>645</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D51" t="s">
         <v>623</v>
@@ -14996,7 +14994,7 @@
         <v>653</v>
       </c>
       <c r="C52" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D52" t="s">
         <v>654</v>
@@ -15038,7 +15036,7 @@
         <v>662</v>
       </c>
       <c r="Q52" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R52" t="s">
         <v>390</v>
@@ -15102,7 +15100,7 @@
         <v>673</v>
       </c>
       <c r="Q53" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R53" t="s">
         <v>390</v>
@@ -15296,7 +15294,7 @@
         <v>706</v>
       </c>
       <c r="Q56" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R56" t="s">
         <v>390</v>
@@ -15384,7 +15382,7 @@
         <v>718</v>
       </c>
       <c r="C58" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
         <v>719</v>
@@ -15456,7 +15454,7 @@
         <v>733</v>
       </c>
       <c r="E59" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F59" t="s">
         <v>721</v>
@@ -15490,7 +15488,7 @@
         <v>739</v>
       </c>
       <c r="Q59" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R59" t="s">
         <v>390</v>
@@ -15578,7 +15576,7 @@
         <v>753</v>
       </c>
       <c r="C61" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D61" t="s">
         <v>754</v>
@@ -15644,7 +15642,7 @@
         <v>766</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D62" t="s">
         <v>474</v>
@@ -15656,7 +15654,7 @@
         <v>755</v>
       </c>
       <c r="G62" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s">
         <v>59</v>
@@ -15750,7 +15748,7 @@
         <v>785</v>
       </c>
       <c r="Q63" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R63" t="s">
         <v>390</v>
@@ -15774,7 +15772,7 @@
         <v>789</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D64" t="s">
         <v>790</v>
@@ -15840,7 +15838,7 @@
         <v>802</v>
       </c>
       <c r="C65" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D65" t="s">
         <v>803</v>
@@ -15882,7 +15880,7 @@
         <v>811</v>
       </c>
       <c r="Q65" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R65" t="s">
         <v>390</v>
@@ -15906,13 +15904,13 @@
         <v>815</v>
       </c>
       <c r="C66" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D66" t="s">
         <v>586</v>
       </c>
       <c r="E66" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F66" t="s">
         <v>816</v>
@@ -15972,7 +15970,7 @@
         <v>827</v>
       </c>
       <c r="C67" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
         <v>828</v>
@@ -16014,7 +16012,7 @@
         <v>835</v>
       </c>
       <c r="Q67" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R67" t="s">
         <v>390</v>
@@ -16038,7 +16036,7 @@
         <v>836</v>
       </c>
       <c r="C68" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D68" t="s">
         <v>837</v>
@@ -16146,7 +16144,7 @@
         <v>852</v>
       </c>
       <c r="Q69" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R69" t="s">
         <v>390</v>
@@ -16212,7 +16210,7 @@
         <v>863</v>
       </c>
       <c r="Q70" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R70" t="s">
         <v>390</v>
@@ -16236,7 +16234,7 @@
         <v>864</v>
       </c>
       <c r="C71" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D71" t="s">
         <v>865</v>
@@ -16278,7 +16276,7 @@
         <v>872</v>
       </c>
       <c r="Q71" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R71" t="s">
         <v>390</v>
@@ -16302,7 +16300,7 @@
         <v>876</v>
       </c>
       <c r="C72" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D72" t="s">
         <v>877</v>
@@ -16314,7 +16312,7 @@
         <v>878</v>
       </c>
       <c r="G72" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s">
         <v>28</v>
@@ -16408,7 +16406,7 @@
         <v>893</v>
       </c>
       <c r="Q73" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R73" t="s">
         <v>390</v>
@@ -16438,7 +16436,7 @@
         <v>586</v>
       </c>
       <c r="E74" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F74" t="s">
         <v>887</v>
@@ -16536,7 +16534,7 @@
         <v>915</v>
       </c>
       <c r="Q75" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R75" t="s">
         <v>390</v>
@@ -16600,7 +16598,7 @@
         <v>925</v>
       </c>
       <c r="Q76" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R76" t="s">
         <v>390</v>
@@ -16624,13 +16622,13 @@
         <v>929</v>
       </c>
       <c r="C77" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D77" t="s">
         <v>930</v>
       </c>
       <c r="E77" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F77" t="s">
         <v>931</v>
@@ -16818,7 +16816,7 @@
         <v>955</v>
       </c>
       <c r="C80" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D80" t="s">
         <v>956</v>
@@ -16860,7 +16858,7 @@
         <v>964</v>
       </c>
       <c r="Q80" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R80" t="s">
         <v>390</v>
@@ -16884,7 +16882,7 @@
         <v>965</v>
       </c>
       <c r="C81" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D81" t="s">
         <v>966</v>
@@ -16992,7 +16990,7 @@
         <v>984</v>
       </c>
       <c r="Q82" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R82" t="s">
         <v>390</v>
@@ -17016,7 +17014,7 @@
         <v>988</v>
       </c>
       <c r="C83" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D83" t="s">
         <v>487</v>
@@ -17028,7 +17026,7 @@
         <v>989</v>
       </c>
       <c r="G83" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H83" t="s">
         <v>233</v>
@@ -17058,7 +17056,7 @@
         <v>996</v>
       </c>
       <c r="Q83" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R83" t="s">
         <v>390</v>
@@ -17082,7 +17080,7 @@
         <v>997</v>
       </c>
       <c r="C84" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D84" t="s">
         <v>998</v>
@@ -17188,7 +17186,7 @@
         <v>1016</v>
       </c>
       <c r="Q85" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R85" t="s">
         <v>390</v>
@@ -17276,7 +17274,7 @@
         <v>1028</v>
       </c>
       <c r="C87" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D87" t="s">
         <v>168</v>
@@ -17318,7 +17316,7 @@
         <v>1036</v>
       </c>
       <c r="Q87" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R87" t="s">
         <v>390</v>
@@ -17348,7 +17346,7 @@
         <v>586</v>
       </c>
       <c r="E88" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F88" t="s">
         <v>1041</v>
@@ -17408,7 +17406,7 @@
         <v>1049</v>
       </c>
       <c r="C89" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D89" t="s">
         <v>297</v>
@@ -17480,7 +17478,7 @@
         <v>1061</v>
       </c>
       <c r="E90" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F90" t="s">
         <v>1062</v>
@@ -17580,7 +17578,7 @@
         <v>1078</v>
       </c>
       <c r="Q91" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R91" t="s">
         <v>390</v>
@@ -17644,7 +17642,7 @@
         <v>1089</v>
       </c>
       <c r="Q92" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R92" t="s">
         <v>390</v>
@@ -17668,7 +17666,7 @@
         <v>1090</v>
       </c>
       <c r="C93" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D93" t="s">
         <v>24</v>
@@ -17710,7 +17708,7 @@
         <v>1098</v>
       </c>
       <c r="Q93" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R93" t="s">
         <v>390</v>
@@ -17734,7 +17732,7 @@
         <v>1102</v>
       </c>
       <c r="C94" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D94" t="s">
         <v>1103</v>
@@ -17800,13 +17798,13 @@
         <v>1115</v>
       </c>
       <c r="C95" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D95" t="s">
         <v>1116</v>
       </c>
       <c r="E95" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F95" t="s">
         <v>1117</v>
@@ -17842,7 +17840,7 @@
         <v>1124</v>
       </c>
       <c r="Q95" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R95" t="s">
         <v>390</v>
@@ -17866,13 +17864,13 @@
         <v>1128</v>
       </c>
       <c r="C96" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D96" t="s">
         <v>1129</v>
       </c>
       <c r="E96" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F96" t="s">
         <v>1130</v>
@@ -17942,7 +17940,7 @@
         <v>1143</v>
       </c>
       <c r="G97" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H97" t="s">
         <v>59</v>
@@ -17972,7 +17970,7 @@
         <v>1150</v>
       </c>
       <c r="Q97" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R97" t="s">
         <v>390</v>
@@ -17996,13 +17994,13 @@
         <v>1154</v>
       </c>
       <c r="C98" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D98" t="s">
         <v>207</v>
       </c>
       <c r="E98" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F98" t="s">
         <v>1155</v>
@@ -18038,7 +18036,7 @@
         <v>1162</v>
       </c>
       <c r="Q98" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R98" t="s">
         <v>390</v>
@@ -18102,7 +18100,7 @@
         <v>1170</v>
       </c>
       <c r="Q99" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R99" t="s">
         <v>390</v>
@@ -18132,7 +18130,7 @@
         <v>733</v>
       </c>
       <c r="E100" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F100" t="s">
         <v>1175</v>
@@ -18168,7 +18166,7 @@
         <v>1182</v>
       </c>
       <c r="Q100" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R100" t="s">
         <v>390</v>
@@ -18192,7 +18190,7 @@
         <v>1183</v>
       </c>
       <c r="C101" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D101" t="s">
         <v>461</v>
@@ -18234,7 +18232,7 @@
         <v>1190</v>
       </c>
       <c r="Q101" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R101" t="s">
         <v>390</v>
@@ -18258,7 +18256,7 @@
         <v>1191</v>
       </c>
       <c r="C102" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D102" t="s">
         <v>1192</v>
@@ -18300,7 +18298,7 @@
         <v>1200</v>
       </c>
       <c r="Q102" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R102" t="s">
         <v>390</v>
@@ -18366,7 +18364,7 @@
         <v>1213</v>
       </c>
       <c r="Q103" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R103" t="s">
         <v>390</v>
@@ -18393,16 +18391,16 @@
         <v>113</v>
       </c>
       <c r="D104" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E104" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F104" t="s">
         <v>1206</v>
       </c>
       <c r="G104" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H104" t="s">
         <v>115</v>
@@ -18432,7 +18430,7 @@
         <v>1224</v>
       </c>
       <c r="Q104" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R104" t="s">
         <v>390</v>
@@ -18498,7 +18496,7 @@
         <v>1236</v>
       </c>
       <c r="Q105" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R105" t="s">
         <v>390</v>
@@ -18564,7 +18562,7 @@
         <v>1245</v>
       </c>
       <c r="Q106" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R106" t="s">
         <v>390</v>
@@ -18588,7 +18586,7 @@
         <v>1249</v>
       </c>
       <c r="C107" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D107" t="s">
         <v>837</v>
@@ -18630,7 +18628,7 @@
         <v>1256</v>
       </c>
       <c r="Q107" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R107" t="s">
         <v>390</v>
@@ -18720,7 +18718,7 @@
         <v>1272</v>
       </c>
       <c r="C109" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D109" t="s">
         <v>1273</v>
@@ -18786,7 +18784,7 @@
         <v>1285</v>
       </c>
       <c r="C110" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D110" t="s">
         <v>195</v>
@@ -18828,7 +18826,7 @@
         <v>1293</v>
       </c>
       <c r="Q110" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R110" t="s">
         <v>390</v>
@@ -18852,7 +18850,7 @@
         <v>1297</v>
       </c>
       <c r="C111" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D111" t="s">
         <v>1298</v>
@@ -18894,7 +18892,7 @@
         <v>1305</v>
       </c>
       <c r="Q111" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R111" t="s">
         <v>390</v>
@@ -18918,7 +18916,7 @@
         <v>1309</v>
       </c>
       <c r="C112" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D112" t="s">
         <v>908</v>
@@ -18960,7 +18958,7 @@
         <v>1316</v>
       </c>
       <c r="Q112" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R112" t="s">
         <v>390</v>
@@ -18984,7 +18982,7 @@
         <v>1317</v>
       </c>
       <c r="C113" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D113" t="s">
         <v>1318</v>
@@ -19092,7 +19090,7 @@
         <v>1335</v>
       </c>
       <c r="Q114" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R114" t="s">
         <v>390</v>
@@ -19158,7 +19156,7 @@
         <v>1347</v>
       </c>
       <c r="Q115" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R115" t="s">
         <v>390</v>
@@ -19224,7 +19222,7 @@
         <v>1358</v>
       </c>
       <c r="Q116" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R116" t="s">
         <v>390</v>
@@ -19290,20 +19288,20 @@
         <v>1371</v>
       </c>
       <c r="Q117" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R117" t="s">
         <v>390</v>
       </c>
       <c r="S117"/>
       <c r="T117" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="U117" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="V117" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="118">
@@ -19314,7 +19312,7 @@
         <v>1372</v>
       </c>
       <c r="C118" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D118" t="s">
         <v>966</v>
@@ -19386,7 +19384,7 @@
         <v>586</v>
       </c>
       <c r="E119" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F119" t="s">
         <v>1364</v>
@@ -19446,7 +19444,7 @@
         <v>1391</v>
       </c>
       <c r="C120" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D120" t="s">
         <v>1392</v>
@@ -19578,7 +19576,7 @@
         <v>1415</v>
       </c>
       <c r="C122" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D122" t="s">
         <v>1103</v>
@@ -19644,7 +19642,7 @@
         <v>1423</v>
       </c>
       <c r="C123" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D123" t="s">
         <v>711</v>
@@ -19686,7 +19684,7 @@
         <v>1431</v>
       </c>
       <c r="Q123" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R123" t="s">
         <v>390</v>
@@ -19716,7 +19714,7 @@
         <v>1433</v>
       </c>
       <c r="E124" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F124" t="s">
         <v>1424</v>
@@ -19752,7 +19750,7 @@
         <v>1440</v>
       </c>
       <c r="Q124" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R124" t="s">
         <v>390</v>
@@ -19816,7 +19814,7 @@
         <v>1448</v>
       </c>
       <c r="Q125" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R125" t="s">
         <v>390</v>
@@ -19880,7 +19878,7 @@
         <v>1458</v>
       </c>
       <c r="Q126" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R126" t="s">
         <v>390</v>
@@ -19904,7 +19902,7 @@
         <v>1462</v>
       </c>
       <c r="C127" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D127" t="s">
         <v>1463</v>
@@ -19946,7 +19944,7 @@
         <v>1471</v>
       </c>
       <c r="Q127" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R127" t="s">
         <v>390</v>
@@ -19970,7 +19968,7 @@
         <v>1475</v>
       </c>
       <c r="C128" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D128" t="s">
         <v>908</v>
@@ -20012,7 +20010,7 @@
         <v>1482</v>
       </c>
       <c r="Q128" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R128" t="s">
         <v>390</v>
@@ -20036,7 +20034,7 @@
         <v>1483</v>
       </c>
       <c r="C129" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D129" t="s">
         <v>1484</v>
@@ -20102,7 +20100,7 @@
         <v>1493</v>
       </c>
       <c r="C130" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D130" t="s">
         <v>143</v>
@@ -20174,7 +20172,7 @@
         <v>1506</v>
       </c>
       <c r="E131" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F131" t="s">
         <v>1507</v>
@@ -20338,7 +20336,7 @@
         <v>1535</v>
       </c>
       <c r="Q133" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R133" t="s">
         <v>390</v>
@@ -20368,7 +20366,7 @@
         <v>1540</v>
       </c>
       <c r="E134" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F134" t="s">
         <v>1541</v>
@@ -20402,7 +20400,7 @@
         <v>1547</v>
       </c>
       <c r="Q134" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R134" t="s">
         <v>390</v>
@@ -20468,7 +20466,7 @@
         <v>1557</v>
       </c>
       <c r="Q135" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R135" t="s">
         <v>390</v>
@@ -20492,7 +20490,7 @@
         <v>1561</v>
       </c>
       <c r="C136" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D136" t="s">
         <v>865</v>
@@ -20558,7 +20556,7 @@
         <v>1573</v>
       </c>
       <c r="C137" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D137" t="s">
         <v>1574</v>
@@ -20598,7 +20596,7 @@
         <v>1582</v>
       </c>
       <c r="Q137" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R137" t="s">
         <v>390</v>
@@ -20662,7 +20660,7 @@
         <v>1593</v>
       </c>
       <c r="Q138" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R138" t="s">
         <v>390</v>
@@ -20686,7 +20684,7 @@
         <v>1597</v>
       </c>
       <c r="C139" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D139" t="s">
         <v>56</v>
@@ -20728,7 +20726,7 @@
         <v>1605</v>
       </c>
       <c r="Q139" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R139" t="s">
         <v>390</v>
@@ -20752,13 +20750,13 @@
         <v>1609</v>
       </c>
       <c r="C140" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D140" t="s">
         <v>1610</v>
       </c>
       <c r="E140" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F140" t="s">
         <v>1611</v>
@@ -20882,7 +20880,7 @@
         <v>1633</v>
       </c>
       <c r="C142" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D142" t="s">
         <v>1634</v>
@@ -20894,7 +20892,7 @@
         <v>1635</v>
       </c>
       <c r="G142" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H142" t="s">
         <v>59</v>
@@ -20990,7 +20988,7 @@
         <v>1655</v>
       </c>
       <c r="Q143" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R143" t="s">
         <v>390</v>
@@ -21014,7 +21012,7 @@
         <v>1659</v>
       </c>
       <c r="C144" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D144" t="s">
         <v>711</v>
@@ -21056,7 +21054,7 @@
         <v>1666</v>
       </c>
       <c r="Q144" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R144" t="s">
         <v>390</v>
@@ -21080,7 +21078,7 @@
         <v>1667</v>
       </c>
       <c r="C145" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D145" t="s">
         <v>1668</v>
@@ -21122,7 +21120,7 @@
         <v>1675</v>
       </c>
       <c r="Q145" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R145" t="s">
         <v>390</v>
@@ -21218,7 +21216,7 @@
         <v>1693</v>
       </c>
       <c r="E147" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F147" t="s">
         <v>1681</v>
@@ -21316,7 +21314,7 @@
         <v>1710</v>
       </c>
       <c r="Q148" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R148" t="s">
         <v>390</v>
@@ -21404,7 +21402,7 @@
         <v>1721</v>
       </c>
       <c r="C150" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D150" t="s">
         <v>711</v>
@@ -21446,7 +21444,7 @@
         <v>1729</v>
       </c>
       <c r="Q150" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R150" t="s">
         <v>390</v>
@@ -21512,7 +21510,7 @@
         <v>1741</v>
       </c>
       <c r="Q151" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R151" t="s">
         <v>390</v>
@@ -21542,7 +21540,7 @@
         <v>1610</v>
       </c>
       <c r="E152" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F152" t="s">
         <v>1734</v>
@@ -21602,13 +21600,13 @@
         <v>1756</v>
       </c>
       <c r="C153" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D153" t="s">
         <v>1757</v>
       </c>
       <c r="E153" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F153" t="s">
         <v>1734</v>
@@ -21644,7 +21642,7 @@
         <v>1764</v>
       </c>
       <c r="Q153" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R153" t="s">
         <v>390</v>
@@ -21674,13 +21672,13 @@
         <v>154</v>
       </c>
       <c r="E154" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F154" t="s">
         <v>1769</v>
       </c>
       <c r="G154" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H154" t="s">
         <v>247</v>
@@ -21734,7 +21732,7 @@
         <v>1780</v>
       </c>
       <c r="C155" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D155" t="s">
         <v>1392</v>
@@ -21776,7 +21774,7 @@
         <v>1788</v>
       </c>
       <c r="Q155" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R155" t="s">
         <v>390</v>
@@ -21800,13 +21798,13 @@
         <v>1792</v>
       </c>
       <c r="C156" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D156" t="s">
         <v>1433</v>
       </c>
       <c r="E156" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F156" t="s">
         <v>1793</v>
@@ -21842,7 +21840,7 @@
         <v>1800</v>
       </c>
       <c r="Q156" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R156" t="s">
         <v>390</v>
@@ -21866,7 +21864,7 @@
         <v>1801</v>
       </c>
       <c r="C157" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D157" t="s">
         <v>1071</v>
@@ -21908,7 +21906,7 @@
         <v>1809</v>
       </c>
       <c r="Q157" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R157" t="s">
         <v>390</v>
@@ -21972,20 +21970,20 @@
         <v>1818</v>
       </c>
       <c r="Q158" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R158" t="s">
         <v>390</v>
       </c>
       <c r="S158"/>
       <c r="T158" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="U158" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="V158" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="159">
@@ -22036,20 +22034,20 @@
         <v>1825</v>
       </c>
       <c r="Q159" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R159" t="s">
         <v>390</v>
       </c>
       <c r="S159"/>
       <c r="T159" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="U159" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="V159" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="160">
@@ -22060,7 +22058,7 @@
         <v>1826</v>
       </c>
       <c r="C160" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D160" t="s">
         <v>1528</v>
@@ -22102,7 +22100,7 @@
         <v>1834</v>
       </c>
       <c r="Q160" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R160" t="s">
         <v>390</v>
@@ -22168,7 +22166,7 @@
         <v>1843</v>
       </c>
       <c r="Q161" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R161" t="s">
         <v>390</v>
@@ -22234,7 +22232,7 @@
         <v>1854</v>
       </c>
       <c r="Q162" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R162" t="s">
         <v>390</v>
@@ -22258,7 +22256,7 @@
         <v>1858</v>
       </c>
       <c r="C163" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D163" t="s">
         <v>1859</v>
@@ -22300,7 +22298,7 @@
         <v>1866</v>
       </c>
       <c r="Q163" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R163" t="s">
         <v>390</v>
@@ -22324,7 +22322,7 @@
         <v>1867</v>
       </c>
       <c r="C164" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D164" t="s">
         <v>1363</v>
@@ -22366,7 +22364,7 @@
         <v>1875</v>
       </c>
       <c r="Q164" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R164" t="s">
         <v>390</v>
@@ -22390,7 +22388,7 @@
         <v>1879</v>
       </c>
       <c r="C165" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D165" t="s">
         <v>114</v>
@@ -22432,7 +22430,7 @@
         <v>1886</v>
       </c>
       <c r="Q165" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R165" t="s">
         <v>390</v>
@@ -22522,7 +22520,7 @@
         <v>1899</v>
       </c>
       <c r="C167" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D167" t="s">
         <v>97</v>
@@ -22564,7 +22562,7 @@
         <v>1907</v>
       </c>
       <c r="Q167" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R167" t="s">
         <v>390</v>
@@ -22588,7 +22586,7 @@
         <v>1911</v>
       </c>
       <c r="C168" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D168" t="s">
         <v>1574</v>
@@ -22692,7 +22690,7 @@
         <v>1930</v>
       </c>
       <c r="Q169" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R169" t="s">
         <v>390</v>
@@ -22756,7 +22754,7 @@
         <v>1937</v>
       </c>
       <c r="Q170" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R170" t="s">
         <v>390</v>
@@ -22790,7 +22788,7 @@
         <v>1940</v>
       </c>
       <c r="G171" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H171" t="s">
         <v>233</v>
@@ -22820,7 +22818,7 @@
         <v>1948</v>
       </c>
       <c r="Q171" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R171" t="s">
         <v>390</v>
@@ -22884,7 +22882,7 @@
         <v>1957</v>
       </c>
       <c r="Q172" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R172" t="s">
         <v>390</v>
@@ -22908,7 +22906,7 @@
         <v>1961</v>
       </c>
       <c r="C173" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D173" t="s">
         <v>1811</v>
@@ -23082,7 +23080,7 @@
         <v>1994</v>
       </c>
       <c r="Q175" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R175" t="s">
         <v>390</v>
@@ -23182,7 +23180,7 @@
         <v>2009</v>
       </c>
       <c r="G177" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H177" t="s">
         <v>1648</v>
@@ -23212,7 +23210,7 @@
         <v>2016</v>
       </c>
       <c r="Q177" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R177" t="s">
         <v>390</v>
@@ -23236,13 +23234,13 @@
         <v>2020</v>
       </c>
       <c r="C178" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D178" t="s">
         <v>2021</v>
       </c>
       <c r="E178" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F178" t="s">
         <v>2009</v>
@@ -23368,7 +23366,7 @@
         <v>2044</v>
       </c>
       <c r="C180" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D180" t="s">
         <v>1528</v>
@@ -23434,7 +23432,7 @@
         <v>2056</v>
       </c>
       <c r="C181" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D181" t="s">
         <v>966</v>
@@ -23476,7 +23474,7 @@
         <v>2063</v>
       </c>
       <c r="Q181" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R181" t="s">
         <v>390</v>
@@ -23542,20 +23540,20 @@
         <v>2074</v>
       </c>
       <c r="Q182" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R182" t="s">
         <v>390</v>
       </c>
       <c r="S182"/>
       <c r="T182" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="U182" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="V182" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="183">
@@ -23566,7 +23564,7 @@
         <v>2075</v>
       </c>
       <c r="C183" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D183" t="s">
         <v>246</v>
@@ -23608,7 +23606,7 @@
         <v>2083</v>
       </c>
       <c r="Q183" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R183" t="s">
         <v>390</v>
@@ -23632,13 +23630,13 @@
         <v>2084</v>
       </c>
       <c r="C184" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D184" t="s">
         <v>2085</v>
       </c>
       <c r="E184" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F184" t="s">
         <v>2086</v>
@@ -23674,7 +23672,7 @@
         <v>2093</v>
       </c>
       <c r="Q184" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R184" t="s">
         <v>390</v>
@@ -23698,7 +23696,7 @@
         <v>2097</v>
       </c>
       <c r="C185" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D185" t="s">
         <v>536</v>
@@ -23806,7 +23804,7 @@
         <v>2117</v>
       </c>
       <c r="Q186" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R186" t="s">
         <v>390</v>
@@ -23830,7 +23828,7 @@
         <v>2118</v>
       </c>
       <c r="C187" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D187" t="s">
         <v>246</v>
@@ -23872,7 +23870,7 @@
         <v>2126</v>
       </c>
       <c r="Q187" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R187" t="s">
         <v>390</v>
@@ -23962,7 +23960,7 @@
         <v>2139</v>
       </c>
       <c r="C189" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D189" t="s">
         <v>2140</v>
@@ -24040,7 +24038,7 @@
         <v>2153</v>
       </c>
       <c r="G190" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H190" t="s">
         <v>1648</v>
@@ -24070,7 +24068,7 @@
         <v>2160</v>
       </c>
       <c r="Q190" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R190" t="s">
         <v>390</v>
@@ -24160,7 +24158,7 @@
         <v>2176</v>
       </c>
       <c r="C192" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D192" t="s">
         <v>2177</v>
@@ -24202,7 +24200,7 @@
         <v>2184</v>
       </c>
       <c r="Q192" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R192" t="s">
         <v>390</v>
@@ -24226,7 +24224,7 @@
         <v>2188</v>
       </c>
       <c r="C193" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D193" t="s">
         <v>1986</v>
@@ -24268,7 +24266,7 @@
         <v>2196</v>
       </c>
       <c r="Q193" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R193" t="s">
         <v>390</v>
@@ -24292,7 +24290,7 @@
         <v>2197</v>
       </c>
       <c r="C194" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D194" t="s">
         <v>2198</v>
@@ -24334,7 +24332,7 @@
         <v>2206</v>
       </c>
       <c r="Q194" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R194" t="s">
         <v>390</v>
@@ -24398,7 +24396,7 @@
         <v>2214</v>
       </c>
       <c r="Q195" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R195" t="s">
         <v>390</v>
@@ -24462,7 +24460,7 @@
         <v>2225</v>
       </c>
       <c r="Q196" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R196" t="s">
         <v>390</v>
@@ -24528,7 +24526,7 @@
         <v>2237</v>
       </c>
       <c r="Q197" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R197" t="s">
         <v>390</v>
@@ -24552,7 +24550,7 @@
         <v>2241</v>
       </c>
       <c r="C198" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D198" t="s">
         <v>2242</v>
@@ -24618,7 +24616,7 @@
         <v>2253</v>
       </c>
       <c r="C199" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D199" t="s">
         <v>2254</v>
@@ -24684,7 +24682,7 @@
         <v>2264</v>
       </c>
       <c r="C200" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D200" t="s">
         <v>1891</v>
@@ -24726,7 +24724,7 @@
         <v>2271</v>
       </c>
       <c r="Q200" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R200" t="s">
         <v>390</v>
@@ -24792,7 +24790,7 @@
         <v>2284</v>
       </c>
       <c r="Q201" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R201" t="s">
         <v>390</v>
@@ -24856,7 +24854,7 @@
         <v>2296</v>
       </c>
       <c r="Q202" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R202" t="s">
         <v>390</v>
@@ -24880,7 +24878,7 @@
         <v>2300</v>
       </c>
       <c r="C203" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D203" t="s">
         <v>908</v>
@@ -24946,13 +24944,13 @@
         <v>2312</v>
       </c>
       <c r="C204" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D204" t="s">
         <v>1757</v>
       </c>
       <c r="E204" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F204" t="s">
         <v>2313</v>
@@ -25076,7 +25074,7 @@
         <v>2333</v>
       </c>
       <c r="C206" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D206" t="s">
         <v>2334</v>
@@ -25142,7 +25140,7 @@
         <v>2346</v>
       </c>
       <c r="C207" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D207" t="s">
         <v>2347</v>
@@ -25278,7 +25276,7 @@
         <v>586</v>
       </c>
       <c r="E209" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F209" t="s">
         <v>2371</v>
@@ -25378,7 +25376,7 @@
         <v>2391</v>
       </c>
       <c r="Q210" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R210" t="s">
         <v>390</v>
@@ -25412,7 +25410,7 @@
         <v>2397</v>
       </c>
       <c r="G211" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H211" t="s">
         <v>145</v>
@@ -25442,7 +25440,7 @@
         <v>2404</v>
       </c>
       <c r="Q211" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R211" t="s">
         <v>390</v>
@@ -25476,7 +25474,7 @@
         <v>2397</v>
       </c>
       <c r="G212" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H212" t="s">
         <v>247</v>
@@ -25506,7 +25504,7 @@
         <v>2415</v>
       </c>
       <c r="Q212" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R212" t="s">
         <v>390</v>
@@ -25536,7 +25534,7 @@
         <v>183</v>
       </c>
       <c r="E213" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F213" t="s">
         <v>369</v>
@@ -25572,7 +25570,7 @@
         <v>2426</v>
       </c>
       <c r="Q213" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R213"/>
       <c r="S213"/>
@@ -25594,7 +25592,7 @@
         <v>2430</v>
       </c>
       <c r="C214" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D214" t="s">
         <v>966</v>
@@ -25670,7 +25668,7 @@
         <v>272</v>
       </c>
       <c r="G215" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H215" t="s">
         <v>233</v>
@@ -25700,7 +25698,7 @@
         <v>2447</v>
       </c>
       <c r="Q215" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R215"/>
       <c r="S215"/>
@@ -25792,7 +25790,7 @@
         <v>2463</v>
       </c>
       <c r="E217" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F217" t="s">
         <v>2464</v>
@@ -25888,7 +25886,7 @@
         <v>2477</v>
       </c>
       <c r="Q218" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R218"/>
       <c r="S218"/>
@@ -25952,7 +25950,7 @@
         <v>2489</v>
       </c>
       <c r="Q219" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R219"/>
       <c r="S219"/>
@@ -26016,7 +26014,7 @@
         <v>2499</v>
       </c>
       <c r="Q220" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R220"/>
       <c r="S220"/>
@@ -26080,7 +26078,7 @@
         <v>2507</v>
       </c>
       <c r="Q221" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R221"/>
       <c r="S221"/>
@@ -26114,7 +26112,7 @@
         <v>2513</v>
       </c>
       <c r="G222" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H222" t="s">
         <v>145</v>
@@ -26178,7 +26176,7 @@
         <v>2513</v>
       </c>
       <c r="G223" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H223" t="s">
         <v>233</v>
@@ -26230,7 +26228,7 @@
         <v>2527</v>
       </c>
       <c r="C224" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D224" t="s">
         <v>1103</v>
@@ -26272,7 +26270,7 @@
         <v>2534</v>
       </c>
       <c r="Q224" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R224"/>
       <c r="S224"/>
@@ -26336,7 +26334,7 @@
         <v>2546</v>
       </c>
       <c r="Q225" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R225"/>
       <c r="S225"/>
@@ -26358,7 +26356,7 @@
         <v>2550</v>
       </c>
       <c r="C226" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D226" t="s">
         <v>2551</v>
@@ -26370,7 +26368,7 @@
         <v>2552</v>
       </c>
       <c r="G226" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H226" t="s">
         <v>233</v>
@@ -26422,7 +26420,7 @@
         <v>2563</v>
       </c>
       <c r="C227" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D227" t="s">
         <v>690</v>
@@ -26464,7 +26462,7 @@
         <v>2571</v>
       </c>
       <c r="Q227" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R227"/>
       <c r="S227"/>
@@ -26588,7 +26586,7 @@
         <v>2585</v>
       </c>
       <c r="Q229" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R229"/>
       <c r="S229"/>
@@ -26650,7 +26648,7 @@
         <v>2595</v>
       </c>
       <c r="Q230" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R230"/>
       <c r="S230"/>
@@ -26740,7 +26738,7 @@
         <v>183</v>
       </c>
       <c r="E232" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F232" t="s">
         <v>322</v>
@@ -26858,7 +26856,7 @@
         <v>2627</v>
       </c>
       <c r="C234" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D234" t="s">
         <v>129</v>
@@ -26870,7 +26868,7 @@
         <v>2628</v>
       </c>
       <c r="G234" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H234" t="s">
         <v>247</v>
@@ -26900,7 +26898,7 @@
         <v>2635</v>
       </c>
       <c r="Q234" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R234"/>
       <c r="S234"/>
@@ -26962,7 +26960,7 @@
         <v>2643</v>
       </c>
       <c r="Q235" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R235"/>
       <c r="S235"/>
@@ -27058,7 +27056,7 @@
         <v>2656</v>
       </c>
       <c r="G237" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H237" t="s">
         <v>145</v>
@@ -27088,7 +27086,7 @@
         <v>2663</v>
       </c>
       <c r="Q237" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R237"/>
       <c r="S237"/>
@@ -27110,13 +27108,13 @@
         <v>2667</v>
       </c>
       <c r="C238" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D238" t="s">
         <v>1433</v>
       </c>
       <c r="E238" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F238" t="s">
         <v>2668</v>
@@ -27152,7 +27150,7 @@
         <v>2675</v>
       </c>
       <c r="Q238" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R238"/>
       <c r="S238"/>
@@ -27174,7 +27172,7 @@
         <v>2679</v>
       </c>
       <c r="C239" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D239" t="s">
         <v>2680</v>
@@ -27216,7 +27214,7 @@
         <v>2688</v>
       </c>
       <c r="Q239" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R239"/>
       <c r="S239"/>
@@ -27278,7 +27276,7 @@
         <v>2699</v>
       </c>
       <c r="Q240" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R240"/>
       <c r="S240"/>
@@ -27300,13 +27298,13 @@
         <v>2700</v>
       </c>
       <c r="C241" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D241" t="s">
         <v>2701</v>
       </c>
       <c r="E241" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F241" t="s">
         <v>2702</v>
@@ -27364,13 +27362,13 @@
         <v>2713</v>
       </c>
       <c r="C242" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D242" t="s">
         <v>183</v>
       </c>
       <c r="E242" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F242" t="s">
         <v>2702</v>
@@ -27406,7 +27404,7 @@
         <v>2720</v>
       </c>
       <c r="Q242" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R242"/>
       <c r="S242"/>
@@ -27428,7 +27426,7 @@
         <v>2721</v>
       </c>
       <c r="C243" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D243" t="s">
         <v>2722</v>
@@ -27498,7 +27496,7 @@
         <v>1757</v>
       </c>
       <c r="E244" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F244" t="s">
         <v>2734</v>
@@ -27556,7 +27554,7 @@
         <v>2742</v>
       </c>
       <c r="C245" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D245" t="s">
         <v>2743</v>
@@ -27598,7 +27596,7 @@
         <v>2750</v>
       </c>
       <c r="Q245" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R245"/>
       <c r="S245"/>
@@ -27620,7 +27618,7 @@
         <v>2751</v>
       </c>
       <c r="C246" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D246" t="s">
         <v>2334</v>
@@ -27684,7 +27682,7 @@
         <v>2763</v>
       </c>
       <c r="C247" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D247" t="s">
         <v>2764</v>
@@ -27696,7 +27694,7 @@
         <v>2752</v>
       </c>
       <c r="G247" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H247" t="s">
         <v>115</v>
@@ -27748,7 +27746,7 @@
         <v>2772</v>
       </c>
       <c r="C248" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D248" t="s">
         <v>334</v>
@@ -27790,7 +27788,7 @@
         <v>2780</v>
       </c>
       <c r="Q248" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R248"/>
       <c r="S248"/>
@@ -27916,7 +27914,7 @@
         <v>2801</v>
       </c>
       <c r="Q250" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R250"/>
       <c r="S250"/>
@@ -27938,7 +27936,7 @@
         <v>2805</v>
       </c>
       <c r="C251" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D251" t="s">
         <v>2782</v>
@@ -28002,13 +28000,13 @@
         <v>2817</v>
       </c>
       <c r="C252" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D252" t="s">
         <v>2818</v>
       </c>
       <c r="E252" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F252" t="s">
         <v>2819</v>
@@ -28044,7 +28042,7 @@
         <v>2826</v>
       </c>
       <c r="Q252" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R252"/>
       <c r="S252"/>
@@ -28072,7 +28070,7 @@
         <v>1433</v>
       </c>
       <c r="E253" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F253" t="s">
         <v>2819</v>
@@ -28108,7 +28106,7 @@
         <v>2837</v>
       </c>
       <c r="Q253" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R253"/>
       <c r="S253"/>
@@ -28130,7 +28128,7 @@
         <v>2841</v>
       </c>
       <c r="C254" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D254" t="s">
         <v>271</v>
@@ -28172,7 +28170,7 @@
         <v>2848</v>
       </c>
       <c r="Q254" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R254"/>
       <c r="S254"/>
@@ -28236,7 +28234,7 @@
         <v>2860</v>
       </c>
       <c r="Q255" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R255"/>
       <c r="S255"/>
@@ -28258,19 +28256,19 @@
         <v>2864</v>
       </c>
       <c r="C256" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D256" t="s">
         <v>2865</v>
       </c>
       <c r="E256" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F256" t="s">
         <v>2853</v>
       </c>
       <c r="G256" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H256" t="s">
         <v>145</v>
@@ -28300,7 +28298,7 @@
         <v>2872</v>
       </c>
       <c r="Q256" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R256"/>
       <c r="S256"/>
@@ -28322,7 +28320,7 @@
         <v>2876</v>
       </c>
       <c r="C257" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D257" t="s">
         <v>2877</v>
@@ -28364,7 +28362,7 @@
         <v>2885</v>
       </c>
       <c r="Q257" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R257"/>
       <c r="S257"/>
@@ -28428,7 +28426,7 @@
         <v>2899</v>
       </c>
       <c r="Q258" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R258"/>
       <c r="S258"/>
@@ -28616,7 +28614,7 @@
         <v>2925</v>
       </c>
       <c r="Q261" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R261"/>
       <c r="S261"/>
@@ -28638,7 +28636,7 @@
         <v>2926</v>
       </c>
       <c r="C262" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D262" t="s">
         <v>2927</v>
@@ -28680,7 +28678,7 @@
         <v>2935</v>
       </c>
       <c r="Q262" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R262"/>
       <c r="S262"/>
@@ -28744,7 +28742,7 @@
         <v>2943</v>
       </c>
       <c r="Q263" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R263"/>
       <c r="S263"/>
@@ -28806,7 +28804,7 @@
         <v>2954</v>
       </c>
       <c r="Q264" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R264"/>
       <c r="S264"/>
@@ -28868,7 +28866,7 @@
         <v>2962</v>
       </c>
       <c r="Q265" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R265"/>
       <c r="S265"/>
@@ -28930,7 +28928,7 @@
         <v>2972</v>
       </c>
       <c r="Q266" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R266"/>
       <c r="S266"/>
@@ -28952,7 +28950,7 @@
         <v>2973</v>
       </c>
       <c r="C267" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D267" t="s">
         <v>1519</v>
@@ -29054,7 +29052,7 @@
         <v>2994</v>
       </c>
       <c r="Q268" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R268"/>
       <c r="S268"/>
@@ -29088,7 +29086,7 @@
         <v>3000</v>
       </c>
       <c r="G269" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H269" t="s">
         <v>45</v>
@@ -29118,7 +29116,7 @@
         <v>3007</v>
       </c>
       <c r="Q269" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R269"/>
       <c r="S269"/>
@@ -29182,7 +29180,7 @@
         <v>3016</v>
       </c>
       <c r="Q270" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R270"/>
       <c r="S270"/>
@@ -29204,7 +29202,7 @@
         <v>3017</v>
       </c>
       <c r="C271" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D271" t="s">
         <v>3018</v>
@@ -29246,7 +29244,7 @@
         <v>3025</v>
       </c>
       <c r="Q271" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R271"/>
       <c r="S271"/>
@@ -29402,7 +29400,7 @@
         <v>3046</v>
       </c>
       <c r="E274" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F274" t="s">
         <v>3009</v>
@@ -29460,7 +29458,7 @@
         <v>3057</v>
       </c>
       <c r="C275" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D275" t="s">
         <v>3058</v>
@@ -29502,7 +29500,7 @@
         <v>3066</v>
       </c>
       <c r="Q275" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R275"/>
       <c r="S275"/>
@@ -29524,13 +29522,13 @@
         <v>3070</v>
       </c>
       <c r="C276" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D276" t="s">
         <v>207</v>
       </c>
       <c r="E276" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F276" t="s">
         <v>3059</v>
@@ -29588,13 +29586,13 @@
         <v>3081</v>
       </c>
       <c r="C277" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D277" t="s">
         <v>3082</v>
       </c>
       <c r="E277" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F277" t="s">
         <v>3083</v>
@@ -29630,7 +29628,7 @@
         <v>3090</v>
       </c>
       <c r="Q277" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R277"/>
       <c r="S277"/>
@@ -29694,7 +29692,7 @@
         <v>3102</v>
       </c>
       <c r="Q278" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R278"/>
       <c r="S278"/>
@@ -29722,7 +29720,7 @@
         <v>3082</v>
       </c>
       <c r="E279" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F279" t="s">
         <v>3095</v>
@@ -29756,7 +29754,7 @@
         <v>3109</v>
       </c>
       <c r="Q279" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R279"/>
       <c r="S279"/>
@@ -29778,7 +29776,7 @@
         <v>3113</v>
       </c>
       <c r="C280" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D280" t="s">
         <v>2890</v>
@@ -29820,7 +29818,7 @@
         <v>3121</v>
       </c>
       <c r="Q280" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R280"/>
       <c r="S280"/>
@@ -29882,7 +29880,7 @@
         <v>3133</v>
       </c>
       <c r="Q281" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R281"/>
       <c r="S281"/>
@@ -29944,7 +29942,7 @@
         <v>3142</v>
       </c>
       <c r="Q282" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R282"/>
       <c r="S282"/>
@@ -30006,7 +30004,7 @@
         <v>3150</v>
       </c>
       <c r="Q283" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R283"/>
       <c r="S283"/>
@@ -30068,7 +30066,7 @@
         <v>3158</v>
       </c>
       <c r="Q284" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R284"/>
       <c r="S284"/>
@@ -30130,7 +30128,7 @@
         <v>3168</v>
       </c>
       <c r="Q285" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R285"/>
       <c r="S285"/>
@@ -30152,7 +30150,7 @@
         <v>3172</v>
       </c>
       <c r="C286" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D286" t="s">
         <v>3173</v>
@@ -30194,7 +30192,7 @@
         <v>3181</v>
       </c>
       <c r="Q286" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R286"/>
       <c r="S286"/>
@@ -30216,7 +30214,7 @@
         <v>3182</v>
       </c>
       <c r="C287" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D287" t="s">
         <v>3183</v>
@@ -30342,7 +30340,7 @@
         <v>3206</v>
       </c>
       <c r="C289" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D289" t="s">
         <v>3207</v>
@@ -30448,7 +30446,7 @@
         <v>3229</v>
       </c>
       <c r="Q290" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R290"/>
       <c r="S290"/>
@@ -30473,10 +30471,10 @@
         <v>113</v>
       </c>
       <c r="D291" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E291" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F291" t="s">
         <v>3221</v>
@@ -30534,7 +30532,7 @@
         <v>3241</v>
       </c>
       <c r="C292" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D292" t="s">
         <v>536</v>
@@ -30598,13 +30596,13 @@
         <v>3252</v>
       </c>
       <c r="C293" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D293" t="s">
         <v>2701</v>
       </c>
       <c r="E293" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F293" t="s">
         <v>3221</v>
@@ -30640,7 +30638,7 @@
         <v>3259</v>
       </c>
       <c r="Q293" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R293"/>
       <c r="S293"/>
@@ -30662,7 +30660,7 @@
         <v>3263</v>
       </c>
       <c r="C294" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D294" t="s">
         <v>1261</v>
@@ -30704,7 +30702,7 @@
         <v>3270</v>
       </c>
       <c r="Q294" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R294"/>
       <c r="S294"/>
@@ -30768,7 +30766,7 @@
         <v>3281</v>
       </c>
       <c r="Q295" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R295"/>
       <c r="S295"/>
@@ -30790,7 +30788,7 @@
         <v>3282</v>
       </c>
       <c r="C296" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D296" t="s">
         <v>1836</v>
@@ -30918,19 +30916,19 @@
         <v>3299</v>
       </c>
       <c r="C298" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D298" t="s">
         <v>2865</v>
       </c>
       <c r="E298" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F298" t="s">
         <v>3300</v>
       </c>
       <c r="G298" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H298" t="s">
         <v>145</v>
@@ -30960,7 +30958,7 @@
         <v>3307</v>
       </c>
       <c r="Q298" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R298"/>
       <c r="S298"/>
@@ -31022,7 +31020,7 @@
         <v>3315</v>
       </c>
       <c r="Q299" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R299"/>
       <c r="S299"/>
@@ -31084,7 +31082,7 @@
         <v>3326</v>
       </c>
       <c r="Q300" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R300"/>
       <c r="S300"/>
@@ -31106,7 +31104,7 @@
         <v>3327</v>
       </c>
       <c r="C301" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D301" t="s">
         <v>654</v>
@@ -31272,7 +31270,7 @@
         <v>3355</v>
       </c>
       <c r="Q303" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R303"/>
       <c r="S303"/>
@@ -31356,7 +31354,7 @@
         <v>3364</v>
       </c>
       <c r="C305" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D305" t="s">
         <v>2680</v>
@@ -31398,7 +31396,7 @@
         <v>3371</v>
       </c>
       <c r="Q305" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R305"/>
       <c r="S305"/>
@@ -31482,13 +31480,13 @@
         <v>3384</v>
       </c>
       <c r="C307" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D307" t="s">
         <v>3385</v>
       </c>
       <c r="E307" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F307" t="s">
         <v>3386</v>
@@ -31524,7 +31522,7 @@
         <v>3393</v>
       </c>
       <c r="Q307" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R307"/>
       <c r="S307"/>
@@ -31586,7 +31584,7 @@
         <v>3403</v>
       </c>
       <c r="Q308" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R308"/>
       <c r="S308"/>
@@ -31714,7 +31712,7 @@
         <v>3422</v>
       </c>
       <c r="Q310" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R310"/>
       <c r="S310"/>
@@ -31736,7 +31734,7 @@
         <v>3423</v>
       </c>
       <c r="C311" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D311" t="s">
         <v>3424</v>
@@ -31800,7 +31798,7 @@
         <v>3436</v>
       </c>
       <c r="C312" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D312" t="s">
         <v>2764</v>
@@ -31812,7 +31810,7 @@
         <v>3425</v>
       </c>
       <c r="G312" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H312" t="s">
         <v>145</v>
@@ -31934,7 +31932,7 @@
         <v>3457</v>
       </c>
       <c r="E314" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F314" t="s">
         <v>3458</v>
@@ -32052,13 +32050,13 @@
         <v>3480</v>
       </c>
       <c r="C316" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D316" t="s">
         <v>1693</v>
       </c>
       <c r="E316" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F316" t="s">
         <v>3481</v>
@@ -32116,13 +32114,13 @@
         <v>3489</v>
       </c>
       <c r="C317" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D317" t="s">
         <v>2021</v>
       </c>
       <c r="E317" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F317" t="s">
         <v>3490</v>
@@ -32192,7 +32190,7 @@
         <v>3500</v>
       </c>
       <c r="G318" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H318" t="s">
         <v>115</v>
@@ -32244,13 +32242,13 @@
         <v>3511</v>
       </c>
       <c r="C319" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D319" t="s">
         <v>3512</v>
       </c>
       <c r="E319" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F319" t="s">
         <v>3513</v>
@@ -32378,7 +32376,7 @@
         <v>1757</v>
       </c>
       <c r="E321" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F321" t="s">
         <v>3537</v>
@@ -32436,7 +32434,7 @@
         <v>3545</v>
       </c>
       <c r="C322" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D322" t="s">
         <v>536</v>
@@ -32506,7 +32504,7 @@
         <v>2818</v>
       </c>
       <c r="E323" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F323" t="s">
         <v>3555</v>
@@ -32606,7 +32604,7 @@
         <v>3574</v>
       </c>
       <c r="Q324" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R324"/>
       <c r="S324"/>
@@ -32634,7 +32632,7 @@
         <v>2701</v>
       </c>
       <c r="E325" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F325" t="s">
         <v>3576</v>
@@ -32696,7 +32694,7 @@
         <v>1693</v>
       </c>
       <c r="E326" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F326" t="s">
         <v>3584</v>
@@ -32730,7 +32728,7 @@
         <v>3590</v>
       </c>
       <c r="Q326" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R326"/>
       <c r="S326"/>
@@ -32752,7 +32750,7 @@
         <v>3591</v>
       </c>
       <c r="C327" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D327" t="s">
         <v>3499</v>
@@ -32764,7 +32762,7 @@
         <v>3592</v>
       </c>
       <c r="G327" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H327" t="s">
         <v>115</v>
@@ -32816,7 +32814,7 @@
         <v>3603</v>
       </c>
       <c r="C328" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D328" t="s">
         <v>3604</v>
@@ -32858,7 +32856,7 @@
         <v>3612</v>
       </c>
       <c r="Q328" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R328"/>
       <c r="S328"/>
@@ -32922,7 +32920,7 @@
         <v>3625</v>
       </c>
       <c r="Q329" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R329"/>
       <c r="S329"/>
@@ -32944,13 +32942,13 @@
         <v>3626</v>
       </c>
       <c r="C330" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D330" t="s">
         <v>3627</v>
       </c>
       <c r="E330" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F330" t="s">
         <v>3628</v>
@@ -32986,7 +32984,7 @@
         <v>3635</v>
       </c>
       <c r="Q330" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R330"/>
       <c r="S330"/>
@@ -33050,7 +33048,7 @@
         <v>3644</v>
       </c>
       <c r="Q331" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R331"/>
       <c r="S331"/>
@@ -33072,7 +33070,7 @@
         <v>3645</v>
       </c>
       <c r="C332" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D332" t="s">
         <v>3646</v>
@@ -33136,19 +33134,19 @@
         <v>3657</v>
       </c>
       <c r="C333" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D333" t="s">
         <v>2865</v>
       </c>
       <c r="E333" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F333" t="s">
         <v>3637</v>
       </c>
       <c r="G333" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H333" t="s">
         <v>247</v>
@@ -33200,7 +33198,7 @@
         <v>3668</v>
       </c>
       <c r="C334" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D334" t="s">
         <v>2722</v>
@@ -33242,7 +33240,7 @@
         <v>3675</v>
       </c>
       <c r="Q334" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R334"/>
       <c r="S334"/>
@@ -33264,13 +33262,13 @@
         <v>3679</v>
       </c>
       <c r="C335" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D335" t="s">
         <v>1540</v>
       </c>
       <c r="E335" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F335" t="s">
         <v>3680</v>
@@ -33370,7 +33368,7 @@
         <v>3697</v>
       </c>
       <c r="Q336" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="R336"/>
       <c r="S336"/>
@@ -33392,7 +33390,7 @@
         <v>3698</v>
       </c>
       <c r="C337" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D337" t="s">
         <v>536</v>
@@ -33434,7 +33432,7 @@
         <v>3706</v>
       </c>
       <c r="Q337" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R337"/>
       <c r="S337"/>
@@ -33456,7 +33454,7 @@
         <v>3707</v>
       </c>
       <c r="C338" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D338" t="s">
         <v>1811</v>
@@ -33526,7 +33524,7 @@
         <v>3082</v>
       </c>
       <c r="E339" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F339" t="s">
         <v>3717</v>
@@ -33584,7 +33582,7 @@
         <v>3728</v>
       </c>
       <c r="C340" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D340" t="s">
         <v>2033</v>
@@ -33626,7 +33624,7 @@
         <v>3735</v>
       </c>
       <c r="Q340" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="R340"/>
       <c r="S340"/>
@@ -33648,7 +33646,7 @@
         <v>3736</v>
       </c>
       <c r="C341" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D341" t="s">
         <v>536</v>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">2025-12-17</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&amp;gt; Das Ruder wieder übernehmen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&amp;gt;  Il est temps de reprendre les choses en main</t>
+    <t xml:space="preserve">xml:space="preserve"&gt; Das Ruder wieder übernehmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt;  Il est temps de reprendre les choses en main</t>
   </si>
   <si>
     <t xml:space="preserve">È tempo di prendere in mano la situazione</t>
@@ -1509,10 +1509,10 @@
     <t xml:space="preserve">25.3893</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&amp;gt; Transparenz und Rechtfertigung der finanziellen Reserven der Suva und Prüfung durch die Eidgenössische Finanzkontrolle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&amp;gt; Transparence et justification des réserves financières de la Suva et contrôle du CDF</t>
+    <t xml:space="preserve">xml:space="preserve"&gt; Transparenz und Rechtfertigung der finanziellen Reserven der Suva und Prüfung durch die Eidgenössische Finanzkontrolle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt; Transparence et justification des réserves financières de la Suva et contrôle du CDF</t>
   </si>
   <si>
     <t xml:space="preserve">Trasparenza e giustificazione delle riserve finanziarie della Suva e controllo del CDF</t>
@@ -1848,13 +1848,13 @@
     <t xml:space="preserve">Schmezer Ueli</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;CO2-Verordnung. Erleichterungsmassnahmen für die Autobranche? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Ordonnance sur le CO2. Des mesures d'allègement pour la branche automobile ? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Ordinanza sul CO2. Misure di agevolazione per il settore automobilistico? </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;CO2-Verordnung. Erleichterungsmassnahmen für die Autobranche? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Ordonnance sur le CO2. Des mesures d'allègement pour la branche automobile ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Ordinanza sul CO2. Misure di agevolazione per il settore automobilistico? </t>
   </si>
   <si>
     <t xml:space="preserve">&amp;amp;lt;p&amp;amp;gt;La révision, ou plus précisément l’adaptation de l’ordonnance sur le CO2 faisant suite à la révision de la loi sur le CO2 (en vigueur depuis le 1.1.2025), revêt une grande importance pour la réalisation des objectifs légaux en matière d'émissions. Cela concerne en particulier les dispositions d'exécution pour les voitures de tourisme.&amp;amp;amp;nbsp;&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;p&amp;amp;gt;&amp;amp;amp;nbsp;&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;p&amp;amp;gt;Le 17 mars 2025, le Conseil fédéral a laissé entendre pendant l’heure des questions qu'il « adopterait l'ordonnance lors d'une prochaine séance ». Il a répondu de façon évasive aux questions sur cette ordonnance.&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;p&amp;amp;gt;&amp;amp;amp;nbsp;&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;p&amp;amp;gt;La présente interpellation s’intéresse aux mesures d'allègement des sanctions pécuniaires qui pourraient éventuellement être (une nouvelle fois) accordées à la branche automobile lorsque celle-ci ne parvient pas à atteindre les valeurs cibles.&amp;amp;amp;nbsp;&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;p&amp;amp;gt;Concrètement, l’ordonnance sur le CO2 soulève les questions suivantes.&amp;amp;amp;nbsp;&amp;amp;lt;br&amp;amp;gt;&amp;amp;amp;nbsp;&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;ol&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;La procédure de consultation s’est achevée le 17 octobre 2024. Pourquoi cette ordonnance dont nous avons urgemment besoin n'est-elle pas entrée en vigueur en mars 2025&amp;amp;amp;nbsp;? Quels sont les facteurs qui ont conduit à ce retard.&amp;amp;amp;nbsp;&amp;amp;lt;br&amp;amp;gt;&amp;amp;amp;nbsp;&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Le projet envoyé en consultation ne prévoyait pas d'alléger les sanctions. Sur les 202 prises de position annoncées par le Conseil fédéral, combien demandaient, dans le délai imparti par la procédure, des allégements en cas de non-respect des objectifs ? Quels étaient leurs principaux arguments ?&amp;amp;amp;nbsp;&amp;amp;lt;br&amp;amp;gt;&amp;amp;amp;nbsp;&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Le Contrôle fédéral des finances (CDF) a évalué l'efficacité des sanctions en matière de CO2 pour les voitures de tourisme neuves : il est clair pour lui qu'il faut renoncer à des mesures d'allégement si les objectifs ne sont pas atteints.&amp;amp;amp;nbsp;&amp;amp;lt;br&amp;amp;gt;Le Conseil fédéral partage-t-il l'appréciation du CDF ? Si ce n'est pas le cas, quels sont ses arguments ?&amp;amp;lt;br&amp;amp;gt;&amp;amp;amp;nbsp;&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Par le passé (notamment en 2015 et en 2020), des dispositions prévoyant des allégements (supercrédits, phase d’introduction) ont été introduites pour réduire les montants des sanctions en cas de dépassement des objectifs d'émission. Quel est le montant cumulé des dépassements d'objectifs non sanctionnés depuis 2010 en Suisse&amp;amp;amp;nbsp;?&amp;amp;amp;nbsp;&amp;amp;lt;br&amp;amp;gt;&amp;amp;amp;nbsp;&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Si le Conseil fédéral introduit des mesures d'allégement dans l'ordonnance : combien de millions de francs d’exonérations cela représentera-t-il pour la branche&amp;amp;amp;nbsp;?&amp;amp;lt;br&amp;amp;gt;&amp;amp;amp;nbsp;&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Si le Conseil fédéral introduit des mesures d'allégement dans l'ordonnance : comment sera-t-il possible, d’après lui, d’atteindre les valeurs cibles prévues par la loi&amp;amp;amp;nbsp;?&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;/ol&amp;amp;gt;</t>
@@ -2163,10 +2163,10 @@
     <t xml:space="preserve">2025-03-11</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Nimmt der Bundesrat die Finanzkontrolle ernst? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Le Conseil fédéral prend-il au sérieux le Contrôle fédéral des finances ? </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Nimmt der Bundesrat die Finanzkontrolle ernst? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Le Conseil fédéral prend-il au sérieux le Contrôle fédéral des finances ? </t>
   </si>
   <si>
     <t xml:space="preserve">&amp;amp;lt;p&amp;amp;gt;L'élaboration de l'ordonnance sur le CO2 revêt une grande importance pour la réalisation des objectifs légaux en matière d'émissions, en particulier les dispositions d'exécution pour les voitures de tourisme.&amp;amp;lt;br&amp;amp;gt;Le Contrôle fédéral des finances a évalué l'efficacité des sanctions en matière de CO2 pour les voitures de tourisme neuves&amp;amp;amp;nbsp;: il est clair pour lui qu'il faut renoncer à des mesures d'allègement si les objectifs ne sont pas atteints.&amp;amp;lt;br&amp;amp;gt;Le Conseil fédéral partage-t-il l'avis du Contrôle fédéral des finances&amp;amp;amp;nbsp;? Dans la négative, pour quelles raisons&amp;amp;amp;nbsp;?&amp;amp;lt;/p&amp;amp;gt;</t>
@@ -2262,10 +2262,10 @@
     <t xml:space="preserve">25.7129</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Ist der Kaufpreis für die F-35 fix? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Le prix d’achat des F-35, est-il fixe ? </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Ist der Kaufpreis für die F-35 fix? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Le prix d’achat des F-35, est-il fixe ? </t>
   </si>
   <si>
     <t xml:space="preserve">&amp;amp;lt;p&amp;amp;gt;Selon les informations régulièrement transmises par le DDPS, les Etats-Unis se sont engagés à fournir les 36 F-35 acquis par la Suisse à un prix d’achat fixe. Mais selon un avis du Contrôle fédéral des finances émis le 8 juillet 2022, il n’existe aucune garantie juridique à ce sujet.&amp;amp;lt;br&amp;amp;gt;A notre connaissance, cette dernière information n’a jamais été démentie par le Conseil fédéral.&amp;amp;lt;br&amp;amp;gt;Le Conseil fédéral la confirme-t-il ?&amp;amp;lt;/p&amp;amp;gt;</t>
@@ -2397,13 +2397,13 @@
     <t xml:space="preserve">2025-01-21</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Schweizer Depotbank für die Ausgleichfonds von AHV, IV und EO </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Schweizer Depotbank für die Ausgleichfonds von AHV, IV und EO </t>
   </si>
   <si>
     <t xml:space="preserve">Banque dépositaire pour les fonds de compensation AVS/AI/APG</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Banca depositaria svizzera per i fondi di compensazione AVS, AI e IPG </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Banca depositaria svizzera per i fondi di compensazione AVS, AI e IPG </t>
   </si>
   <si>
     <t xml:space="preserve">&amp;amp;lt;p&amp;amp;gt;Les fonds de compensation AVS/AI/APG sont responsables de la gestion des liquidités et de la fortune de ces trois assurances. En décembre&amp;amp;amp;nbsp;2023, le conseil d’administration de Compenswiss, l’autorité compétente, a décidé de confier le mandat de banque dépositaire, qui était alors assumé par UBS, à un établissement bancaire américain, la State Street Bank International GmbH. Le transfert à la nouvelle banque dépositaire a eu lieu fin juillet&amp;amp;amp;nbsp;2024.&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;p&amp;amp;gt;Le Conseil fédéral est chargé d’encourager Compenswiss à résilier le mandat confié à la State Street Bank International GmbH pour le remettre à une banque suisse. Si, pour des raisons juridiques, cela n’est pas possible, le Conseil fédéral est chargé de créer les conditions légales nécessaires.&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;p&amp;amp;gt;Une minorité (Bertschy, Grossen Jürg, Roth David, Ryser, Walti Beat, Wermuth, Widmer Céline) propose de rejeter la motion.&amp;amp;lt;/p&amp;amp;gt;</t>
@@ -2499,10 +2499,10 @@
     <t xml:space="preserve">2024-12-11</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;ETH-Top vs. ETH-Baumanagement-Flop </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;EPFZ. Un top et un flop </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;ETH-Top vs. ETH-Baumanagement-Flop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;EPFZ. Un top et un flop </t>
   </si>
   <si>
     <t xml:space="preserve">&amp;amp;lt;p&amp;amp;gt;Top&amp;amp;amp;nbsp;: 7e place dans le classement mondial des universités 2025. Flop&amp;amp;amp;nbsp;: l’EPFZ comme maître d’ouvrage. 2019&amp;amp;amp;nbsp;: rapport du CDF à propos du projet BSS (Bâle)&amp;amp;amp;nbsp;: «&amp;amp;amp;nbsp;la direction du projet BSS n’a pas mis en œuvre de processus valables pour la gestion du changement&amp;amp;amp;nbsp;»&amp;amp;amp;nbsp;; «&amp;amp;amp;nbsp;il n’existe pas d’instruments continus pour le pilotage financier de l’ensemble du projet ». 2023-2024&amp;amp;amp;nbsp;: projet GLC (Zurich)&amp;amp;amp;nbsp;: une centaine de PME et d’entreprises générales attendent encore le versement de plusieurs millions de francs. L’EPFZ refuse de donner suite aux demandes d’entretien des entreprises générales en vue de résoudre le problème.&amp;amp;lt;br&amp;amp;gt;Que fait le Conseil fédéral pour protéger les entreprises concernées et la réputation de l’EPFZ&amp;amp;amp;nbsp;?&amp;amp;lt;/p&amp;amp;gt;</t>
@@ -3408,10 +3408,10 @@
     <t xml:space="preserve">2024-02-26</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Unterstellung von Organisationen ausserhalb der Bundesverwaltung unter die Aufsicht durch die Eidgenössische Finanzkontrolle. Wann wird der Bundesrat seinen Bericht veröffentlichen? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Assujettissement des organisations externes à l’administration au Contrôle fédéral des finances. Quand le Conseil fédéral publiera-t-il son rapport ? </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Unterstellung von Organisationen ausserhalb der Bundesverwaltung unter die Aufsicht durch die Eidgenössische Finanzkontrolle. Wann wird der Bundesrat seinen Bericht veröffentlichen? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Assujettissement des organisations externes à l’administration au Contrôle fédéral des finances. Quand le Conseil fédéral publiera-t-il son rapport ? </t>
   </si>
   <si>
     <t xml:space="preserve">&amp;amp;lt;p&amp;amp;gt;Le postulat 15.4112 intitulé «&amp;amp;amp;nbsp;Examen des critères selon lesquels les organisations externes à l’administration doivent être soumises à la surveillance du Contrôle fédéral des finances&amp;amp;amp;nbsp;» a été accepté par le Conseil national le 18 mars 2016. En réponse à la question 19.5385, le Conseil fédéral a indiqué que le rapport demandé par le postulat serait publié à la fin de l’année 2019. Pour l’heure, le rapport n’a pas encore été publié.&amp;amp;lt;br&amp;amp;gt;Quand le sera-t-il&amp;amp;amp;nbsp;?&amp;amp;amp;nbsp;&amp;amp;lt;/p&amp;amp;gt;</t>
@@ -3594,7 +3594,7 @@
     <t xml:space="preserve">Fonds pour la démocratie et l'état de droit en commémoration de 1848</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&amp;gt; Fondo per la democrazia e lo Stato di diritto in commemorazione del 1848</t>
+    <t xml:space="preserve">xml:space="preserve"&gt; Fondo per la democrazia e lo Stato di diritto in commemorazione del 1848</t>
   </si>
   <si>
     <t xml:space="preserve">&amp;amp;lt;p&amp;amp;gt;Le Conseil fédéral est invité à élaborer les bases légales pour le financement d’un fonds pour la démocratie et l’État de droit. Ce fonds doit, d’une part, soutenir des activités pouvant renforcer la compréhension et l’engagement pour les institutions politiques de l’État fédéral suisse, en particulier chez les jeunes. D’autre part, afin de renforcer la cohésion de la Suisse, le fonds doit encourager la connaissance et la pratique des langues nationales.&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;p&amp;amp;gt;&amp;amp;amp;nbsp;&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;p&amp;amp;gt;Le fonds doit être géré par un comité indépendant du Parlement et de l’administration, composé de cinq à neuf personnes au maximum, nommées par le Conseil fédéral pour une durée de quatre ans et rééligibles deux fois au maximum. Les comptes annuels doivent être soumis au Contrôle fédéral des finances pour révision.&amp;amp;lt;/p&amp;amp;gt;</t>
@@ -3630,7 +3630,7 @@
     <t xml:space="preserve">Une manifestation en faveur du pouvoir d'achat doit-elle être considérée comme une manifestation électorale?</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Una manifestazione a favore del potere d'acquisto è una manifestazione elettorale o no? </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Una manifestazione a favore del potere d'acquisto è una manifestazione elettorale o no? </t>
   </si>
   <si>
     <t xml:space="preserve">&amp;amp;lt;p&amp;amp;gt;Dans le « Tagesanzeiger » du 22 septembre 2023, le directeur du Contrôle fédéral des finances, Pascal Stirnimann, a affirmé, à propos d’une manifestation en faveur du pouvoir d’achat qui a été organisée par l’Union syndicale suisse (USS) et à laquelle participaient des parlementaires fédéraux socialistes et verts, que si, lors d’une grande manifestation, dix candidats d’un même parti scandaient leurs slogans électoraux, mais que les organisateurs de la manifestation affirmaient néanmoins qu’il ne s’agissait pas d’une campagne électorale, le CDF allait examiner la chose de près.&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;p&amp;amp;gt;Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes&amp;amp;amp;nbsp;:&amp;amp;amp;nbsp;&amp;amp;lt;/p&amp;amp;gt;&amp;amp;lt;ol&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;A-t-on, après la manifestation sur le pouvoir d’achat organisée par les syndicats, ouvert une enquête pour déterminer si la loi sur le financement de la vie politique avait été violée&amp;amp;amp;nbsp;?&amp;amp;lt;br&amp;amp;gt;a. Dans l’affirmative, pourquoi&amp;amp;amp;nbsp;?&amp;amp;lt;br&amp;amp;gt;b. Dans la négative, pourquoi&amp;amp;amp;nbsp;?&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Dans le cas où une enquête a été ouverte, quand disposera-t-on, selon le Conseil fédéral, des premiers résultats&amp;amp;amp;nbsp;?&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Selon lui, une manifestation disposant d’un budget de 150&amp;amp;amp;nbsp;000&amp;amp;amp;nbsp;francs (comme ce fut le cas pour la manifestation en faveur du pouvoir d’achat) doit-elle faire l’objet d’une déclaration conformément à la loi sur le financement de la vie politique&amp;amp;amp;nbsp;?&amp;amp;amp;nbsp;&amp;amp;lt;br&amp;amp;gt;a. Dans l’affirmative, pourquoi&amp;amp;amp;nbsp;?&amp;amp;lt;br&amp;amp;gt;b. Dans la négative, pourquoi&amp;amp;amp;nbsp;?&amp;amp;amp;nbsp;&amp;amp;amp;nbsp;&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Le Conseil fédéral approuve-t-il l’affirmation de Pascal Stirnimann selon laquelle toute personne qui dépense, en vue d’influer sur une élection, des montants dépassant les plafonds fixés par la loi est tenue de les déclarer&amp;amp;amp;nbsp;?&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Où se situe, pour le Conseil fédéral, la limite entre une manifestation ne visant pas à influer sur une élection et une manifestation visant une telle fin&amp;amp;amp;nbsp;?&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Que pense-t-il de l’argument avancé par le porte-parole de l’USS selon lequel ladite manifestation portait sur les négociations salariales, qu’elle ne constituait pas une manifestation électorale au sens de la loi et qu’elle ne devait, par conséquent, pas faire l’objet d’une déclaration&amp;amp;amp;nbsp;?&amp;amp;amp;nbsp;&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;li&amp;amp;gt;Est-il d’avis que toutes les manifestations susceptibles d’être considérées comme des manifestations électorales en raison de leur rayonnement ou du sujet sur lequel elles portent sont soumises à la loi sur le financement de la vie politique&amp;amp;amp;nbsp;?&amp;amp;lt;/li&amp;amp;gt;&amp;amp;lt;/ol&amp;amp;gt;</t>
@@ -4254,7 +4254,7 @@
     <t xml:space="preserve">Die Schweizerische Radio- und Fernsehgesellschaft der Eidgenössischen Finanzkontrolle unterstellen</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Soumettre la Société suisse de radiodiffusion et télévision au Contrôle fédéral des finances </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Soumettre la Société suisse de radiodiffusion et télévision au Contrôle fédéral des finances </t>
   </si>
   <si>
     <t xml:space="preserve">Società svizzera di radiotelevisione da sottoporre al Controllo federale delle finanze</t>
@@ -7572,10 +7572,10 @@
     <t xml:space="preserve">25.8273</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Kostendeckende Erträge aus dem Artenschutz? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Des revenus couvrant les coûts liés à la protection des espèces ? </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Kostendeckende Erträge aus dem Artenschutz? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Des revenus couvrant les coûts liés à la protection des espèces ? </t>
   </si>
   <si>
     <t xml:space="preserve">&amp;amp;lt;p&amp;amp;gt;Chaque année, la Suisse délivre environ 100&amp;amp;amp;nbsp;000 autorisations pour le commerce d'espèces végétales et animales menacées et effectue quelque 20&amp;amp;amp;nbsp;000 contrôles à l'importation. Elle perçoit à cet effet des émoluments d'environ 4&amp;amp;amp;nbsp;millions de francs. Selon le CDF, ces émoluments ne couvriraient pas les coûts et constitueraient donc une subvention dommageable à la biodiversité.&amp;amp;lt;br&amp;amp;gt;Compte tenu des débats en cours concernant le budget,&amp;amp;lt;br&amp;amp;gt;le Conseil fédéral est-il prêt à introduire des émoluments couvrant les coûts dans ce domaine&amp;amp;amp;nbsp;?&amp;amp;lt;br&amp;amp;gt;Si oui, quand&amp;amp;amp;nbsp;?&amp;amp;lt;br&amp;amp;gt;Si non, pourquoi&amp;amp;amp;nbsp;?&amp;amp;lt;/p&amp;amp;gt;</t>
@@ -7740,10 +7740,10 @@
     <t xml:space="preserve">25.4225</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Giftiger Rasen. Warum sind toxische PFAS-Pestizide ausgerechnet zur Anwendung auf Spiel- und Sportplätzen oder in Wohnquartieren zugelassen? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Gazon toxique. Pourquoi les pesticides PFAS sont-ils autorisés sur les terrains de jeux et de sport ainsi que dans les quartiers résidentiels ? </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Giftiger Rasen. Warum sind toxische PFAS-Pestizide ausgerechnet zur Anwendung auf Spiel- und Sportplätzen oder in Wohnquartieren zugelassen? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Gazon toxique. Pourquoi les pesticides PFAS sont-ils autorisés sur les terrains de jeux et de sport ainsi que dans les quartiers résidentiels ? </t>
   </si>
   <si>
     <t xml:space="preserve">Superfici erbose inquinate. Perché i pesticidi tossici contenenti PFAS sono omologati per l'uso sui campi sportivi e da gioco e nei quartieri residenziali?</t>
@@ -7926,10 +7926,10 @@
     <t xml:space="preserve">25.789</t>
   </si>
   <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Rolle des Bundes bei der Sanierung der Deponie Gamsenried </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&amp;gt;Rôle de la Confédération dans l’assainissement de la décharge de Gamsenried </t>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Rolle des Bundes bei der Sanierung der Deponie Gamsenried </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml:space="preserve"&gt;xml:space="preserve"&gt;Rôle de la Confédération dans l’assainissement de la décharge de Gamsenried </t>
   </si>
   <si>
     <t xml:space="preserve">&amp;amp;lt;p&amp;amp;gt;Concernant le suivi de l’assainissement de cette décharge, le Contrôle fédéral des finances (CDF) souligne «&amp;amp;amp;nbsp;l’absence d’une vision d’ensemble des risques et d’un suivi coordonné des différentes entités fédérales&amp;amp;amp;nbsp;».&amp;amp;lt;br&amp;amp;gt;- Comment le Conseil fédéral réagit-il aux critiques du CDF?&amp;amp;lt;br&amp;amp;gt;- Entend-il réaliser une analyse globale des risques, en tenant compte des interfaces avec l'A9 et la correction du Rhône puis, sur cette base, établir un concept de surveillance avec des responsabilités clairement définies?&amp;amp;lt;/p&amp;amp;gt;</t>
@@ -11430,10 +11430,10 @@
     <t xml:space="preserve">Sottoporre la SUVA alla vigilanza finanziaria del Controllo federale delle finanze</t>
   </si>
   <si>
-    <t xml:space="preserve">&amp;lt;p&amp;gt;Le Conseil fédéral est chargé de proposer aux Chambres fédérales d'abroger l'article 1, alinéa , lettera , de la loi sur le Contrôle des finances (LCF ; RS 614.0) lorsqu'elles procéderont à la prochaine révision de la loi en question.&amp;lt;/p&amp;gt;&amp;lt;p&amp;gt;Une minorité (Gasche, Gilli, Gmür, Gössi, Gschwind, Kiener Nellen, Müller Leo, Schneeberger, Siegenthaler, Vischer Daniel) propose le rejet de la motion.&amp;lt;/p&amp;gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;lt;p&amp;gt;Der Bundesrat wird beauftragt, der Bundesversammlung im Rahmen der nächsten Revision des Finanzkontrollgesetzes (FKG; SR 614.0) die ersatzlose Streichung von Artikel 19 Absatz 1 Buchstabe b vorzulegen.&amp;lt;/p&amp;gt;&amp;lt;p&amp;gt;Eine Minderheit (Gasche, Gilli, Gmür, Gössi, Gschwind, Kiener Nellen, Müller Leo, Schneeberger, Siegenthaler, Vischer Daniel) beantragt die Ablehnung der Motion.&amp;lt;/p&amp;gt;</t>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de proposer aux Chambres fédérales d'abroger l'article 1, alinéa , lettera , de la loi sur le Contrôle des finances (LCF ; RS 614.0) lorsqu'elles procéderont à la prochaine révision de la loi en question.&lt;/p&gt;&lt;p&gt;Une minorité (Gasche, Gilli, Gmür, Gössi, Gschwind, Kiener Nellen, Müller Leo, Schneeberger, Siegenthaler, Vischer Daniel) propose le rejet de la motion.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, der Bundesversammlung im Rahmen der nächsten Revision des Finanzkontrollgesetzes (FKG; SR 614.0) die ersatzlose Streichung von Artikel 19 Absatz 1 Buchstabe b vorzulegen.&lt;/p&gt;&lt;p&gt;Eine Minderheit (Gasche, Gilli, Gmür, Gössi, Gschwind, Kiener Nellen, Müller Leo, Schneeberger, Siegenthaler, Vischer Daniel) beantragt die Ablehnung der Motion.&lt;/p&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20153828</t>
@@ -11472,10 +11472,10 @@
     <t xml:space="preserve">Bloccare l'effettivo del personale della Confederazione al livello del 2015</t>
   </si>
   <si>
-    <t xml:space="preserve">&amp;lt;p&amp;gt;Le Conseil fédéral est chargé de prendre des mesures afin que les effectifs de la Confédération ne dépassent pas le nombre fixé dans le budget 2015 (à savoir 35 000 équivalents plein temps).&amp;lt;/p&amp;gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;lt;p&amp;gt;Der Bundesrat wird beauftragt, Massnahmen zu ergreifen mit dem Ziel, dass der Bundespersonalbestand den Stand gemäss Voranschlag 2015 (35 000 FTE) nicht überschreitet.&amp;lt;/p&amp;gt;</t>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de prendre des mesures afin que les effectifs de la Confédération ne dépassent pas le nombre fixé dans le budget 2015 (à savoir 35 000 équivalents plein temps).&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, Massnahmen zu ergreifen mit dem Ziel, dass der Bundespersonalbestand den Stand gemäss Voranschlag 2015 (35 000 FTE) nicht überschreitet.&lt;/p&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20153494</t>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -257,10 +257,10 @@
     <t xml:space="preserve">Titel folgt</t>
   </si>
   <si>
-    <t xml:space="preserve">Réintroduction de l’obligation de visas pour les Géorgiens </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reintrodurre l’obbligo del visto per i Georgiani</t>
+    <t xml:space="preserve">Réintroduction de l'obligation de visas pour les Géorgiens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reintrodurre l'obbligo del visto per i Georgiani</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’intervenir auprès de l’Union européenne afin de demander la réintroduction de l’obligation de visas pour les ressortissants géorgiens. Cette mesure vise à enrayer le tourisme médical qui n’a pas tari.&lt;/p&gt;</t>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Axe ferroviaire du Saint-Gothard. Le Conseil fédéral a-t-il l'intention de remédier aux lacunes constatées lors de la préparation du message 2027 ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Asse ferroviario del San Gottardo: il Consiglio federale intende correggere le lacune emerse nella preparazione del Messaggio 2027?</t>
+    <t xml:space="preserve">Asse ferroviario del San Gottardo. Il Consiglio federale intende correggere le lacune emerse nella preparazione del Messaggio 2027?</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Compte tenu de l'importance stratégique de l'axe du Saint-Gothard pour le trafic voyageurs national et international ainsi que pour le transfert du trafic marchandises de la route au rail, le Conseil fédéral est prié de répondre aux questions suivantes&amp;nbsp;:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Pour quelles raisons les propositions d'infrastructures présentées par le canton du Tessin – notamment le doublement de la ligne Cadenazzo-Locarno sur les ponts de la Verzasca et du Ticino, la modernisation du nœud ferroviaire de Mendrisio et le renforcement des nœuds ferroviaires de Bellinzone et de Lugano – n’ont-elles pas été incluses dans le mandat d’évaluation confié à l’EPFZ dans le cadre de l’expertise «&amp;nbsp;Transports ’45&amp;nbsp;»&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Le Conseil fédéral estime-t-il juste que les mesures qui n'ont pas fait l'objet d'une évaluation par les experts de l'EPFZ soient de fait a priori exclues de la possibilité d'être prises en compte dans le message 2027&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Partage-t-il l'avis selon lequel l'infrastructure actuellement prévue au sud du Saint-Gothard pourrait s'avérer insuffisante pour faire face à l'évolution attendue de la demande dans le trafic régional, national, international et de marchandises&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Quelles vérifications l'OFT et les CFF ont-ils effectuées concernant la faisabilité du projet d'offre 2035 pour le Tessin, et quelles critiques ont été émises&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Pourquoi les nouvelles exigences récemment formulées par les CFF concernant le trafic grandes lignes entre Zurich/Lucerne et Lugano n'ont-elles pas été accompagnées d'une réévaluation complète des infrastructures nécessaires&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Le Conseil fédéral est-il disposé à réexaminer, dans le cadre de la préparation du message 2027, les mesures proposées par le canton du Tessin si elles devaient s’avérer nécessaires pour atteindre les objectifs d'offre fixés par la Confédération elle-même&amp;nbsp;?&lt;/li&gt;&lt;li&gt;A-t-il l'intention de promouvoir une étude globale sur l'axe ferroviaire nord-sud, à l'instar de celle réalisée pour l'axe ouest-est dans le cadre du programme «&amp;nbsp;Transports ’45&amp;nbsp;», comme base pour les futures étapes d’aménagement de l'infrastructure ferroviaire nationale&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Comment compte-t-il garantir que le rôle stratégique du corridor du Saint-Gothard, en tant qu’axe principal de transit international de la Suisse, soit dûment pris en compte dans la planification ferroviaire jusqu'en 2050&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Le Contrôle fédéral des finances a récemment constaté que le processus de planification financière du fonds d'infrastructure ferroviaire restait fragile, que les rapports ne mettaient pas suffisamment en évidence les principales incertitudes et que la qualité des projections à long terme restait insuffisante. Au vu de ces constatations, le Conseil fédéral estime-t-il que les bases financières et méthodologiques utilisées pour définir les priorités dans le cadre de «&amp;nbsp;Transports '45&amp;nbsp;» et du message 2027 sont suffisamment solides pour justifier l'exclusion de certains projets d'infrastructure&amp;nbsp;?&lt;/li&gt;&lt;/ol&gt;</t>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -104,7 +104,7 @@
     <t xml:space="preserve">UVEK</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotthard-Eisenbahnachse: Plant der Bundesrat, die bei der Ausarbeitung der Botschaft 2027 aufgetretenen Mängel zu beheben?</t>
+    <t xml:space="preserve">Gotthard-Eisenbahnachse. Plant der Bundesrat, die bei der Ausarbeitung der Botschaft 2027 aufgetretenen Mängel zu beheben?</t>
   </si>
   <si>
     <t xml:space="preserve">Axe ferroviaire du Saint-Gothard. Le Conseil fédéral a-t-il l'intention de remédier aux lacunes constatées lors de la préparation du message 2027 ?</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">Titre suit</t>
   </si>
   <si>
-    <t xml:space="preserve">Attuazione coerente dell’Agenda 2030 nelle politiche settoriali</t>
+    <t xml:space="preserve">Attuazione coerente dell'Agenda 2030 nelle politiche settoriali</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, Massnahmen zu ergreifen, um eine umfassende, kohärente und wirkungsvolle Umsetzung der Agenda 2030 in den Sektoralpolitiken sicherzustellen:&amp;nbsp;&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Auf Basis des Länderberichts (Voluntary National Review) 2026 ist eine gezielte Analyse der notwendigen Massnahmen vorzunehmen, um die festgestellten Lücken zu schliessen.&amp;nbsp;&lt;/li&gt;&lt;li&gt;Der Bundesrat muss sicherstellen, dass das Direktionskomitee Agenda 2030 seine koordinierende und steuernde Rolle wahrnimmt und die Agenda 2030 kohärent in die Sektoralpolitiken übersetzt.&amp;nbsp;&lt;/li&gt;&lt;li&gt;Der Bundesrat muss dem Parlament in regelmässigen Abständen über die zusätzlichen Massnahmen berichten.&amp;nbsp;&lt;/li&gt;&lt;/ol&gt;</t>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -245,7 +245,7 @@
     <t xml:space="preserve">Kohärente Umsetzung der Agenda 2030 über die Sektoralpolitiken</t>
   </si>
   <si>
-    <t xml:space="preserve">Pour la mise en œuvre cohérente de l’Agenda 2030 dans les politiques sectorielles</t>
+    <t xml:space="preserve">Pour la mise en oeuvre cohérente de l'Agenda 2030 dans les politiques sectorielles</t>
   </si>
   <si>
     <t xml:space="preserve">Attuazione coerente dell'Agenda 2030 nelle politiche settoriali</t>

--- a/Objets_parlementaires_CDF_EFK.xlsx
+++ b/Objets_parlementaires_CDF_EFK.xlsx
@@ -12025,9 +12025,7 @@
       <c r="R2" t="s">
         <v>39</v>
       </c>
-      <c r="S2" t="s">
-        <v>39</v>
-      </c>
+      <c r="S2"/>
       <c r="T2" t="s">
         <v>40</v>
       </c>
